--- a/images/image manifest.xlsx
+++ b/images/image manifest.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\Github\CS-Graphics\images\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41C84FA5-8A46-47BD-BCC9-9D751975EC94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4D8C480-1220-47B1-B455-836D118CF091}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="21480" windowHeight="11520" xr2:uid="{620D0F7A-D0D3-4EA0-8A4D-C0BB25CE06A6}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1033" uniqueCount="913">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1049" uniqueCount="919">
   <si>
     <t>Filename</t>
   </si>
@@ -2776,6 +2776,24 @@
   </si>
   <si>
     <t>TODO(Name) Death animation</t>
+  </si>
+  <si>
+    <t>Animation stacked</t>
+  </si>
+  <si>
+    <t>Yes</t>
+  </si>
+  <si>
+    <t>Tola healthy idle</t>
+  </si>
+  <si>
+    <t>Status bar</t>
+  </si>
+  <si>
+    <t>Tola warning idle</t>
+  </si>
+  <si>
+    <t>Tola danger idle</t>
   </si>
 </sst>
 </file>
@@ -2836,16 +2854,17 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D76A0E2E-5EF1-4C76-B441-AB9216212B3A}" name="Table1" displayName="Table1" ref="A1:G900" totalsRowShown="0">
-  <autoFilter ref="A1:G900" xr:uid="{D76A0E2E-5EF1-4C76-B441-AB9216212B3A}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A7:F869">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D76A0E2E-5EF1-4C76-B441-AB9216212B3A}" name="Table1" displayName="Table1" ref="A1:H900" totalsRowShown="0">
+  <autoFilter ref="A1:H900" xr:uid="{D76A0E2E-5EF1-4C76-B441-AB9216212B3A}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A7:G869">
     <sortCondition ref="A1:A900"/>
   </sortState>
-  <tableColumns count="7">
+  <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{5BE264B2-3040-4E26-A5F7-09EDCD3E654D}" name="Filename"/>
     <tableColumn id="2" xr3:uid="{AA34CE9E-8179-4C54-86B6-0527AB82EA40}" name="Size" dataDxfId="0"/>
     <tableColumn id="3" xr3:uid="{67331664-BB23-4B18-BAE5-9C442B93DC80}" name="Palette"/>
     <tableColumn id="4" xr3:uid="{939C3ADC-1918-446F-8F03-0323F831EA15}" name="Frames"/>
+    <tableColumn id="8" xr3:uid="{9479E81C-320D-4A48-BCAE-E8694A4258D2}" name="Animation stacked"/>
     <tableColumn id="5" xr3:uid="{38C11265-21A9-4D92-ADAC-81770284CD74}" name="Type"/>
     <tableColumn id="6" xr3:uid="{E8D6B3ED-E7AB-4418-98DF-3F96091191AB}" name="Description"/>
     <tableColumn id="7" xr3:uid="{12717EBE-E94A-4C45-AE7E-ADDEC9F71820}" name="Purpose"/>
@@ -3171,17 +3190,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{847C270E-F408-4D3B-B2DA-3B018BAD355D}">
-  <dimension ref="A1:G900"/>
+  <dimension ref="A1:H900"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.7109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="9.7109375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="18.140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="24.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.85546875" customWidth="1"/>
+    <col min="6" max="6" width="18.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="24.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -3195,16 +3215,19 @@
         <v>5</v>
       </c>
       <c r="E1" t="s">
+        <v>913</v>
+      </c>
+      <c r="F1" t="s">
         <v>2</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>3</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>910</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>752</v>
       </c>
@@ -3212,7 +3235,7 @@
         <v>75376</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>753</v>
       </c>
@@ -3220,7 +3243,7 @@
         <v>129265</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>754</v>
       </c>
@@ -3228,7 +3251,7 @@
         <v>35736</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>755</v>
       </c>
@@ -3236,7 +3259,7 @@
         <v>17697</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>756</v>
       </c>
@@ -3244,31 +3267,85 @@
         <v>50366</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>6</v>
       </c>
       <c r="B7" s="1">
         <v>6370</v>
       </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C7" t="s">
+        <v>909</v>
+      </c>
+      <c r="D7">
+        <v>30</v>
+      </c>
+      <c r="E7" t="s">
+        <v>914</v>
+      </c>
+      <c r="F7" t="s">
+        <v>908</v>
+      </c>
+      <c r="G7" t="s">
+        <v>915</v>
+      </c>
+      <c r="H7" t="s">
+        <v>916</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>7</v>
       </c>
       <c r="B8" s="1">
         <v>20545</v>
       </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C8" t="s">
+        <v>909</v>
+      </c>
+      <c r="D8">
+        <v>30</v>
+      </c>
+      <c r="E8" t="s">
+        <v>914</v>
+      </c>
+      <c r="F8" t="s">
+        <v>908</v>
+      </c>
+      <c r="G8" t="s">
+        <v>917</v>
+      </c>
+      <c r="H8" t="s">
+        <v>916</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>8</v>
       </c>
       <c r="B9" s="1">
         <v>12833</v>
       </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C9" t="s">
+        <v>909</v>
+      </c>
+      <c r="D9">
+        <v>30</v>
+      </c>
+      <c r="E9" t="s">
+        <v>914</v>
+      </c>
+      <c r="F9" t="s">
+        <v>908</v>
+      </c>
+      <c r="G9" t="s">
+        <v>918</v>
+      </c>
+      <c r="H9" t="s">
+        <v>916</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>9</v>
       </c>
@@ -3281,17 +3358,17 @@
       <c r="D10">
         <v>4</v>
       </c>
-      <c r="E10" t="s">
+      <c r="F10" t="s">
         <v>908</v>
       </c>
-      <c r="F10" t="s">
+      <c r="G10" t="s">
         <v>912</v>
       </c>
-      <c r="G10" t="s">
+      <c r="H10" t="s">
         <v>911</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>10</v>
       </c>
@@ -3299,7 +3376,7 @@
         <v>3837</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>11</v>
       </c>
@@ -3307,7 +3384,7 @@
         <v>17892</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>12</v>
       </c>
@@ -3315,7 +3392,7 @@
         <v>19255</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>13</v>
       </c>
@@ -3328,17 +3405,17 @@
       <c r="D14">
         <v>4</v>
       </c>
-      <c r="E14" t="s">
+      <c r="F14" t="s">
         <v>908</v>
       </c>
-      <c r="F14" t="s">
+      <c r="G14" t="s">
         <v>912</v>
       </c>
-      <c r="G14" t="s">
+      <c r="H14" t="s">
         <v>911</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>14</v>
       </c>
@@ -3346,7 +3423,7 @@
         <v>4962</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>15</v>
       </c>
@@ -3354,7 +3431,7 @@
         <v>27484</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>16</v>
       </c>
@@ -3362,7 +3439,7 @@
         <v>28958</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>17</v>
       </c>
@@ -3375,17 +3452,17 @@
       <c r="D18">
         <v>4</v>
       </c>
-      <c r="E18" t="s">
+      <c r="F18" t="s">
         <v>908</v>
       </c>
-      <c r="F18" t="s">
+      <c r="G18" t="s">
         <v>912</v>
       </c>
-      <c r="G18" t="s">
+      <c r="H18" t="s">
         <v>911</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>18</v>
       </c>
@@ -3393,7 +3470,7 @@
         <v>4760</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>19</v>
       </c>
@@ -3401,7 +3478,7 @@
         <v>18746</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>20</v>
       </c>
@@ -3409,7 +3486,7 @@
         <v>17387</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>21</v>
       </c>
@@ -3422,17 +3499,17 @@
       <c r="D22">
         <v>4</v>
       </c>
-      <c r="E22" t="s">
+      <c r="F22" t="s">
         <v>908</v>
       </c>
-      <c r="F22" t="s">
+      <c r="G22" t="s">
         <v>912</v>
       </c>
-      <c r="G22" t="s">
+      <c r="H22" t="s">
         <v>911</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>22</v>
       </c>
@@ -3440,7 +3517,7 @@
         <v>4613</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>23</v>
       </c>
@@ -3448,7 +3525,7 @@
         <v>18010</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>24</v>
       </c>
@@ -3456,7 +3533,7 @@
         <v>21511</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>25</v>
       </c>
@@ -3469,17 +3546,17 @@
       <c r="D26">
         <v>4</v>
       </c>
-      <c r="E26" t="s">
+      <c r="F26" t="s">
         <v>908</v>
       </c>
-      <c r="F26" t="s">
+      <c r="G26" t="s">
         <v>912</v>
       </c>
-      <c r="G26" t="s">
+      <c r="H26" t="s">
         <v>911</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>26</v>
       </c>
@@ -3487,7 +3564,7 @@
         <v>4056</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>27</v>
       </c>
@@ -3495,7 +3572,7 @@
         <v>26577</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>28</v>
       </c>
@@ -3503,7 +3580,7 @@
         <v>20293</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>29</v>
       </c>
@@ -3516,17 +3593,17 @@
       <c r="D30">
         <v>4</v>
       </c>
-      <c r="E30" t="s">
+      <c r="F30" t="s">
         <v>908</v>
       </c>
-      <c r="F30" t="s">
+      <c r="G30" t="s">
         <v>912</v>
       </c>
-      <c r="G30" t="s">
+      <c r="H30" t="s">
         <v>911</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>30</v>
       </c>
@@ -3534,7 +3611,7 @@
         <v>4494</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>31</v>
       </c>
@@ -3542,7 +3619,7 @@
         <v>18509</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>32</v>
       </c>
@@ -3550,7 +3627,7 @@
         <v>30532</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>33</v>
       </c>
@@ -3563,17 +3640,17 @@
       <c r="D34">
         <v>4</v>
       </c>
-      <c r="E34" t="s">
+      <c r="F34" t="s">
         <v>908</v>
       </c>
-      <c r="F34" t="s">
+      <c r="G34" t="s">
         <v>912</v>
       </c>
-      <c r="G34" t="s">
+      <c r="H34" t="s">
         <v>911</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>34</v>
       </c>
@@ -3581,7 +3658,7 @@
         <v>5475</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>35</v>
       </c>
@@ -3589,7 +3666,7 @@
         <v>23999</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>36</v>
       </c>
@@ -3597,7 +3674,7 @@
         <v>14302</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>37</v>
       </c>
@@ -3610,17 +3687,17 @@
       <c r="D38">
         <v>4</v>
       </c>
-      <c r="E38" t="s">
+      <c r="F38" t="s">
         <v>908</v>
       </c>
-      <c r="F38" t="s">
+      <c r="G38" t="s">
         <v>912</v>
       </c>
-      <c r="G38" t="s">
+      <c r="H38" t="s">
         <v>911</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>38</v>
       </c>
@@ -3628,7 +3705,7 @@
         <v>5028</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>39</v>
       </c>
@@ -3636,7 +3713,7 @@
         <v>14517</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>40</v>
       </c>
@@ -3644,7 +3721,7 @@
         <v>28308</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>41</v>
       </c>
@@ -3657,17 +3734,17 @@
       <c r="D42">
         <v>4</v>
       </c>
-      <c r="E42" t="s">
+      <c r="F42" t="s">
         <v>908</v>
       </c>
-      <c r="F42" t="s">
+      <c r="G42" t="s">
         <v>912</v>
       </c>
-      <c r="G42" t="s">
+      <c r="H42" t="s">
         <v>911</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>42</v>
       </c>
@@ -3675,7 +3752,7 @@
         <v>3841</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>43</v>
       </c>
@@ -3683,7 +3760,7 @@
         <v>13899</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>44</v>
       </c>
@@ -3691,7 +3768,7 @@
         <v>14453</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>45</v>
       </c>
@@ -3704,17 +3781,17 @@
       <c r="D46">
         <v>4</v>
       </c>
-      <c r="E46" t="s">
+      <c r="F46" t="s">
         <v>908</v>
       </c>
-      <c r="F46" t="s">
+      <c r="G46" t="s">
         <v>912</v>
       </c>
-      <c r="G46" t="s">
+      <c r="H46" t="s">
         <v>911</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>46</v>
       </c>
@@ -3722,7 +3799,7 @@
         <v>4674</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>47</v>
       </c>
@@ -3730,7 +3807,7 @@
         <v>8011</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>48</v>
       </c>
@@ -3738,7 +3815,7 @@
         <v>14578</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>49</v>
       </c>
@@ -3751,17 +3828,17 @@
       <c r="D50">
         <v>4</v>
       </c>
-      <c r="E50" t="s">
+      <c r="F50" t="s">
         <v>908</v>
       </c>
-      <c r="F50" t="s">
+      <c r="G50" t="s">
         <v>912</v>
       </c>
-      <c r="G50" t="s">
+      <c r="H50" t="s">
         <v>911</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>50</v>
       </c>
@@ -3769,7 +3846,7 @@
         <v>3811</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>51</v>
       </c>
@@ -3777,7 +3854,7 @@
         <v>16595</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>52</v>
       </c>
@@ -3785,7 +3862,7 @@
         <v>19139</v>
       </c>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>53</v>
       </c>
@@ -3798,17 +3875,17 @@
       <c r="D54">
         <v>4</v>
       </c>
-      <c r="E54" t="s">
+      <c r="F54" t="s">
         <v>908</v>
       </c>
-      <c r="F54" t="s">
+      <c r="G54" t="s">
         <v>912</v>
       </c>
-      <c r="G54" t="s">
+      <c r="H54" t="s">
         <v>911</v>
       </c>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>54</v>
       </c>
@@ -3816,7 +3893,7 @@
         <v>4255</v>
       </c>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>55</v>
       </c>
@@ -3824,7 +3901,7 @@
         <v>21576</v>
       </c>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>56</v>
       </c>
@@ -3832,7 +3909,7 @@
         <v>20087</v>
       </c>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>57</v>
       </c>
@@ -3845,17 +3922,17 @@
       <c r="D58">
         <v>4</v>
       </c>
-      <c r="E58" t="s">
+      <c r="F58" t="s">
         <v>908</v>
       </c>
-      <c r="F58" t="s">
+      <c r="G58" t="s">
         <v>912</v>
       </c>
-      <c r="G58" t="s">
+      <c r="H58" t="s">
         <v>911</v>
       </c>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>58</v>
       </c>
@@ -3863,7 +3940,7 @@
         <v>3585</v>
       </c>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>59</v>
       </c>
@@ -3871,7 +3948,7 @@
         <v>16072</v>
       </c>
     </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>60</v>
       </c>
@@ -3879,7 +3956,7 @@
         <v>9368</v>
       </c>
     </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>61</v>
       </c>
@@ -3892,17 +3969,17 @@
       <c r="D62">
         <v>4</v>
       </c>
-      <c r="E62" t="s">
+      <c r="F62" t="s">
         <v>908</v>
       </c>
-      <c r="F62" t="s">
+      <c r="G62" t="s">
         <v>912</v>
       </c>
-      <c r="G62" t="s">
+      <c r="H62" t="s">
         <v>911</v>
       </c>
     </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>62</v>
       </c>
@@ -3910,7 +3987,7 @@
         <v>4241</v>
       </c>
     </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>63</v>
       </c>
@@ -3918,7 +3995,7 @@
         <v>14284</v>
       </c>
     </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>64</v>
       </c>
@@ -3926,7 +4003,7 @@
         <v>16266</v>
       </c>
     </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>65</v>
       </c>
@@ -3939,17 +4016,17 @@
       <c r="D66">
         <v>4</v>
       </c>
-      <c r="E66" t="s">
+      <c r="F66" t="s">
         <v>908</v>
       </c>
-      <c r="F66" t="s">
+      <c r="G66" t="s">
         <v>912</v>
       </c>
-      <c r="G66" t="s">
+      <c r="H66" t="s">
         <v>911</v>
       </c>
     </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>66</v>
       </c>
@@ -3957,7 +4034,7 @@
         <v>3848</v>
       </c>
     </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>67</v>
       </c>
@@ -3965,7 +4042,7 @@
         <v>14535</v>
       </c>
     </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>68</v>
       </c>
@@ -3973,7 +4050,7 @@
         <v>13543</v>
       </c>
     </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>69</v>
       </c>
@@ -3986,17 +4063,17 @@
       <c r="D70">
         <v>4</v>
       </c>
-      <c r="E70" t="s">
+      <c r="F70" t="s">
         <v>908</v>
       </c>
-      <c r="F70" t="s">
+      <c r="G70" t="s">
         <v>912</v>
       </c>
-      <c r="G70" t="s">
+      <c r="H70" t="s">
         <v>911</v>
       </c>
     </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>70</v>
       </c>
@@ -4004,7 +4081,7 @@
         <v>4113</v>
       </c>
     </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>71</v>
       </c>
@@ -4012,7 +4089,7 @@
         <v>22095</v>
       </c>
     </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>72</v>
       </c>
@@ -4020,7 +4097,7 @@
         <v>10361</v>
       </c>
     </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>73</v>
       </c>
@@ -4033,17 +4110,17 @@
       <c r="D74">
         <v>4</v>
       </c>
-      <c r="E74" t="s">
+      <c r="F74" t="s">
         <v>908</v>
       </c>
-      <c r="F74" t="s">
+      <c r="G74" t="s">
         <v>912</v>
       </c>
-      <c r="G74" t="s">
+      <c r="H74" t="s">
         <v>911</v>
       </c>
     </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>74</v>
       </c>
@@ -4051,7 +4128,7 @@
         <v>5462</v>
       </c>
     </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>75</v>
       </c>
@@ -4059,7 +4136,7 @@
         <v>16262</v>
       </c>
     </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>76</v>
       </c>
@@ -4067,7 +4144,7 @@
         <v>22865</v>
       </c>
     </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>77</v>
       </c>
@@ -4080,17 +4157,17 @@
       <c r="D78">
         <v>4</v>
       </c>
-      <c r="E78" t="s">
+      <c r="F78" t="s">
         <v>908</v>
       </c>
-      <c r="F78" t="s">
+      <c r="G78" t="s">
         <v>912</v>
       </c>
-      <c r="G78" t="s">
+      <c r="H78" t="s">
         <v>911</v>
       </c>
     </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>78</v>
       </c>
@@ -4098,7 +4175,7 @@
         <v>3708</v>
       </c>
     </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>79</v>
       </c>
@@ -4106,7 +4183,7 @@
         <v>12093</v>
       </c>
     </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>80</v>
       </c>
@@ -4114,7 +4191,7 @@
         <v>22277</v>
       </c>
     </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>81</v>
       </c>
@@ -4127,17 +4204,17 @@
       <c r="D82">
         <v>4</v>
       </c>
-      <c r="E82" t="s">
+      <c r="F82" t="s">
         <v>908</v>
       </c>
-      <c r="F82" t="s">
+      <c r="G82" t="s">
         <v>912</v>
       </c>
-      <c r="G82" t="s">
+      <c r="H82" t="s">
         <v>911</v>
       </c>
     </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>82</v>
       </c>
@@ -4145,7 +4222,7 @@
         <v>3975</v>
       </c>
     </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>83</v>
       </c>
@@ -4153,7 +4230,7 @@
         <v>20506</v>
       </c>
     </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>84</v>
       </c>
@@ -4161,7 +4238,7 @@
         <v>33413</v>
       </c>
     </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>85</v>
       </c>
@@ -4174,17 +4251,17 @@
       <c r="D86">
         <v>4</v>
       </c>
-      <c r="E86" t="s">
+      <c r="F86" t="s">
         <v>908</v>
       </c>
-      <c r="F86" t="s">
+      <c r="G86" t="s">
         <v>912</v>
       </c>
-      <c r="G86" t="s">
+      <c r="H86" t="s">
         <v>911</v>
       </c>
     </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>86</v>
       </c>
@@ -4192,7 +4269,7 @@
         <v>6827</v>
       </c>
     </row>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>87</v>
       </c>
@@ -4200,7 +4277,7 @@
         <v>15644</v>
       </c>
     </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>88</v>
       </c>
@@ -4208,7 +4285,7 @@
         <v>10144</v>
       </c>
     </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>89</v>
       </c>
@@ -4221,17 +4298,17 @@
       <c r="D90">
         <v>4</v>
       </c>
-      <c r="E90" t="s">
+      <c r="F90" t="s">
         <v>908</v>
       </c>
-      <c r="F90" t="s">
+      <c r="G90" t="s">
         <v>912</v>
       </c>
-      <c r="G90" t="s">
+      <c r="H90" t="s">
         <v>911</v>
       </c>
     </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>90</v>
       </c>
@@ -4239,7 +4316,7 @@
         <v>3942</v>
       </c>
     </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>91</v>
       </c>
@@ -4247,7 +4324,7 @@
         <v>25907</v>
       </c>
     </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>92</v>
       </c>
@@ -4255,7 +4332,7 @@
         <v>17779</v>
       </c>
     </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>93</v>
       </c>
@@ -4268,17 +4345,17 @@
       <c r="D94">
         <v>4</v>
       </c>
-      <c r="E94" t="s">
+      <c r="F94" t="s">
         <v>908</v>
       </c>
-      <c r="F94" t="s">
+      <c r="G94" t="s">
         <v>912</v>
       </c>
-      <c r="G94" t="s">
+      <c r="H94" t="s">
         <v>911</v>
       </c>
     </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>94</v>
       </c>
@@ -4286,7 +4363,7 @@
         <v>4141</v>
       </c>
     </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>95</v>
       </c>
@@ -4294,7 +4371,7 @@
         <v>7629</v>
       </c>
     </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>96</v>
       </c>
@@ -4302,7 +4379,7 @@
         <v>10819</v>
       </c>
     </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>97</v>
       </c>
@@ -4315,17 +4392,17 @@
       <c r="D98">
         <v>4</v>
       </c>
-      <c r="E98" t="s">
+      <c r="F98" t="s">
         <v>908</v>
       </c>
-      <c r="F98" t="s">
+      <c r="G98" t="s">
         <v>912</v>
       </c>
-      <c r="G98" t="s">
+      <c r="H98" t="s">
         <v>911</v>
       </c>
     </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>98</v>
       </c>
@@ -4333,7 +4410,7 @@
         <v>3552</v>
       </c>
     </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>99</v>
       </c>
@@ -4341,7 +4418,7 @@
         <v>14723</v>
       </c>
     </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>100</v>
       </c>
@@ -4349,7 +4426,7 @@
         <v>9891</v>
       </c>
     </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>101</v>
       </c>
@@ -4362,17 +4439,17 @@
       <c r="D102">
         <v>4</v>
       </c>
-      <c r="E102" t="s">
+      <c r="F102" t="s">
         <v>908</v>
       </c>
-      <c r="F102" t="s">
+      <c r="G102" t="s">
         <v>912</v>
       </c>
-      <c r="G102" t="s">
+      <c r="H102" t="s">
         <v>911</v>
       </c>
     </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>102</v>
       </c>
@@ -4380,7 +4457,7 @@
         <v>12582</v>
       </c>
     </row>
-    <row r="104" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>103</v>
       </c>
@@ -4388,7 +4465,7 @@
         <v>15891</v>
       </c>
     </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>104</v>
       </c>
@@ -4396,7 +4473,7 @@
         <v>17579</v>
       </c>
     </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>105</v>
       </c>
@@ -4409,17 +4486,17 @@
       <c r="D106">
         <v>4</v>
       </c>
-      <c r="E106" t="s">
+      <c r="F106" t="s">
         <v>908</v>
       </c>
-      <c r="F106" t="s">
+      <c r="G106" t="s">
         <v>912</v>
       </c>
-      <c r="G106" t="s">
+      <c r="H106" t="s">
         <v>911</v>
       </c>
     </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>106</v>
       </c>
@@ -4427,7 +4504,7 @@
         <v>3307</v>
       </c>
     </row>
-    <row r="108" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>107</v>
       </c>
@@ -4435,7 +4512,7 @@
         <v>26686</v>
       </c>
     </row>
-    <row r="109" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>108</v>
       </c>
@@ -4443,7 +4520,7 @@
         <v>14228</v>
       </c>
     </row>
-    <row r="110" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>109</v>
       </c>
@@ -4456,17 +4533,17 @@
       <c r="D110">
         <v>4</v>
       </c>
-      <c r="E110" t="s">
+      <c r="F110" t="s">
         <v>908</v>
       </c>
-      <c r="F110" t="s">
+      <c r="G110" t="s">
         <v>912</v>
       </c>
-      <c r="G110" t="s">
+      <c r="H110" t="s">
         <v>911</v>
       </c>
     </row>
-    <row r="111" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>110</v>
       </c>
@@ -4474,7 +4551,7 @@
         <v>3359</v>
       </c>
     </row>
-    <row r="112" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>111</v>
       </c>
@@ -4482,7 +4559,7 @@
         <v>18248</v>
       </c>
     </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>112</v>
       </c>
@@ -4490,7 +4567,7 @@
         <v>13247</v>
       </c>
     </row>
-    <row r="114" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>113</v>
       </c>
@@ -4503,17 +4580,17 @@
       <c r="D114">
         <v>4</v>
       </c>
-      <c r="E114" t="s">
+      <c r="F114" t="s">
         <v>908</v>
       </c>
-      <c r="F114" t="s">
+      <c r="G114" t="s">
         <v>912</v>
       </c>
-      <c r="G114" t="s">
+      <c r="H114" t="s">
         <v>911</v>
       </c>
     </row>
-    <row r="115" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>114</v>
       </c>
@@ -4521,7 +4598,7 @@
         <v>3928</v>
       </c>
     </row>
-    <row r="116" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>115</v>
       </c>
@@ -4529,7 +4606,7 @@
         <v>13748</v>
       </c>
     </row>
-    <row r="117" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>116</v>
       </c>
@@ -4537,7 +4614,7 @@
         <v>14399</v>
       </c>
     </row>
-    <row r="118" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>117</v>
       </c>
@@ -4550,17 +4627,17 @@
       <c r="D118">
         <v>4</v>
       </c>
-      <c r="E118" t="s">
+      <c r="F118" t="s">
         <v>908</v>
       </c>
-      <c r="F118" t="s">
+      <c r="G118" t="s">
         <v>912</v>
       </c>
-      <c r="G118" t="s">
+      <c r="H118" t="s">
         <v>911</v>
       </c>
     </row>
-    <row r="119" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>118</v>
       </c>
@@ -4568,7 +4645,7 @@
         <v>4177</v>
       </c>
     </row>
-    <row r="120" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>119</v>
       </c>
@@ -4576,7 +4653,7 @@
         <v>17458</v>
       </c>
     </row>
-    <row r="121" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>120</v>
       </c>
@@ -4584,7 +4661,7 @@
         <v>22349</v>
       </c>
     </row>
-    <row r="122" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>121</v>
       </c>
@@ -4597,17 +4674,17 @@
       <c r="D122">
         <v>4</v>
       </c>
-      <c r="E122" t="s">
+      <c r="F122" t="s">
         <v>908</v>
       </c>
-      <c r="F122" t="s">
+      <c r="G122" t="s">
         <v>912</v>
       </c>
-      <c r="G122" t="s">
+      <c r="H122" t="s">
         <v>911</v>
       </c>
     </row>
-    <row r="123" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>122</v>
       </c>
@@ -4615,7 +4692,7 @@
         <v>3728</v>
       </c>
     </row>
-    <row r="124" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>123</v>
       </c>
@@ -4623,7 +4700,7 @@
         <v>20617</v>
       </c>
     </row>
-    <row r="125" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>124</v>
       </c>
@@ -4631,7 +4708,7 @@
         <v>14916</v>
       </c>
     </row>
-    <row r="126" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>125</v>
       </c>
@@ -4644,17 +4721,17 @@
       <c r="D126">
         <v>4</v>
       </c>
-      <c r="E126" t="s">
+      <c r="F126" t="s">
         <v>908</v>
       </c>
-      <c r="F126" t="s">
+      <c r="G126" t="s">
         <v>912</v>
       </c>
-      <c r="G126" t="s">
+      <c r="H126" t="s">
         <v>911</v>
       </c>
     </row>
-    <row r="127" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>126</v>
       </c>
@@ -4662,7 +4739,7 @@
         <v>5462</v>
       </c>
     </row>
-    <row r="128" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>127</v>
       </c>
@@ -4670,7 +4747,7 @@
         <v>16262</v>
       </c>
     </row>
-    <row r="129" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>128</v>
       </c>
@@ -4678,7 +4755,7 @@
         <v>22865</v>
       </c>
     </row>
-    <row r="130" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>129</v>
       </c>
@@ -4691,17 +4768,17 @@
       <c r="D130">
         <v>4</v>
       </c>
-      <c r="E130" t="s">
+      <c r="F130" t="s">
         <v>908</v>
       </c>
-      <c r="F130" t="s">
+      <c r="G130" t="s">
         <v>912</v>
       </c>
-      <c r="G130" t="s">
+      <c r="H130" t="s">
         <v>911</v>
       </c>
     </row>
-    <row r="131" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>757</v>
       </c>
@@ -4709,7 +4786,7 @@
         <v>19481</v>
       </c>
     </row>
-    <row r="132" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>758</v>
       </c>
@@ -4717,7 +4794,7 @@
         <v>25838</v>
       </c>
     </row>
-    <row r="133" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>759</v>
       </c>
@@ -4725,7 +4802,7 @@
         <v>15438</v>
       </c>
     </row>
-    <row r="134" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>760</v>
       </c>
@@ -4733,7 +4810,7 @@
         <v>1434824</v>
       </c>
     </row>
-    <row r="135" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>761</v>
       </c>
@@ -4741,7 +4818,7 @@
         <v>2086653</v>
       </c>
     </row>
-    <row r="136" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>762</v>
       </c>
@@ -4749,7 +4826,7 @@
         <v>1007413</v>
       </c>
     </row>
-    <row r="137" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>763</v>
       </c>
@@ -4757,7 +4834,7 @@
         <v>50601</v>
       </c>
     </row>
-    <row r="138" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>764</v>
       </c>
@@ -4765,7 +4842,7 @@
         <v>164306</v>
       </c>
     </row>
-    <row r="139" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>765</v>
       </c>
@@ -4773,7 +4850,7 @@
         <v>663860</v>
       </c>
     </row>
-    <row r="140" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>766</v>
       </c>
@@ -4781,7 +4858,7 @@
         <v>739003</v>
       </c>
     </row>
-    <row r="141" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>767</v>
       </c>
@@ -4789,7 +4866,7 @@
         <v>665272</v>
       </c>
     </row>
-    <row r="142" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>768</v>
       </c>
@@ -4797,7 +4874,7 @@
         <v>635163</v>
       </c>
     </row>
-    <row r="143" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>769</v>
       </c>
@@ -4805,7 +4882,7 @@
         <v>760300</v>
       </c>
     </row>
-    <row r="144" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>770</v>
       </c>
@@ -10829,7 +10906,7 @@
         <v>757884</v>
       </c>
     </row>
-    <row r="897" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="897" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A897" t="s">
         <v>904</v>
       </c>
@@ -10842,14 +10919,14 @@
       <c r="D897">
         <v>1</v>
       </c>
-      <c r="E897" t="s">
+      <c r="F897" t="s">
         <v>906</v>
       </c>
-      <c r="F897" t="s">
+      <c r="G897" t="s">
         <v>907</v>
       </c>
     </row>
-    <row r="898" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="898" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A898" t="s">
         <v>901</v>
       </c>
@@ -10857,7 +10934,7 @@
         <v>2851</v>
       </c>
     </row>
-    <row r="899" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="899" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A899" t="s">
         <v>902</v>
       </c>
@@ -10865,7 +10942,7 @@
         <v>186389</v>
       </c>
     </row>
-    <row r="900" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="900" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A900" t="s">
         <v>903</v>
       </c>

--- a/images/image manifest.xlsx
+++ b/images/image manifest.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\Github\CS-Graphics\images\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4D8C480-1220-47B1-B455-836D118CF091}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2911D216-6E45-4439-87FA-BD143F5C5F09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="21480" windowHeight="11520" xr2:uid="{620D0F7A-D0D3-4EA0-8A4D-C0BB25CE06A6}"/>
+    <workbookView xWindow="6570" yWindow="810" windowWidth="21600" windowHeight="11295" xr2:uid="{620D0F7A-D0D3-4EA0-8A4D-C0BB25CE06A6}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1049" uniqueCount="919">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1759" uniqueCount="929">
   <si>
     <t>Filename</t>
   </si>
@@ -2794,6 +2794,36 @@
   </si>
   <si>
     <t>Tola danger idle</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>Dynamic Palette</t>
+  </si>
+  <si>
+    <t>Multiple duties</t>
+  </si>
+  <si>
+    <t>Main Menu</t>
+  </si>
+  <si>
+    <t>Building lights</t>
+  </si>
+  <si>
+    <t>Visual activity</t>
+  </si>
+  <si>
+    <t>MAINMENU.PLX</t>
+  </si>
+  <si>
+    <t>TODO(Name) healthy idle</t>
+  </si>
+  <si>
+    <t>TODO(Name) warning idle</t>
+  </si>
+  <si>
+    <t>TODO(Name) danger idle</t>
   </si>
 </sst>
 </file>
@@ -2854,17 +2884,19 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D76A0E2E-5EF1-4C76-B441-AB9216212B3A}" name="Table1" displayName="Table1" ref="A1:H900" totalsRowShown="0">
-  <autoFilter ref="A1:H900" xr:uid="{D76A0E2E-5EF1-4C76-B441-AB9216212B3A}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A7:G869">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D76A0E2E-5EF1-4C76-B441-AB9216212B3A}" name="Table1" displayName="Table1" ref="A1:J900" totalsRowShown="0">
+  <autoFilter ref="A1:J900" xr:uid="{D76A0E2E-5EF1-4C76-B441-AB9216212B3A}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A7:I869">
     <sortCondition ref="A1:A900"/>
   </sortState>
-  <tableColumns count="8">
+  <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{5BE264B2-3040-4E26-A5F7-09EDCD3E654D}" name="Filename"/>
     <tableColumn id="2" xr3:uid="{AA34CE9E-8179-4C54-86B6-0527AB82EA40}" name="Size" dataDxfId="0"/>
     <tableColumn id="3" xr3:uid="{67331664-BB23-4B18-BAE5-9C442B93DC80}" name="Palette"/>
     <tableColumn id="4" xr3:uid="{939C3ADC-1918-446F-8F03-0323F831EA15}" name="Frames"/>
     <tableColumn id="8" xr3:uid="{9479E81C-320D-4A48-BCAE-E8694A4258D2}" name="Animation stacked"/>
+    <tableColumn id="9" xr3:uid="{7FE2A3D8-8AF2-4005-AB3E-AB67EA76E700}" name="Dynamic Palette"/>
+    <tableColumn id="10" xr3:uid="{848C53D0-28FE-439E-8146-64439AFB27ED}" name="Multiple duties"/>
     <tableColumn id="5" xr3:uid="{38C11265-21A9-4D92-ADAC-81770284CD74}" name="Type"/>
     <tableColumn id="6" xr3:uid="{E8D6B3ED-E7AB-4418-98DF-3F96091191AB}" name="Description"/>
     <tableColumn id="7" xr3:uid="{12717EBE-E94A-4C45-AE7E-ADDEC9F71820}" name="Purpose"/>
@@ -3190,18 +3222,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{847C270E-F408-4D3B-B2DA-3B018BAD355D}">
-  <dimension ref="A1:H900"/>
+  <dimension ref="A1:J900"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.7109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="9.7109375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.85546875" customWidth="1"/>
-    <col min="6" max="6" width="18.140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="24.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="7" width="9.85546875" customWidth="1"/>
+    <col min="8" max="8" width="18.140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="24.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -3218,24 +3250,54 @@
         <v>913</v>
       </c>
       <c r="F1" t="s">
+        <v>920</v>
+      </c>
+      <c r="G1" t="s">
+        <v>921</v>
+      </c>
+      <c r="H1" t="s">
         <v>2</v>
       </c>
-      <c r="G1" t="s">
+      <c r="I1" t="s">
         <v>3</v>
       </c>
-      <c r="H1" t="s">
+      <c r="J1" t="s">
         <v>910</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>752</v>
       </c>
       <c r="B2" s="1">
         <v>75376</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C2" t="s">
+        <v>925</v>
+      </c>
+      <c r="D2">
+        <v>10</v>
+      </c>
+      <c r="E2" t="s">
+        <v>914</v>
+      </c>
+      <c r="F2" t="s">
+        <v>919</v>
+      </c>
+      <c r="G2" t="s">
+        <v>914</v>
+      </c>
+      <c r="H2" t="s">
+        <v>922</v>
+      </c>
+      <c r="I2" t="s">
+        <v>923</v>
+      </c>
+      <c r="J2" t="s">
+        <v>924</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>753</v>
       </c>
@@ -3243,7 +3305,7 @@
         <v>129265</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>754</v>
       </c>
@@ -3251,7 +3313,7 @@
         <v>35736</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>755</v>
       </c>
@@ -3259,7 +3321,7 @@
         <v>17697</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>756</v>
       </c>
@@ -3267,7 +3329,7 @@
         <v>50366</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -3284,16 +3346,22 @@
         <v>914</v>
       </c>
       <c r="F7" t="s">
+        <v>919</v>
+      </c>
+      <c r="G7" t="s">
+        <v>919</v>
+      </c>
+      <c r="H7" t="s">
         <v>908</v>
       </c>
-      <c r="G7" t="s">
+      <c r="I7" t="s">
         <v>915</v>
       </c>
-      <c r="H7" t="s">
+      <c r="J7" t="s">
         <v>916</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -3310,16 +3378,22 @@
         <v>914</v>
       </c>
       <c r="F8" t="s">
+        <v>919</v>
+      </c>
+      <c r="G8" t="s">
+        <v>919</v>
+      </c>
+      <c r="H8" t="s">
         <v>908</v>
       </c>
-      <c r="G8" t="s">
+      <c r="I8" t="s">
         <v>917</v>
       </c>
-      <c r="H8" t="s">
+      <c r="J8" t="s">
         <v>916</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>8</v>
       </c>
@@ -3336,16 +3410,22 @@
         <v>914</v>
       </c>
       <c r="F9" t="s">
+        <v>919</v>
+      </c>
+      <c r="G9" t="s">
+        <v>919</v>
+      </c>
+      <c r="H9" t="s">
         <v>908</v>
       </c>
-      <c r="G9" t="s">
+      <c r="I9" t="s">
         <v>918</v>
       </c>
-      <c r="H9" t="s">
+      <c r="J9" t="s">
         <v>916</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>9</v>
       </c>
@@ -3358,41 +3438,122 @@
       <c r="D10">
         <v>4</v>
       </c>
+      <c r="E10" t="s">
+        <v>919</v>
+      </c>
       <c r="F10" t="s">
+        <v>919</v>
+      </c>
+      <c r="G10" t="s">
+        <v>919</v>
+      </c>
+      <c r="H10" t="s">
         <v>908</v>
       </c>
-      <c r="G10" t="s">
+      <c r="I10" t="s">
         <v>912</v>
       </c>
-      <c r="H10" t="s">
+      <c r="J10" t="s">
         <v>911</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>10</v>
       </c>
       <c r="B11" s="1">
         <v>3837</v>
       </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C11" t="s">
+        <v>909</v>
+      </c>
+      <c r="D11">
+        <v>30</v>
+      </c>
+      <c r="E11" t="s">
+        <v>914</v>
+      </c>
+      <c r="F11" t="s">
+        <v>919</v>
+      </c>
+      <c r="G11" t="s">
+        <v>919</v>
+      </c>
+      <c r="H11" t="s">
+        <v>908</v>
+      </c>
+      <c r="I11" t="s">
+        <v>926</v>
+      </c>
+      <c r="J11" t="s">
+        <v>916</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>11</v>
       </c>
       <c r="B12" s="1">
         <v>17892</v>
       </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C12" t="s">
+        <v>909</v>
+      </c>
+      <c r="D12">
+        <v>30</v>
+      </c>
+      <c r="E12" t="s">
+        <v>914</v>
+      </c>
+      <c r="F12" t="s">
+        <v>919</v>
+      </c>
+      <c r="G12" t="s">
+        <v>919</v>
+      </c>
+      <c r="H12" t="s">
+        <v>908</v>
+      </c>
+      <c r="I12" t="s">
+        <v>927</v>
+      </c>
+      <c r="J12" t="s">
+        <v>916</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>12</v>
       </c>
       <c r="B13" s="1">
         <v>19255</v>
       </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C13" t="s">
+        <v>909</v>
+      </c>
+      <c r="D13">
+        <v>30</v>
+      </c>
+      <c r="E13" t="s">
+        <v>914</v>
+      </c>
+      <c r="F13" t="s">
+        <v>919</v>
+      </c>
+      <c r="G13" t="s">
+        <v>919</v>
+      </c>
+      <c r="H13" t="s">
+        <v>908</v>
+      </c>
+      <c r="I13" t="s">
+        <v>928</v>
+      </c>
+      <c r="J13" t="s">
+        <v>916</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>13</v>
       </c>
@@ -3405,41 +3566,122 @@
       <c r="D14">
         <v>4</v>
       </c>
+      <c r="E14" t="s">
+        <v>919</v>
+      </c>
       <c r="F14" t="s">
+        <v>919</v>
+      </c>
+      <c r="G14" t="s">
+        <v>919</v>
+      </c>
+      <c r="H14" t="s">
         <v>908</v>
       </c>
-      <c r="G14" t="s">
+      <c r="I14" t="s">
         <v>912</v>
       </c>
-      <c r="H14" t="s">
+      <c r="J14" t="s">
         <v>911</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>14</v>
       </c>
       <c r="B15" s="1">
         <v>4962</v>
       </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C15" t="s">
+        <v>909</v>
+      </c>
+      <c r="D15">
+        <v>30</v>
+      </c>
+      <c r="E15" t="s">
+        <v>914</v>
+      </c>
+      <c r="F15" t="s">
+        <v>919</v>
+      </c>
+      <c r="G15" t="s">
+        <v>919</v>
+      </c>
+      <c r="H15" t="s">
+        <v>908</v>
+      </c>
+      <c r="I15" t="s">
+        <v>926</v>
+      </c>
+      <c r="J15" t="s">
+        <v>916</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>15</v>
       </c>
       <c r="B16" s="1">
         <v>27484</v>
       </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C16" t="s">
+        <v>909</v>
+      </c>
+      <c r="D16">
+        <v>30</v>
+      </c>
+      <c r="E16" t="s">
+        <v>914</v>
+      </c>
+      <c r="F16" t="s">
+        <v>919</v>
+      </c>
+      <c r="G16" t="s">
+        <v>919</v>
+      </c>
+      <c r="H16" t="s">
+        <v>908</v>
+      </c>
+      <c r="I16" t="s">
+        <v>927</v>
+      </c>
+      <c r="J16" t="s">
+        <v>916</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>16</v>
       </c>
       <c r="B17" s="1">
         <v>28958</v>
       </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C17" t="s">
+        <v>909</v>
+      </c>
+      <c r="D17">
+        <v>30</v>
+      </c>
+      <c r="E17" t="s">
+        <v>914</v>
+      </c>
+      <c r="F17" t="s">
+        <v>919</v>
+      </c>
+      <c r="G17" t="s">
+        <v>919</v>
+      </c>
+      <c r="H17" t="s">
+        <v>908</v>
+      </c>
+      <c r="I17" t="s">
+        <v>928</v>
+      </c>
+      <c r="J17" t="s">
+        <v>916</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>17</v>
       </c>
@@ -3452,41 +3694,119 @@
       <c r="D18">
         <v>4</v>
       </c>
+      <c r="E18" t="s">
+        <v>919</v>
+      </c>
       <c r="F18" t="s">
+        <v>919</v>
+      </c>
+      <c r="H18" t="s">
         <v>908</v>
       </c>
-      <c r="G18" t="s">
+      <c r="I18" t="s">
         <v>912</v>
       </c>
-      <c r="H18" t="s">
+      <c r="J18" t="s">
         <v>911</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>18</v>
       </c>
       <c r="B19" s="1">
         <v>4760</v>
       </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C19" t="s">
+        <v>909</v>
+      </c>
+      <c r="D19">
+        <v>30</v>
+      </c>
+      <c r="E19" t="s">
+        <v>914</v>
+      </c>
+      <c r="F19" t="s">
+        <v>919</v>
+      </c>
+      <c r="G19" t="s">
+        <v>919</v>
+      </c>
+      <c r="H19" t="s">
+        <v>908</v>
+      </c>
+      <c r="I19" t="s">
+        <v>926</v>
+      </c>
+      <c r="J19" t="s">
+        <v>916</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>19</v>
       </c>
       <c r="B20" s="1">
         <v>18746</v>
       </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C20" t="s">
+        <v>909</v>
+      </c>
+      <c r="D20">
+        <v>30</v>
+      </c>
+      <c r="E20" t="s">
+        <v>914</v>
+      </c>
+      <c r="F20" t="s">
+        <v>919</v>
+      </c>
+      <c r="G20" t="s">
+        <v>919</v>
+      </c>
+      <c r="H20" t="s">
+        <v>908</v>
+      </c>
+      <c r="I20" t="s">
+        <v>927</v>
+      </c>
+      <c r="J20" t="s">
+        <v>916</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>20</v>
       </c>
       <c r="B21" s="1">
         <v>17387</v>
       </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C21" t="s">
+        <v>909</v>
+      </c>
+      <c r="D21">
+        <v>30</v>
+      </c>
+      <c r="E21" t="s">
+        <v>914</v>
+      </c>
+      <c r="F21" t="s">
+        <v>919</v>
+      </c>
+      <c r="G21" t="s">
+        <v>919</v>
+      </c>
+      <c r="H21" t="s">
+        <v>908</v>
+      </c>
+      <c r="I21" t="s">
+        <v>928</v>
+      </c>
+      <c r="J21" t="s">
+        <v>916</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>21</v>
       </c>
@@ -3499,41 +3819,119 @@
       <c r="D22">
         <v>4</v>
       </c>
+      <c r="E22" t="s">
+        <v>919</v>
+      </c>
       <c r="F22" t="s">
+        <v>919</v>
+      </c>
+      <c r="H22" t="s">
         <v>908</v>
       </c>
-      <c r="G22" t="s">
+      <c r="I22" t="s">
         <v>912</v>
       </c>
-      <c r="H22" t="s">
+      <c r="J22" t="s">
         <v>911</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>22</v>
       </c>
       <c r="B23" s="1">
         <v>4613</v>
       </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C23" t="s">
+        <v>909</v>
+      </c>
+      <c r="D23">
+        <v>30</v>
+      </c>
+      <c r="E23" t="s">
+        <v>914</v>
+      </c>
+      <c r="F23" t="s">
+        <v>919</v>
+      </c>
+      <c r="G23" t="s">
+        <v>919</v>
+      </c>
+      <c r="H23" t="s">
+        <v>908</v>
+      </c>
+      <c r="I23" t="s">
+        <v>926</v>
+      </c>
+      <c r="J23" t="s">
+        <v>916</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>23</v>
       </c>
       <c r="B24" s="1">
         <v>18010</v>
       </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C24" t="s">
+        <v>909</v>
+      </c>
+      <c r="D24">
+        <v>30</v>
+      </c>
+      <c r="E24" t="s">
+        <v>914</v>
+      </c>
+      <c r="F24" t="s">
+        <v>919</v>
+      </c>
+      <c r="G24" t="s">
+        <v>919</v>
+      </c>
+      <c r="H24" t="s">
+        <v>908</v>
+      </c>
+      <c r="I24" t="s">
+        <v>927</v>
+      </c>
+      <c r="J24" t="s">
+        <v>916</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>24</v>
       </c>
       <c r="B25" s="1">
         <v>21511</v>
       </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C25" t="s">
+        <v>909</v>
+      </c>
+      <c r="D25">
+        <v>30</v>
+      </c>
+      <c r="E25" t="s">
+        <v>914</v>
+      </c>
+      <c r="F25" t="s">
+        <v>919</v>
+      </c>
+      <c r="G25" t="s">
+        <v>919</v>
+      </c>
+      <c r="H25" t="s">
+        <v>908</v>
+      </c>
+      <c r="I25" t="s">
+        <v>928</v>
+      </c>
+      <c r="J25" t="s">
+        <v>916</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>25</v>
       </c>
@@ -3546,41 +3944,119 @@
       <c r="D26">
         <v>4</v>
       </c>
+      <c r="E26" t="s">
+        <v>919</v>
+      </c>
       <c r="F26" t="s">
+        <v>919</v>
+      </c>
+      <c r="H26" t="s">
         <v>908</v>
       </c>
-      <c r="G26" t="s">
+      <c r="I26" t="s">
         <v>912</v>
       </c>
-      <c r="H26" t="s">
+      <c r="J26" t="s">
         <v>911</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>26</v>
       </c>
       <c r="B27" s="1">
         <v>4056</v>
       </c>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C27" t="s">
+        <v>909</v>
+      </c>
+      <c r="D27">
+        <v>30</v>
+      </c>
+      <c r="E27" t="s">
+        <v>914</v>
+      </c>
+      <c r="F27" t="s">
+        <v>919</v>
+      </c>
+      <c r="G27" t="s">
+        <v>919</v>
+      </c>
+      <c r="H27" t="s">
+        <v>908</v>
+      </c>
+      <c r="I27" t="s">
+        <v>926</v>
+      </c>
+      <c r="J27" t="s">
+        <v>916</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>27</v>
       </c>
       <c r="B28" s="1">
         <v>26577</v>
       </c>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C28" t="s">
+        <v>909</v>
+      </c>
+      <c r="D28">
+        <v>30</v>
+      </c>
+      <c r="E28" t="s">
+        <v>914</v>
+      </c>
+      <c r="F28" t="s">
+        <v>919</v>
+      </c>
+      <c r="G28" t="s">
+        <v>919</v>
+      </c>
+      <c r="H28" t="s">
+        <v>908</v>
+      </c>
+      <c r="I28" t="s">
+        <v>927</v>
+      </c>
+      <c r="J28" t="s">
+        <v>916</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>28</v>
       </c>
       <c r="B29" s="1">
         <v>20293</v>
       </c>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C29" t="s">
+        <v>909</v>
+      </c>
+      <c r="D29">
+        <v>30</v>
+      </c>
+      <c r="E29" t="s">
+        <v>914</v>
+      </c>
+      <c r="F29" t="s">
+        <v>919</v>
+      </c>
+      <c r="G29" t="s">
+        <v>919</v>
+      </c>
+      <c r="H29" t="s">
+        <v>908</v>
+      </c>
+      <c r="I29" t="s">
+        <v>928</v>
+      </c>
+      <c r="J29" t="s">
+        <v>916</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>29</v>
       </c>
@@ -3593,41 +4069,119 @@
       <c r="D30">
         <v>4</v>
       </c>
+      <c r="E30" t="s">
+        <v>919</v>
+      </c>
       <c r="F30" t="s">
+        <v>919</v>
+      </c>
+      <c r="H30" t="s">
         <v>908</v>
       </c>
-      <c r="G30" t="s">
+      <c r="I30" t="s">
         <v>912</v>
       </c>
-      <c r="H30" t="s">
+      <c r="J30" t="s">
         <v>911</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>30</v>
       </c>
       <c r="B31" s="1">
         <v>4494</v>
       </c>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C31" t="s">
+        <v>909</v>
+      </c>
+      <c r="D31">
+        <v>30</v>
+      </c>
+      <c r="E31" t="s">
+        <v>914</v>
+      </c>
+      <c r="F31" t="s">
+        <v>919</v>
+      </c>
+      <c r="G31" t="s">
+        <v>919</v>
+      </c>
+      <c r="H31" t="s">
+        <v>908</v>
+      </c>
+      <c r="I31" t="s">
+        <v>926</v>
+      </c>
+      <c r="J31" t="s">
+        <v>916</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>31</v>
       </c>
       <c r="B32" s="1">
         <v>18509</v>
       </c>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C32" t="s">
+        <v>909</v>
+      </c>
+      <c r="D32">
+        <v>30</v>
+      </c>
+      <c r="E32" t="s">
+        <v>914</v>
+      </c>
+      <c r="F32" t="s">
+        <v>919</v>
+      </c>
+      <c r="G32" t="s">
+        <v>919</v>
+      </c>
+      <c r="H32" t="s">
+        <v>908</v>
+      </c>
+      <c r="I32" t="s">
+        <v>927</v>
+      </c>
+      <c r="J32" t="s">
+        <v>916</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>32</v>
       </c>
       <c r="B33" s="1">
         <v>30532</v>
       </c>
-    </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C33" t="s">
+        <v>909</v>
+      </c>
+      <c r="D33">
+        <v>30</v>
+      </c>
+      <c r="E33" t="s">
+        <v>914</v>
+      </c>
+      <c r="F33" t="s">
+        <v>919</v>
+      </c>
+      <c r="G33" t="s">
+        <v>919</v>
+      </c>
+      <c r="H33" t="s">
+        <v>908</v>
+      </c>
+      <c r="I33" t="s">
+        <v>928</v>
+      </c>
+      <c r="J33" t="s">
+        <v>916</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>33</v>
       </c>
@@ -3640,41 +4194,119 @@
       <c r="D34">
         <v>4</v>
       </c>
+      <c r="E34" t="s">
+        <v>919</v>
+      </c>
       <c r="F34" t="s">
+        <v>919</v>
+      </c>
+      <c r="H34" t="s">
         <v>908</v>
       </c>
-      <c r="G34" t="s">
+      <c r="I34" t="s">
         <v>912</v>
       </c>
-      <c r="H34" t="s">
+      <c r="J34" t="s">
         <v>911</v>
       </c>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>34</v>
       </c>
       <c r="B35" s="1">
         <v>5475</v>
       </c>
-    </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C35" t="s">
+        <v>909</v>
+      </c>
+      <c r="D35">
+        <v>31</v>
+      </c>
+      <c r="E35" t="s">
+        <v>914</v>
+      </c>
+      <c r="F35" t="s">
+        <v>919</v>
+      </c>
+      <c r="G35" t="s">
+        <v>919</v>
+      </c>
+      <c r="H35" t="s">
+        <v>908</v>
+      </c>
+      <c r="I35" t="s">
+        <v>926</v>
+      </c>
+      <c r="J35" t="s">
+        <v>916</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>35</v>
       </c>
       <c r="B36" s="1">
         <v>23999</v>
       </c>
-    </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C36" t="s">
+        <v>909</v>
+      </c>
+      <c r="D36">
+        <v>30</v>
+      </c>
+      <c r="E36" t="s">
+        <v>914</v>
+      </c>
+      <c r="F36" t="s">
+        <v>919</v>
+      </c>
+      <c r="G36" t="s">
+        <v>919</v>
+      </c>
+      <c r="H36" t="s">
+        <v>908</v>
+      </c>
+      <c r="I36" t="s">
+        <v>927</v>
+      </c>
+      <c r="J36" t="s">
+        <v>916</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>36</v>
       </c>
       <c r="B37" s="1">
         <v>14302</v>
       </c>
-    </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C37" t="s">
+        <v>909</v>
+      </c>
+      <c r="D37">
+        <v>30</v>
+      </c>
+      <c r="E37" t="s">
+        <v>914</v>
+      </c>
+      <c r="F37" t="s">
+        <v>919</v>
+      </c>
+      <c r="G37" t="s">
+        <v>919</v>
+      </c>
+      <c r="H37" t="s">
+        <v>908</v>
+      </c>
+      <c r="I37" t="s">
+        <v>928</v>
+      </c>
+      <c r="J37" t="s">
+        <v>916</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>37</v>
       </c>
@@ -3687,41 +4319,119 @@
       <c r="D38">
         <v>4</v>
       </c>
+      <c r="E38" t="s">
+        <v>919</v>
+      </c>
       <c r="F38" t="s">
+        <v>919</v>
+      </c>
+      <c r="H38" t="s">
         <v>908</v>
       </c>
-      <c r="G38" t="s">
+      <c r="I38" t="s">
         <v>912</v>
       </c>
-      <c r="H38" t="s">
+      <c r="J38" t="s">
         <v>911</v>
       </c>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>38</v>
       </c>
       <c r="B39" s="1">
         <v>5028</v>
       </c>
-    </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C39" t="s">
+        <v>909</v>
+      </c>
+      <c r="D39">
+        <v>30</v>
+      </c>
+      <c r="E39" t="s">
+        <v>914</v>
+      </c>
+      <c r="F39" t="s">
+        <v>919</v>
+      </c>
+      <c r="G39" t="s">
+        <v>919</v>
+      </c>
+      <c r="H39" t="s">
+        <v>908</v>
+      </c>
+      <c r="I39" t="s">
+        <v>926</v>
+      </c>
+      <c r="J39" t="s">
+        <v>916</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>39</v>
       </c>
       <c r="B40" s="1">
         <v>14517</v>
       </c>
-    </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C40" t="s">
+        <v>909</v>
+      </c>
+      <c r="D40">
+        <v>30</v>
+      </c>
+      <c r="E40" t="s">
+        <v>914</v>
+      </c>
+      <c r="F40" t="s">
+        <v>919</v>
+      </c>
+      <c r="G40" t="s">
+        <v>919</v>
+      </c>
+      <c r="H40" t="s">
+        <v>908</v>
+      </c>
+      <c r="I40" t="s">
+        <v>927</v>
+      </c>
+      <c r="J40" t="s">
+        <v>916</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>40</v>
       </c>
       <c r="B41" s="1">
         <v>28308</v>
       </c>
-    </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C41" t="s">
+        <v>909</v>
+      </c>
+      <c r="D41">
+        <v>30</v>
+      </c>
+      <c r="E41" t="s">
+        <v>914</v>
+      </c>
+      <c r="F41" t="s">
+        <v>919</v>
+      </c>
+      <c r="G41" t="s">
+        <v>919</v>
+      </c>
+      <c r="H41" t="s">
+        <v>908</v>
+      </c>
+      <c r="I41" t="s">
+        <v>928</v>
+      </c>
+      <c r="J41" t="s">
+        <v>916</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>41</v>
       </c>
@@ -3734,41 +4444,119 @@
       <c r="D42">
         <v>4</v>
       </c>
+      <c r="E42" t="s">
+        <v>919</v>
+      </c>
       <c r="F42" t="s">
+        <v>919</v>
+      </c>
+      <c r="H42" t="s">
         <v>908</v>
       </c>
-      <c r="G42" t="s">
+      <c r="I42" t="s">
         <v>912</v>
       </c>
-      <c r="H42" t="s">
+      <c r="J42" t="s">
         <v>911</v>
       </c>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>42</v>
       </c>
       <c r="B43" s="1">
         <v>3841</v>
       </c>
-    </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C43" t="s">
+        <v>909</v>
+      </c>
+      <c r="D43">
+        <v>30</v>
+      </c>
+      <c r="E43" t="s">
+        <v>914</v>
+      </c>
+      <c r="F43" t="s">
+        <v>919</v>
+      </c>
+      <c r="G43" t="s">
+        <v>919</v>
+      </c>
+      <c r="H43" t="s">
+        <v>908</v>
+      </c>
+      <c r="I43" t="s">
+        <v>926</v>
+      </c>
+      <c r="J43" t="s">
+        <v>916</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>43</v>
       </c>
       <c r="B44" s="1">
         <v>13899</v>
       </c>
-    </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C44" t="s">
+        <v>909</v>
+      </c>
+      <c r="D44">
+        <v>30</v>
+      </c>
+      <c r="E44" t="s">
+        <v>914</v>
+      </c>
+      <c r="F44" t="s">
+        <v>919</v>
+      </c>
+      <c r="G44" t="s">
+        <v>919</v>
+      </c>
+      <c r="H44" t="s">
+        <v>908</v>
+      </c>
+      <c r="I44" t="s">
+        <v>927</v>
+      </c>
+      <c r="J44" t="s">
+        <v>916</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>44</v>
       </c>
       <c r="B45" s="1">
         <v>14453</v>
       </c>
-    </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C45" t="s">
+        <v>909</v>
+      </c>
+      <c r="D45">
+        <v>30</v>
+      </c>
+      <c r="E45" t="s">
+        <v>914</v>
+      </c>
+      <c r="F45" t="s">
+        <v>919</v>
+      </c>
+      <c r="G45" t="s">
+        <v>919</v>
+      </c>
+      <c r="H45" t="s">
+        <v>908</v>
+      </c>
+      <c r="I45" t="s">
+        <v>928</v>
+      </c>
+      <c r="J45" t="s">
+        <v>916</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>45</v>
       </c>
@@ -3781,41 +4569,119 @@
       <c r="D46">
         <v>4</v>
       </c>
+      <c r="E46" t="s">
+        <v>919</v>
+      </c>
       <c r="F46" t="s">
+        <v>919</v>
+      </c>
+      <c r="H46" t="s">
         <v>908</v>
       </c>
-      <c r="G46" t="s">
+      <c r="I46" t="s">
         <v>912</v>
       </c>
-      <c r="H46" t="s">
+      <c r="J46" t="s">
         <v>911</v>
       </c>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>46</v>
       </c>
       <c r="B47" s="1">
         <v>4674</v>
       </c>
-    </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C47" t="s">
+        <v>909</v>
+      </c>
+      <c r="D47">
+        <v>30</v>
+      </c>
+      <c r="E47" t="s">
+        <v>914</v>
+      </c>
+      <c r="F47" t="s">
+        <v>919</v>
+      </c>
+      <c r="G47" t="s">
+        <v>919</v>
+      </c>
+      <c r="H47" t="s">
+        <v>908</v>
+      </c>
+      <c r="I47" t="s">
+        <v>926</v>
+      </c>
+      <c r="J47" t="s">
+        <v>916</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>47</v>
       </c>
       <c r="B48" s="1">
         <v>8011</v>
       </c>
-    </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C48" t="s">
+        <v>909</v>
+      </c>
+      <c r="D48">
+        <v>30</v>
+      </c>
+      <c r="E48" t="s">
+        <v>914</v>
+      </c>
+      <c r="F48" t="s">
+        <v>919</v>
+      </c>
+      <c r="G48" t="s">
+        <v>919</v>
+      </c>
+      <c r="H48" t="s">
+        <v>908</v>
+      </c>
+      <c r="I48" t="s">
+        <v>927</v>
+      </c>
+      <c r="J48" t="s">
+        <v>916</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>48</v>
       </c>
       <c r="B49" s="1">
         <v>14578</v>
       </c>
-    </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C49" t="s">
+        <v>909</v>
+      </c>
+      <c r="D49">
+        <v>30</v>
+      </c>
+      <c r="E49" t="s">
+        <v>914</v>
+      </c>
+      <c r="F49" t="s">
+        <v>919</v>
+      </c>
+      <c r="G49" t="s">
+        <v>919</v>
+      </c>
+      <c r="H49" t="s">
+        <v>908</v>
+      </c>
+      <c r="I49" t="s">
+        <v>928</v>
+      </c>
+      <c r="J49" t="s">
+        <v>916</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>49</v>
       </c>
@@ -3828,41 +4694,119 @@
       <c r="D50">
         <v>4</v>
       </c>
+      <c r="E50" t="s">
+        <v>919</v>
+      </c>
       <c r="F50" t="s">
+        <v>919</v>
+      </c>
+      <c r="H50" t="s">
         <v>908</v>
       </c>
-      <c r="G50" t="s">
+      <c r="I50" t="s">
         <v>912</v>
       </c>
-      <c r="H50" t="s">
+      <c r="J50" t="s">
         <v>911</v>
       </c>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>50</v>
       </c>
       <c r="B51" s="1">
         <v>3811</v>
       </c>
-    </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C51" t="s">
+        <v>909</v>
+      </c>
+      <c r="D51">
+        <v>30</v>
+      </c>
+      <c r="E51" t="s">
+        <v>914</v>
+      </c>
+      <c r="F51" t="s">
+        <v>919</v>
+      </c>
+      <c r="G51" t="s">
+        <v>919</v>
+      </c>
+      <c r="H51" t="s">
+        <v>908</v>
+      </c>
+      <c r="I51" t="s">
+        <v>926</v>
+      </c>
+      <c r="J51" t="s">
+        <v>916</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>51</v>
       </c>
       <c r="B52" s="1">
         <v>16595</v>
       </c>
-    </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C52" t="s">
+        <v>909</v>
+      </c>
+      <c r="D52">
+        <v>30</v>
+      </c>
+      <c r="E52" t="s">
+        <v>914</v>
+      </c>
+      <c r="F52" t="s">
+        <v>919</v>
+      </c>
+      <c r="G52" t="s">
+        <v>919</v>
+      </c>
+      <c r="H52" t="s">
+        <v>908</v>
+      </c>
+      <c r="I52" t="s">
+        <v>927</v>
+      </c>
+      <c r="J52" t="s">
+        <v>916</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>52</v>
       </c>
       <c r="B53" s="1">
         <v>19139</v>
       </c>
-    </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C53" t="s">
+        <v>909</v>
+      </c>
+      <c r="D53">
+        <v>30</v>
+      </c>
+      <c r="E53" t="s">
+        <v>914</v>
+      </c>
+      <c r="F53" t="s">
+        <v>919</v>
+      </c>
+      <c r="G53" t="s">
+        <v>919</v>
+      </c>
+      <c r="H53" t="s">
+        <v>908</v>
+      </c>
+      <c r="I53" t="s">
+        <v>928</v>
+      </c>
+      <c r="J53" t="s">
+        <v>916</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>53</v>
       </c>
@@ -3875,41 +4819,119 @@
       <c r="D54">
         <v>4</v>
       </c>
+      <c r="E54" t="s">
+        <v>919</v>
+      </c>
       <c r="F54" t="s">
+        <v>919</v>
+      </c>
+      <c r="H54" t="s">
         <v>908</v>
       </c>
-      <c r="G54" t="s">
+      <c r="I54" t="s">
         <v>912</v>
       </c>
-      <c r="H54" t="s">
+      <c r="J54" t="s">
         <v>911</v>
       </c>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>54</v>
       </c>
       <c r="B55" s="1">
         <v>4255</v>
       </c>
-    </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C55" t="s">
+        <v>909</v>
+      </c>
+      <c r="D55">
+        <v>30</v>
+      </c>
+      <c r="E55" t="s">
+        <v>914</v>
+      </c>
+      <c r="F55" t="s">
+        <v>919</v>
+      </c>
+      <c r="G55" t="s">
+        <v>919</v>
+      </c>
+      <c r="H55" t="s">
+        <v>908</v>
+      </c>
+      <c r="I55" t="s">
+        <v>926</v>
+      </c>
+      <c r="J55" t="s">
+        <v>916</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>55</v>
       </c>
       <c r="B56" s="1">
         <v>21576</v>
       </c>
-    </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C56" t="s">
+        <v>909</v>
+      </c>
+      <c r="D56">
+        <v>30</v>
+      </c>
+      <c r="E56" t="s">
+        <v>914</v>
+      </c>
+      <c r="F56" t="s">
+        <v>919</v>
+      </c>
+      <c r="G56" t="s">
+        <v>919</v>
+      </c>
+      <c r="H56" t="s">
+        <v>908</v>
+      </c>
+      <c r="I56" t="s">
+        <v>927</v>
+      </c>
+      <c r="J56" t="s">
+        <v>916</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>56</v>
       </c>
       <c r="B57" s="1">
         <v>20087</v>
       </c>
-    </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C57" t="s">
+        <v>909</v>
+      </c>
+      <c r="D57">
+        <v>30</v>
+      </c>
+      <c r="E57" t="s">
+        <v>914</v>
+      </c>
+      <c r="F57" t="s">
+        <v>919</v>
+      </c>
+      <c r="G57" t="s">
+        <v>919</v>
+      </c>
+      <c r="H57" t="s">
+        <v>908</v>
+      </c>
+      <c r="I57" t="s">
+        <v>928</v>
+      </c>
+      <c r="J57" t="s">
+        <v>916</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>57</v>
       </c>
@@ -3922,41 +4944,119 @@
       <c r="D58">
         <v>4</v>
       </c>
+      <c r="E58" t="s">
+        <v>919</v>
+      </c>
       <c r="F58" t="s">
+        <v>919</v>
+      </c>
+      <c r="H58" t="s">
         <v>908</v>
       </c>
-      <c r="G58" t="s">
+      <c r="I58" t="s">
         <v>912</v>
       </c>
-      <c r="H58" t="s">
+      <c r="J58" t="s">
         <v>911</v>
       </c>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>58</v>
       </c>
       <c r="B59" s="1">
         <v>3585</v>
       </c>
-    </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C59" t="s">
+        <v>909</v>
+      </c>
+      <c r="D59">
+        <v>30</v>
+      </c>
+      <c r="E59" t="s">
+        <v>914</v>
+      </c>
+      <c r="F59" t="s">
+        <v>919</v>
+      </c>
+      <c r="G59" t="s">
+        <v>919</v>
+      </c>
+      <c r="H59" t="s">
+        <v>908</v>
+      </c>
+      <c r="I59" t="s">
+        <v>926</v>
+      </c>
+      <c r="J59" t="s">
+        <v>916</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>59</v>
       </c>
       <c r="B60" s="1">
         <v>16072</v>
       </c>
-    </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C60" t="s">
+        <v>909</v>
+      </c>
+      <c r="D60">
+        <v>30</v>
+      </c>
+      <c r="E60" t="s">
+        <v>914</v>
+      </c>
+      <c r="F60" t="s">
+        <v>919</v>
+      </c>
+      <c r="G60" t="s">
+        <v>919</v>
+      </c>
+      <c r="H60" t="s">
+        <v>908</v>
+      </c>
+      <c r="I60" t="s">
+        <v>927</v>
+      </c>
+      <c r="J60" t="s">
+        <v>916</v>
+      </c>
+    </row>
+    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>60</v>
       </c>
       <c r="B61" s="1">
         <v>9368</v>
       </c>
-    </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C61" t="s">
+        <v>909</v>
+      </c>
+      <c r="D61">
+        <v>30</v>
+      </c>
+      <c r="E61" t="s">
+        <v>914</v>
+      </c>
+      <c r="F61" t="s">
+        <v>919</v>
+      </c>
+      <c r="G61" t="s">
+        <v>919</v>
+      </c>
+      <c r="H61" t="s">
+        <v>908</v>
+      </c>
+      <c r="I61" t="s">
+        <v>928</v>
+      </c>
+      <c r="J61" t="s">
+        <v>916</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>61</v>
       </c>
@@ -3969,41 +5069,119 @@
       <c r="D62">
         <v>4</v>
       </c>
+      <c r="E62" t="s">
+        <v>919</v>
+      </c>
       <c r="F62" t="s">
+        <v>919</v>
+      </c>
+      <c r="H62" t="s">
         <v>908</v>
       </c>
-      <c r="G62" t="s">
+      <c r="I62" t="s">
         <v>912</v>
       </c>
-      <c r="H62" t="s">
+      <c r="J62" t="s">
         <v>911</v>
       </c>
     </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>62</v>
       </c>
       <c r="B63" s="1">
         <v>4241</v>
       </c>
-    </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C63" t="s">
+        <v>909</v>
+      </c>
+      <c r="D63">
+        <v>30</v>
+      </c>
+      <c r="E63" t="s">
+        <v>914</v>
+      </c>
+      <c r="F63" t="s">
+        <v>919</v>
+      </c>
+      <c r="G63" t="s">
+        <v>919</v>
+      </c>
+      <c r="H63" t="s">
+        <v>908</v>
+      </c>
+      <c r="I63" t="s">
+        <v>926</v>
+      </c>
+      <c r="J63" t="s">
+        <v>916</v>
+      </c>
+    </row>
+    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>63</v>
       </c>
       <c r="B64" s="1">
         <v>14284</v>
       </c>
-    </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C64" t="s">
+        <v>909</v>
+      </c>
+      <c r="D64">
+        <v>30</v>
+      </c>
+      <c r="E64" t="s">
+        <v>914</v>
+      </c>
+      <c r="F64" t="s">
+        <v>919</v>
+      </c>
+      <c r="G64" t="s">
+        <v>919</v>
+      </c>
+      <c r="H64" t="s">
+        <v>908</v>
+      </c>
+      <c r="I64" t="s">
+        <v>927</v>
+      </c>
+      <c r="J64" t="s">
+        <v>916</v>
+      </c>
+    </row>
+    <row r="65" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>64</v>
       </c>
       <c r="B65" s="1">
         <v>16266</v>
       </c>
-    </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C65" t="s">
+        <v>909</v>
+      </c>
+      <c r="D65">
+        <v>30</v>
+      </c>
+      <c r="E65" t="s">
+        <v>914</v>
+      </c>
+      <c r="F65" t="s">
+        <v>919</v>
+      </c>
+      <c r="G65" t="s">
+        <v>919</v>
+      </c>
+      <c r="H65" t="s">
+        <v>908</v>
+      </c>
+      <c r="I65" t="s">
+        <v>928</v>
+      </c>
+      <c r="J65" t="s">
+        <v>916</v>
+      </c>
+    </row>
+    <row r="66" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>65</v>
       </c>
@@ -4016,41 +5194,119 @@
       <c r="D66">
         <v>4</v>
       </c>
+      <c r="E66" t="s">
+        <v>919</v>
+      </c>
       <c r="F66" t="s">
+        <v>919</v>
+      </c>
+      <c r="H66" t="s">
         <v>908</v>
       </c>
-      <c r="G66" t="s">
+      <c r="I66" t="s">
         <v>912</v>
       </c>
-      <c r="H66" t="s">
+      <c r="J66" t="s">
         <v>911</v>
       </c>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>66</v>
       </c>
       <c r="B67" s="1">
         <v>3848</v>
       </c>
-    </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C67" t="s">
+        <v>909</v>
+      </c>
+      <c r="D67">
+        <v>30</v>
+      </c>
+      <c r="E67" t="s">
+        <v>914</v>
+      </c>
+      <c r="F67" t="s">
+        <v>919</v>
+      </c>
+      <c r="G67" t="s">
+        <v>919</v>
+      </c>
+      <c r="H67" t="s">
+        <v>908</v>
+      </c>
+      <c r="I67" t="s">
+        <v>926</v>
+      </c>
+      <c r="J67" t="s">
+        <v>916</v>
+      </c>
+    </row>
+    <row r="68" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>67</v>
       </c>
       <c r="B68" s="1">
         <v>14535</v>
       </c>
-    </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C68" t="s">
+        <v>909</v>
+      </c>
+      <c r="D68">
+        <v>30</v>
+      </c>
+      <c r="E68" t="s">
+        <v>914</v>
+      </c>
+      <c r="F68" t="s">
+        <v>919</v>
+      </c>
+      <c r="G68" t="s">
+        <v>919</v>
+      </c>
+      <c r="H68" t="s">
+        <v>908</v>
+      </c>
+      <c r="I68" t="s">
+        <v>927</v>
+      </c>
+      <c r="J68" t="s">
+        <v>916</v>
+      </c>
+    </row>
+    <row r="69" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>68</v>
       </c>
       <c r="B69" s="1">
         <v>13543</v>
       </c>
-    </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C69" t="s">
+        <v>909</v>
+      </c>
+      <c r="D69">
+        <v>30</v>
+      </c>
+      <c r="E69" t="s">
+        <v>914</v>
+      </c>
+      <c r="F69" t="s">
+        <v>919</v>
+      </c>
+      <c r="G69" t="s">
+        <v>919</v>
+      </c>
+      <c r="H69" t="s">
+        <v>908</v>
+      </c>
+      <c r="I69" t="s">
+        <v>928</v>
+      </c>
+      <c r="J69" t="s">
+        <v>916</v>
+      </c>
+    </row>
+    <row r="70" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>69</v>
       </c>
@@ -4063,41 +5319,119 @@
       <c r="D70">
         <v>4</v>
       </c>
+      <c r="E70" t="s">
+        <v>919</v>
+      </c>
       <c r="F70" t="s">
+        <v>919</v>
+      </c>
+      <c r="H70" t="s">
         <v>908</v>
       </c>
-      <c r="G70" t="s">
+      <c r="I70" t="s">
         <v>912</v>
       </c>
-      <c r="H70" t="s">
+      <c r="J70" t="s">
         <v>911</v>
       </c>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>70</v>
       </c>
       <c r="B71" s="1">
         <v>4113</v>
       </c>
-    </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C71" t="s">
+        <v>909</v>
+      </c>
+      <c r="D71">
+        <v>30</v>
+      </c>
+      <c r="E71" t="s">
+        <v>914</v>
+      </c>
+      <c r="F71" t="s">
+        <v>919</v>
+      </c>
+      <c r="G71" t="s">
+        <v>919</v>
+      </c>
+      <c r="H71" t="s">
+        <v>908</v>
+      </c>
+      <c r="I71" t="s">
+        <v>926</v>
+      </c>
+      <c r="J71" t="s">
+        <v>916</v>
+      </c>
+    </row>
+    <row r="72" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>71</v>
       </c>
       <c r="B72" s="1">
         <v>22095</v>
       </c>
-    </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C72" t="s">
+        <v>909</v>
+      </c>
+      <c r="D72">
+        <v>30</v>
+      </c>
+      <c r="E72" t="s">
+        <v>914</v>
+      </c>
+      <c r="F72" t="s">
+        <v>919</v>
+      </c>
+      <c r="G72" t="s">
+        <v>919</v>
+      </c>
+      <c r="H72" t="s">
+        <v>908</v>
+      </c>
+      <c r="I72" t="s">
+        <v>927</v>
+      </c>
+      <c r="J72" t="s">
+        <v>916</v>
+      </c>
+    </row>
+    <row r="73" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>72</v>
       </c>
       <c r="B73" s="1">
         <v>10361</v>
       </c>
-    </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C73" t="s">
+        <v>909</v>
+      </c>
+      <c r="D73">
+        <v>30</v>
+      </c>
+      <c r="E73" t="s">
+        <v>914</v>
+      </c>
+      <c r="F73" t="s">
+        <v>919</v>
+      </c>
+      <c r="G73" t="s">
+        <v>919</v>
+      </c>
+      <c r="H73" t="s">
+        <v>908</v>
+      </c>
+      <c r="I73" t="s">
+        <v>928</v>
+      </c>
+      <c r="J73" t="s">
+        <v>916</v>
+      </c>
+    </row>
+    <row r="74" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>73</v>
       </c>
@@ -4110,41 +5444,119 @@
       <c r="D74">
         <v>4</v>
       </c>
+      <c r="E74" t="s">
+        <v>919</v>
+      </c>
       <c r="F74" t="s">
+        <v>919</v>
+      </c>
+      <c r="H74" t="s">
         <v>908</v>
       </c>
-      <c r="G74" t="s">
+      <c r="I74" t="s">
         <v>912</v>
       </c>
-      <c r="H74" t="s">
+      <c r="J74" t="s">
         <v>911</v>
       </c>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>74</v>
       </c>
       <c r="B75" s="1">
         <v>5462</v>
       </c>
-    </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C75" t="s">
+        <v>909</v>
+      </c>
+      <c r="D75">
+        <v>30</v>
+      </c>
+      <c r="E75" t="s">
+        <v>914</v>
+      </c>
+      <c r="F75" t="s">
+        <v>919</v>
+      </c>
+      <c r="G75" t="s">
+        <v>919</v>
+      </c>
+      <c r="H75" t="s">
+        <v>908</v>
+      </c>
+      <c r="I75" t="s">
+        <v>926</v>
+      </c>
+      <c r="J75" t="s">
+        <v>916</v>
+      </c>
+    </row>
+    <row r="76" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>75</v>
       </c>
       <c r="B76" s="1">
         <v>16262</v>
       </c>
-    </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C76" t="s">
+        <v>909</v>
+      </c>
+      <c r="D76">
+        <v>30</v>
+      </c>
+      <c r="E76" t="s">
+        <v>914</v>
+      </c>
+      <c r="F76" t="s">
+        <v>919</v>
+      </c>
+      <c r="G76" t="s">
+        <v>919</v>
+      </c>
+      <c r="H76" t="s">
+        <v>908</v>
+      </c>
+      <c r="I76" t="s">
+        <v>927</v>
+      </c>
+      <c r="J76" t="s">
+        <v>916</v>
+      </c>
+    </row>
+    <row r="77" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>76</v>
       </c>
       <c r="B77" s="1">
         <v>22865</v>
       </c>
-    </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C77" t="s">
+        <v>909</v>
+      </c>
+      <c r="D77">
+        <v>30</v>
+      </c>
+      <c r="E77" t="s">
+        <v>914</v>
+      </c>
+      <c r="F77" t="s">
+        <v>919</v>
+      </c>
+      <c r="G77" t="s">
+        <v>919</v>
+      </c>
+      <c r="H77" t="s">
+        <v>908</v>
+      </c>
+      <c r="I77" t="s">
+        <v>928</v>
+      </c>
+      <c r="J77" t="s">
+        <v>916</v>
+      </c>
+    </row>
+    <row r="78" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>77</v>
       </c>
@@ -4157,41 +5569,119 @@
       <c r="D78">
         <v>4</v>
       </c>
+      <c r="E78" t="s">
+        <v>919</v>
+      </c>
       <c r="F78" t="s">
+        <v>919</v>
+      </c>
+      <c r="H78" t="s">
         <v>908</v>
       </c>
-      <c r="G78" t="s">
+      <c r="I78" t="s">
         <v>912</v>
       </c>
-      <c r="H78" t="s">
+      <c r="J78" t="s">
         <v>911</v>
       </c>
     </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>78</v>
       </c>
       <c r="B79" s="1">
         <v>3708</v>
       </c>
-    </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C79" t="s">
+        <v>909</v>
+      </c>
+      <c r="D79">
+        <v>30</v>
+      </c>
+      <c r="E79" t="s">
+        <v>914</v>
+      </c>
+      <c r="F79" t="s">
+        <v>919</v>
+      </c>
+      <c r="G79" t="s">
+        <v>919</v>
+      </c>
+      <c r="H79" t="s">
+        <v>908</v>
+      </c>
+      <c r="I79" t="s">
+        <v>926</v>
+      </c>
+      <c r="J79" t="s">
+        <v>916</v>
+      </c>
+    </row>
+    <row r="80" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>79</v>
       </c>
       <c r="B80" s="1">
         <v>12093</v>
       </c>
-    </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C80" t="s">
+        <v>909</v>
+      </c>
+      <c r="D80">
+        <v>30</v>
+      </c>
+      <c r="E80" t="s">
+        <v>914</v>
+      </c>
+      <c r="F80" t="s">
+        <v>919</v>
+      </c>
+      <c r="G80" t="s">
+        <v>919</v>
+      </c>
+      <c r="H80" t="s">
+        <v>908</v>
+      </c>
+      <c r="I80" t="s">
+        <v>927</v>
+      </c>
+      <c r="J80" t="s">
+        <v>916</v>
+      </c>
+    </row>
+    <row r="81" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>80</v>
       </c>
       <c r="B81" s="1">
         <v>22277</v>
       </c>
-    </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C81" t="s">
+        <v>909</v>
+      </c>
+      <c r="D81">
+        <v>29</v>
+      </c>
+      <c r="E81" t="s">
+        <v>914</v>
+      </c>
+      <c r="F81" t="s">
+        <v>919</v>
+      </c>
+      <c r="G81" t="s">
+        <v>919</v>
+      </c>
+      <c r="H81" t="s">
+        <v>908</v>
+      </c>
+      <c r="I81" t="s">
+        <v>928</v>
+      </c>
+      <c r="J81" t="s">
+        <v>916</v>
+      </c>
+    </row>
+    <row r="82" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>81</v>
       </c>
@@ -4204,41 +5694,119 @@
       <c r="D82">
         <v>4</v>
       </c>
+      <c r="E82" t="s">
+        <v>919</v>
+      </c>
       <c r="F82" t="s">
+        <v>919</v>
+      </c>
+      <c r="H82" t="s">
         <v>908</v>
       </c>
-      <c r="G82" t="s">
+      <c r="I82" t="s">
         <v>912</v>
       </c>
-      <c r="H82" t="s">
+      <c r="J82" t="s">
         <v>911</v>
       </c>
     </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>82</v>
       </c>
       <c r="B83" s="1">
         <v>3975</v>
       </c>
-    </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C83" t="s">
+        <v>909</v>
+      </c>
+      <c r="D83">
+        <v>30</v>
+      </c>
+      <c r="E83" t="s">
+        <v>914</v>
+      </c>
+      <c r="F83" t="s">
+        <v>919</v>
+      </c>
+      <c r="G83" t="s">
+        <v>919</v>
+      </c>
+      <c r="H83" t="s">
+        <v>908</v>
+      </c>
+      <c r="I83" t="s">
+        <v>926</v>
+      </c>
+      <c r="J83" t="s">
+        <v>916</v>
+      </c>
+    </row>
+    <row r="84" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>83</v>
       </c>
       <c r="B84" s="1">
         <v>20506</v>
       </c>
-    </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C84" t="s">
+        <v>909</v>
+      </c>
+      <c r="D84">
+        <v>30</v>
+      </c>
+      <c r="E84" t="s">
+        <v>914</v>
+      </c>
+      <c r="F84" t="s">
+        <v>919</v>
+      </c>
+      <c r="G84" t="s">
+        <v>919</v>
+      </c>
+      <c r="H84" t="s">
+        <v>908</v>
+      </c>
+      <c r="I84" t="s">
+        <v>927</v>
+      </c>
+      <c r="J84" t="s">
+        <v>916</v>
+      </c>
+    </row>
+    <row r="85" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>84</v>
       </c>
       <c r="B85" s="1">
         <v>33413</v>
       </c>
-    </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C85" t="s">
+        <v>909</v>
+      </c>
+      <c r="D85">
+        <v>30</v>
+      </c>
+      <c r="E85" t="s">
+        <v>914</v>
+      </c>
+      <c r="F85" t="s">
+        <v>919</v>
+      </c>
+      <c r="G85" t="s">
+        <v>919</v>
+      </c>
+      <c r="H85" t="s">
+        <v>908</v>
+      </c>
+      <c r="I85" t="s">
+        <v>928</v>
+      </c>
+      <c r="J85" t="s">
+        <v>916</v>
+      </c>
+    </row>
+    <row r="86" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>85</v>
       </c>
@@ -4251,41 +5819,119 @@
       <c r="D86">
         <v>4</v>
       </c>
+      <c r="E86" t="s">
+        <v>919</v>
+      </c>
       <c r="F86" t="s">
+        <v>919</v>
+      </c>
+      <c r="H86" t="s">
         <v>908</v>
       </c>
-      <c r="G86" t="s">
+      <c r="I86" t="s">
         <v>912</v>
       </c>
-      <c r="H86" t="s">
+      <c r="J86" t="s">
         <v>911</v>
       </c>
     </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>86</v>
       </c>
       <c r="B87" s="1">
         <v>6827</v>
       </c>
-    </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C87" t="s">
+        <v>909</v>
+      </c>
+      <c r="D87">
+        <v>30</v>
+      </c>
+      <c r="E87" t="s">
+        <v>914</v>
+      </c>
+      <c r="F87" t="s">
+        <v>919</v>
+      </c>
+      <c r="G87" t="s">
+        <v>919</v>
+      </c>
+      <c r="H87" t="s">
+        <v>908</v>
+      </c>
+      <c r="I87" t="s">
+        <v>926</v>
+      </c>
+      <c r="J87" t="s">
+        <v>916</v>
+      </c>
+    </row>
+    <row r="88" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>87</v>
       </c>
       <c r="B88" s="1">
         <v>15644</v>
       </c>
-    </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C88" t="s">
+        <v>909</v>
+      </c>
+      <c r="D88">
+        <v>30</v>
+      </c>
+      <c r="E88" t="s">
+        <v>914</v>
+      </c>
+      <c r="F88" t="s">
+        <v>919</v>
+      </c>
+      <c r="G88" t="s">
+        <v>919</v>
+      </c>
+      <c r="H88" t="s">
+        <v>908</v>
+      </c>
+      <c r="I88" t="s">
+        <v>927</v>
+      </c>
+      <c r="J88" t="s">
+        <v>916</v>
+      </c>
+    </row>
+    <row r="89" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>88</v>
       </c>
       <c r="B89" s="1">
         <v>10144</v>
       </c>
-    </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C89" t="s">
+        <v>909</v>
+      </c>
+      <c r="D89">
+        <v>30</v>
+      </c>
+      <c r="E89" t="s">
+        <v>914</v>
+      </c>
+      <c r="F89" t="s">
+        <v>919</v>
+      </c>
+      <c r="G89" t="s">
+        <v>919</v>
+      </c>
+      <c r="H89" t="s">
+        <v>908</v>
+      </c>
+      <c r="I89" t="s">
+        <v>928</v>
+      </c>
+      <c r="J89" t="s">
+        <v>916</v>
+      </c>
+    </row>
+    <row r="90" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>89</v>
       </c>
@@ -4298,41 +5944,119 @@
       <c r="D90">
         <v>4</v>
       </c>
+      <c r="E90" t="s">
+        <v>919</v>
+      </c>
       <c r="F90" t="s">
+        <v>919</v>
+      </c>
+      <c r="H90" t="s">
         <v>908</v>
       </c>
-      <c r="G90" t="s">
+      <c r="I90" t="s">
         <v>912</v>
       </c>
-      <c r="H90" t="s">
+      <c r="J90" t="s">
         <v>911</v>
       </c>
     </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>90</v>
       </c>
       <c r="B91" s="1">
         <v>3942</v>
       </c>
-    </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C91" t="s">
+        <v>909</v>
+      </c>
+      <c r="D91">
+        <v>30</v>
+      </c>
+      <c r="E91" t="s">
+        <v>914</v>
+      </c>
+      <c r="F91" t="s">
+        <v>919</v>
+      </c>
+      <c r="G91" t="s">
+        <v>919</v>
+      </c>
+      <c r="H91" t="s">
+        <v>908</v>
+      </c>
+      <c r="I91" t="s">
+        <v>926</v>
+      </c>
+      <c r="J91" t="s">
+        <v>916</v>
+      </c>
+    </row>
+    <row r="92" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>91</v>
       </c>
       <c r="B92" s="1">
         <v>25907</v>
       </c>
-    </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C92" t="s">
+        <v>909</v>
+      </c>
+      <c r="D92">
+        <v>30</v>
+      </c>
+      <c r="E92" t="s">
+        <v>914</v>
+      </c>
+      <c r="F92" t="s">
+        <v>919</v>
+      </c>
+      <c r="G92" t="s">
+        <v>919</v>
+      </c>
+      <c r="H92" t="s">
+        <v>908</v>
+      </c>
+      <c r="I92" t="s">
+        <v>927</v>
+      </c>
+      <c r="J92" t="s">
+        <v>916</v>
+      </c>
+    </row>
+    <row r="93" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>92</v>
       </c>
       <c r="B93" s="1">
         <v>17779</v>
       </c>
-    </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C93" t="s">
+        <v>909</v>
+      </c>
+      <c r="D93">
+        <v>30</v>
+      </c>
+      <c r="E93" t="s">
+        <v>914</v>
+      </c>
+      <c r="F93" t="s">
+        <v>919</v>
+      </c>
+      <c r="G93" t="s">
+        <v>919</v>
+      </c>
+      <c r="H93" t="s">
+        <v>908</v>
+      </c>
+      <c r="I93" t="s">
+        <v>928</v>
+      </c>
+      <c r="J93" t="s">
+        <v>916</v>
+      </c>
+    </row>
+    <row r="94" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>93</v>
       </c>
@@ -4345,41 +6069,119 @@
       <c r="D94">
         <v>4</v>
       </c>
+      <c r="E94" t="s">
+        <v>919</v>
+      </c>
       <c r="F94" t="s">
+        <v>919</v>
+      </c>
+      <c r="H94" t="s">
         <v>908</v>
       </c>
-      <c r="G94" t="s">
+      <c r="I94" t="s">
         <v>912</v>
       </c>
-      <c r="H94" t="s">
+      <c r="J94" t="s">
         <v>911</v>
       </c>
     </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>94</v>
       </c>
       <c r="B95" s="1">
         <v>4141</v>
       </c>
-    </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C95" t="s">
+        <v>909</v>
+      </c>
+      <c r="D95">
+        <v>30</v>
+      </c>
+      <c r="E95" t="s">
+        <v>914</v>
+      </c>
+      <c r="F95" t="s">
+        <v>919</v>
+      </c>
+      <c r="G95" t="s">
+        <v>919</v>
+      </c>
+      <c r="H95" t="s">
+        <v>908</v>
+      </c>
+      <c r="I95" t="s">
+        <v>926</v>
+      </c>
+      <c r="J95" t="s">
+        <v>916</v>
+      </c>
+    </row>
+    <row r="96" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>95</v>
       </c>
       <c r="B96" s="1">
         <v>7629</v>
       </c>
-    </row>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C96" t="s">
+        <v>909</v>
+      </c>
+      <c r="D96">
+        <v>30</v>
+      </c>
+      <c r="E96" t="s">
+        <v>914</v>
+      </c>
+      <c r="F96" t="s">
+        <v>919</v>
+      </c>
+      <c r="G96" t="s">
+        <v>919</v>
+      </c>
+      <c r="H96" t="s">
+        <v>908</v>
+      </c>
+      <c r="I96" t="s">
+        <v>927</v>
+      </c>
+      <c r="J96" t="s">
+        <v>916</v>
+      </c>
+    </row>
+    <row r="97" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>96</v>
       </c>
       <c r="B97" s="1">
         <v>10819</v>
       </c>
-    </row>
-    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C97" t="s">
+        <v>909</v>
+      </c>
+      <c r="D97">
+        <v>30</v>
+      </c>
+      <c r="E97" t="s">
+        <v>914</v>
+      </c>
+      <c r="F97" t="s">
+        <v>919</v>
+      </c>
+      <c r="G97" t="s">
+        <v>919</v>
+      </c>
+      <c r="H97" t="s">
+        <v>908</v>
+      </c>
+      <c r="I97" t="s">
+        <v>928</v>
+      </c>
+      <c r="J97" t="s">
+        <v>916</v>
+      </c>
+    </row>
+    <row r="98" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>97</v>
       </c>
@@ -4392,41 +6194,119 @@
       <c r="D98">
         <v>4</v>
       </c>
+      <c r="E98" t="s">
+        <v>919</v>
+      </c>
       <c r="F98" t="s">
+        <v>919</v>
+      </c>
+      <c r="H98" t="s">
         <v>908</v>
       </c>
-      <c r="G98" t="s">
+      <c r="I98" t="s">
         <v>912</v>
       </c>
-      <c r="H98" t="s">
+      <c r="J98" t="s">
         <v>911</v>
       </c>
     </row>
-    <row r="99" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>98</v>
       </c>
       <c r="B99" s="1">
         <v>3552</v>
       </c>
-    </row>
-    <row r="100" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C99" t="s">
+        <v>909</v>
+      </c>
+      <c r="D99">
+        <v>30</v>
+      </c>
+      <c r="E99" t="s">
+        <v>914</v>
+      </c>
+      <c r="F99" t="s">
+        <v>919</v>
+      </c>
+      <c r="G99" t="s">
+        <v>919</v>
+      </c>
+      <c r="H99" t="s">
+        <v>908</v>
+      </c>
+      <c r="I99" t="s">
+        <v>926</v>
+      </c>
+      <c r="J99" t="s">
+        <v>916</v>
+      </c>
+    </row>
+    <row r="100" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>99</v>
       </c>
       <c r="B100" s="1">
         <v>14723</v>
       </c>
-    </row>
-    <row r="101" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C100" t="s">
+        <v>909</v>
+      </c>
+      <c r="D100">
+        <v>30</v>
+      </c>
+      <c r="E100" t="s">
+        <v>914</v>
+      </c>
+      <c r="F100" t="s">
+        <v>919</v>
+      </c>
+      <c r="G100" t="s">
+        <v>919</v>
+      </c>
+      <c r="H100" t="s">
+        <v>908</v>
+      </c>
+      <c r="I100" t="s">
+        <v>927</v>
+      </c>
+      <c r="J100" t="s">
+        <v>916</v>
+      </c>
+    </row>
+    <row r="101" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>100</v>
       </c>
       <c r="B101" s="1">
         <v>9891</v>
       </c>
-    </row>
-    <row r="102" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C101" t="s">
+        <v>909</v>
+      </c>
+      <c r="D101">
+        <v>30</v>
+      </c>
+      <c r="E101" t="s">
+        <v>914</v>
+      </c>
+      <c r="F101" t="s">
+        <v>919</v>
+      </c>
+      <c r="G101" t="s">
+        <v>919</v>
+      </c>
+      <c r="H101" t="s">
+        <v>908</v>
+      </c>
+      <c r="I101" t="s">
+        <v>928</v>
+      </c>
+      <c r="J101" t="s">
+        <v>916</v>
+      </c>
+    </row>
+    <row r="102" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>101</v>
       </c>
@@ -4439,41 +6319,119 @@
       <c r="D102">
         <v>4</v>
       </c>
+      <c r="E102" t="s">
+        <v>919</v>
+      </c>
       <c r="F102" t="s">
+        <v>919</v>
+      </c>
+      <c r="H102" t="s">
         <v>908</v>
       </c>
-      <c r="G102" t="s">
+      <c r="I102" t="s">
         <v>912</v>
       </c>
-      <c r="H102" t="s">
+      <c r="J102" t="s">
         <v>911</v>
       </c>
     </row>
-    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>102</v>
       </c>
       <c r="B103" s="1">
         <v>12582</v>
       </c>
-    </row>
-    <row r="104" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C103" t="s">
+        <v>909</v>
+      </c>
+      <c r="D103">
+        <v>30</v>
+      </c>
+      <c r="E103" t="s">
+        <v>914</v>
+      </c>
+      <c r="F103" t="s">
+        <v>919</v>
+      </c>
+      <c r="G103" t="s">
+        <v>919</v>
+      </c>
+      <c r="H103" t="s">
+        <v>908</v>
+      </c>
+      <c r="I103" t="s">
+        <v>926</v>
+      </c>
+      <c r="J103" t="s">
+        <v>916</v>
+      </c>
+    </row>
+    <row r="104" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>103</v>
       </c>
       <c r="B104" s="1">
         <v>15891</v>
       </c>
-    </row>
-    <row r="105" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C104" t="s">
+        <v>909</v>
+      </c>
+      <c r="D104">
+        <v>30</v>
+      </c>
+      <c r="E104" t="s">
+        <v>914</v>
+      </c>
+      <c r="F104" t="s">
+        <v>919</v>
+      </c>
+      <c r="G104" t="s">
+        <v>919</v>
+      </c>
+      <c r="H104" t="s">
+        <v>908</v>
+      </c>
+      <c r="I104" t="s">
+        <v>927</v>
+      </c>
+      <c r="J104" t="s">
+        <v>916</v>
+      </c>
+    </row>
+    <row r="105" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>104</v>
       </c>
       <c r="B105" s="1">
         <v>17579</v>
       </c>
-    </row>
-    <row r="106" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C105" t="s">
+        <v>909</v>
+      </c>
+      <c r="D105">
+        <v>30</v>
+      </c>
+      <c r="E105" t="s">
+        <v>914</v>
+      </c>
+      <c r="F105" t="s">
+        <v>919</v>
+      </c>
+      <c r="G105" t="s">
+        <v>919</v>
+      </c>
+      <c r="H105" t="s">
+        <v>908</v>
+      </c>
+      <c r="I105" t="s">
+        <v>928</v>
+      </c>
+      <c r="J105" t="s">
+        <v>916</v>
+      </c>
+    </row>
+    <row r="106" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>105</v>
       </c>
@@ -4486,41 +6444,119 @@
       <c r="D106">
         <v>4</v>
       </c>
+      <c r="E106" t="s">
+        <v>919</v>
+      </c>
       <c r="F106" t="s">
+        <v>919</v>
+      </c>
+      <c r="H106" t="s">
         <v>908</v>
       </c>
-      <c r="G106" t="s">
+      <c r="I106" t="s">
         <v>912</v>
       </c>
-      <c r="H106" t="s">
+      <c r="J106" t="s">
         <v>911</v>
       </c>
     </row>
-    <row r="107" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>106</v>
       </c>
       <c r="B107" s="1">
         <v>3307</v>
       </c>
-    </row>
-    <row r="108" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C107" t="s">
+        <v>909</v>
+      </c>
+      <c r="D107">
+        <v>30</v>
+      </c>
+      <c r="E107" t="s">
+        <v>914</v>
+      </c>
+      <c r="F107" t="s">
+        <v>919</v>
+      </c>
+      <c r="G107" t="s">
+        <v>919</v>
+      </c>
+      <c r="H107" t="s">
+        <v>908</v>
+      </c>
+      <c r="I107" t="s">
+        <v>926</v>
+      </c>
+      <c r="J107" t="s">
+        <v>916</v>
+      </c>
+    </row>
+    <row r="108" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>107</v>
       </c>
       <c r="B108" s="1">
         <v>26686</v>
       </c>
-    </row>
-    <row r="109" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C108" t="s">
+        <v>909</v>
+      </c>
+      <c r="D108">
+        <v>30</v>
+      </c>
+      <c r="E108" t="s">
+        <v>914</v>
+      </c>
+      <c r="F108" t="s">
+        <v>919</v>
+      </c>
+      <c r="G108" t="s">
+        <v>919</v>
+      </c>
+      <c r="H108" t="s">
+        <v>908</v>
+      </c>
+      <c r="I108" t="s">
+        <v>927</v>
+      </c>
+      <c r="J108" t="s">
+        <v>916</v>
+      </c>
+    </row>
+    <row r="109" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>108</v>
       </c>
       <c r="B109" s="1">
         <v>14228</v>
       </c>
-    </row>
-    <row r="110" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C109" t="s">
+        <v>909</v>
+      </c>
+      <c r="D109">
+        <v>30</v>
+      </c>
+      <c r="E109" t="s">
+        <v>914</v>
+      </c>
+      <c r="F109" t="s">
+        <v>919</v>
+      </c>
+      <c r="G109" t="s">
+        <v>919</v>
+      </c>
+      <c r="H109" t="s">
+        <v>908</v>
+      </c>
+      <c r="I109" t="s">
+        <v>928</v>
+      </c>
+      <c r="J109" t="s">
+        <v>916</v>
+      </c>
+    </row>
+    <row r="110" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>109</v>
       </c>
@@ -4533,41 +6569,122 @@
       <c r="D110">
         <v>4</v>
       </c>
+      <c r="E110" t="s">
+        <v>919</v>
+      </c>
       <c r="F110" t="s">
+        <v>919</v>
+      </c>
+      <c r="G110" t="s">
+        <v>919</v>
+      </c>
+      <c r="H110" t="s">
         <v>908</v>
       </c>
-      <c r="G110" t="s">
+      <c r="I110" t="s">
         <v>912</v>
       </c>
-      <c r="H110" t="s">
+      <c r="J110" t="s">
         <v>911</v>
       </c>
     </row>
-    <row r="111" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>110</v>
       </c>
       <c r="B111" s="1">
         <v>3359</v>
       </c>
-    </row>
-    <row r="112" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C111" t="s">
+        <v>909</v>
+      </c>
+      <c r="D111">
+        <v>30</v>
+      </c>
+      <c r="E111" t="s">
+        <v>914</v>
+      </c>
+      <c r="F111" t="s">
+        <v>919</v>
+      </c>
+      <c r="G111" t="s">
+        <v>919</v>
+      </c>
+      <c r="H111" t="s">
+        <v>908</v>
+      </c>
+      <c r="I111" t="s">
+        <v>926</v>
+      </c>
+      <c r="J111" t="s">
+        <v>916</v>
+      </c>
+    </row>
+    <row r="112" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>111</v>
       </c>
       <c r="B112" s="1">
         <v>18248</v>
       </c>
-    </row>
-    <row r="113" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C112" t="s">
+        <v>909</v>
+      </c>
+      <c r="D112">
+        <v>30</v>
+      </c>
+      <c r="E112" t="s">
+        <v>914</v>
+      </c>
+      <c r="F112" t="s">
+        <v>919</v>
+      </c>
+      <c r="G112" t="s">
+        <v>919</v>
+      </c>
+      <c r="H112" t="s">
+        <v>908</v>
+      </c>
+      <c r="I112" t="s">
+        <v>927</v>
+      </c>
+      <c r="J112" t="s">
+        <v>916</v>
+      </c>
+    </row>
+    <row r="113" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>112</v>
       </c>
       <c r="B113" s="1">
         <v>13247</v>
       </c>
-    </row>
-    <row r="114" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C113" t="s">
+        <v>909</v>
+      </c>
+      <c r="D113">
+        <v>30</v>
+      </c>
+      <c r="E113" t="s">
+        <v>914</v>
+      </c>
+      <c r="F113" t="s">
+        <v>919</v>
+      </c>
+      <c r="G113" t="s">
+        <v>919</v>
+      </c>
+      <c r="H113" t="s">
+        <v>908</v>
+      </c>
+      <c r="I113" t="s">
+        <v>928</v>
+      </c>
+      <c r="J113" t="s">
+        <v>916</v>
+      </c>
+    </row>
+    <row r="114" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>113</v>
       </c>
@@ -4580,41 +6697,119 @@
       <c r="D114">
         <v>4</v>
       </c>
+      <c r="E114" t="s">
+        <v>919</v>
+      </c>
       <c r="F114" t="s">
+        <v>919</v>
+      </c>
+      <c r="H114" t="s">
         <v>908</v>
       </c>
-      <c r="G114" t="s">
+      <c r="I114" t="s">
         <v>912</v>
       </c>
-      <c r="H114" t="s">
+      <c r="J114" t="s">
         <v>911</v>
       </c>
     </row>
-    <row r="115" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>114</v>
       </c>
       <c r="B115" s="1">
         <v>3928</v>
       </c>
-    </row>
-    <row r="116" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C115" t="s">
+        <v>909</v>
+      </c>
+      <c r="D115">
+        <v>30</v>
+      </c>
+      <c r="E115" t="s">
+        <v>914</v>
+      </c>
+      <c r="F115" t="s">
+        <v>919</v>
+      </c>
+      <c r="G115" t="s">
+        <v>919</v>
+      </c>
+      <c r="H115" t="s">
+        <v>908</v>
+      </c>
+      <c r="I115" t="s">
+        <v>926</v>
+      </c>
+      <c r="J115" t="s">
+        <v>916</v>
+      </c>
+    </row>
+    <row r="116" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>115</v>
       </c>
       <c r="B116" s="1">
         <v>13748</v>
       </c>
-    </row>
-    <row r="117" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C116" t="s">
+        <v>909</v>
+      </c>
+      <c r="D116">
+        <v>30</v>
+      </c>
+      <c r="E116" t="s">
+        <v>914</v>
+      </c>
+      <c r="F116" t="s">
+        <v>919</v>
+      </c>
+      <c r="G116" t="s">
+        <v>919</v>
+      </c>
+      <c r="H116" t="s">
+        <v>908</v>
+      </c>
+      <c r="I116" t="s">
+        <v>927</v>
+      </c>
+      <c r="J116" t="s">
+        <v>916</v>
+      </c>
+    </row>
+    <row r="117" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>116</v>
       </c>
       <c r="B117" s="1">
         <v>14399</v>
       </c>
-    </row>
-    <row r="118" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C117" t="s">
+        <v>909</v>
+      </c>
+      <c r="D117">
+        <v>30</v>
+      </c>
+      <c r="E117" t="s">
+        <v>914</v>
+      </c>
+      <c r="F117" t="s">
+        <v>919</v>
+      </c>
+      <c r="G117" t="s">
+        <v>919</v>
+      </c>
+      <c r="H117" t="s">
+        <v>908</v>
+      </c>
+      <c r="I117" t="s">
+        <v>928</v>
+      </c>
+      <c r="J117" t="s">
+        <v>916</v>
+      </c>
+    </row>
+    <row r="118" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>117</v>
       </c>
@@ -4627,41 +6822,119 @@
       <c r="D118">
         <v>4</v>
       </c>
+      <c r="E118" t="s">
+        <v>919</v>
+      </c>
       <c r="F118" t="s">
+        <v>919</v>
+      </c>
+      <c r="H118" t="s">
         <v>908</v>
       </c>
-      <c r="G118" t="s">
+      <c r="I118" t="s">
         <v>912</v>
       </c>
-      <c r="H118" t="s">
+      <c r="J118" t="s">
         <v>911</v>
       </c>
     </row>
-    <row r="119" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>118</v>
       </c>
       <c r="B119" s="1">
         <v>4177</v>
       </c>
-    </row>
-    <row r="120" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C119" t="s">
+        <v>909</v>
+      </c>
+      <c r="D119">
+        <v>30</v>
+      </c>
+      <c r="E119" t="s">
+        <v>914</v>
+      </c>
+      <c r="F119" t="s">
+        <v>919</v>
+      </c>
+      <c r="G119" t="s">
+        <v>919</v>
+      </c>
+      <c r="H119" t="s">
+        <v>908</v>
+      </c>
+      <c r="I119" t="s">
+        <v>926</v>
+      </c>
+      <c r="J119" t="s">
+        <v>916</v>
+      </c>
+    </row>
+    <row r="120" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>119</v>
       </c>
       <c r="B120" s="1">
         <v>17458</v>
       </c>
-    </row>
-    <row r="121" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C120" t="s">
+        <v>909</v>
+      </c>
+      <c r="D120">
+        <v>30</v>
+      </c>
+      <c r="E120" t="s">
+        <v>914</v>
+      </c>
+      <c r="F120" t="s">
+        <v>919</v>
+      </c>
+      <c r="G120" t="s">
+        <v>919</v>
+      </c>
+      <c r="H120" t="s">
+        <v>908</v>
+      </c>
+      <c r="I120" t="s">
+        <v>927</v>
+      </c>
+      <c r="J120" t="s">
+        <v>916</v>
+      </c>
+    </row>
+    <row r="121" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>120</v>
       </c>
       <c r="B121" s="1">
         <v>22349</v>
       </c>
-    </row>
-    <row r="122" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C121" t="s">
+        <v>909</v>
+      </c>
+      <c r="D121">
+        <v>30</v>
+      </c>
+      <c r="E121" t="s">
+        <v>914</v>
+      </c>
+      <c r="F121" t="s">
+        <v>919</v>
+      </c>
+      <c r="G121" t="s">
+        <v>919</v>
+      </c>
+      <c r="H121" t="s">
+        <v>908</v>
+      </c>
+      <c r="I121" t="s">
+        <v>928</v>
+      </c>
+      <c r="J121" t="s">
+        <v>916</v>
+      </c>
+    </row>
+    <row r="122" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>121</v>
       </c>
@@ -4674,41 +6947,119 @@
       <c r="D122">
         <v>4</v>
       </c>
+      <c r="E122" t="s">
+        <v>919</v>
+      </c>
       <c r="F122" t="s">
+        <v>919</v>
+      </c>
+      <c r="H122" t="s">
         <v>908</v>
       </c>
-      <c r="G122" t="s">
+      <c r="I122" t="s">
         <v>912</v>
       </c>
-      <c r="H122" t="s">
+      <c r="J122" t="s">
         <v>911</v>
       </c>
     </row>
-    <row r="123" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>122</v>
       </c>
       <c r="B123" s="1">
         <v>3728</v>
       </c>
-    </row>
-    <row r="124" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C123" t="s">
+        <v>909</v>
+      </c>
+      <c r="D123">
+        <v>30</v>
+      </c>
+      <c r="E123" t="s">
+        <v>914</v>
+      </c>
+      <c r="F123" t="s">
+        <v>919</v>
+      </c>
+      <c r="G123" t="s">
+        <v>919</v>
+      </c>
+      <c r="H123" t="s">
+        <v>908</v>
+      </c>
+      <c r="I123" t="s">
+        <v>926</v>
+      </c>
+      <c r="J123" t="s">
+        <v>916</v>
+      </c>
+    </row>
+    <row r="124" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>123</v>
       </c>
       <c r="B124" s="1">
         <v>20617</v>
       </c>
-    </row>
-    <row r="125" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C124" t="s">
+        <v>909</v>
+      </c>
+      <c r="D124">
+        <v>30</v>
+      </c>
+      <c r="E124" t="s">
+        <v>914</v>
+      </c>
+      <c r="F124" t="s">
+        <v>919</v>
+      </c>
+      <c r="G124" t="s">
+        <v>919</v>
+      </c>
+      <c r="H124" t="s">
+        <v>908</v>
+      </c>
+      <c r="I124" t="s">
+        <v>927</v>
+      </c>
+      <c r="J124" t="s">
+        <v>916</v>
+      </c>
+    </row>
+    <row r="125" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>124</v>
       </c>
       <c r="B125" s="1">
         <v>14916</v>
       </c>
-    </row>
-    <row r="126" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C125" t="s">
+        <v>909</v>
+      </c>
+      <c r="D125">
+        <v>30</v>
+      </c>
+      <c r="E125" t="s">
+        <v>914</v>
+      </c>
+      <c r="F125" t="s">
+        <v>919</v>
+      </c>
+      <c r="G125" t="s">
+        <v>919</v>
+      </c>
+      <c r="H125" t="s">
+        <v>908</v>
+      </c>
+      <c r="I125" t="s">
+        <v>928</v>
+      </c>
+      <c r="J125" t="s">
+        <v>916</v>
+      </c>
+    </row>
+    <row r="126" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>125</v>
       </c>
@@ -4721,41 +7072,119 @@
       <c r="D126">
         <v>4</v>
       </c>
+      <c r="E126" t="s">
+        <v>919</v>
+      </c>
       <c r="F126" t="s">
+        <v>919</v>
+      </c>
+      <c r="H126" t="s">
         <v>908</v>
       </c>
-      <c r="G126" t="s">
+      <c r="I126" t="s">
         <v>912</v>
       </c>
-      <c r="H126" t="s">
+      <c r="J126" t="s">
         <v>911</v>
       </c>
     </row>
-    <row r="127" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>126</v>
       </c>
       <c r="B127" s="1">
         <v>5462</v>
       </c>
-    </row>
-    <row r="128" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C127" t="s">
+        <v>909</v>
+      </c>
+      <c r="D127">
+        <v>30</v>
+      </c>
+      <c r="E127" t="s">
+        <v>914</v>
+      </c>
+      <c r="F127" t="s">
+        <v>919</v>
+      </c>
+      <c r="G127" t="s">
+        <v>919</v>
+      </c>
+      <c r="H127" t="s">
+        <v>908</v>
+      </c>
+      <c r="I127" t="s">
+        <v>926</v>
+      </c>
+      <c r="J127" t="s">
+        <v>916</v>
+      </c>
+    </row>
+    <row r="128" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>127</v>
       </c>
       <c r="B128" s="1">
         <v>16262</v>
       </c>
-    </row>
-    <row r="129" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C128" t="s">
+        <v>909</v>
+      </c>
+      <c r="D128">
+        <v>30</v>
+      </c>
+      <c r="E128" t="s">
+        <v>914</v>
+      </c>
+      <c r="F128" t="s">
+        <v>919</v>
+      </c>
+      <c r="G128" t="s">
+        <v>919</v>
+      </c>
+      <c r="H128" t="s">
+        <v>908</v>
+      </c>
+      <c r="I128" t="s">
+        <v>927</v>
+      </c>
+      <c r="J128" t="s">
+        <v>916</v>
+      </c>
+    </row>
+    <row r="129" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>128</v>
       </c>
       <c r="B129" s="1">
         <v>22865</v>
       </c>
-    </row>
-    <row r="130" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C129" t="s">
+        <v>909</v>
+      </c>
+      <c r="D129">
+        <v>30</v>
+      </c>
+      <c r="E129" t="s">
+        <v>914</v>
+      </c>
+      <c r="F129" t="s">
+        <v>919</v>
+      </c>
+      <c r="G129" t="s">
+        <v>919</v>
+      </c>
+      <c r="H129" t="s">
+        <v>908</v>
+      </c>
+      <c r="I129" t="s">
+        <v>928</v>
+      </c>
+      <c r="J129" t="s">
+        <v>916</v>
+      </c>
+    </row>
+    <row r="130" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>129</v>
       </c>
@@ -4768,17 +7197,23 @@
       <c r="D130">
         <v>4</v>
       </c>
+      <c r="E130" t="s">
+        <v>919</v>
+      </c>
       <c r="F130" t="s">
+        <v>919</v>
+      </c>
+      <c r="H130" t="s">
         <v>908</v>
       </c>
-      <c r="G130" t="s">
+      <c r="I130" t="s">
         <v>912</v>
       </c>
-      <c r="H130" t="s">
+      <c r="J130" t="s">
         <v>911</v>
       </c>
     </row>
-    <row r="131" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>757</v>
       </c>
@@ -4786,7 +7221,7 @@
         <v>19481</v>
       </c>
     </row>
-    <row r="132" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>758</v>
       </c>
@@ -4794,7 +7229,7 @@
         <v>25838</v>
       </c>
     </row>
-    <row r="133" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>759</v>
       </c>
@@ -4802,7 +7237,7 @@
         <v>15438</v>
       </c>
     </row>
-    <row r="134" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>760</v>
       </c>
@@ -4810,7 +7245,7 @@
         <v>1434824</v>
       </c>
     </row>
-    <row r="135" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>761</v>
       </c>
@@ -4818,7 +7253,7 @@
         <v>2086653</v>
       </c>
     </row>
-    <row r="136" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>762</v>
       </c>
@@ -4826,7 +7261,7 @@
         <v>1007413</v>
       </c>
     </row>
-    <row r="137" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>763</v>
       </c>
@@ -4834,7 +7269,7 @@
         <v>50601</v>
       </c>
     </row>
-    <row r="138" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>764</v>
       </c>
@@ -4842,7 +7277,7 @@
         <v>164306</v>
       </c>
     </row>
-    <row r="139" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>765</v>
       </c>
@@ -4850,7 +7285,7 @@
         <v>663860</v>
       </c>
     </row>
-    <row r="140" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>766</v>
       </c>
@@ -4858,7 +7293,7 @@
         <v>739003</v>
       </c>
     </row>
-    <row r="141" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>767</v>
       </c>
@@ -4866,7 +7301,7 @@
         <v>665272</v>
       </c>
     </row>
-    <row r="142" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>768</v>
       </c>
@@ -4874,7 +7309,7 @@
         <v>635163</v>
       </c>
     </row>
-    <row r="143" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>769</v>
       </c>
@@ -4882,7 +7317,7 @@
         <v>760300</v>
       </c>
     </row>
-    <row r="144" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>770</v>
       </c>
@@ -10906,7 +13341,7 @@
         <v>757884</v>
       </c>
     </row>
-    <row r="897" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="897" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A897" t="s">
         <v>904</v>
       </c>
@@ -10919,14 +13354,14 @@
       <c r="D897">
         <v>1</v>
       </c>
-      <c r="F897" t="s">
+      <c r="H897" t="s">
         <v>906</v>
       </c>
-      <c r="G897" t="s">
+      <c r="I897" t="s">
         <v>907</v>
       </c>
     </row>
-    <row r="898" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="898" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A898" t="s">
         <v>901</v>
       </c>
@@ -10934,7 +13369,7 @@
         <v>2851</v>
       </c>
     </row>
-    <row r="899" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="899" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A899" t="s">
         <v>902</v>
       </c>
@@ -10942,7 +13377,7 @@
         <v>186389</v>
       </c>
     </row>
-    <row r="900" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="900" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A900" t="s">
         <v>903</v>
       </c>

--- a/images/image manifest.xlsx
+++ b/images/image manifest.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\Github\CS-Graphics\images\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2911D216-6E45-4439-87FA-BD143F5C5F09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5B09CAA-8A69-4A9F-B34C-666860D8A036}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6570" yWindow="810" windowWidth="21600" windowHeight="11295" xr2:uid="{620D0F7A-D0D3-4EA0-8A4D-C0BB25CE06A6}"/>
+    <workbookView xWindow="4905" yWindow="2730" windowWidth="15930" windowHeight="8145" xr2:uid="{620D0F7A-D0D3-4EA0-8A4D-C0BB25CE06A6}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1759" uniqueCount="929">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2290" uniqueCount="981">
   <si>
     <t>Filename</t>
   </si>
@@ -2824,6 +2824,162 @@
   </si>
   <si>
     <t>TODO(Name) danger idle</t>
+  </si>
+  <si>
+    <t>UI</t>
+  </si>
+  <si>
+    <t>Red Hex background</t>
+  </si>
+  <si>
+    <t>Layer behind game hex tiles</t>
+  </si>
+  <si>
+    <t>Green Hex background</t>
+  </si>
+  <si>
+    <t>Battle FX</t>
+  </si>
+  <si>
+    <t>Mushroom cloud explosion</t>
+  </si>
+  <si>
+    <t>Explosion</t>
+  </si>
+  <si>
+    <t>Nova Explosion</t>
+  </si>
+  <si>
+    <t>Orb</t>
+  </si>
+  <si>
+    <t>Fire</t>
+  </si>
+  <si>
+    <t>Shields</t>
+  </si>
+  <si>
+    <t>Blue Plasma Ball</t>
+  </si>
+  <si>
+    <t>Red Plasma Ball</t>
+  </si>
+  <si>
+    <t>Flair</t>
+  </si>
+  <si>
+    <t>Directional Projectile</t>
+  </si>
+  <si>
+    <t>Long Directional Projectile</t>
+  </si>
+  <si>
+    <t>Wide Directional Projectile</t>
+  </si>
+  <si>
+    <t>Short Directional Projectile</t>
+  </si>
+  <si>
+    <t>Missile Projectile</t>
+  </si>
+  <si>
+    <t>Smoke</t>
+  </si>
+  <si>
+    <t>Sphere</t>
+  </si>
+  <si>
+    <t>SIMGUI.PLX</t>
+  </si>
+  <si>
+    <t>Crouched man with sword</t>
+  </si>
+  <si>
+    <t>TODO (Label)</t>
+  </si>
+  <si>
+    <t>Shadow</t>
+  </si>
+  <si>
+    <t>Standing</t>
+  </si>
+  <si>
+    <t>Cadaver</t>
+  </si>
+  <si>
+    <t>Crouched</t>
+  </si>
+  <si>
+    <t>North stand to crouching</t>
+  </si>
+  <si>
+    <t>Northwest stand to crouching</t>
+  </si>
+  <si>
+    <t>Southwest stand to crouching</t>
+  </si>
+  <si>
+    <t>South stand to crouching</t>
+  </si>
+  <si>
+    <t>Southeast stand to crouching</t>
+  </si>
+  <si>
+    <t>Northeast stand to crouching</t>
+  </si>
+  <si>
+    <t>Northwest jump</t>
+  </si>
+  <si>
+    <t>North jump</t>
+  </si>
+  <si>
+    <t>Southwest jump</t>
+  </si>
+  <si>
+    <t>South jump</t>
+  </si>
+  <si>
+    <t>Southeast jump</t>
+  </si>
+  <si>
+    <t>Northeast jump</t>
+  </si>
+  <si>
+    <t>North walk short</t>
+  </si>
+  <si>
+    <t>Northwest walk short</t>
+  </si>
+  <si>
+    <t>Southwest walk short</t>
+  </si>
+  <si>
+    <t>South walk short</t>
+  </si>
+  <si>
+    <t>Southeast walk short</t>
+  </si>
+  <si>
+    <t>Northeast walk short</t>
+  </si>
+  <si>
+    <t>Northwest walk long</t>
+  </si>
+  <si>
+    <t>Southwest walk long</t>
+  </si>
+  <si>
+    <t>South walk long</t>
+  </si>
+  <si>
+    <t>Southeast walk long</t>
+  </si>
+  <si>
+    <t>Northeast walk long</t>
+  </si>
+  <si>
+    <t>North walk long</t>
   </si>
 </sst>
 </file>
@@ -3226,6 +3382,7 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.140625" customWidth="1"/>
     <col min="3" max="3" width="9.7109375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="9.85546875" bestFit="1" customWidth="1"/>
     <col min="5" max="7" width="9.85546875" customWidth="1"/>
@@ -3320,6 +3477,30 @@
       <c r="B5" s="1">
         <v>17697</v>
       </c>
+      <c r="C5" t="s">
+        <v>909</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
+      <c r="E5" t="s">
+        <v>919</v>
+      </c>
+      <c r="F5" t="s">
+        <v>919</v>
+      </c>
+      <c r="G5" t="s">
+        <v>919</v>
+      </c>
+      <c r="H5" t="s">
+        <v>929</v>
+      </c>
+      <c r="I5" t="s">
+        <v>932</v>
+      </c>
+      <c r="J5" t="s">
+        <v>931</v>
+      </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
@@ -7203,6 +7384,9 @@
       <c r="F130" t="s">
         <v>919</v>
       </c>
+      <c r="G130" t="s">
+        <v>919</v>
+      </c>
       <c r="H130" t="s">
         <v>908</v>
       </c>
@@ -7220,6 +7404,30 @@
       <c r="B131" s="1">
         <v>19481</v>
       </c>
+      <c r="C131" t="s">
+        <v>909</v>
+      </c>
+      <c r="D131">
+        <v>1</v>
+      </c>
+      <c r="E131" t="s">
+        <v>919</v>
+      </c>
+      <c r="F131" t="s">
+        <v>919</v>
+      </c>
+      <c r="G131" t="s">
+        <v>919</v>
+      </c>
+      <c r="H131" t="s">
+        <v>929</v>
+      </c>
+      <c r="I131" t="s">
+        <v>930</v>
+      </c>
+      <c r="J131" t="s">
+        <v>931</v>
+      </c>
     </row>
     <row r="132" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
@@ -7581,7 +7789,7 @@
         <v>4102</v>
       </c>
     </row>
-    <row r="177" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
         <v>803</v>
       </c>
@@ -7589,7 +7797,7 @@
         <v>1749</v>
       </c>
     </row>
-    <row r="178" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
         <v>804</v>
       </c>
@@ -7597,7 +7805,7 @@
         <v>10895</v>
       </c>
     </row>
-    <row r="179" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
         <v>805</v>
       </c>
@@ -7605,191 +7813,671 @@
         <v>16865</v>
       </c>
     </row>
-    <row r="180" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
         <v>806</v>
       </c>
       <c r="B180" s="1">
         <v>9019</v>
       </c>
-    </row>
-    <row r="181" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C180" t="s">
+        <v>909</v>
+      </c>
+      <c r="D180">
+        <v>15</v>
+      </c>
+      <c r="E180" t="s">
+        <v>914</v>
+      </c>
+      <c r="F180" t="s">
+        <v>919</v>
+      </c>
+      <c r="G180" t="s">
+        <v>919</v>
+      </c>
+      <c r="H180" t="s">
+        <v>933</v>
+      </c>
+      <c r="I180" t="s">
+        <v>934</v>
+      </c>
+    </row>
+    <row r="181" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
         <v>807</v>
       </c>
       <c r="B181" s="1">
         <v>8786</v>
       </c>
-    </row>
-    <row r="182" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C181" t="s">
+        <v>909</v>
+      </c>
+      <c r="D181">
+        <v>16</v>
+      </c>
+      <c r="E181" t="s">
+        <v>914</v>
+      </c>
+      <c r="F181" t="s">
+        <v>919</v>
+      </c>
+      <c r="G181" t="s">
+        <v>919</v>
+      </c>
+      <c r="H181" t="s">
+        <v>933</v>
+      </c>
+      <c r="I181" t="s">
+        <v>935</v>
+      </c>
+    </row>
+    <row r="182" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
         <v>808</v>
       </c>
       <c r="B182" s="1">
         <v>30883</v>
       </c>
-    </row>
-    <row r="183" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C182" t="s">
+        <v>909</v>
+      </c>
+      <c r="D182">
+        <v>31</v>
+      </c>
+      <c r="E182" t="s">
+        <v>914</v>
+      </c>
+      <c r="F182" t="s">
+        <v>919</v>
+      </c>
+      <c r="G182" t="s">
+        <v>919</v>
+      </c>
+      <c r="H182" t="s">
+        <v>933</v>
+      </c>
+      <c r="I182" t="s">
+        <v>935</v>
+      </c>
+    </row>
+    <row r="183" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
         <v>809</v>
       </c>
       <c r="B183" s="1">
         <v>16796</v>
       </c>
-    </row>
-    <row r="184" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C183" t="s">
+        <v>909</v>
+      </c>
+      <c r="D183">
+        <v>15</v>
+      </c>
+      <c r="E183" t="s">
+        <v>914</v>
+      </c>
+      <c r="F183" t="s">
+        <v>919</v>
+      </c>
+      <c r="G183" t="s">
+        <v>919</v>
+      </c>
+      <c r="H183" t="s">
+        <v>933</v>
+      </c>
+      <c r="I183" t="s">
+        <v>935</v>
+      </c>
+    </row>
+    <row r="184" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
         <v>810</v>
       </c>
       <c r="B184" s="1">
         <v>10120</v>
       </c>
-    </row>
-    <row r="185" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C184" t="s">
+        <v>909</v>
+      </c>
+      <c r="D184">
+        <v>30</v>
+      </c>
+      <c r="E184" t="s">
+        <v>914</v>
+      </c>
+      <c r="F184" t="s">
+        <v>919</v>
+      </c>
+      <c r="G184" t="s">
+        <v>919</v>
+      </c>
+      <c r="H184" t="s">
+        <v>933</v>
+      </c>
+    </row>
+    <row r="185" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
         <v>811</v>
       </c>
       <c r="B185" s="1">
         <v>15870</v>
       </c>
-    </row>
-    <row r="186" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C185" t="s">
+        <v>909</v>
+      </c>
+      <c r="D185">
+        <v>15</v>
+      </c>
+      <c r="E185" t="s">
+        <v>914</v>
+      </c>
+      <c r="F185" t="s">
+        <v>919</v>
+      </c>
+      <c r="G185" t="s">
+        <v>919</v>
+      </c>
+      <c r="H185" t="s">
+        <v>933</v>
+      </c>
+      <c r="I185" t="s">
+        <v>935</v>
+      </c>
+    </row>
+    <row r="186" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
         <v>812</v>
       </c>
       <c r="B186" s="1">
         <v>26036</v>
       </c>
-    </row>
-    <row r="187" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C186" t="s">
+        <v>909</v>
+      </c>
+      <c r="D186">
+        <v>24</v>
+      </c>
+      <c r="E186" t="s">
+        <v>914</v>
+      </c>
+      <c r="F186" t="s">
+        <v>919</v>
+      </c>
+      <c r="G186" t="s">
+        <v>919</v>
+      </c>
+      <c r="H186" t="s">
+        <v>933</v>
+      </c>
+      <c r="I186" t="s">
+        <v>936</v>
+      </c>
+    </row>
+    <row r="187" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
         <v>813</v>
       </c>
       <c r="B187" s="1">
         <v>50678</v>
       </c>
-    </row>
-    <row r="188" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C187" t="s">
+        <v>909</v>
+      </c>
+      <c r="D187">
+        <v>20</v>
+      </c>
+      <c r="E187" t="s">
+        <v>914</v>
+      </c>
+      <c r="F187" t="s">
+        <v>919</v>
+      </c>
+      <c r="G187" t="s">
+        <v>919</v>
+      </c>
+      <c r="H187" t="s">
+        <v>933</v>
+      </c>
+      <c r="I187" t="s">
+        <v>935</v>
+      </c>
+    </row>
+    <row r="188" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
         <v>814</v>
       </c>
       <c r="B188" s="1">
         <v>11718</v>
       </c>
-    </row>
-    <row r="189" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C188" t="s">
+        <v>909</v>
+      </c>
+      <c r="D188">
+        <v>30</v>
+      </c>
+      <c r="E188" t="s">
+        <v>914</v>
+      </c>
+      <c r="F188" t="s">
+        <v>919</v>
+      </c>
+      <c r="G188" t="s">
+        <v>919</v>
+      </c>
+      <c r="H188" t="s">
+        <v>933</v>
+      </c>
+      <c r="I188" t="s">
+        <v>935</v>
+      </c>
+    </row>
+    <row r="189" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
         <v>815</v>
       </c>
       <c r="B189" s="1">
         <v>8697</v>
       </c>
-    </row>
-    <row r="190" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C189" t="s">
+        <v>909</v>
+      </c>
+      <c r="D189">
+        <v>11</v>
+      </c>
+      <c r="E189" t="s">
+        <v>914</v>
+      </c>
+      <c r="F189" t="s">
+        <v>919</v>
+      </c>
+      <c r="G189" t="s">
+        <v>919</v>
+      </c>
+      <c r="H189" t="s">
+        <v>933</v>
+      </c>
+      <c r="I189" t="s">
+        <v>937</v>
+      </c>
+    </row>
+    <row r="190" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
         <v>816</v>
       </c>
       <c r="B190" s="1">
         <v>11351</v>
       </c>
-    </row>
-    <row r="191" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C190" t="s">
+        <v>909</v>
+      </c>
+      <c r="D190">
+        <v>31</v>
+      </c>
+      <c r="E190" t="s">
+        <v>914</v>
+      </c>
+      <c r="F190" t="s">
+        <v>919</v>
+      </c>
+      <c r="G190" t="s">
+        <v>919</v>
+      </c>
+      <c r="H190" t="s">
+        <v>933</v>
+      </c>
+      <c r="I190" t="s">
+        <v>935</v>
+      </c>
+    </row>
+    <row r="191" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
         <v>817</v>
       </c>
       <c r="B191" s="1">
         <v>18961</v>
       </c>
-    </row>
-    <row r="192" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C191" t="s">
+        <v>909</v>
+      </c>
+      <c r="D191">
+        <v>44</v>
+      </c>
+      <c r="E191" t="s">
+        <v>914</v>
+      </c>
+      <c r="F191" t="s">
+        <v>919</v>
+      </c>
+      <c r="G191" t="s">
+        <v>919</v>
+      </c>
+      <c r="H191" t="s">
+        <v>933</v>
+      </c>
+      <c r="I191" t="s">
+        <v>935</v>
+      </c>
+    </row>
+    <row r="192" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
         <v>818</v>
       </c>
       <c r="B192" s="1">
         <v>41109</v>
       </c>
-    </row>
-    <row r="193" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C192" t="s">
+        <v>909</v>
+      </c>
+      <c r="D192">
+        <v>24</v>
+      </c>
+      <c r="E192" t="s">
+        <v>914</v>
+      </c>
+      <c r="F192" t="s">
+        <v>919</v>
+      </c>
+      <c r="G192" t="s">
+        <v>919</v>
+      </c>
+      <c r="H192" t="s">
+        <v>933</v>
+      </c>
+      <c r="I192" t="s">
+        <v>935</v>
+      </c>
+    </row>
+    <row r="193" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
         <v>819</v>
       </c>
       <c r="B193" s="1">
         <v>1813</v>
       </c>
-    </row>
-    <row r="194" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C193" t="s">
+        <v>909</v>
+      </c>
+      <c r="D193">
+        <v>6</v>
+      </c>
+      <c r="E193" t="s">
+        <v>914</v>
+      </c>
+      <c r="F193" t="s">
+        <v>919</v>
+      </c>
+      <c r="G193" t="s">
+        <v>919</v>
+      </c>
+      <c r="H193" t="s">
+        <v>933</v>
+      </c>
+      <c r="I193" t="s">
+        <v>935</v>
+      </c>
+    </row>
+    <row r="194" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
         <v>820</v>
       </c>
       <c r="B194" s="1">
         <v>30736</v>
       </c>
-    </row>
-    <row r="195" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C194" t="s">
+        <v>909</v>
+      </c>
+      <c r="D194">
+        <v>26</v>
+      </c>
+      <c r="E194" t="s">
+        <v>914</v>
+      </c>
+      <c r="F194" t="s">
+        <v>919</v>
+      </c>
+      <c r="G194" t="s">
+        <v>919</v>
+      </c>
+      <c r="H194" t="s">
+        <v>933</v>
+      </c>
+      <c r="I194" t="s">
+        <v>935</v>
+      </c>
+    </row>
+    <row r="195" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
         <v>821</v>
       </c>
       <c r="B195" s="1">
         <v>89108</v>
       </c>
-    </row>
-    <row r="196" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C195" t="s">
+        <v>909</v>
+      </c>
+      <c r="D195">
+        <v>31</v>
+      </c>
+      <c r="E195" t="s">
+        <v>914</v>
+      </c>
+      <c r="F195" t="s">
+        <v>919</v>
+      </c>
+      <c r="G195" t="s">
+        <v>919</v>
+      </c>
+      <c r="H195" t="s">
+        <v>933</v>
+      </c>
+      <c r="I195" t="s">
+        <v>935</v>
+      </c>
+    </row>
+    <row r="196" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
         <v>822</v>
       </c>
       <c r="B196" s="1">
         <v>136329</v>
       </c>
-    </row>
-    <row r="197" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C196" t="s">
+        <v>909</v>
+      </c>
+      <c r="D196">
+        <v>31</v>
+      </c>
+      <c r="E196" t="s">
+        <v>914</v>
+      </c>
+      <c r="F196" t="s">
+        <v>919</v>
+      </c>
+      <c r="G196" t="s">
+        <v>919</v>
+      </c>
+      <c r="H196" t="s">
+        <v>933</v>
+      </c>
+      <c r="I196" t="s">
+        <v>935</v>
+      </c>
+    </row>
+    <row r="197" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
         <v>823</v>
       </c>
       <c r="B197" s="1">
         <v>40852</v>
       </c>
-    </row>
-    <row r="198" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C197" t="s">
+        <v>909</v>
+      </c>
+      <c r="D197">
+        <v>31</v>
+      </c>
+      <c r="E197" t="s">
+        <v>914</v>
+      </c>
+      <c r="F197" t="s">
+        <v>919</v>
+      </c>
+      <c r="G197" t="s">
+        <v>919</v>
+      </c>
+      <c r="H197" t="s">
+        <v>933</v>
+      </c>
+      <c r="I197" t="s">
+        <v>935</v>
+      </c>
+    </row>
+    <row r="198" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
         <v>824</v>
       </c>
       <c r="B198" s="1">
         <v>84638</v>
       </c>
-    </row>
-    <row r="199" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C198" t="s">
+        <v>909</v>
+      </c>
+      <c r="D198">
+        <v>31</v>
+      </c>
+      <c r="E198" t="s">
+        <v>914</v>
+      </c>
+      <c r="F198" t="s">
+        <v>919</v>
+      </c>
+      <c r="G198" t="s">
+        <v>919</v>
+      </c>
+      <c r="H198" t="s">
+        <v>933</v>
+      </c>
+      <c r="I198" t="s">
+        <v>935</v>
+      </c>
+    </row>
+    <row r="199" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
         <v>825</v>
       </c>
       <c r="B199" s="1">
         <v>21077</v>
       </c>
-    </row>
-    <row r="200" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C199" t="s">
+        <v>909</v>
+      </c>
+      <c r="D199">
+        <v>29</v>
+      </c>
+      <c r="E199" t="s">
+        <v>914</v>
+      </c>
+      <c r="F199" t="s">
+        <v>919</v>
+      </c>
+      <c r="G199" t="s">
+        <v>919</v>
+      </c>
+      <c r="H199" t="s">
+        <v>933</v>
+      </c>
+      <c r="I199" t="s">
+        <v>935</v>
+      </c>
+    </row>
+    <row r="200" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
         <v>826</v>
       </c>
       <c r="B200" s="1">
         <v>3737</v>
       </c>
-    </row>
-    <row r="201" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C200" t="s">
+        <v>909</v>
+      </c>
+      <c r="D200">
+        <v>14</v>
+      </c>
+      <c r="E200" t="s">
+        <v>914</v>
+      </c>
+      <c r="F200" t="s">
+        <v>919</v>
+      </c>
+      <c r="G200" t="s">
+        <v>919</v>
+      </c>
+      <c r="H200" t="s">
+        <v>933</v>
+      </c>
+      <c r="I200" t="s">
+        <v>935</v>
+      </c>
+    </row>
+    <row r="201" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
         <v>827</v>
       </c>
       <c r="B201" s="1">
         <v>52188</v>
       </c>
-    </row>
-    <row r="202" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C201" t="s">
+        <v>909</v>
+      </c>
+      <c r="D201">
+        <v>77</v>
+      </c>
+      <c r="E201" t="s">
+        <v>914</v>
+      </c>
+      <c r="F201" t="s">
+        <v>919</v>
+      </c>
+      <c r="G201" t="s">
+        <v>919</v>
+      </c>
+      <c r="H201" t="s">
+        <v>933</v>
+      </c>
+      <c r="I201" t="s">
+        <v>938</v>
+      </c>
+    </row>
+    <row r="202" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
         <v>828</v>
       </c>
       <c r="B202" s="1">
         <v>16624</v>
       </c>
-    </row>
-    <row r="203" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C202" t="s">
+        <v>909</v>
+      </c>
+      <c r="D202">
+        <v>19</v>
+      </c>
+      <c r="E202" t="s">
+        <v>914</v>
+      </c>
+      <c r="F202" t="s">
+        <v>919</v>
+      </c>
+      <c r="G202" t="s">
+        <v>919</v>
+      </c>
+      <c r="H202" t="s">
+        <v>933</v>
+      </c>
+      <c r="I202" t="s">
+        <v>935</v>
+      </c>
+    </row>
+    <row r="203" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
         <v>829</v>
       </c>
@@ -7797,7 +8485,7 @@
         <v>11616</v>
       </c>
     </row>
-    <row r="204" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
         <v>830</v>
       </c>
@@ -7805,7 +8493,7 @@
         <v>21117</v>
       </c>
     </row>
-    <row r="205" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
         <v>831</v>
       </c>
@@ -7813,303 +8501,1047 @@
         <v>14596</v>
       </c>
     </row>
-    <row r="206" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
         <v>832</v>
       </c>
       <c r="B206" s="1">
         <v>12306</v>
       </c>
-    </row>
-    <row r="207" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C206" t="s">
+        <v>909</v>
+      </c>
+      <c r="D206">
+        <v>30</v>
+      </c>
+      <c r="E206" t="s">
+        <v>914</v>
+      </c>
+      <c r="F206" t="s">
+        <v>919</v>
+      </c>
+      <c r="G206" t="s">
+        <v>919</v>
+      </c>
+      <c r="H206" t="s">
+        <v>933</v>
+      </c>
+      <c r="I206" t="s">
+        <v>939</v>
+      </c>
+    </row>
+    <row r="207" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
         <v>833</v>
       </c>
       <c r="B207" s="1">
         <v>14881</v>
       </c>
-    </row>
-    <row r="208" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C207" t="s">
+        <v>909</v>
+      </c>
+      <c r="D207">
+        <v>30</v>
+      </c>
+      <c r="E207" t="s">
+        <v>914</v>
+      </c>
+      <c r="F207" t="s">
+        <v>919</v>
+      </c>
+      <c r="G207" t="s">
+        <v>919</v>
+      </c>
+      <c r="H207" t="s">
+        <v>933</v>
+      </c>
+      <c r="I207" t="s">
+        <v>939</v>
+      </c>
+    </row>
+    <row r="208" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
         <v>834</v>
       </c>
       <c r="B208" s="1">
         <v>15823</v>
       </c>
-    </row>
-    <row r="209" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C208" t="s">
+        <v>909</v>
+      </c>
+      <c r="D208">
+        <v>30</v>
+      </c>
+      <c r="E208" t="s">
+        <v>914</v>
+      </c>
+      <c r="F208" t="s">
+        <v>919</v>
+      </c>
+      <c r="G208" t="s">
+        <v>919</v>
+      </c>
+      <c r="H208" t="s">
+        <v>933</v>
+      </c>
+      <c r="I208" t="s">
+        <v>939</v>
+      </c>
+    </row>
+    <row r="209" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
         <v>835</v>
       </c>
       <c r="B209" s="1">
         <v>8784</v>
       </c>
-    </row>
-    <row r="210" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C209" t="s">
+        <v>909</v>
+      </c>
+      <c r="D209">
+        <v>30</v>
+      </c>
+      <c r="E209" t="s">
+        <v>914</v>
+      </c>
+      <c r="F209" t="s">
+        <v>919</v>
+      </c>
+      <c r="G209" t="s">
+        <v>919</v>
+      </c>
+      <c r="H209" t="s">
+        <v>933</v>
+      </c>
+      <c r="I209" t="s">
+        <v>939</v>
+      </c>
+    </row>
+    <row r="210" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
         <v>836</v>
       </c>
       <c r="B210">
         <v>758</v>
       </c>
-    </row>
-    <row r="211" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C210" t="s">
+        <v>909</v>
+      </c>
+      <c r="D210">
+        <v>12</v>
+      </c>
+      <c r="E210" t="s">
+        <v>914</v>
+      </c>
+      <c r="F210" t="s">
+        <v>919</v>
+      </c>
+      <c r="G210" t="s">
+        <v>919</v>
+      </c>
+      <c r="H210" t="s">
+        <v>933</v>
+      </c>
+      <c r="I210" t="s">
+        <v>940</v>
+      </c>
+    </row>
+    <row r="211" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
         <v>837</v>
       </c>
       <c r="B211">
         <v>642</v>
       </c>
-    </row>
-    <row r="212" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C211" t="s">
+        <v>909</v>
+      </c>
+      <c r="D211">
+        <v>12</v>
+      </c>
+      <c r="E211" t="s">
+        <v>914</v>
+      </c>
+      <c r="F211" t="s">
+        <v>919</v>
+      </c>
+      <c r="G211" t="s">
+        <v>919</v>
+      </c>
+      <c r="H211" t="s">
+        <v>933</v>
+      </c>
+      <c r="I211" t="s">
+        <v>941</v>
+      </c>
+    </row>
+    <row r="212" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
         <v>838</v>
       </c>
       <c r="B212" s="1">
         <v>7574</v>
       </c>
-    </row>
-    <row r="213" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C212" t="s">
+        <v>909</v>
+      </c>
+      <c r="D212">
+        <v>24</v>
+      </c>
+      <c r="E212" t="s">
+        <v>914</v>
+      </c>
+      <c r="F212" t="s">
+        <v>919</v>
+      </c>
+      <c r="G212" t="s">
+        <v>919</v>
+      </c>
+      <c r="H212" t="s">
+        <v>933</v>
+      </c>
+      <c r="I212" t="s">
+        <v>942</v>
+      </c>
+    </row>
+    <row r="213" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
         <v>839</v>
       </c>
       <c r="B213" s="1">
         <v>3884</v>
       </c>
-    </row>
-    <row r="214" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C213" t="s">
+        <v>909</v>
+      </c>
+      <c r="D213">
+        <v>25</v>
+      </c>
+      <c r="E213" t="s">
+        <v>914</v>
+      </c>
+      <c r="F213" t="s">
+        <v>919</v>
+      </c>
+      <c r="G213" t="s">
+        <v>919</v>
+      </c>
+      <c r="H213" t="s">
+        <v>933</v>
+      </c>
+      <c r="I213" t="s">
+        <v>942</v>
+      </c>
+    </row>
+    <row r="214" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
         <v>840</v>
       </c>
       <c r="B214" s="1">
         <v>2475</v>
       </c>
-    </row>
-    <row r="215" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C214" t="s">
+        <v>909</v>
+      </c>
+      <c r="D214">
+        <v>25</v>
+      </c>
+      <c r="E214" t="s">
+        <v>914</v>
+      </c>
+      <c r="F214" t="s">
+        <v>919</v>
+      </c>
+      <c r="G214" t="s">
+        <v>919</v>
+      </c>
+      <c r="H214" t="s">
+        <v>933</v>
+      </c>
+      <c r="I214" t="s">
+        <v>942</v>
+      </c>
+    </row>
+    <row r="215" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
         <v>841</v>
       </c>
       <c r="B215" s="1">
         <v>1318</v>
       </c>
-    </row>
-    <row r="216" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C215" t="s">
+        <v>909</v>
+      </c>
+      <c r="D215">
+        <v>24</v>
+      </c>
+      <c r="E215" t="s">
+        <v>919</v>
+      </c>
+      <c r="F215" t="s">
+        <v>919</v>
+      </c>
+      <c r="G215" t="s">
+        <v>914</v>
+      </c>
+      <c r="H215" t="s">
+        <v>933</v>
+      </c>
+      <c r="I215" t="s">
+        <v>943</v>
+      </c>
+    </row>
+    <row r="216" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
         <v>842</v>
       </c>
       <c r="B216" s="1">
         <v>1178</v>
       </c>
-    </row>
-    <row r="217" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C216" t="s">
+        <v>909</v>
+      </c>
+      <c r="D216">
+        <v>24</v>
+      </c>
+      <c r="E216" t="s">
+        <v>919</v>
+      </c>
+      <c r="F216" t="s">
+        <v>919</v>
+      </c>
+      <c r="G216" t="s">
+        <v>914</v>
+      </c>
+      <c r="H216" t="s">
+        <v>933</v>
+      </c>
+      <c r="I216" t="s">
+        <v>943</v>
+      </c>
+    </row>
+    <row r="217" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
         <v>843</v>
       </c>
       <c r="B217" s="1">
         <v>1263</v>
       </c>
-    </row>
-    <row r="218" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C217" t="s">
+        <v>909</v>
+      </c>
+      <c r="D217">
+        <v>24</v>
+      </c>
+      <c r="E217" t="s">
+        <v>919</v>
+      </c>
+      <c r="F217" t="s">
+        <v>919</v>
+      </c>
+      <c r="G217" t="s">
+        <v>914</v>
+      </c>
+      <c r="H217" t="s">
+        <v>933</v>
+      </c>
+      <c r="I217" t="s">
+        <v>943</v>
+      </c>
+    </row>
+    <row r="218" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
         <v>844</v>
       </c>
       <c r="B218" s="1">
         <v>1210</v>
       </c>
-    </row>
-    <row r="219" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C218" t="s">
+        <v>909</v>
+      </c>
+      <c r="D218">
+        <v>24</v>
+      </c>
+      <c r="E218" t="s">
+        <v>919</v>
+      </c>
+      <c r="F218" t="s">
+        <v>919</v>
+      </c>
+      <c r="G218" t="s">
+        <v>914</v>
+      </c>
+      <c r="H218" t="s">
+        <v>933</v>
+      </c>
+      <c r="I218" t="s">
+        <v>943</v>
+      </c>
+    </row>
+    <row r="219" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
         <v>845</v>
       </c>
       <c r="B219" s="1">
         <v>9002</v>
       </c>
-    </row>
-    <row r="220" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C219" t="s">
+        <v>909</v>
+      </c>
+      <c r="D219">
+        <v>24</v>
+      </c>
+      <c r="E219" t="s">
+        <v>919</v>
+      </c>
+      <c r="F219" t="s">
+        <v>919</v>
+      </c>
+      <c r="G219" t="s">
+        <v>914</v>
+      </c>
+      <c r="H219" t="s">
+        <v>933</v>
+      </c>
+      <c r="I219" t="s">
+        <v>944</v>
+      </c>
+    </row>
+    <row r="220" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
         <v>846</v>
       </c>
       <c r="B220" s="1">
         <v>1233</v>
       </c>
-    </row>
-    <row r="221" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C220" t="s">
+        <v>909</v>
+      </c>
+      <c r="D220">
+        <v>24</v>
+      </c>
+      <c r="E220" t="s">
+        <v>919</v>
+      </c>
+      <c r="F220" t="s">
+        <v>919</v>
+      </c>
+      <c r="G220" t="s">
+        <v>914</v>
+      </c>
+      <c r="H220" t="s">
+        <v>933</v>
+      </c>
+      <c r="I220" t="s">
+        <v>943</v>
+      </c>
+    </row>
+    <row r="221" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
         <v>847</v>
       </c>
       <c r="B221" s="1">
         <v>1524</v>
       </c>
-    </row>
-    <row r="222" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C221" t="s">
+        <v>909</v>
+      </c>
+      <c r="D221">
+        <v>24</v>
+      </c>
+      <c r="E221" t="s">
+        <v>919</v>
+      </c>
+      <c r="F221" t="s">
+        <v>919</v>
+      </c>
+      <c r="G221" t="s">
+        <v>914</v>
+      </c>
+      <c r="H221" t="s">
+        <v>933</v>
+      </c>
+      <c r="I221" t="s">
+        <v>945</v>
+      </c>
+    </row>
+    <row r="222" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
         <v>848</v>
       </c>
       <c r="B222">
         <v>444</v>
       </c>
-    </row>
-    <row r="223" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C222" t="s">
+        <v>909</v>
+      </c>
+      <c r="D222">
+        <v>24</v>
+      </c>
+      <c r="E222" t="s">
+        <v>919</v>
+      </c>
+      <c r="F222" t="s">
+        <v>919</v>
+      </c>
+      <c r="G222" t="s">
+        <v>914</v>
+      </c>
+      <c r="H222" t="s">
+        <v>933</v>
+      </c>
+      <c r="I222" t="s">
+        <v>946</v>
+      </c>
+    </row>
+    <row r="223" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
         <v>849</v>
       </c>
       <c r="B223">
         <v>803</v>
       </c>
-    </row>
-    <row r="224" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C223" t="s">
+        <v>909</v>
+      </c>
+      <c r="D223">
+        <v>24</v>
+      </c>
+      <c r="E223" t="s">
+        <v>919</v>
+      </c>
+      <c r="F223" t="s">
+        <v>919</v>
+      </c>
+      <c r="G223" t="s">
+        <v>914</v>
+      </c>
+      <c r="H223" t="s">
+        <v>933</v>
+      </c>
+      <c r="I223" t="s">
+        <v>947</v>
+      </c>
+    </row>
+    <row r="224" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
         <v>850</v>
       </c>
       <c r="B224" s="1">
         <v>1218</v>
       </c>
-    </row>
-    <row r="225" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C224" t="s">
+        <v>909</v>
+      </c>
+      <c r="D224">
+        <v>24</v>
+      </c>
+      <c r="E224" t="s">
+        <v>919</v>
+      </c>
+      <c r="F224" t="s">
+        <v>919</v>
+      </c>
+      <c r="G224" t="s">
+        <v>914</v>
+      </c>
+      <c r="H224" t="s">
+        <v>933</v>
+      </c>
+      <c r="I224" t="s">
+        <v>947</v>
+      </c>
+    </row>
+    <row r="225" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
         <v>851</v>
       </c>
       <c r="B225">
         <v>871</v>
       </c>
-    </row>
-    <row r="226" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C225" t="s">
+        <v>909</v>
+      </c>
+      <c r="D225">
+        <v>24</v>
+      </c>
+      <c r="E225" t="s">
+        <v>919</v>
+      </c>
+      <c r="F225" t="s">
+        <v>919</v>
+      </c>
+      <c r="G225" t="s">
+        <v>914</v>
+      </c>
+      <c r="H225" t="s">
+        <v>933</v>
+      </c>
+      <c r="I225" t="s">
+        <v>947</v>
+      </c>
+    </row>
+    <row r="226" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
         <v>852</v>
       </c>
       <c r="B226">
         <v>559</v>
       </c>
-    </row>
-    <row r="227" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C226" t="s">
+        <v>909</v>
+      </c>
+      <c r="D226">
+        <v>12</v>
+      </c>
+      <c r="E226" t="s">
+        <v>919</v>
+      </c>
+      <c r="F226" t="s">
+        <v>919</v>
+      </c>
+      <c r="G226" t="s">
+        <v>914</v>
+      </c>
+      <c r="H226" t="s">
+        <v>933</v>
+      </c>
+    </row>
+    <row r="227" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
         <v>853</v>
       </c>
       <c r="B227">
         <v>618</v>
       </c>
-    </row>
-    <row r="228" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C227" t="s">
+        <v>909</v>
+      </c>
+      <c r="D227">
+        <v>12</v>
+      </c>
+      <c r="E227" t="s">
+        <v>919</v>
+      </c>
+      <c r="F227" t="s">
+        <v>919</v>
+      </c>
+      <c r="G227" t="s">
+        <v>914</v>
+      </c>
+      <c r="H227" t="s">
+        <v>933</v>
+      </c>
+    </row>
+    <row r="228" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
         <v>854</v>
       </c>
       <c r="B228">
         <v>582</v>
       </c>
-    </row>
-    <row r="229" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C228" t="s">
+        <v>909</v>
+      </c>
+      <c r="D228">
+        <v>12</v>
+      </c>
+      <c r="E228" t="s">
+        <v>919</v>
+      </c>
+      <c r="F228" t="s">
+        <v>919</v>
+      </c>
+      <c r="G228" t="s">
+        <v>914</v>
+      </c>
+      <c r="H228" t="s">
+        <v>933</v>
+      </c>
+    </row>
+    <row r="229" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
         <v>855</v>
       </c>
       <c r="B229">
         <v>411</v>
       </c>
-    </row>
-    <row r="230" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C229" t="s">
+        <v>909</v>
+      </c>
+      <c r="D229">
+        <v>12</v>
+      </c>
+      <c r="E229" t="s">
+        <v>919</v>
+      </c>
+      <c r="F229" t="s">
+        <v>919</v>
+      </c>
+      <c r="G229" t="s">
+        <v>914</v>
+      </c>
+      <c r="H229" t="s">
+        <v>933</v>
+      </c>
+    </row>
+    <row r="230" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
         <v>856</v>
       </c>
       <c r="B230">
         <v>327</v>
       </c>
-    </row>
-    <row r="231" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C230" t="s">
+        <v>909</v>
+      </c>
+      <c r="D230">
+        <v>4</v>
+      </c>
+      <c r="E230" t="s">
+        <v>919</v>
+      </c>
+      <c r="F230" t="s">
+        <v>919</v>
+      </c>
+      <c r="G230" t="s">
+        <v>914</v>
+      </c>
+      <c r="H230" t="s">
+        <v>933</v>
+      </c>
+    </row>
+    <row r="231" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
         <v>857</v>
       </c>
       <c r="B231">
         <v>310</v>
       </c>
-    </row>
-    <row r="232" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C231" t="s">
+        <v>909</v>
+      </c>
+      <c r="D231">
+        <v>4</v>
+      </c>
+      <c r="E231" t="s">
+        <v>919</v>
+      </c>
+      <c r="F231" t="s">
+        <v>919</v>
+      </c>
+      <c r="G231" t="s">
+        <v>914</v>
+      </c>
+      <c r="H231" t="s">
+        <v>933</v>
+      </c>
+    </row>
+    <row r="232" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
         <v>858</v>
       </c>
       <c r="B232">
         <v>317</v>
       </c>
-    </row>
-    <row r="233" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C232" t="s">
+        <v>909</v>
+      </c>
+      <c r="D232">
+        <v>4</v>
+      </c>
+      <c r="E232" t="s">
+        <v>919</v>
+      </c>
+      <c r="F232" t="s">
+        <v>919</v>
+      </c>
+      <c r="G232" t="s">
+        <v>914</v>
+      </c>
+      <c r="H232" t="s">
+        <v>933</v>
+      </c>
+    </row>
+    <row r="233" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
         <v>859</v>
       </c>
       <c r="B233">
         <v>323</v>
       </c>
-    </row>
-    <row r="234" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C233" t="s">
+        <v>909</v>
+      </c>
+      <c r="D233">
+        <v>4</v>
+      </c>
+      <c r="E233" t="s">
+        <v>919</v>
+      </c>
+      <c r="F233" t="s">
+        <v>919</v>
+      </c>
+      <c r="G233" t="s">
+        <v>914</v>
+      </c>
+      <c r="H233" t="s">
+        <v>933</v>
+      </c>
+    </row>
+    <row r="234" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
         <v>860</v>
       </c>
       <c r="B234">
         <v>316</v>
       </c>
-    </row>
-    <row r="235" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C234" t="s">
+        <v>909</v>
+      </c>
+      <c r="D234">
+        <v>4</v>
+      </c>
+      <c r="E234" t="s">
+        <v>919</v>
+      </c>
+      <c r="F234" t="s">
+        <v>919</v>
+      </c>
+      <c r="G234" t="s">
+        <v>914</v>
+      </c>
+      <c r="H234" t="s">
+        <v>933</v>
+      </c>
+    </row>
+    <row r="235" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
         <v>861</v>
       </c>
       <c r="B235">
         <v>309</v>
       </c>
-    </row>
-    <row r="236" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C235" t="s">
+        <v>909</v>
+      </c>
+      <c r="D235">
+        <v>4</v>
+      </c>
+      <c r="E235" t="s">
+        <v>919</v>
+      </c>
+      <c r="F235" t="s">
+        <v>919</v>
+      </c>
+      <c r="G235" t="s">
+        <v>914</v>
+      </c>
+      <c r="H235" t="s">
+        <v>933</v>
+      </c>
+    </row>
+    <row r="236" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
         <v>862</v>
       </c>
       <c r="B236" s="1">
         <v>3833</v>
       </c>
-    </row>
-    <row r="237" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C236" t="s">
+        <v>909</v>
+      </c>
+      <c r="D236">
+        <v>93</v>
+      </c>
+      <c r="E236" t="s">
+        <v>914</v>
+      </c>
+      <c r="F236" t="s">
+        <v>919</v>
+      </c>
+      <c r="G236" t="s">
+        <v>919</v>
+      </c>
+      <c r="H236" t="s">
+        <v>933</v>
+      </c>
+      <c r="I236" t="s">
+        <v>948</v>
+      </c>
+    </row>
+    <row r="237" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
         <v>863</v>
       </c>
       <c r="B237" s="1">
         <v>2227</v>
       </c>
-    </row>
-    <row r="238" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C237" t="s">
+        <v>909</v>
+      </c>
+      <c r="D237">
+        <v>47</v>
+      </c>
+      <c r="E237" t="s">
+        <v>914</v>
+      </c>
+      <c r="F237" t="s">
+        <v>919</v>
+      </c>
+      <c r="G237" t="s">
+        <v>919</v>
+      </c>
+      <c r="H237" t="s">
+        <v>933</v>
+      </c>
+      <c r="I237" t="s">
+        <v>948</v>
+      </c>
+    </row>
+    <row r="238" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
         <v>864</v>
       </c>
       <c r="B238" s="1">
         <v>1576</v>
       </c>
-    </row>
-    <row r="239" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C238" t="s">
+        <v>909</v>
+      </c>
+      <c r="D238">
+        <v>31</v>
+      </c>
+      <c r="E238" t="s">
+        <v>914</v>
+      </c>
+      <c r="F238" t="s">
+        <v>919</v>
+      </c>
+      <c r="G238" t="s">
+        <v>919</v>
+      </c>
+      <c r="H238" t="s">
+        <v>933</v>
+      </c>
+      <c r="I238" t="s">
+        <v>948</v>
+      </c>
+    </row>
+    <row r="239" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
         <v>865</v>
       </c>
       <c r="B239" s="1">
         <v>1261</v>
       </c>
-    </row>
-    <row r="240" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C239" t="s">
+        <v>909</v>
+      </c>
+      <c r="D239">
+        <v>24</v>
+      </c>
+      <c r="E239" t="s">
+        <v>914</v>
+      </c>
+      <c r="F239" t="s">
+        <v>919</v>
+      </c>
+      <c r="G239" t="s">
+        <v>919</v>
+      </c>
+      <c r="H239" t="s">
+        <v>933</v>
+      </c>
+      <c r="I239" t="s">
+        <v>948</v>
+      </c>
+    </row>
+    <row r="240" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
         <v>866</v>
       </c>
       <c r="B240" s="1">
         <v>11996</v>
       </c>
-    </row>
-    <row r="241" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C240" t="s">
+        <v>909</v>
+      </c>
+      <c r="D240">
+        <v>55</v>
+      </c>
+      <c r="E240" t="s">
+        <v>914</v>
+      </c>
+      <c r="F240" t="s">
+        <v>919</v>
+      </c>
+      <c r="G240" t="s">
+        <v>919</v>
+      </c>
+      <c r="H240" t="s">
+        <v>933</v>
+      </c>
+      <c r="I240" t="s">
+        <v>948</v>
+      </c>
+    </row>
+    <row r="241" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
         <v>867</v>
       </c>
       <c r="B241" s="1">
         <v>2296</v>
       </c>
-    </row>
-    <row r="242" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C241" t="s">
+        <v>909</v>
+      </c>
+      <c r="D241">
+        <v>26</v>
+      </c>
+      <c r="E241" t="s">
+        <v>914</v>
+      </c>
+      <c r="F241" t="s">
+        <v>919</v>
+      </c>
+      <c r="G241" t="s">
+        <v>919</v>
+      </c>
+      <c r="H241" t="s">
+        <v>933</v>
+      </c>
+      <c r="I241" t="s">
+        <v>948</v>
+      </c>
+    </row>
+    <row r="242" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
         <v>868</v>
       </c>
       <c r="B242">
         <v>422</v>
       </c>
-    </row>
-    <row r="243" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C242" t="s">
+        <v>909</v>
+      </c>
+      <c r="D242">
+        <v>1</v>
+      </c>
+      <c r="E242" t="s">
+        <v>919</v>
+      </c>
+      <c r="F242" t="s">
+        <v>919</v>
+      </c>
+      <c r="G242" t="s">
+        <v>919</v>
+      </c>
+      <c r="I242" t="s">
+        <v>949</v>
+      </c>
+    </row>
+    <row r="243" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
         <v>869</v>
       </c>
@@ -8117,7 +9549,7 @@
         <v>312159</v>
       </c>
     </row>
-    <row r="244" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
         <v>870</v>
       </c>
@@ -8125,7 +9557,7 @@
         <v>34370</v>
       </c>
     </row>
-    <row r="245" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
         <v>871</v>
       </c>
@@ -8133,7 +9565,7 @@
         <v>1990</v>
       </c>
     </row>
-    <row r="246" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
         <v>872</v>
       </c>
@@ -8141,231 +9573,819 @@
         <v>3440</v>
       </c>
     </row>
-    <row r="247" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
         <v>873</v>
       </c>
       <c r="B247" s="1">
         <v>357500</v>
       </c>
-    </row>
-    <row r="248" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C247" t="s">
+        <v>950</v>
+      </c>
+      <c r="D247">
+        <v>60</v>
+      </c>
+      <c r="E247" t="s">
+        <v>914</v>
+      </c>
+      <c r="F247" t="s">
+        <v>919</v>
+      </c>
+      <c r="G247" t="s">
+        <v>919</v>
+      </c>
+      <c r="H247" t="s">
+        <v>952</v>
+      </c>
+      <c r="I247" t="s">
+        <v>951</v>
+      </c>
+    </row>
+    <row r="248" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
         <v>130</v>
       </c>
       <c r="B248" s="1">
         <v>8929</v>
       </c>
-    </row>
-    <row r="249" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C248" t="s">
+        <v>909</v>
+      </c>
+      <c r="D248">
+        <v>6</v>
+      </c>
+      <c r="E248" t="s">
+        <v>919</v>
+      </c>
+      <c r="F248" t="s">
+        <v>914</v>
+      </c>
+      <c r="G248" t="s">
+        <v>914</v>
+      </c>
+      <c r="H248" t="s">
+        <v>953</v>
+      </c>
+      <c r="I248" t="s">
+        <v>954</v>
+      </c>
+    </row>
+    <row r="249" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
         <v>131</v>
       </c>
       <c r="B249" s="1">
         <v>6902</v>
       </c>
-    </row>
-    <row r="250" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C249" t="s">
+        <v>909</v>
+      </c>
+      <c r="D249">
+        <v>6</v>
+      </c>
+      <c r="E249" t="s">
+        <v>919</v>
+      </c>
+      <c r="F249" t="s">
+        <v>914</v>
+      </c>
+      <c r="G249" t="s">
+        <v>914</v>
+      </c>
+      <c r="H249" t="s">
+        <v>953</v>
+      </c>
+      <c r="I249" t="s">
+        <v>955</v>
+      </c>
+    </row>
+    <row r="250" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
         <v>132</v>
       </c>
       <c r="B250" s="1">
         <v>8395</v>
       </c>
-    </row>
-    <row r="251" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C250" t="s">
+        <v>909</v>
+      </c>
+      <c r="D250">
+        <v>6</v>
+      </c>
+      <c r="E250" t="s">
+        <v>919</v>
+      </c>
+      <c r="F250" t="s">
+        <v>914</v>
+      </c>
+      <c r="G250" t="s">
+        <v>914</v>
+      </c>
+      <c r="H250" t="s">
+        <v>953</v>
+      </c>
+      <c r="I250" t="s">
+        <v>956</v>
+      </c>
+    </row>
+    <row r="251" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
         <v>133</v>
       </c>
       <c r="B251" s="1">
         <v>4678</v>
       </c>
-    </row>
-    <row r="252" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C251" t="s">
+        <v>909</v>
+      </c>
+      <c r="D251">
+        <v>4</v>
+      </c>
+      <c r="E251" t="s">
+        <v>914</v>
+      </c>
+      <c r="F251" t="s">
+        <v>919</v>
+      </c>
+      <c r="G251" t="s">
+        <v>919</v>
+      </c>
+      <c r="H251" t="s">
+        <v>953</v>
+      </c>
+      <c r="I251" t="s">
+        <v>957</v>
+      </c>
+    </row>
+    <row r="252" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
         <v>134</v>
       </c>
       <c r="B252" s="1">
         <v>5378</v>
       </c>
-    </row>
-    <row r="253" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C252" t="s">
+        <v>909</v>
+      </c>
+      <c r="D252">
+        <v>4</v>
+      </c>
+      <c r="E252" t="s">
+        <v>914</v>
+      </c>
+      <c r="F252" t="s">
+        <v>919</v>
+      </c>
+      <c r="G252" t="s">
+        <v>919</v>
+      </c>
+      <c r="H252" t="s">
+        <v>953</v>
+      </c>
+      <c r="I252" t="s">
+        <v>958</v>
+      </c>
+    </row>
+    <row r="253" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
         <v>135</v>
       </c>
       <c r="B253" s="1">
         <v>6150</v>
       </c>
-    </row>
-    <row r="254" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C253" t="s">
+        <v>909</v>
+      </c>
+      <c r="D253">
+        <v>4</v>
+      </c>
+      <c r="E253" t="s">
+        <v>914</v>
+      </c>
+      <c r="F253" t="s">
+        <v>919</v>
+      </c>
+      <c r="G253" t="s">
+        <v>919</v>
+      </c>
+      <c r="H253" t="s">
+        <v>953</v>
+      </c>
+      <c r="I253" t="s">
+        <v>959</v>
+      </c>
+    </row>
+    <row r="254" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
         <v>136</v>
       </c>
       <c r="B254" s="1">
         <v>5967</v>
       </c>
-    </row>
-    <row r="255" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C254" t="s">
+        <v>909</v>
+      </c>
+      <c r="D254">
+        <v>4</v>
+      </c>
+      <c r="E254" t="s">
+        <v>914</v>
+      </c>
+      <c r="F254" t="s">
+        <v>919</v>
+      </c>
+      <c r="G254" t="s">
+        <v>919</v>
+      </c>
+      <c r="H254" t="s">
+        <v>953</v>
+      </c>
+      <c r="I254" t="s">
+        <v>960</v>
+      </c>
+    </row>
+    <row r="255" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
         <v>137</v>
       </c>
       <c r="B255" s="1">
         <v>5420</v>
       </c>
-    </row>
-    <row r="256" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C255" t="s">
+        <v>909</v>
+      </c>
+      <c r="D255">
+        <v>4</v>
+      </c>
+      <c r="E255" t="s">
+        <v>914</v>
+      </c>
+      <c r="F255" t="s">
+        <v>919</v>
+      </c>
+      <c r="G255" t="s">
+        <v>919</v>
+      </c>
+      <c r="H255" t="s">
+        <v>953</v>
+      </c>
+      <c r="I255" t="s">
+        <v>961</v>
+      </c>
+    </row>
+    <row r="256" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
         <v>138</v>
       </c>
       <c r="B256" s="1">
         <v>5443</v>
       </c>
-    </row>
-    <row r="257" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C256" t="s">
+        <v>909</v>
+      </c>
+      <c r="D256">
+        <v>4</v>
+      </c>
+      <c r="E256" t="s">
+        <v>914</v>
+      </c>
+      <c r="F256" t="s">
+        <v>919</v>
+      </c>
+      <c r="G256" t="s">
+        <v>919</v>
+      </c>
+      <c r="H256" t="s">
+        <v>953</v>
+      </c>
+      <c r="I256" t="s">
+        <v>962</v>
+      </c>
+    </row>
+    <row r="257" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
         <v>139</v>
       </c>
       <c r="B257" s="1">
         <v>19735</v>
       </c>
-    </row>
-    <row r="258" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C257" t="s">
+        <v>909</v>
+      </c>
+      <c r="D257">
+        <v>21</v>
+      </c>
+      <c r="E257" t="s">
+        <v>914</v>
+      </c>
+      <c r="F257" t="s">
+        <v>919</v>
+      </c>
+      <c r="G257" t="s">
+        <v>919</v>
+      </c>
+      <c r="H257" t="s">
+        <v>953</v>
+      </c>
+      <c r="I257" t="s">
+        <v>964</v>
+      </c>
+    </row>
+    <row r="258" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
         <v>140</v>
       </c>
       <c r="B258" s="1">
         <v>21806</v>
       </c>
-    </row>
-    <row r="259" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C258" t="s">
+        <v>909</v>
+      </c>
+      <c r="D258">
+        <v>21</v>
+      </c>
+      <c r="E258" t="s">
+        <v>914</v>
+      </c>
+      <c r="F258" t="s">
+        <v>919</v>
+      </c>
+      <c r="G258" t="s">
+        <v>919</v>
+      </c>
+      <c r="H258" t="s">
+        <v>953</v>
+      </c>
+      <c r="I258" t="s">
+        <v>963</v>
+      </c>
+    </row>
+    <row r="259" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
         <v>141</v>
       </c>
       <c r="B259" s="1">
         <v>24116</v>
       </c>
-    </row>
-    <row r="260" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C259" t="s">
+        <v>909</v>
+      </c>
+      <c r="D259">
+        <v>21</v>
+      </c>
+      <c r="E259" t="s">
+        <v>914</v>
+      </c>
+      <c r="F259" t="s">
+        <v>919</v>
+      </c>
+      <c r="G259" t="s">
+        <v>919</v>
+      </c>
+      <c r="H259" t="s">
+        <v>953</v>
+      </c>
+      <c r="I259" t="s">
+        <v>965</v>
+      </c>
+    </row>
+    <row r="260" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
         <v>142</v>
       </c>
       <c r="B260" s="1">
         <v>23458</v>
       </c>
-    </row>
-    <row r="261" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C260" t="s">
+        <v>909</v>
+      </c>
+      <c r="D260">
+        <v>21</v>
+      </c>
+      <c r="E260" t="s">
+        <v>914</v>
+      </c>
+      <c r="F260" t="s">
+        <v>914</v>
+      </c>
+      <c r="G260" t="s">
+        <v>919</v>
+      </c>
+      <c r="H260" t="s">
+        <v>953</v>
+      </c>
+      <c r="I260" t="s">
+        <v>966</v>
+      </c>
+    </row>
+    <row r="261" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
         <v>143</v>
       </c>
       <c r="B261" s="1">
         <v>20956</v>
       </c>
-    </row>
-    <row r="262" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C261" t="s">
+        <v>909</v>
+      </c>
+      <c r="D261">
+        <v>21</v>
+      </c>
+      <c r="E261" t="s">
+        <v>914</v>
+      </c>
+      <c r="F261" t="s">
+        <v>919</v>
+      </c>
+      <c r="G261" t="s">
+        <v>919</v>
+      </c>
+      <c r="H261" t="s">
+        <v>953</v>
+      </c>
+      <c r="I261" t="s">
+        <v>967</v>
+      </c>
+    </row>
+    <row r="262" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
         <v>144</v>
       </c>
       <c r="B262" s="1">
         <v>22525</v>
       </c>
-    </row>
-    <row r="263" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C262" t="s">
+        <v>909</v>
+      </c>
+      <c r="D262">
+        <v>21</v>
+      </c>
+      <c r="E262" t="s">
+        <v>914</v>
+      </c>
+      <c r="F262" t="s">
+        <v>919</v>
+      </c>
+      <c r="G262" t="s">
+        <v>919</v>
+      </c>
+      <c r="H262" t="s">
+        <v>953</v>
+      </c>
+      <c r="I262" t="s">
+        <v>968</v>
+      </c>
+    </row>
+    <row r="263" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
         <v>145</v>
       </c>
       <c r="B263" s="1">
         <v>11785</v>
       </c>
-    </row>
-    <row r="264" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C263" t="s">
+        <v>909</v>
+      </c>
+      <c r="D263">
+        <v>8</v>
+      </c>
+      <c r="E263" t="s">
+        <v>914</v>
+      </c>
+      <c r="F263" t="s">
+        <v>919</v>
+      </c>
+      <c r="G263" t="s">
+        <v>919</v>
+      </c>
+      <c r="H263" t="s">
+        <v>953</v>
+      </c>
+      <c r="I263" t="s">
+        <v>969</v>
+      </c>
+    </row>
+    <row r="264" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
         <v>146</v>
       </c>
       <c r="B264" s="1">
         <v>13416</v>
       </c>
-    </row>
-    <row r="265" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C264" t="s">
+        <v>909</v>
+      </c>
+      <c r="D264">
+        <v>8</v>
+      </c>
+      <c r="E264" t="s">
+        <v>914</v>
+      </c>
+      <c r="F264" t="s">
+        <v>919</v>
+      </c>
+      <c r="G264" t="s">
+        <v>919</v>
+      </c>
+      <c r="H264" t="s">
+        <v>953</v>
+      </c>
+      <c r="I264" t="s">
+        <v>970</v>
+      </c>
+    </row>
+    <row r="265" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
         <v>147</v>
       </c>
       <c r="B265" s="1">
         <v>13969</v>
       </c>
-    </row>
-    <row r="266" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C265" t="s">
+        <v>909</v>
+      </c>
+      <c r="D265">
+        <v>8</v>
+      </c>
+      <c r="E265" t="s">
+        <v>914</v>
+      </c>
+      <c r="F265" t="s">
+        <v>919</v>
+      </c>
+      <c r="G265" t="s">
+        <v>919</v>
+      </c>
+      <c r="H265" t="s">
+        <v>953</v>
+      </c>
+      <c r="I265" t="s">
+        <v>971</v>
+      </c>
+    </row>
+    <row r="266" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
         <v>148</v>
       </c>
       <c r="B266" s="1">
         <v>13428</v>
       </c>
-    </row>
-    <row r="267" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C266" t="s">
+        <v>909</v>
+      </c>
+      <c r="D266">
+        <v>8</v>
+      </c>
+      <c r="E266" t="s">
+        <v>914</v>
+      </c>
+      <c r="F266" t="s">
+        <v>914</v>
+      </c>
+      <c r="G266" t="s">
+        <v>919</v>
+      </c>
+      <c r="H266" t="s">
+        <v>953</v>
+      </c>
+      <c r="I266" t="s">
+        <v>972</v>
+      </c>
+    </row>
+    <row r="267" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
         <v>149</v>
       </c>
       <c r="B267" s="1">
         <v>13929</v>
       </c>
-    </row>
-    <row r="268" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C267" t="s">
+        <v>909</v>
+      </c>
+      <c r="D267">
+        <v>8</v>
+      </c>
+      <c r="E267" t="s">
+        <v>914</v>
+      </c>
+      <c r="F267" t="s">
+        <v>919</v>
+      </c>
+      <c r="G267" t="s">
+        <v>919</v>
+      </c>
+      <c r="H267" t="s">
+        <v>953</v>
+      </c>
+      <c r="I267" t="s">
+        <v>973</v>
+      </c>
+    </row>
+    <row r="268" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
         <v>150</v>
       </c>
       <c r="B268" s="1">
         <v>13644</v>
       </c>
-    </row>
-    <row r="269" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C268" t="s">
+        <v>909</v>
+      </c>
+      <c r="D268">
+        <v>8</v>
+      </c>
+      <c r="E268" t="s">
+        <v>914</v>
+      </c>
+      <c r="F268" t="s">
+        <v>919</v>
+      </c>
+      <c r="G268" t="s">
+        <v>919</v>
+      </c>
+      <c r="H268" t="s">
+        <v>953</v>
+      </c>
+      <c r="I268" t="s">
+        <v>974</v>
+      </c>
+    </row>
+    <row r="269" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
         <v>151</v>
       </c>
       <c r="B269" s="1">
         <v>23053</v>
       </c>
-    </row>
-    <row r="270" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C269" t="s">
+        <v>909</v>
+      </c>
+      <c r="D269">
+        <v>16</v>
+      </c>
+      <c r="E269" t="s">
+        <v>914</v>
+      </c>
+      <c r="F269" t="s">
+        <v>919</v>
+      </c>
+      <c r="G269" t="s">
+        <v>919</v>
+      </c>
+      <c r="H269" t="s">
+        <v>953</v>
+      </c>
+      <c r="I269" t="s">
+        <v>980</v>
+      </c>
+    </row>
+    <row r="270" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
         <v>152</v>
       </c>
       <c r="B270" s="1">
         <v>25837</v>
       </c>
-    </row>
-    <row r="271" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C270" t="s">
+        <v>909</v>
+      </c>
+      <c r="D270">
+        <v>16</v>
+      </c>
+      <c r="E270" t="s">
+        <v>914</v>
+      </c>
+      <c r="F270" t="s">
+        <v>919</v>
+      </c>
+      <c r="G270" t="s">
+        <v>919</v>
+      </c>
+      <c r="H270" t="s">
+        <v>953</v>
+      </c>
+      <c r="I270" t="s">
+        <v>975</v>
+      </c>
+    </row>
+    <row r="271" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
         <v>153</v>
       </c>
       <c r="B271" s="1">
         <v>27049</v>
       </c>
-    </row>
-    <row r="272" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C271" t="s">
+        <v>909</v>
+      </c>
+      <c r="D271">
+        <v>16</v>
+      </c>
+      <c r="E271" t="s">
+        <v>914</v>
+      </c>
+      <c r="F271" t="s">
+        <v>919</v>
+      </c>
+      <c r="G271" t="s">
+        <v>919</v>
+      </c>
+      <c r="H271" t="s">
+        <v>953</v>
+      </c>
+      <c r="I271" t="s">
+        <v>976</v>
+      </c>
+    </row>
+    <row r="272" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
         <v>154</v>
       </c>
       <c r="B272" s="1">
         <v>26011</v>
       </c>
-    </row>
-    <row r="273" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C272" t="s">
+        <v>909</v>
+      </c>
+      <c r="D272">
+        <v>16</v>
+      </c>
+      <c r="E272" t="s">
+        <v>914</v>
+      </c>
+      <c r="F272" t="s">
+        <v>914</v>
+      </c>
+      <c r="G272" t="s">
+        <v>919</v>
+      </c>
+      <c r="H272" t="s">
+        <v>953</v>
+      </c>
+      <c r="I272" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="273" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
         <v>155</v>
       </c>
       <c r="B273" s="1">
         <v>26963</v>
       </c>
-    </row>
-    <row r="274" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C273" t="s">
+        <v>909</v>
+      </c>
+      <c r="D273">
+        <v>16</v>
+      </c>
+      <c r="E273" t="s">
+        <v>914</v>
+      </c>
+      <c r="F273" t="s">
+        <v>919</v>
+      </c>
+      <c r="G273" t="s">
+        <v>919</v>
+      </c>
+      <c r="H273" t="s">
+        <v>953</v>
+      </c>
+      <c r="I273" t="s">
+        <v>978</v>
+      </c>
+    </row>
+    <row r="274" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
         <v>156</v>
       </c>
       <c r="B274" s="1">
         <v>26692</v>
       </c>
-    </row>
-    <row r="275" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C274" t="s">
+        <v>909</v>
+      </c>
+      <c r="D274">
+        <v>16</v>
+      </c>
+      <c r="E274" t="s">
+        <v>914</v>
+      </c>
+      <c r="F274" t="s">
+        <v>919</v>
+      </c>
+      <c r="G274" t="s">
+        <v>919</v>
+      </c>
+      <c r="H274" t="s">
+        <v>953</v>
+      </c>
+      <c r="I274" t="s">
+        <v>979</v>
+      </c>
+    </row>
+    <row r="275" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
         <v>157</v>
       </c>
@@ -8373,7 +10393,7 @@
         <v>7602</v>
       </c>
     </row>
-    <row r="276" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
         <v>158</v>
       </c>
@@ -8381,7 +10401,7 @@
         <v>7733</v>
       </c>
     </row>
-    <row r="277" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
         <v>159</v>
       </c>
@@ -8389,7 +10409,7 @@
         <v>6960</v>
       </c>
     </row>
-    <row r="278" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
         <v>160</v>
       </c>
@@ -8397,7 +10417,7 @@
         <v>3255</v>
       </c>
     </row>
-    <row r="279" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
         <v>161</v>
       </c>
@@ -8405,7 +10425,7 @@
         <v>4509</v>
       </c>
     </row>
-    <row r="280" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
         <v>162</v>
       </c>
@@ -8413,7 +10433,7 @@
         <v>5545</v>
       </c>
     </row>
-    <row r="281" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
         <v>163</v>
       </c>
@@ -8421,7 +10441,7 @@
         <v>5098</v>
       </c>
     </row>
-    <row r="282" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
         <v>164</v>
       </c>
@@ -8429,7 +10449,7 @@
         <v>5546</v>
       </c>
     </row>
-    <row r="283" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
         <v>165</v>
       </c>
@@ -8437,7 +10457,7 @@
         <v>4286</v>
       </c>
     </row>
-    <row r="284" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
         <v>166</v>
       </c>
@@ -8445,7 +10465,7 @@
         <v>21256</v>
       </c>
     </row>
-    <row r="285" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
         <v>167</v>
       </c>
@@ -8453,7 +10473,7 @@
         <v>26579</v>
       </c>
     </row>
-    <row r="286" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
         <v>168</v>
       </c>
@@ -8461,7 +10481,7 @@
         <v>29383</v>
       </c>
     </row>
-    <row r="287" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
         <v>169</v>
       </c>
@@ -8469,7 +10489,7 @@
         <v>24919</v>
       </c>
     </row>
-    <row r="288" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
         <v>170</v>
       </c>

--- a/images/image manifest.xlsx
+++ b/images/image manifest.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\Github\CS-Graphics\images\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CB2C26B-5704-4263-A600-DB38692269BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13724119-A7DC-442C-B966-BA62A4A5FA30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="21480" windowHeight="11520" xr2:uid="{620D0F7A-D0D3-4EA0-8A4D-C0BB25CE06A6}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5927" uniqueCount="1028">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6781" uniqueCount="1073">
   <si>
     <t>Filename</t>
   </si>
@@ -3125,6 +3125,141 @@
   </si>
   <si>
     <t>S3P3.PLX</t>
+  </si>
+  <si>
+    <t>Healthy</t>
+  </si>
+  <si>
+    <t>Destroyed</t>
+  </si>
+  <si>
+    <t>Damaged</t>
+  </si>
+  <si>
+    <t>Cybrid Building 1 (TODO)</t>
+  </si>
+  <si>
+    <t>Cybrid Building 2 (TODO)</t>
+  </si>
+  <si>
+    <t>Cybrid Building 3 (TODO)</t>
+  </si>
+  <si>
+    <t>Healthy North</t>
+  </si>
+  <si>
+    <t>Healthy Northwest</t>
+  </si>
+  <si>
+    <t>Healthy Southwest</t>
+  </si>
+  <si>
+    <t>Healthy South</t>
+  </si>
+  <si>
+    <t>Healthy Southeast</t>
+  </si>
+  <si>
+    <t>Healthy Northeast</t>
+  </si>
+  <si>
+    <t>Damaged North</t>
+  </si>
+  <si>
+    <t>Damaged Northwest</t>
+  </si>
+  <si>
+    <t>Damaged Southwest</t>
+  </si>
+  <si>
+    <t>Damaged South</t>
+  </si>
+  <si>
+    <t>Damaged Southeast</t>
+  </si>
+  <si>
+    <t>Damaged Northeast</t>
+  </si>
+  <si>
+    <t>Healthy Soustwest</t>
+  </si>
+  <si>
+    <t>Cybrid Building 4 (TODO)</t>
+  </si>
+  <si>
+    <t>Cybrid Building 5 (TODO)</t>
+  </si>
+  <si>
+    <t>Unitech  Building 1 (TODO)</t>
+  </si>
+  <si>
+    <t>Unitech  Building 2 (TODO)</t>
+  </si>
+  <si>
+    <t>Unitech  Building 3 (TODO)</t>
+  </si>
+  <si>
+    <t>Unitech  Building 4 (TODO)</t>
+  </si>
+  <si>
+    <t>Unitech  Building 5 (TODO)</t>
+  </si>
+  <si>
+    <t>Unitech Carrier</t>
+  </si>
+  <si>
+    <t>North</t>
+  </si>
+  <si>
+    <t>Northwest</t>
+  </si>
+  <si>
+    <t>Southwest</t>
+  </si>
+  <si>
+    <t>South</t>
+  </si>
+  <si>
+    <t>Southeast</t>
+  </si>
+  <si>
+    <t>Duplicate?</t>
+  </si>
+  <si>
+    <t>Cybrid Building 6 (TODO)</t>
+  </si>
+  <si>
+    <t>Cybrid Building 7 (TODO)</t>
+  </si>
+  <si>
+    <t>Doodad</t>
+  </si>
+  <si>
+    <t>Tree directional</t>
+  </si>
+  <si>
+    <t>Bush directional</t>
+  </si>
+  <si>
+    <t>Yuca directional</t>
+  </si>
+  <si>
+    <t>Shurb directional</t>
+  </si>
+  <si>
+    <t>Palm tree directional</t>
+  </si>
+  <si>
+    <t>Crystal directional</t>
+  </si>
+  <si>
+    <t>Rock directional</t>
+  </si>
+  <si>
+    <t>Duplicate</t>
+  </si>
+  <si>
+    <t>Target Cursor</t>
   </si>
 </sst>
 </file>
@@ -3191,7 +3326,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="User" refreshedDate="46270.672301041668" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="899" xr:uid="{475285A3-2F52-4B23-B5E6-6919749F1CF6}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="User" refreshedDate="46270.770469212963" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="899" xr:uid="{475285A3-2F52-4B23-B5E6-6919749F1CF6}">
   <cacheSource type="worksheet">
     <worksheetSource name="Table1"/>
   </cacheSource>
@@ -3460,7 +3595,7 @@
     <n v="4"/>
     <s v="No"/>
     <s v="No"/>
-    <m/>
+    <s v="No"/>
     <s v="Face"/>
     <s v="TODO(Name) Death animation"/>
     <s v="I think the BGMMI##E.ANX format is an unused static representation of Bioderm health for the status bar. Even at the lowest settings, Bioderm faces are still animated."/>
@@ -3512,7 +3647,7 @@
     <n v="4"/>
     <s v="No"/>
     <s v="No"/>
-    <m/>
+    <s v="No"/>
     <s v="Face"/>
     <s v="TODO(Name) Death animation"/>
     <s v="I think the BGMMI##E.ANX format is an unused static representation of Bioderm health for the status bar. Even at the lowest settings, Bioderm faces are still animated."/>
@@ -3564,7 +3699,7 @@
     <n v="4"/>
     <s v="No"/>
     <s v="No"/>
-    <m/>
+    <s v="No"/>
     <s v="Face"/>
     <s v="TODO(Name) Death animation"/>
     <s v="I think the BGMMI##E.ANX format is an unused static representation of Bioderm health for the status bar. Even at the lowest settings, Bioderm faces are still animated."/>
@@ -3616,7 +3751,7 @@
     <n v="4"/>
     <s v="No"/>
     <s v="No"/>
-    <m/>
+    <s v="No"/>
     <s v="Face"/>
     <s v="TODO(Name) Death animation"/>
     <s v="I think the BGMMI##E.ANX format is an unused static representation of Bioderm health for the status bar. Even at the lowest settings, Bioderm faces are still animated."/>
@@ -3668,7 +3803,7 @@
     <n v="4"/>
     <s v="No"/>
     <s v="No"/>
-    <m/>
+    <s v="No"/>
     <s v="Face"/>
     <s v="TODO(Name) Death animation"/>
     <s v="I think the BGMMI##E.ANX format is an unused static representation of Bioderm health for the status bar. Even at the lowest settings, Bioderm faces are still animated."/>
@@ -3720,7 +3855,7 @@
     <n v="4"/>
     <s v="No"/>
     <s v="No"/>
-    <m/>
+    <s v="No"/>
     <s v="Face"/>
     <s v="TODO(Name) Death animation"/>
     <s v="I think the BGMMI##E.ANX format is an unused static representation of Bioderm health for the status bar. Even at the lowest settings, Bioderm faces are still animated."/>
@@ -3772,7 +3907,7 @@
     <n v="4"/>
     <s v="No"/>
     <s v="No"/>
-    <m/>
+    <s v="No"/>
     <s v="Face"/>
     <s v="TODO(Name) Death animation"/>
     <s v="I think the BGMMI##E.ANX format is an unused static representation of Bioderm health for the status bar. Even at the lowest settings, Bioderm faces are still animated."/>
@@ -3824,7 +3959,7 @@
     <n v="4"/>
     <s v="No"/>
     <s v="No"/>
-    <m/>
+    <s v="No"/>
     <s v="Face"/>
     <s v="TODO(Name) Death animation"/>
     <s v="I think the BGMMI##E.ANX format is an unused static representation of Bioderm health for the status bar. Even at the lowest settings, Bioderm faces are still animated."/>
@@ -3876,7 +4011,7 @@
     <n v="4"/>
     <s v="No"/>
     <s v="No"/>
-    <m/>
+    <s v="No"/>
     <s v="Face"/>
     <s v="TODO(Name) Death animation"/>
     <s v="I think the BGMMI##E.ANX format is an unused static representation of Bioderm health for the status bar. Even at the lowest settings, Bioderm faces are still animated."/>
@@ -3928,7 +4063,7 @@
     <n v="4"/>
     <s v="No"/>
     <s v="No"/>
-    <m/>
+    <s v="No"/>
     <s v="Face"/>
     <s v="TODO(Name) Death animation"/>
     <s v="I think the BGMMI##E.ANX format is an unused static representation of Bioderm health for the status bar. Even at the lowest settings, Bioderm faces are still animated."/>
@@ -3980,7 +4115,7 @@
     <n v="4"/>
     <s v="No"/>
     <s v="No"/>
-    <m/>
+    <s v="No"/>
     <s v="Face"/>
     <s v="TODO(Name) Death animation"/>
     <s v="I think the BGMMI##E.ANX format is an unused static representation of Bioderm health for the status bar. Even at the lowest settings, Bioderm faces are still animated."/>
@@ -4032,7 +4167,7 @@
     <n v="4"/>
     <s v="No"/>
     <s v="No"/>
-    <m/>
+    <s v="No"/>
     <s v="Face"/>
     <s v="TODO(Name) Death animation"/>
     <s v="I think the BGMMI##E.ANX format is an unused static representation of Bioderm health for the status bar. Even at the lowest settings, Bioderm faces are still animated."/>
@@ -4084,7 +4219,7 @@
     <n v="4"/>
     <s v="No"/>
     <s v="No"/>
-    <m/>
+    <s v="No"/>
     <s v="Face"/>
     <s v="TODO(Name) Death animation"/>
     <s v="I think the BGMMI##E.ANX format is an unused static representation of Bioderm health for the status bar. Even at the lowest settings, Bioderm faces are still animated."/>
@@ -4136,7 +4271,7 @@
     <n v="4"/>
     <s v="No"/>
     <s v="No"/>
-    <m/>
+    <s v="No"/>
     <s v="Face"/>
     <s v="TODO(Name) Death animation"/>
     <s v="I think the BGMMI##E.ANX format is an unused static representation of Bioderm health for the status bar. Even at the lowest settings, Bioderm faces are still animated."/>
@@ -4188,7 +4323,7 @@
     <n v="4"/>
     <s v="No"/>
     <s v="No"/>
-    <m/>
+    <s v="No"/>
     <s v="Face"/>
     <s v="TODO(Name) Death animation"/>
     <s v="I think the BGMMI##E.ANX format is an unused static representation of Bioderm health for the status bar. Even at the lowest settings, Bioderm faces are still animated."/>
@@ -4240,7 +4375,7 @@
     <n v="4"/>
     <s v="No"/>
     <s v="No"/>
-    <m/>
+    <s v="No"/>
     <s v="Face"/>
     <s v="TODO(Name) Death animation"/>
     <s v="I think the BGMMI##E.ANX format is an unused static representation of Bioderm health for the status bar. Even at the lowest settings, Bioderm faces are still animated."/>
@@ -4292,7 +4427,7 @@
     <n v="4"/>
     <s v="No"/>
     <s v="No"/>
-    <m/>
+    <s v="No"/>
     <s v="Face"/>
     <s v="TODO(Name) Death animation"/>
     <s v="I think the BGMMI##E.ANX format is an unused static representation of Bioderm health for the status bar. Even at the lowest settings, Bioderm faces are still animated."/>
@@ -4396,7 +4531,7 @@
     <n v="4"/>
     <s v="No"/>
     <s v="No"/>
-    <m/>
+    <s v="No"/>
     <s v="Face"/>
     <s v="TODO(Name) Death animation"/>
     <s v="I think the BGMMI##E.ANX format is an unused static representation of Bioderm health for the status bar. Even at the lowest settings, Bioderm faces are still animated."/>
@@ -4448,7 +4583,7 @@
     <n v="4"/>
     <s v="No"/>
     <s v="No"/>
-    <m/>
+    <s v="No"/>
     <s v="Face"/>
     <s v="TODO(Name) Death animation"/>
     <s v="I think the BGMMI##E.ANX format is an unused static representation of Bioderm health for the status bar. Even at the lowest settings, Bioderm faces are still animated."/>
@@ -4500,7 +4635,7 @@
     <n v="4"/>
     <s v="No"/>
     <s v="No"/>
-    <m/>
+    <s v="No"/>
     <s v="Face"/>
     <s v="TODO(Name) Death animation"/>
     <s v="I think the BGMMI##E.ANX format is an unused static representation of Bioderm health for the status bar. Even at the lowest settings, Bioderm faces are still animated."/>
@@ -4552,7 +4687,7 @@
     <n v="4"/>
     <s v="No"/>
     <s v="No"/>
-    <m/>
+    <s v="No"/>
     <s v="Face"/>
     <s v="TODO(Name) Death animation"/>
     <s v="I think the BGMMI##E.ANX format is an unused static representation of Bioderm health for the status bar. Even at the lowest settings, Bioderm faces are still animated."/>
@@ -4604,7 +4739,7 @@
     <n v="4"/>
     <s v="No"/>
     <s v="No"/>
-    <m/>
+    <s v="No"/>
     <s v="Face"/>
     <s v="TODO(Name) Death animation"/>
     <s v="I think the BGMMI##E.ANX format is an unused static representation of Bioderm health for the status bar. Even at the lowest settings, Bioderm faces are still animated."/>
@@ -4708,7 +4843,7 @@
     <n v="4"/>
     <s v="No"/>
     <s v="No"/>
-    <m/>
+    <s v="No"/>
     <s v="Face"/>
     <s v="TODO(Name) Death animation"/>
     <s v="I think the BGMMI##E.ANX format is an unused static representation of Bioderm health for the status bar. Even at the lowest settings, Bioderm faces are still animated."/>
@@ -4760,7 +4895,7 @@
     <n v="4"/>
     <s v="No"/>
     <s v="No"/>
-    <m/>
+    <s v="No"/>
     <s v="Face"/>
     <s v="TODO(Name) Death animation"/>
     <s v="I think the BGMMI##E.ANX format is an unused static representation of Bioderm health for the status bar. Even at the lowest settings, Bioderm faces are still animated."/>
@@ -4812,7 +4947,7 @@
     <n v="4"/>
     <s v="No"/>
     <s v="No"/>
-    <m/>
+    <s v="No"/>
     <s v="Face"/>
     <s v="TODO(Name) Death animation"/>
     <s v="I think the BGMMI##E.ANX format is an unused static representation of Bioderm health for the status bar. Even at the lowest settings, Bioderm faces are still animated."/>
@@ -4864,7 +4999,7 @@
     <n v="4"/>
     <s v="No"/>
     <s v="No"/>
-    <m/>
+    <s v="No"/>
     <s v="Face"/>
     <s v="TODO(Name) Death animation"/>
     <s v="I think the BGMMI##E.ANX format is an unused static representation of Bioderm health for the status bar. Even at the lowest settings, Bioderm faces are still animated."/>
@@ -12413,208 +12548,208 @@
     <s v="HRC018A0.ANX"/>
     <x v="1"/>
     <n v="19499"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <s v="S1P1.PLX"/>
+    <n v="1"/>
+    <s v="No"/>
+    <s v="Yes"/>
+    <s v="No"/>
+    <s v="Cybrid Building 1 (TODO)"/>
+    <s v="Healthy"/>
     <m/>
   </r>
   <r>
     <s v="HRC018B0.ANX"/>
     <x v="1"/>
     <n v="16037"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <s v="S1P1.PLX"/>
+    <n v="1"/>
+    <s v="No"/>
+    <s v="Yes"/>
+    <s v="No"/>
+    <s v="Cybrid Building 1 (TODO)"/>
+    <s v="Destroyed"/>
     <m/>
   </r>
   <r>
     <s v="HRC018C0.ANX"/>
     <x v="1"/>
     <n v="18631"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <s v="S1P1.PLX"/>
+    <n v="1"/>
+    <s v="No"/>
+    <s v="Yes"/>
+    <s v="No"/>
+    <s v="Cybrid Building 1 (TODO)"/>
+    <s v="Damaged"/>
     <m/>
   </r>
   <r>
     <s v="HRC019A0.ANX"/>
     <x v="1"/>
     <n v="13390"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <s v="S1P1.PLX"/>
+    <n v="1"/>
+    <s v="No"/>
+    <s v="Yes"/>
+    <s v="No"/>
+    <s v="Cybrid Building 2 (TODO)"/>
+    <s v="Healthy North"/>
     <m/>
   </r>
   <r>
     <s v="HRC019A1.ANX"/>
     <x v="1"/>
     <n v="13713"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <s v="S1P1.PLX"/>
+    <n v="1"/>
+    <s v="No"/>
+    <s v="Yes"/>
+    <s v="No"/>
+    <s v="Cybrid Building 2 (TODO)"/>
+    <s v="Healthy Northwest"/>
     <m/>
   </r>
   <r>
     <s v="HRC019A2.ANX"/>
     <x v="1"/>
     <n v="12794"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <s v="S1P1.PLX"/>
+    <n v="1"/>
+    <s v="No"/>
+    <s v="Yes"/>
+    <s v="No"/>
+    <s v="Cybrid Building 2 (TODO)"/>
+    <s v="Healthy Soustwest"/>
     <m/>
   </r>
   <r>
     <s v="HRC019A3.ANX"/>
     <x v="1"/>
     <n v="13111"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <s v="S1P1.PLX"/>
+    <n v="1"/>
+    <s v="No"/>
+    <s v="Yes"/>
+    <s v="No"/>
+    <s v="Cybrid Building 2 (TODO)"/>
+    <s v="Healthy South"/>
     <m/>
   </r>
   <r>
     <s v="HRC019A4.ANX"/>
     <x v="1"/>
     <n v="12883"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <s v="S1P1.PLX"/>
+    <n v="1"/>
+    <s v="No"/>
+    <s v="Yes"/>
+    <s v="No"/>
+    <s v="Cybrid Building 2 (TODO)"/>
+    <s v="Healthy Southeast"/>
     <m/>
   </r>
   <r>
     <s v="HRC019A5.ANX"/>
     <x v="1"/>
     <n v="12621"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <s v="S1P1.PLX"/>
+    <n v="1"/>
+    <s v="No"/>
+    <s v="Yes"/>
+    <s v="No"/>
+    <s v="Cybrid Building 2 (TODO)"/>
+    <s v="Healthy Northeast"/>
     <m/>
   </r>
   <r>
     <s v="HRC019B0.ANX"/>
     <x v="1"/>
     <n v="11001"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <s v="S1P1.PLX"/>
+    <n v="1"/>
+    <s v="No"/>
+    <s v="Yes"/>
+    <s v="No"/>
+    <s v="Cybrid Building 2 (TODO)"/>
+    <s v="Destroyed"/>
     <m/>
   </r>
   <r>
     <s v="HRC019C0.ANX"/>
     <x v="1"/>
     <n v="13492"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <s v="S1P1.PLX"/>
+    <n v="1"/>
+    <s v="No"/>
+    <s v="Yes"/>
+    <s v="No"/>
+    <s v="Cybrid Building 2 (TODO)"/>
+    <s v="Damaged North"/>
     <m/>
   </r>
   <r>
     <s v="HRC019C1.ANX"/>
     <x v="1"/>
     <n v="13935"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <s v="S1P1.PLX"/>
+    <n v="1"/>
+    <s v="No"/>
+    <s v="Yes"/>
+    <s v="No"/>
+    <s v="Cybrid Building 2 (TODO)"/>
+    <s v="Damaged Northwest"/>
     <m/>
   </r>
   <r>
     <s v="HRC019C2.ANX"/>
     <x v="1"/>
     <n v="13217"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <s v="S1P1.PLX"/>
+    <n v="1"/>
+    <s v="No"/>
+    <s v="Yes"/>
+    <s v="No"/>
+    <s v="Cybrid Building 2 (TODO)"/>
+    <s v="Damaged Southwest"/>
     <m/>
   </r>
   <r>
     <s v="HRC019C3.ANX"/>
     <x v="1"/>
     <n v="12920"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <s v="S1P1.PLX"/>
+    <n v="1"/>
+    <s v="No"/>
+    <s v="Yes"/>
+    <s v="No"/>
+    <s v="Cybrid Building 2 (TODO)"/>
+    <s v="Damaged South"/>
     <m/>
   </r>
   <r>
     <s v="HRC019C4.ANX"/>
     <x v="1"/>
     <n v="13158"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <s v="S1P1.PLX"/>
+    <n v="1"/>
+    <s v="No"/>
+    <s v="Yes"/>
+    <s v="No"/>
+    <s v="Cybrid Building 2 (TODO)"/>
+    <s v="Damaged Southeast"/>
     <m/>
   </r>
   <r>
     <s v="HRC019C5.ANX"/>
     <x v="1"/>
     <n v="12768"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <s v="S1P1.PLX"/>
+    <n v="1"/>
+    <s v="No"/>
+    <s v="Yes"/>
+    <s v="No"/>
+    <s v="Cybrid Building 2 (TODO)"/>
+    <s v="Damaged Northeast"/>
     <m/>
   </r>
   <r>
@@ -12660,208 +12795,208 @@
     <s v="HRC021A0.ANX"/>
     <x v="1"/>
     <n v="15134"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <s v="S1P1.PLX"/>
+    <n v="1"/>
+    <s v="No"/>
+    <s v="Yes"/>
+    <s v="No"/>
+    <s v="Cybrid Building 3 (TODO)"/>
+    <s v="Healthy North"/>
     <m/>
   </r>
   <r>
     <s v="HRC021A1.ANX"/>
     <x v="1"/>
     <n v="15737"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <s v="S1P1.PLX"/>
+    <n v="1"/>
+    <s v="No"/>
+    <s v="Yes"/>
+    <s v="No"/>
+    <s v="Cybrid Building 3 (TODO)"/>
+    <s v="Healthy Northwest"/>
     <m/>
   </r>
   <r>
     <s v="HRC021A2.ANX"/>
     <x v="1"/>
     <n v="15119"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <s v="S1P1.PLX"/>
+    <n v="1"/>
+    <s v="No"/>
+    <s v="Yes"/>
+    <s v="No"/>
+    <s v="Cybrid Building 3 (TODO)"/>
+    <s v="Healthy Southwest"/>
     <m/>
   </r>
   <r>
     <s v="HRC021A3.ANX"/>
     <x v="1"/>
     <n v="15321"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <s v="S1P1.PLX"/>
+    <n v="1"/>
+    <s v="No"/>
+    <s v="Yes"/>
+    <s v="No"/>
+    <s v="Cybrid Building 3 (TODO)"/>
+    <s v="Healthy South"/>
     <m/>
   </r>
   <r>
     <s v="HRC021A4.ANX"/>
     <x v="1"/>
     <n v="16083"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <s v="S1P1.PLX"/>
+    <n v="1"/>
+    <s v="No"/>
+    <s v="Yes"/>
+    <s v="No"/>
+    <s v="Cybrid Building 3 (TODO)"/>
+    <s v="Healthy Southeast"/>
     <m/>
   </r>
   <r>
     <s v="HRC021A5.ANX"/>
     <x v="1"/>
     <n v="15327"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <s v="S1P1.PLX"/>
+    <n v="1"/>
+    <s v="No"/>
+    <s v="Yes"/>
+    <s v="No"/>
+    <s v="Cybrid Building 3 (TODO)"/>
+    <s v="Healthy Northeast"/>
     <m/>
   </r>
   <r>
     <s v="HRC021B0.ANX"/>
     <x v="1"/>
     <n v="15653"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <s v="S1P1.PLX"/>
+    <n v="1"/>
+    <s v="No"/>
+    <s v="Yes"/>
+    <s v="No"/>
+    <s v="Cybrid Building 3 (TODO)"/>
+    <s v="Destroyed"/>
     <m/>
   </r>
   <r>
     <s v="HRC021C0.ANX"/>
     <x v="1"/>
     <n v="16710"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <s v="S1P1.PLX"/>
+    <n v="1"/>
+    <s v="No"/>
+    <s v="Yes"/>
+    <s v="No"/>
+    <s v="Cybrid Building 4 (TODO)"/>
+    <s v="Healthy North"/>
     <m/>
   </r>
   <r>
     <s v="HRC021C1.ANX"/>
     <x v="1"/>
     <n v="16474"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <s v="S1P1.PLX"/>
+    <n v="1"/>
+    <s v="No"/>
+    <s v="Yes"/>
+    <s v="No"/>
+    <s v="Cybrid Building 4 (TODO)"/>
+    <s v="Healthy Northwest"/>
     <m/>
   </r>
   <r>
     <s v="HRC021C2.ANX"/>
     <x v="1"/>
     <n v="17446"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <s v="S1P1.PLX"/>
+    <n v="1"/>
+    <s v="No"/>
+    <s v="Yes"/>
+    <s v="No"/>
+    <s v="Cybrid Building 4 (TODO)"/>
+    <s v="Healthy Southwest"/>
     <m/>
   </r>
   <r>
     <s v="HRC021C3.ANX"/>
     <x v="1"/>
     <n v="17213"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <s v="S1P1.PLX"/>
+    <n v="1"/>
+    <s v="No"/>
+    <s v="Yes"/>
+    <s v="No"/>
+    <s v="Cybrid Building 4 (TODO)"/>
+    <s v="Healthy South"/>
     <m/>
   </r>
   <r>
     <s v="HRC021C4.ANX"/>
     <x v="1"/>
     <n v="16844"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <s v="S1P1.PLX"/>
+    <n v="1"/>
+    <s v="No"/>
+    <s v="Yes"/>
+    <s v="No"/>
+    <s v="Cybrid Building 4 (TODO)"/>
+    <s v="Healthy Southeast"/>
     <m/>
   </r>
   <r>
     <s v="HRC021C5.ANX"/>
     <x v="1"/>
     <n v="16959"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <s v="S1P1.PLX"/>
+    <n v="1"/>
+    <s v="No"/>
+    <s v="Yes"/>
+    <s v="No"/>
+    <s v="Cybrid Building 4 (TODO)"/>
+    <s v="Healthy Northeast"/>
     <m/>
   </r>
   <r>
     <s v="HRC022A0.ANX"/>
     <x v="1"/>
     <n v="16966"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <s v="S1P1.PLX"/>
+    <n v="1"/>
+    <s v="No"/>
+    <s v="Yes"/>
+    <s v="No"/>
+    <s v="Cybrid Building 5 (TODO)"/>
+    <s v="Healthy"/>
     <m/>
   </r>
   <r>
     <s v="HRC022B0.ANX"/>
     <x v="1"/>
     <n v="16402"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <s v="S1P1.PLX"/>
+    <n v="1"/>
+    <s v="No"/>
+    <s v="Yes"/>
+    <s v="No"/>
+    <s v="Cybrid Building 5 (TODO)"/>
+    <s v="Destroyed"/>
     <m/>
   </r>
   <r>
     <s v="HRC022C0.ANX"/>
     <x v="1"/>
     <n v="16941"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <s v="S1P1.PLX"/>
+    <n v="1"/>
+    <s v="No"/>
+    <s v="Yes"/>
+    <s v="No"/>
+    <s v="Cybrid Building 5 (TODO)"/>
+    <s v="Damaged"/>
     <m/>
   </r>
   <r>
@@ -13180,793 +13315,793 @@
     <s v="HRC026A0.ANX"/>
     <x v="1"/>
     <n v="6217"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <s v="S1P1.PLX"/>
+    <n v="1"/>
+    <s v="No"/>
+    <s v="Yes"/>
+    <s v="No"/>
+    <s v="Unitech  Building 1 (TODO)"/>
+    <s v="Healthy North"/>
     <m/>
   </r>
   <r>
     <s v="HRC026A1.ANX"/>
     <x v="1"/>
     <n v="6367"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <s v="S1P1.PLX"/>
+    <n v="1"/>
+    <s v="No"/>
+    <s v="Yes"/>
+    <s v="No"/>
+    <s v="Unitech  Building 1 (TODO)"/>
+    <s v="Healthy Northwest"/>
     <m/>
   </r>
   <r>
     <s v="HRC026A2.ANX"/>
     <x v="1"/>
     <n v="6287"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <s v="S1P1.PLX"/>
+    <n v="1"/>
+    <s v="No"/>
+    <s v="Yes"/>
+    <s v="No"/>
+    <s v="Unitech  Building 1 (TODO)"/>
+    <s v="Healthy Southwest"/>
     <m/>
   </r>
   <r>
     <s v="HRC026A3.ANX"/>
     <x v="1"/>
     <n v="5958"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <s v="S1P1.PLX"/>
+    <n v="1"/>
+    <s v="No"/>
+    <s v="Yes"/>
+    <s v="No"/>
+    <s v="Unitech  Building 1 (TODO)"/>
+    <s v="Healthy South"/>
     <m/>
   </r>
   <r>
     <s v="HRC026A4.ANX"/>
     <x v="1"/>
     <n v="6348"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <s v="S1P1.PLX"/>
+    <n v="1"/>
+    <s v="No"/>
+    <s v="Yes"/>
+    <s v="No"/>
+    <s v="Unitech  Building 1 (TODO)"/>
+    <s v="Healthy Southeast"/>
     <m/>
   </r>
   <r>
     <s v="HRC026A5.ANX"/>
     <x v="1"/>
     <n v="6636"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <s v="S1P1.PLX"/>
+    <n v="1"/>
+    <s v="No"/>
+    <s v="Yes"/>
+    <s v="No"/>
+    <s v="Unitech  Building 1 (TODO)"/>
+    <s v="Healthy Northeast"/>
     <m/>
   </r>
   <r>
     <s v="HRC026B0.ANX"/>
     <x v="1"/>
     <n v="7606"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <s v="S1P1.PLX"/>
+    <n v="1"/>
+    <s v="No"/>
+    <s v="Yes"/>
+    <s v="No"/>
+    <s v="Unitech  Building 1 (TODO)"/>
+    <s v="Destroyed"/>
     <m/>
   </r>
   <r>
     <s v="HRC026C0.ANX"/>
     <x v="1"/>
     <n v="6075"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <s v="S1P1.PLX"/>
+    <n v="1"/>
+    <s v="No"/>
+    <s v="Yes"/>
+    <s v="No"/>
+    <s v="Unitech  Building 1 (TODO)"/>
+    <s v="Damaged North"/>
     <m/>
   </r>
   <r>
     <s v="HRC026C1.ANX"/>
     <x v="1"/>
     <n v="6226"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <s v="S1P1.PLX"/>
+    <n v="1"/>
+    <s v="No"/>
+    <s v="Yes"/>
+    <s v="No"/>
+    <s v="Unitech  Building 1 (TODO)"/>
+    <s v="Damaged Northwest"/>
     <m/>
   </r>
   <r>
     <s v="HRC026C2.ANX"/>
     <x v="1"/>
     <n v="6188"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <s v="S1P1.PLX"/>
+    <n v="1"/>
+    <s v="No"/>
+    <s v="Yes"/>
+    <s v="No"/>
+    <s v="Unitech  Building 1 (TODO)"/>
+    <s v="Damaged Southwest"/>
     <m/>
   </r>
   <r>
     <s v="HRC026C3.ANX"/>
     <x v="1"/>
     <n v="5819"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <s v="S1P1.PLX"/>
+    <n v="1"/>
+    <s v="No"/>
+    <s v="Yes"/>
+    <s v="No"/>
+    <s v="Unitech  Building 1 (TODO)"/>
+    <s v="Damaged South"/>
     <m/>
   </r>
   <r>
     <s v="HRC026C4.ANX"/>
     <x v="1"/>
     <n v="6030"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <s v="S1P1.PLX"/>
+    <n v="1"/>
+    <s v="No"/>
+    <s v="Yes"/>
+    <s v="No"/>
+    <s v="Unitech  Building 1 (TODO)"/>
+    <s v="Damaged Southeast"/>
     <m/>
   </r>
   <r>
     <s v="HRC026C5.ANX"/>
     <x v="1"/>
     <n v="6091"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <s v="S1P1.PLX"/>
+    <n v="1"/>
+    <s v="No"/>
+    <s v="Yes"/>
+    <s v="No"/>
+    <s v="Unitech  Building 1 (TODO)"/>
+    <s v="Damaged Northeast"/>
     <m/>
   </r>
   <r>
     <s v="HRC027A0.ANX"/>
     <x v="1"/>
     <n v="14351"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <s v="S1P1.PLX"/>
+    <n v="1"/>
+    <s v="No"/>
+    <s v="Yes"/>
+    <s v="No"/>
+    <s v="Unitech  Building 2 (TODO)"/>
+    <s v="Healthy"/>
     <m/>
   </r>
   <r>
     <s v="HRC027B0.ANX"/>
     <x v="1"/>
     <n v="12986"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <s v="S1P1.PLX"/>
+    <n v="1"/>
+    <s v="No"/>
+    <s v="Yes"/>
+    <s v="No"/>
+    <s v="Unitech  Building 2 (TODO)"/>
+    <s v="Destroyed"/>
     <m/>
   </r>
   <r>
     <s v="HRC027C0.ANX"/>
     <x v="1"/>
     <n v="13420"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <s v="S1P1.PLX"/>
+    <n v="1"/>
+    <s v="No"/>
+    <s v="Yes"/>
+    <s v="No"/>
+    <s v="Unitech  Building 2 (TODO)"/>
+    <s v="Damaged"/>
     <m/>
   </r>
   <r>
     <s v="HRC028A0.ANX"/>
     <x v="1"/>
     <n v="11440"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <s v="S1P1.PLX"/>
+    <n v="1"/>
+    <s v="No"/>
+    <s v="Yes"/>
+    <s v="No"/>
+    <s v="Unitech  Building 3 (TODO)"/>
+    <s v="Healthy North"/>
     <m/>
   </r>
   <r>
     <s v="HRC028A1.ANX"/>
     <x v="1"/>
     <n v="11579"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <s v="S1P1.PLX"/>
+    <n v="1"/>
+    <s v="No"/>
+    <s v="Yes"/>
+    <s v="No"/>
+    <s v="Unitech  Building 3 (TODO)"/>
+    <s v="Healthy Northwest"/>
     <m/>
   </r>
   <r>
     <s v="HRC028A2.ANX"/>
     <x v="1"/>
     <n v="11639"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <s v="S1P1.PLX"/>
+    <n v="1"/>
+    <s v="No"/>
+    <s v="Yes"/>
+    <s v="No"/>
+    <s v="Unitech  Building 3 (TODO)"/>
+    <s v="Healthy Southwest"/>
     <m/>
   </r>
   <r>
     <s v="HRC028A3.ANX"/>
     <x v="1"/>
     <n v="11291"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <s v="S1P1.PLX"/>
+    <n v="1"/>
+    <s v="No"/>
+    <s v="Yes"/>
+    <s v="No"/>
+    <s v="Unitech  Building 3 (TODO)"/>
+    <s v="Healthy South"/>
     <m/>
   </r>
   <r>
     <s v="HRC028A4.ANX"/>
     <x v="1"/>
     <n v="11534"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <s v="S1P1.PLX"/>
+    <n v="1"/>
+    <s v="No"/>
+    <s v="Yes"/>
+    <s v="No"/>
+    <s v="Unitech  Building 3 (TODO)"/>
+    <s v="Healthy Southeast"/>
     <m/>
   </r>
   <r>
     <s v="HRC028A5.ANX"/>
     <x v="1"/>
     <n v="11459"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <s v="S1P1.PLX"/>
+    <n v="1"/>
+    <s v="No"/>
+    <s v="Yes"/>
+    <s v="No"/>
+    <s v="Unitech  Building 3 (TODO)"/>
+    <s v="Healthy Northeast"/>
     <m/>
   </r>
   <r>
     <s v="HRC028B0.ANX"/>
     <x v="1"/>
     <n v="8305"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <s v="S1P1.PLX"/>
+    <n v="1"/>
+    <s v="No"/>
+    <s v="Yes"/>
+    <s v="No"/>
+    <s v="Unitech  Building 3 (TODO)"/>
+    <s v="Destroyed"/>
     <m/>
   </r>
   <r>
     <s v="HRC028C0.ANX"/>
     <x v="1"/>
     <n v="12403"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <s v="S1P1.PLX"/>
+    <n v="1"/>
+    <s v="No"/>
+    <s v="Yes"/>
+    <s v="No"/>
+    <s v="Unitech  Building 3 (TODO)"/>
+    <s v="Damaged North"/>
     <m/>
   </r>
   <r>
     <s v="HRC028C1.ANX"/>
     <x v="1"/>
     <n v="12582"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <s v="S1P1.PLX"/>
+    <n v="1"/>
+    <s v="No"/>
+    <s v="Yes"/>
+    <s v="No"/>
+    <s v="Unitech  Building 3 (TODO)"/>
+    <s v="Damaged Northwest"/>
     <m/>
   </r>
   <r>
     <s v="HRC028C2.ANX"/>
     <x v="1"/>
     <n v="12436"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <s v="S1P1.PLX"/>
+    <n v="1"/>
+    <s v="No"/>
+    <s v="Yes"/>
+    <s v="No"/>
+    <s v="Unitech  Building 3 (TODO)"/>
+    <s v="Damaged Southwest"/>
     <m/>
   </r>
   <r>
     <s v="HRC028C3.ANX"/>
     <x v="1"/>
     <n v="12478"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <s v="S1P1.PLX"/>
+    <n v="1"/>
+    <s v="No"/>
+    <s v="Yes"/>
+    <s v="No"/>
+    <s v="Unitech  Building 3 (TODO)"/>
+    <s v="Damaged South"/>
     <m/>
   </r>
   <r>
     <s v="HRC028C4.ANX"/>
     <x v="1"/>
     <n v="12694"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <s v="S1P1.PLX"/>
+    <n v="1"/>
+    <s v="No"/>
+    <s v="Yes"/>
+    <s v="No"/>
+    <s v="Unitech  Building 3 (TODO)"/>
+    <s v="Damaged Southeast"/>
     <m/>
   </r>
   <r>
     <s v="HRC028C5.ANX"/>
     <x v="1"/>
     <n v="12693"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <s v="S1P1.PLX"/>
+    <n v="1"/>
+    <s v="No"/>
+    <s v="Yes"/>
+    <s v="No"/>
+    <s v="Unitech  Building 3 (TODO)"/>
+    <s v="Damaged Northeast"/>
     <m/>
   </r>
   <r>
     <s v="HRC029A0.ANX"/>
     <x v="1"/>
     <n v="7711"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <s v="S1P1.PLX"/>
+    <n v="1"/>
+    <s v="No"/>
+    <s v="Yes"/>
+    <s v="No"/>
+    <s v="Unitech  Building 4 (TODO)"/>
+    <s v="Healthy North"/>
     <m/>
   </r>
   <r>
     <s v="HRC029A1.ANX"/>
     <x v="1"/>
     <n v="7471"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <s v="S1P1.PLX"/>
+    <n v="1"/>
+    <s v="No"/>
+    <s v="Yes"/>
+    <s v="No"/>
+    <s v="Unitech  Building 4 (TODO)"/>
+    <s v="Healthy Northwest"/>
     <m/>
   </r>
   <r>
     <s v="HRC029A2.ANX"/>
     <x v="1"/>
     <n v="7727"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <s v="S1P1.PLX"/>
+    <n v="1"/>
+    <s v="No"/>
+    <s v="Yes"/>
+    <s v="No"/>
+    <s v="Unitech  Building 4 (TODO)"/>
+    <s v="Healthy Southwest"/>
     <m/>
   </r>
   <r>
     <s v="HRC029A3.ANX"/>
     <x v="1"/>
     <n v="7789"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <s v="S1P1.PLX"/>
+    <n v="1"/>
+    <s v="No"/>
+    <s v="Yes"/>
+    <s v="No"/>
+    <s v="Unitech  Building 4 (TODO)"/>
+    <s v="Healthy South"/>
     <m/>
   </r>
   <r>
     <s v="HRC029A4.ANX"/>
     <x v="1"/>
     <n v="7686"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <s v="S1P1.PLX"/>
+    <n v="1"/>
+    <s v="No"/>
+    <s v="Yes"/>
+    <s v="No"/>
+    <s v="Unitech  Building 4 (TODO)"/>
+    <s v="Healthy Southeast"/>
     <m/>
   </r>
   <r>
     <s v="HRC029A5.ANX"/>
     <x v="1"/>
     <n v="7420"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <s v="S1P1.PLX"/>
+    <n v="1"/>
+    <s v="No"/>
+    <s v="Yes"/>
+    <s v="No"/>
+    <s v="Unitech  Building 4 (TODO)"/>
+    <s v="Healthy Northeast"/>
     <m/>
   </r>
   <r>
     <s v="HRC029B0.ANX"/>
     <x v="1"/>
     <n v="5878"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <s v="S1P1.PLX"/>
+    <n v="1"/>
+    <s v="No"/>
+    <s v="Yes"/>
+    <s v="No"/>
+    <s v="Unitech  Building 4 (TODO)"/>
+    <s v="Destroyed"/>
     <m/>
   </r>
   <r>
     <s v="HRC029C0.ANX"/>
     <x v="1"/>
     <n v="6341"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <s v="S1P1.PLX"/>
+    <n v="1"/>
+    <s v="No"/>
+    <s v="Yes"/>
+    <s v="No"/>
+    <s v="Unitech  Building 4 (TODO)"/>
+    <s v="Damaged North"/>
     <m/>
   </r>
   <r>
     <s v="HRC029C1.ANX"/>
     <x v="1"/>
     <n v="6444"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <s v="S1P1.PLX"/>
+    <n v="1"/>
+    <s v="No"/>
+    <s v="Yes"/>
+    <s v="No"/>
+    <s v="Unitech  Building 4 (TODO)"/>
+    <s v="Damaged Northwest"/>
     <m/>
   </r>
   <r>
     <s v="HRC029C2.ANX"/>
     <x v="1"/>
     <n v="7251"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <s v="S1P1.PLX"/>
+    <n v="1"/>
+    <s v="No"/>
+    <s v="Yes"/>
+    <s v="No"/>
+    <s v="Unitech  Building 4 (TODO)"/>
+    <s v="Damaged Southwest"/>
     <m/>
   </r>
   <r>
     <s v="HRC029C3.ANX"/>
     <x v="1"/>
     <n v="7552"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <s v="S1P1.PLX"/>
+    <n v="1"/>
+    <s v="No"/>
+    <s v="Yes"/>
+    <s v="No"/>
+    <s v="Unitech  Building 4 (TODO)"/>
+    <s v="Damaged South"/>
     <m/>
   </r>
   <r>
     <s v="HRC029C4.ANX"/>
     <x v="1"/>
     <n v="7716"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <s v="S1P1.PLX"/>
+    <n v="1"/>
+    <s v="No"/>
+    <s v="Yes"/>
+    <s v="No"/>
+    <s v="Unitech  Building 4 (TODO)"/>
+    <s v="Damaged Southeast"/>
     <m/>
   </r>
   <r>
     <s v="HRC029C5.ANX"/>
     <x v="1"/>
     <n v="6206"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <s v="S1P1.PLX"/>
+    <n v="1"/>
+    <s v="No"/>
+    <s v="Yes"/>
+    <s v="No"/>
+    <s v="Unitech  Building 4 (TODO)"/>
+    <s v="Damaged Northeast"/>
     <m/>
   </r>
   <r>
     <s v="HRC030A0.ANX"/>
     <x v="1"/>
     <n v="7763"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <s v="S1P1.PLX"/>
+    <n v="1"/>
+    <s v="No"/>
+    <s v="Yes"/>
+    <s v="No"/>
+    <s v="Unitech  Building 5 (TODO)"/>
+    <s v="Healthy North"/>
     <m/>
   </r>
   <r>
     <s v="HRC030A1.ANX"/>
     <x v="1"/>
     <n v="7551"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <s v="S1P1.PLX"/>
+    <n v="1"/>
+    <s v="No"/>
+    <s v="Yes"/>
+    <s v="No"/>
+    <s v="Unitech  Building 5 (TODO)"/>
+    <s v="Healthy Northwest"/>
     <m/>
   </r>
   <r>
     <s v="HRC030A2.ANX"/>
     <x v="1"/>
     <n v="7976"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <s v="S1P1.PLX"/>
+    <n v="1"/>
+    <s v="No"/>
+    <s v="Yes"/>
+    <s v="No"/>
+    <s v="Unitech  Building 5 (TODO)"/>
+    <s v="Healthy Southwest"/>
     <m/>
   </r>
   <r>
     <s v="HRC030A3.ANX"/>
     <x v="1"/>
     <n v="7207"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <s v="S1P1.PLX"/>
+    <n v="1"/>
+    <s v="No"/>
+    <s v="Yes"/>
+    <s v="No"/>
+    <s v="Unitech  Building 5 (TODO)"/>
+    <s v="Healthy South"/>
     <m/>
   </r>
   <r>
     <s v="HRC030A4.ANX"/>
     <x v="1"/>
     <n v="8001"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <s v="S1P1.PLX"/>
+    <n v="1"/>
+    <s v="No"/>
+    <s v="Yes"/>
+    <s v="No"/>
+    <s v="Unitech  Building 5 (TODO)"/>
+    <s v="Healthy Southeast"/>
     <m/>
   </r>
   <r>
     <s v="HRC030A5.ANX"/>
     <x v="1"/>
     <n v="7795"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <s v="S1P1.PLX"/>
+    <n v="1"/>
+    <s v="No"/>
+    <s v="Yes"/>
+    <s v="No"/>
+    <s v="Unitech  Building 5 (TODO)"/>
+    <s v="Healthy Northeast"/>
     <m/>
   </r>
   <r>
     <s v="HRC030B0.ANX"/>
     <x v="1"/>
     <n v="8039"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <s v="S1P1.PLX"/>
+    <n v="1"/>
+    <s v="No"/>
+    <s v="Yes"/>
+    <s v="No"/>
+    <s v="Unitech  Building 5 (TODO)"/>
+    <s v="Destroyed"/>
     <m/>
   </r>
   <r>
     <s v="HRC030C0.ANX"/>
     <x v="1"/>
     <n v="8026"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <s v="S1P1.PLX"/>
+    <n v="1"/>
+    <s v="No"/>
+    <s v="Yes"/>
+    <s v="No"/>
+    <s v="Unitech  Building 5 (TODO)"/>
+    <s v="Damaged North"/>
     <m/>
   </r>
   <r>
     <s v="HRC030C1.ANX"/>
     <x v="1"/>
     <n v="7930"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <s v="S1P1.PLX"/>
+    <n v="1"/>
+    <s v="No"/>
+    <s v="Yes"/>
+    <s v="No"/>
+    <s v="Unitech  Building 5 (TODO)"/>
+    <s v="Damaged Northwest"/>
     <m/>
   </r>
   <r>
     <s v="HRC030C2.ANX"/>
     <x v="1"/>
     <n v="7605"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <s v="S1P1.PLX"/>
+    <n v="1"/>
+    <s v="No"/>
+    <s v="Yes"/>
+    <s v="No"/>
+    <s v="Unitech  Building 5 (TODO)"/>
+    <s v="Damaged Southwest"/>
     <m/>
   </r>
   <r>
     <s v="HRC030C3.ANX"/>
     <x v="1"/>
     <n v="6051"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <s v="S1P1.PLX"/>
+    <n v="1"/>
+    <s v="No"/>
+    <s v="Yes"/>
+    <s v="No"/>
+    <s v="Unitech  Building 5 (TODO)"/>
+    <s v="Damaged South"/>
     <m/>
   </r>
   <r>
     <s v="HRC030C4.ANX"/>
     <x v="1"/>
     <n v="7685"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <s v="S1P1.PLX"/>
+    <n v="1"/>
+    <s v="No"/>
+    <s v="Yes"/>
+    <s v="No"/>
+    <s v="Unitech  Building 5 (TODO)"/>
+    <s v="Damaged Southeast"/>
     <m/>
   </r>
   <r>
     <s v="HRC030C5.ANX"/>
     <x v="1"/>
     <n v="8278"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <s v="S1P1.PLX"/>
+    <n v="1"/>
+    <s v="No"/>
+    <s v="Yes"/>
+    <s v="No"/>
+    <s v="Unitech  Building 5 (TODO)"/>
+    <s v="Damaged Northeast"/>
     <m/>
   </r>
   <r>
     <s v="HRC031A0.ANX"/>
     <x v="1"/>
     <n v="7714"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <s v="S1P1.PLX"/>
+    <n v="1"/>
+    <s v="No"/>
+    <s v="Yes"/>
+    <s v="No"/>
+    <s v="Unitech Carrier"/>
+    <s v="North"/>
     <m/>
   </r>
   <r>
     <s v="HRC031A1.ANX"/>
     <x v="1"/>
     <n v="7868"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <s v="S1P1.PLX"/>
+    <n v="1"/>
+    <s v="No"/>
+    <s v="Yes"/>
+    <s v="No"/>
+    <s v="Unitech Carrier"/>
+    <s v="Northwest"/>
     <m/>
   </r>
   <r>
     <s v="HRC031A2.ANX"/>
     <x v="1"/>
     <n v="8581"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <s v="S1P1.PLX"/>
+    <n v="1"/>
+    <s v="No"/>
+    <s v="Yes"/>
+    <s v="No"/>
+    <s v="Unitech Carrier"/>
+    <s v="Southwest"/>
     <m/>
   </r>
   <r>
     <s v="HRC031A3.ANX"/>
     <x v="1"/>
     <n v="8463"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <s v="S1P1.PLX"/>
+    <n v="1"/>
+    <s v="No"/>
+    <s v="Yes"/>
+    <s v="No"/>
+    <s v="Unitech Carrier"/>
+    <s v="South"/>
     <m/>
   </r>
   <r>
     <s v="HRC031A4.ANX"/>
     <x v="1"/>
     <n v="8138"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <s v="S1P1.PLX"/>
+    <n v="1"/>
+    <s v="No"/>
+    <s v="Yes"/>
+    <s v="No"/>
+    <s v="Unitech Carrier"/>
+    <s v="Southeast"/>
     <m/>
   </r>
   <r>
     <s v="HRC031A5.ANX"/>
     <x v="1"/>
     <n v="7772"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <s v="S1P1.PLX"/>
+    <n v="1"/>
+    <s v="No"/>
+    <s v="Yes"/>
+    <s v="No"/>
+    <s v="Unitech Carrier"/>
+    <s v="Southwest"/>
     <m/>
   </r>
   <r>
@@ -13986,546 +14121,546 @@
     <s v="HRC031C0.ANX"/>
     <x v="1"/>
     <n v="7930"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <s v="S1P1.PLX"/>
+    <n v="1"/>
+    <s v="No"/>
+    <s v="Yes"/>
+    <s v="No"/>
+    <s v="Unitech Carrier"/>
+    <s v="North"/>
+    <s v="Duplicate?"/>
   </r>
   <r>
     <s v="HRC031C1.ANX"/>
     <x v="1"/>
     <n v="8338"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <s v="S1P1.PLX"/>
+    <n v="1"/>
+    <s v="No"/>
+    <s v="Yes"/>
+    <s v="No"/>
+    <s v="Unitech Carrier"/>
+    <s v="Northwest"/>
+    <s v="Duplicate?"/>
   </r>
   <r>
     <s v="HRC031C2.ANX"/>
     <x v="1"/>
     <n v="8929"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <s v="S1P1.PLX"/>
+    <n v="1"/>
+    <s v="No"/>
+    <s v="Yes"/>
+    <s v="No"/>
+    <s v="Unitech Carrier"/>
+    <s v="Southwest"/>
+    <s v="Duplicate?"/>
   </r>
   <r>
     <s v="HRC031C3.ANX"/>
     <x v="1"/>
     <n v="8246"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <s v="S1P1.PLX"/>
+    <n v="1"/>
+    <s v="No"/>
+    <s v="Yes"/>
+    <s v="No"/>
+    <s v="Unitech Carrier"/>
+    <s v="South"/>
+    <s v="Duplicate?"/>
   </r>
   <r>
     <s v="HRC031C4.ANX"/>
     <x v="1"/>
     <n v="8676"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <s v="S1P1.PLX"/>
+    <n v="1"/>
+    <s v="No"/>
+    <s v="Yes"/>
+    <s v="No"/>
+    <s v="Unitech Carrier"/>
+    <s v="Southeast"/>
+    <s v="Duplicate?"/>
   </r>
   <r>
     <s v="HRC031C5.ANX"/>
     <x v="1"/>
     <n v="8108"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <s v="S1P1.PLX"/>
+    <n v="1"/>
+    <s v="No"/>
+    <s v="Yes"/>
+    <s v="No"/>
+    <s v="Unitech Carrier"/>
+    <s v="Southwest"/>
+    <s v="Duplicate?"/>
   </r>
   <r>
     <s v="HRC032A0.ANX"/>
     <x v="1"/>
     <n v="12790"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <s v="S1P1.PLX"/>
+    <n v="1"/>
+    <s v="No"/>
+    <s v="Yes"/>
+    <s v="No"/>
+    <s v="Cybrid Building 6 (TODO)"/>
+    <s v="Healthy North"/>
     <m/>
   </r>
   <r>
     <s v="HRC032A1.ANX"/>
     <x v="1"/>
     <n v="12606"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <s v="S1P1.PLX"/>
+    <n v="1"/>
+    <s v="No"/>
+    <s v="Yes"/>
+    <s v="No"/>
+    <s v="Cybrid Building 6 (TODO)"/>
+    <s v="Healthy Northwest"/>
     <m/>
   </r>
   <r>
     <s v="HRC032A2.ANX"/>
     <x v="1"/>
     <n v="12526"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <s v="S1P1.PLX"/>
+    <n v="1"/>
+    <s v="No"/>
+    <s v="Yes"/>
+    <s v="No"/>
+    <s v="Cybrid Building 6 (TODO)"/>
+    <s v="Healthy Southwest"/>
     <m/>
   </r>
   <r>
     <s v="HRC032A3.ANX"/>
     <x v="1"/>
     <n v="12797"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <s v="S1P1.PLX"/>
+    <n v="1"/>
+    <s v="No"/>
+    <s v="Yes"/>
+    <s v="No"/>
+    <s v="Cybrid Building 6 (TODO)"/>
+    <s v="Healthy South"/>
     <m/>
   </r>
   <r>
     <s v="HRC032A4.ANX"/>
     <x v="1"/>
     <n v="12942"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <s v="S1P1.PLX"/>
+    <n v="1"/>
+    <s v="No"/>
+    <s v="Yes"/>
+    <s v="No"/>
+    <s v="Cybrid Building 6 (TODO)"/>
+    <s v="Healthy Southeast"/>
     <m/>
   </r>
   <r>
     <s v="HRC032A5.ANX"/>
     <x v="1"/>
     <n v="12750"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <s v="S1P1.PLX"/>
+    <n v="1"/>
+    <s v="No"/>
+    <s v="Yes"/>
+    <s v="No"/>
+    <s v="Cybrid Building 6 (TODO)"/>
+    <s v="Healthy Northeast"/>
     <m/>
   </r>
   <r>
     <s v="HRC032B0.ANX"/>
     <x v="1"/>
     <n v="11760"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <s v="S1P1.PLX"/>
+    <n v="1"/>
+    <s v="No"/>
+    <s v="Yes"/>
+    <s v="No"/>
+    <s v="Cybrid Building 6 (TODO)"/>
+    <s v="Destroyed"/>
     <m/>
   </r>
   <r>
     <s v="HRC032C0.ANX"/>
     <x v="1"/>
     <n v="11873"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <s v="S1P1.PLX"/>
+    <n v="1"/>
+    <s v="No"/>
+    <s v="Yes"/>
+    <s v="No"/>
+    <s v="Cybrid Building 6 (TODO)"/>
+    <s v="Damaged North"/>
     <m/>
   </r>
   <r>
     <s v="HRC032C1.ANX"/>
     <x v="1"/>
     <n v="12070"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <s v="S1P1.PLX"/>
+    <n v="1"/>
+    <s v="No"/>
+    <s v="Yes"/>
+    <s v="No"/>
+    <s v="Cybrid Building 6 (TODO)"/>
+    <s v="Damaged Northwest"/>
     <m/>
   </r>
   <r>
     <s v="HRC032C2.ANX"/>
     <x v="1"/>
     <n v="12169"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <s v="S1P1.PLX"/>
+    <n v="1"/>
+    <s v="No"/>
+    <s v="Yes"/>
+    <s v="No"/>
+    <s v="Cybrid Building 6 (TODO)"/>
+    <s v="Damaged Southwest"/>
     <m/>
   </r>
   <r>
     <s v="HRC032C3.ANX"/>
     <x v="1"/>
     <n v="11962"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <s v="S1P1.PLX"/>
+    <n v="1"/>
+    <s v="No"/>
+    <s v="Yes"/>
+    <s v="No"/>
+    <s v="Cybrid Building 6 (TODO)"/>
+    <s v="Damaged South"/>
     <m/>
   </r>
   <r>
     <s v="HRC032C4.ANX"/>
     <x v="1"/>
     <n v="12213"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <s v="S1P1.PLX"/>
+    <n v="1"/>
+    <s v="No"/>
+    <s v="Yes"/>
+    <s v="No"/>
+    <s v="Cybrid Building 6 (TODO)"/>
+    <s v="Damaged Southeast"/>
     <m/>
   </r>
   <r>
     <s v="HRC032C5.ANX"/>
     <x v="1"/>
     <n v="12166"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <s v="S1P1.PLX"/>
+    <n v="1"/>
+    <s v="No"/>
+    <s v="Yes"/>
+    <s v="No"/>
+    <s v="Cybrid Building 6 (TODO)"/>
+    <s v="Damaged Northeast"/>
     <m/>
   </r>
   <r>
     <s v="HRC033A0.ANX"/>
     <x v="1"/>
     <n v="15464"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <s v="S1P1.PLX"/>
+    <n v="1"/>
+    <s v="No"/>
+    <s v="Yes"/>
+    <s v="No"/>
+    <s v="Cybrid Building 7 (TODO)"/>
+    <s v="Healthy"/>
     <m/>
   </r>
   <r>
     <s v="HRC033B0.ANX"/>
     <x v="1"/>
     <n v="13171"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <s v="S1P1.PLX"/>
+    <n v="1"/>
+    <s v="No"/>
+    <s v="Yes"/>
+    <s v="No"/>
+    <s v="Cybrid Building 7 (TODO)"/>
+    <s v="Destroyed"/>
     <m/>
   </r>
   <r>
     <s v="HRC033C0.ANX"/>
     <x v="1"/>
     <n v="14913"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <s v="S1P1.PLX"/>
+    <n v="1"/>
+    <s v="No"/>
+    <s v="Yes"/>
+    <s v="No"/>
+    <s v="Cybrid Building 7 (TODO)"/>
+    <s v="Damaged"/>
     <m/>
   </r>
   <r>
     <s v="HRC034A0.ANX"/>
     <x v="1"/>
     <n v="25070"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <s v="S1P1.PLX"/>
+    <n v="6"/>
+    <s v="No"/>
+    <s v="No"/>
+    <s v="No"/>
+    <s v="Doodad"/>
+    <s v="Tree directional"/>
     <m/>
   </r>
   <r>
     <s v="HRC035A0.ANX"/>
     <x v="1"/>
     <n v="8578"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <s v="S1P1.PLX"/>
+    <n v="6"/>
+    <s v="No"/>
+    <s v="No"/>
+    <s v="No"/>
+    <s v="Doodad"/>
+    <s v="Bush directional"/>
     <m/>
   </r>
   <r>
     <s v="HRC036A0.ANX"/>
     <x v="1"/>
     <n v="8732"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <s v="S1P1.PLX"/>
+    <n v="6"/>
+    <s v="No"/>
+    <s v="No"/>
+    <s v="No"/>
+    <s v="Doodad"/>
+    <s v="Yuca directional"/>
     <m/>
   </r>
   <r>
     <s v="HRC037A0.ANX"/>
     <x v="1"/>
     <n v="16214"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <s v="S1P1.PLX"/>
+    <n v="6"/>
+    <s v="No"/>
+    <s v="No"/>
+    <s v="No"/>
+    <s v="Doodad"/>
+    <s v="Shurb directional"/>
     <m/>
   </r>
   <r>
     <s v="HRC038A0.ANX"/>
     <x v="1"/>
     <n v="30592"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <s v="S1P1.PLX"/>
+    <n v="6"/>
+    <s v="No"/>
+    <s v="No"/>
+    <s v="No"/>
+    <s v="Doodad"/>
+    <s v="Palm tree directional"/>
     <m/>
   </r>
   <r>
     <s v="HRC039A0.ANX"/>
     <x v="1"/>
     <n v="9177"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <s v="S1P1.PLX"/>
+    <n v="6"/>
+    <s v="No"/>
+    <s v="No"/>
+    <s v="No"/>
+    <s v="Doodad"/>
+    <s v="Tree directional"/>
     <m/>
   </r>
   <r>
     <s v="HRC040A0.ANX"/>
     <x v="1"/>
     <n v="8410"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <s v="S1P1.PLX"/>
+    <n v="6"/>
+    <s v="No"/>
+    <s v="No"/>
+    <s v="No"/>
+    <s v="Doodad"/>
+    <s v="Yuca directional"/>
     <m/>
   </r>
   <r>
     <s v="HRC041A0.ANX"/>
     <x v="1"/>
     <n v="19433"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <s v="S1P1.PLX"/>
+    <n v="6"/>
+    <s v="No"/>
+    <s v="No"/>
+    <s v="No"/>
+    <s v="Doodad"/>
+    <s v="Tree directional"/>
     <m/>
   </r>
   <r>
     <s v="HRC042A0.ANX"/>
     <x v="1"/>
     <n v="15550"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <s v="S1P1.PLX"/>
+    <n v="6"/>
+    <s v="No"/>
+    <s v="No"/>
+    <s v="No"/>
+    <s v="Doodad"/>
+    <s v="Tree directional"/>
     <m/>
   </r>
   <r>
     <s v="HRC043A0.ANX"/>
     <x v="1"/>
     <n v="7700"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <s v="S1P1.PLX"/>
+    <n v="6"/>
+    <s v="No"/>
+    <s v="No"/>
+    <s v="No"/>
+    <s v="Doodad"/>
+    <s v="Tree directional"/>
     <m/>
   </r>
   <r>
     <s v="HRC044A0.ANX"/>
     <x v="1"/>
     <n v="26117"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <s v="S1P1.PLX"/>
+    <n v="6"/>
+    <s v="No"/>
+    <s v="No"/>
+    <s v="No"/>
+    <s v="Doodad"/>
+    <s v="Palm tree directional"/>
     <m/>
   </r>
   <r>
     <s v="HRC045A0.ANX"/>
     <x v="1"/>
     <n v="13325"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <s v="S1P1.PLX"/>
+    <n v="6"/>
+    <s v="No"/>
+    <s v="No"/>
+    <s v="No"/>
+    <s v="Doodad"/>
+    <s v="Crystal directional"/>
     <m/>
   </r>
   <r>
     <s v="HRC046A0.ANX"/>
     <x v="1"/>
     <n v="28862"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <s v="S1P1.PLX"/>
+    <n v="6"/>
+    <s v="No"/>
+    <s v="No"/>
+    <s v="No"/>
+    <s v="Doodad"/>
+    <s v="Tree directional"/>
     <m/>
   </r>
   <r>
     <s v="HRC047A0.ANX"/>
     <x v="1"/>
     <n v="14296"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <s v="S1P1.PLX"/>
+    <n v="6"/>
+    <s v="No"/>
+    <s v="No"/>
+    <s v="No"/>
+    <s v="Doodad"/>
+    <s v="Crystal directional"/>
     <m/>
   </r>
   <r>
     <s v="HRC048A0.ANX"/>
     <x v="1"/>
     <n v="63519"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <s v="S1P1.PLX"/>
+    <n v="6"/>
+    <s v="No"/>
+    <s v="No"/>
+    <s v="No"/>
+    <s v="Doodad"/>
+    <s v="Rock directional"/>
     <m/>
   </r>
   <r>
     <s v="HRC049A0.ANX"/>
     <x v="1"/>
     <n v="21951"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <s v="S1P1.PLX"/>
+    <n v="6"/>
+    <s v="No"/>
+    <s v="No"/>
+    <s v="No"/>
+    <s v="Doodad"/>
+    <s v="Rock directional"/>
     <m/>
   </r>
   <r>
     <s v="HRC050A0.ANX"/>
     <x v="1"/>
     <n v="21596"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <s v="S1P1.PLX"/>
+    <n v="6"/>
+    <s v="No"/>
+    <s v="No"/>
+    <s v="No"/>
+    <s v="Doodad"/>
+    <s v="Rock directional"/>
     <m/>
   </r>
   <r>
     <s v="HRC051A0.ANX"/>
     <x v="1"/>
     <n v="21357"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <s v="S1P1.PLX"/>
+    <n v="6"/>
+    <s v="No"/>
+    <s v="No"/>
+    <s v="No"/>
+    <s v="Doodad"/>
+    <s v="Rock directional"/>
     <m/>
   </r>
   <r>
     <s v="HRC052A0.ANX"/>
     <x v="1"/>
     <n v="22222"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <s v="S1P1.PLX"/>
+    <n v="6"/>
+    <s v="No"/>
+    <s v="No"/>
+    <s v="No"/>
+    <s v="Doodad"/>
+    <s v="Rock directional"/>
     <m/>
   </r>
   <r>
     <s v="HRC053A0.ANX"/>
     <x v="1"/>
     <n v="21541"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <s v="S1P1.PLX"/>
+    <n v="6"/>
+    <s v="No"/>
+    <s v="No"/>
+    <s v="No"/>
+    <s v="Doodad"/>
+    <s v="Crystal directional"/>
     <m/>
   </r>
   <r>
@@ -14545,26 +14680,26 @@
     <s v="POPSHLD1.BMX"/>
     <x v="0"/>
     <n v="3690"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <s v="S1P1.PLX"/>
+    <n v="18"/>
+    <s v="Yes"/>
+    <s v="No"/>
+    <s v="No"/>
+    <s v="UI"/>
+    <s v="Target Cursor"/>
     <m/>
   </r>
   <r>
     <s v="POPSHLD2.BMX"/>
     <x v="0"/>
     <n v="3690"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <s v="S1P1.PLX"/>
+    <n v="18"/>
+    <s v="Yes"/>
+    <s v="No"/>
+    <s v="No"/>
+    <s v="UI"/>
+    <s v="Duplicate"/>
     <m/>
   </r>
   <r>
@@ -15899,6 +16034,9 @@
       <c r="G18" t="s">
         <v>919</v>
       </c>
+      <c r="H18" t="s">
+        <v>919</v>
+      </c>
       <c r="I18" t="s">
         <v>908</v>
       </c>
@@ -16036,6 +16174,9 @@
       <c r="G22" t="s">
         <v>919</v>
       </c>
+      <c r="H22" t="s">
+        <v>919</v>
+      </c>
       <c r="I22" t="s">
         <v>908</v>
       </c>
@@ -16173,6 +16314,9 @@
       <c r="G26" t="s">
         <v>919</v>
       </c>
+      <c r="H26" t="s">
+        <v>919</v>
+      </c>
       <c r="I26" t="s">
         <v>908</v>
       </c>
@@ -16310,6 +16454,9 @@
       <c r="G30" t="s">
         <v>919</v>
       </c>
+      <c r="H30" t="s">
+        <v>919</v>
+      </c>
       <c r="I30" t="s">
         <v>908</v>
       </c>
@@ -16447,6 +16594,9 @@
       <c r="G34" t="s">
         <v>919</v>
       </c>
+      <c r="H34" t="s">
+        <v>919</v>
+      </c>
       <c r="I34" t="s">
         <v>908</v>
       </c>
@@ -16584,6 +16734,9 @@
       <c r="G38" t="s">
         <v>919</v>
       </c>
+      <c r="H38" t="s">
+        <v>919</v>
+      </c>
       <c r="I38" t="s">
         <v>908</v>
       </c>
@@ -16721,6 +16874,9 @@
       <c r="G42" t="s">
         <v>919</v>
       </c>
+      <c r="H42" t="s">
+        <v>919</v>
+      </c>
       <c r="I42" t="s">
         <v>908</v>
       </c>
@@ -16858,6 +17014,9 @@
       <c r="G46" t="s">
         <v>919</v>
       </c>
+      <c r="H46" t="s">
+        <v>919</v>
+      </c>
       <c r="I46" t="s">
         <v>908</v>
       </c>
@@ -16995,6 +17154,9 @@
       <c r="G50" t="s">
         <v>919</v>
       </c>
+      <c r="H50" t="s">
+        <v>919</v>
+      </c>
       <c r="I50" t="s">
         <v>908</v>
       </c>
@@ -17132,6 +17294,9 @@
       <c r="G54" t="s">
         <v>919</v>
       </c>
+      <c r="H54" t="s">
+        <v>919</v>
+      </c>
       <c r="I54" t="s">
         <v>908</v>
       </c>
@@ -17269,6 +17434,9 @@
       <c r="G58" t="s">
         <v>919</v>
       </c>
+      <c r="H58" t="s">
+        <v>919</v>
+      </c>
       <c r="I58" t="s">
         <v>908</v>
       </c>
@@ -17406,6 +17574,9 @@
       <c r="G62" t="s">
         <v>919</v>
       </c>
+      <c r="H62" t="s">
+        <v>919</v>
+      </c>
       <c r="I62" t="s">
         <v>908</v>
       </c>
@@ -17543,6 +17714,9 @@
       <c r="G66" t="s">
         <v>919</v>
       </c>
+      <c r="H66" t="s">
+        <v>919</v>
+      </c>
       <c r="I66" t="s">
         <v>908</v>
       </c>
@@ -17680,6 +17854,9 @@
       <c r="G70" t="s">
         <v>919</v>
       </c>
+      <c r="H70" t="s">
+        <v>919</v>
+      </c>
       <c r="I70" t="s">
         <v>908</v>
       </c>
@@ -17817,6 +17994,9 @@
       <c r="G74" t="s">
         <v>919</v>
       </c>
+      <c r="H74" t="s">
+        <v>919</v>
+      </c>
       <c r="I74" t="s">
         <v>908</v>
       </c>
@@ -17954,6 +18134,9 @@
       <c r="G78" t="s">
         <v>919</v>
       </c>
+      <c r="H78" t="s">
+        <v>919</v>
+      </c>
       <c r="I78" t="s">
         <v>908</v>
       </c>
@@ -18091,6 +18274,9 @@
       <c r="G82" t="s">
         <v>919</v>
       </c>
+      <c r="H82" t="s">
+        <v>919</v>
+      </c>
       <c r="I82" t="s">
         <v>908</v>
       </c>
@@ -18365,6 +18551,9 @@
       <c r="G90" t="s">
         <v>919</v>
       </c>
+      <c r="H90" t="s">
+        <v>919</v>
+      </c>
       <c r="I90" t="s">
         <v>908</v>
       </c>
@@ -18502,6 +18691,9 @@
       <c r="G94" t="s">
         <v>919</v>
       </c>
+      <c r="H94" t="s">
+        <v>919</v>
+      </c>
       <c r="I94" t="s">
         <v>908</v>
       </c>
@@ -18639,6 +18831,9 @@
       <c r="G98" t="s">
         <v>919</v>
       </c>
+      <c r="H98" t="s">
+        <v>919</v>
+      </c>
       <c r="I98" t="s">
         <v>908</v>
       </c>
@@ -18776,6 +18971,9 @@
       <c r="G102" t="s">
         <v>919</v>
       </c>
+      <c r="H102" t="s">
+        <v>919</v>
+      </c>
       <c r="I102" t="s">
         <v>908</v>
       </c>
@@ -18913,6 +19111,9 @@
       <c r="G106" t="s">
         <v>919</v>
       </c>
+      <c r="H106" t="s">
+        <v>919</v>
+      </c>
       <c r="I106" t="s">
         <v>908</v>
       </c>
@@ -19190,6 +19391,9 @@
       <c r="G114" t="s">
         <v>919</v>
       </c>
+      <c r="H114" t="s">
+        <v>919</v>
+      </c>
       <c r="I114" t="s">
         <v>908</v>
       </c>
@@ -19327,6 +19531,9 @@
       <c r="G118" t="s">
         <v>919</v>
       </c>
+      <c r="H118" t="s">
+        <v>919</v>
+      </c>
       <c r="I118" t="s">
         <v>908</v>
       </c>
@@ -19464,6 +19671,9 @@
       <c r="G122" t="s">
         <v>919</v>
       </c>
+      <c r="H122" t="s">
+        <v>919</v>
+      </c>
       <c r="I122" t="s">
         <v>908</v>
       </c>
@@ -19601,6 +19811,9 @@
       <c r="G126" t="s">
         <v>919</v>
       </c>
+      <c r="H126" t="s">
+        <v>919</v>
+      </c>
       <c r="I126" t="s">
         <v>908</v>
       </c>
@@ -37005,6 +37218,27 @@
       <c r="C707" s="4">
         <v>19499</v>
       </c>
+      <c r="D707" t="s">
+        <v>909</v>
+      </c>
+      <c r="E707">
+        <v>1</v>
+      </c>
+      <c r="F707" t="s">
+        <v>919</v>
+      </c>
+      <c r="G707" t="s">
+        <v>914</v>
+      </c>
+      <c r="H707" t="s">
+        <v>919</v>
+      </c>
+      <c r="I707" t="s">
+        <v>1031</v>
+      </c>
+      <c r="J707" t="s">
+        <v>1028</v>
+      </c>
     </row>
     <row r="708" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A708" t="s">
@@ -37016,6 +37250,27 @@
       <c r="C708" s="4">
         <v>16037</v>
       </c>
+      <c r="D708" t="s">
+        <v>909</v>
+      </c>
+      <c r="E708">
+        <v>1</v>
+      </c>
+      <c r="F708" t="s">
+        <v>919</v>
+      </c>
+      <c r="G708" t="s">
+        <v>914</v>
+      </c>
+      <c r="H708" t="s">
+        <v>919</v>
+      </c>
+      <c r="I708" t="s">
+        <v>1031</v>
+      </c>
+      <c r="J708" t="s">
+        <v>1029</v>
+      </c>
     </row>
     <row r="709" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A709" t="s">
@@ -37027,6 +37282,27 @@
       <c r="C709" s="4">
         <v>18631</v>
       </c>
+      <c r="D709" t="s">
+        <v>909</v>
+      </c>
+      <c r="E709">
+        <v>1</v>
+      </c>
+      <c r="F709" t="s">
+        <v>919</v>
+      </c>
+      <c r="G709" t="s">
+        <v>914</v>
+      </c>
+      <c r="H709" t="s">
+        <v>919</v>
+      </c>
+      <c r="I709" t="s">
+        <v>1031</v>
+      </c>
+      <c r="J709" t="s">
+        <v>1030</v>
+      </c>
     </row>
     <row r="710" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A710" t="s">
@@ -37038,6 +37314,27 @@
       <c r="C710" s="4">
         <v>13390</v>
       </c>
+      <c r="D710" t="s">
+        <v>909</v>
+      </c>
+      <c r="E710">
+        <v>1</v>
+      </c>
+      <c r="F710" t="s">
+        <v>919</v>
+      </c>
+      <c r="G710" t="s">
+        <v>914</v>
+      </c>
+      <c r="H710" t="s">
+        <v>919</v>
+      </c>
+      <c r="I710" t="s">
+        <v>1032</v>
+      </c>
+      <c r="J710" t="s">
+        <v>1034</v>
+      </c>
     </row>
     <row r="711" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A711" t="s">
@@ -37049,6 +37346,27 @@
       <c r="C711" s="4">
         <v>13713</v>
       </c>
+      <c r="D711" t="s">
+        <v>909</v>
+      </c>
+      <c r="E711">
+        <v>1</v>
+      </c>
+      <c r="F711" t="s">
+        <v>919</v>
+      </c>
+      <c r="G711" t="s">
+        <v>914</v>
+      </c>
+      <c r="H711" t="s">
+        <v>919</v>
+      </c>
+      <c r="I711" t="s">
+        <v>1032</v>
+      </c>
+      <c r="J711" t="s">
+        <v>1035</v>
+      </c>
     </row>
     <row r="712" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A712" t="s">
@@ -37060,6 +37378,27 @@
       <c r="C712" s="4">
         <v>12794</v>
       </c>
+      <c r="D712" t="s">
+        <v>909</v>
+      </c>
+      <c r="E712">
+        <v>1</v>
+      </c>
+      <c r="F712" t="s">
+        <v>919</v>
+      </c>
+      <c r="G712" t="s">
+        <v>914</v>
+      </c>
+      <c r="H712" t="s">
+        <v>919</v>
+      </c>
+      <c r="I712" t="s">
+        <v>1032</v>
+      </c>
+      <c r="J712" t="s">
+        <v>1046</v>
+      </c>
     </row>
     <row r="713" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A713" t="s">
@@ -37071,6 +37410,27 @@
       <c r="C713" s="4">
         <v>13111</v>
       </c>
+      <c r="D713" t="s">
+        <v>909</v>
+      </c>
+      <c r="E713">
+        <v>1</v>
+      </c>
+      <c r="F713" t="s">
+        <v>919</v>
+      </c>
+      <c r="G713" t="s">
+        <v>914</v>
+      </c>
+      <c r="H713" t="s">
+        <v>919</v>
+      </c>
+      <c r="I713" t="s">
+        <v>1032</v>
+      </c>
+      <c r="J713" t="s">
+        <v>1037</v>
+      </c>
     </row>
     <row r="714" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A714" t="s">
@@ -37082,6 +37442,27 @@
       <c r="C714" s="4">
         <v>12883</v>
       </c>
+      <c r="D714" t="s">
+        <v>909</v>
+      </c>
+      <c r="E714">
+        <v>1</v>
+      </c>
+      <c r="F714" t="s">
+        <v>919</v>
+      </c>
+      <c r="G714" t="s">
+        <v>914</v>
+      </c>
+      <c r="H714" t="s">
+        <v>919</v>
+      </c>
+      <c r="I714" t="s">
+        <v>1032</v>
+      </c>
+      <c r="J714" t="s">
+        <v>1038</v>
+      </c>
     </row>
     <row r="715" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A715" t="s">
@@ -37093,6 +37474,27 @@
       <c r="C715" s="4">
         <v>12621</v>
       </c>
+      <c r="D715" t="s">
+        <v>909</v>
+      </c>
+      <c r="E715">
+        <v>1</v>
+      </c>
+      <c r="F715" t="s">
+        <v>919</v>
+      </c>
+      <c r="G715" t="s">
+        <v>914</v>
+      </c>
+      <c r="H715" t="s">
+        <v>919</v>
+      </c>
+      <c r="I715" t="s">
+        <v>1032</v>
+      </c>
+      <c r="J715" t="s">
+        <v>1039</v>
+      </c>
     </row>
     <row r="716" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A716" t="s">
@@ -37104,6 +37506,27 @@
       <c r="C716" s="4">
         <v>11001</v>
       </c>
+      <c r="D716" t="s">
+        <v>909</v>
+      </c>
+      <c r="E716">
+        <v>1</v>
+      </c>
+      <c r="F716" t="s">
+        <v>919</v>
+      </c>
+      <c r="G716" t="s">
+        <v>914</v>
+      </c>
+      <c r="H716" t="s">
+        <v>919</v>
+      </c>
+      <c r="I716" t="s">
+        <v>1032</v>
+      </c>
+      <c r="J716" t="s">
+        <v>1029</v>
+      </c>
     </row>
     <row r="717" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A717" t="s">
@@ -37115,6 +37538,27 @@
       <c r="C717" s="4">
         <v>13492</v>
       </c>
+      <c r="D717" t="s">
+        <v>909</v>
+      </c>
+      <c r="E717">
+        <v>1</v>
+      </c>
+      <c r="F717" t="s">
+        <v>919</v>
+      </c>
+      <c r="G717" t="s">
+        <v>914</v>
+      </c>
+      <c r="H717" t="s">
+        <v>919</v>
+      </c>
+      <c r="I717" t="s">
+        <v>1032</v>
+      </c>
+      <c r="J717" t="s">
+        <v>1040</v>
+      </c>
     </row>
     <row r="718" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A718" t="s">
@@ -37126,6 +37570,27 @@
       <c r="C718" s="4">
         <v>13935</v>
       </c>
+      <c r="D718" t="s">
+        <v>909</v>
+      </c>
+      <c r="E718">
+        <v>1</v>
+      </c>
+      <c r="F718" t="s">
+        <v>919</v>
+      </c>
+      <c r="G718" t="s">
+        <v>914</v>
+      </c>
+      <c r="H718" t="s">
+        <v>919</v>
+      </c>
+      <c r="I718" t="s">
+        <v>1032</v>
+      </c>
+      <c r="J718" t="s">
+        <v>1041</v>
+      </c>
     </row>
     <row r="719" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A719" t="s">
@@ -37137,6 +37602,27 @@
       <c r="C719" s="4">
         <v>13217</v>
       </c>
+      <c r="D719" t="s">
+        <v>909</v>
+      </c>
+      <c r="E719">
+        <v>1</v>
+      </c>
+      <c r="F719" t="s">
+        <v>919</v>
+      </c>
+      <c r="G719" t="s">
+        <v>914</v>
+      </c>
+      <c r="H719" t="s">
+        <v>919</v>
+      </c>
+      <c r="I719" t="s">
+        <v>1032</v>
+      </c>
+      <c r="J719" t="s">
+        <v>1042</v>
+      </c>
     </row>
     <row r="720" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A720" t="s">
@@ -37148,8 +37634,29 @@
       <c r="C720" s="4">
         <v>12920</v>
       </c>
-    </row>
-    <row r="721" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D720" t="s">
+        <v>909</v>
+      </c>
+      <c r="E720">
+        <v>1</v>
+      </c>
+      <c r="F720" t="s">
+        <v>919</v>
+      </c>
+      <c r="G720" t="s">
+        <v>914</v>
+      </c>
+      <c r="H720" t="s">
+        <v>919</v>
+      </c>
+      <c r="I720" t="s">
+        <v>1032</v>
+      </c>
+      <c r="J720" t="s">
+        <v>1043</v>
+      </c>
+    </row>
+    <row r="721" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A721" t="s">
         <v>603</v>
       </c>
@@ -37159,8 +37666,29 @@
       <c r="C721" s="4">
         <v>13158</v>
       </c>
-    </row>
-    <row r="722" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D721" t="s">
+        <v>909</v>
+      </c>
+      <c r="E721">
+        <v>1</v>
+      </c>
+      <c r="F721" t="s">
+        <v>919</v>
+      </c>
+      <c r="G721" t="s">
+        <v>914</v>
+      </c>
+      <c r="H721" t="s">
+        <v>919</v>
+      </c>
+      <c r="I721" t="s">
+        <v>1032</v>
+      </c>
+      <c r="J721" t="s">
+        <v>1044</v>
+      </c>
+    </row>
+    <row r="722" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A722" t="s">
         <v>604</v>
       </c>
@@ -37170,8 +37698,29 @@
       <c r="C722" s="4">
         <v>12768</v>
       </c>
-    </row>
-    <row r="723" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D722" t="s">
+        <v>909</v>
+      </c>
+      <c r="E722">
+        <v>1</v>
+      </c>
+      <c r="F722" t="s">
+        <v>919</v>
+      </c>
+      <c r="G722" t="s">
+        <v>914</v>
+      </c>
+      <c r="H722" t="s">
+        <v>919</v>
+      </c>
+      <c r="I722" t="s">
+        <v>1032</v>
+      </c>
+      <c r="J722" t="s">
+        <v>1045</v>
+      </c>
+    </row>
+    <row r="723" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A723" t="s">
         <v>605</v>
       </c>
@@ -37182,7 +37731,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="724" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="724" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A724" t="s">
         <v>606</v>
       </c>
@@ -37193,7 +37742,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="725" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="725" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A725" t="s">
         <v>607</v>
       </c>
@@ -37204,7 +37753,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="726" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="726" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A726" t="s">
         <v>608</v>
       </c>
@@ -37214,8 +37763,29 @@
       <c r="C726" s="4">
         <v>15134</v>
       </c>
-    </row>
-    <row r="727" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D726" t="s">
+        <v>909</v>
+      </c>
+      <c r="E726">
+        <v>1</v>
+      </c>
+      <c r="F726" t="s">
+        <v>919</v>
+      </c>
+      <c r="G726" t="s">
+        <v>914</v>
+      </c>
+      <c r="H726" t="s">
+        <v>919</v>
+      </c>
+      <c r="I726" t="s">
+        <v>1033</v>
+      </c>
+      <c r="J726" t="s">
+        <v>1034</v>
+      </c>
+    </row>
+    <row r="727" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A727" t="s">
         <v>609</v>
       </c>
@@ -37225,8 +37795,29 @@
       <c r="C727" s="4">
         <v>15737</v>
       </c>
-    </row>
-    <row r="728" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D727" t="s">
+        <v>909</v>
+      </c>
+      <c r="E727">
+        <v>1</v>
+      </c>
+      <c r="F727" t="s">
+        <v>919</v>
+      </c>
+      <c r="G727" t="s">
+        <v>914</v>
+      </c>
+      <c r="H727" t="s">
+        <v>919</v>
+      </c>
+      <c r="I727" t="s">
+        <v>1033</v>
+      </c>
+      <c r="J727" t="s">
+        <v>1035</v>
+      </c>
+    </row>
+    <row r="728" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A728" t="s">
         <v>610</v>
       </c>
@@ -37236,8 +37827,29 @@
       <c r="C728" s="4">
         <v>15119</v>
       </c>
-    </row>
-    <row r="729" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D728" t="s">
+        <v>909</v>
+      </c>
+      <c r="E728">
+        <v>1</v>
+      </c>
+      <c r="F728" t="s">
+        <v>919</v>
+      </c>
+      <c r="G728" t="s">
+        <v>914</v>
+      </c>
+      <c r="H728" t="s">
+        <v>919</v>
+      </c>
+      <c r="I728" t="s">
+        <v>1033</v>
+      </c>
+      <c r="J728" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="729" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A729" t="s">
         <v>611</v>
       </c>
@@ -37247,8 +37859,29 @@
       <c r="C729" s="4">
         <v>15321</v>
       </c>
-    </row>
-    <row r="730" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D729" t="s">
+        <v>909</v>
+      </c>
+      <c r="E729">
+        <v>1</v>
+      </c>
+      <c r="F729" t="s">
+        <v>919</v>
+      </c>
+      <c r="G729" t="s">
+        <v>914</v>
+      </c>
+      <c r="H729" t="s">
+        <v>919</v>
+      </c>
+      <c r="I729" t="s">
+        <v>1033</v>
+      </c>
+      <c r="J729" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="730" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A730" t="s">
         <v>612</v>
       </c>
@@ -37258,8 +37891,29 @@
       <c r="C730" s="4">
         <v>16083</v>
       </c>
-    </row>
-    <row r="731" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D730" t="s">
+        <v>909</v>
+      </c>
+      <c r="E730">
+        <v>1</v>
+      </c>
+      <c r="F730" t="s">
+        <v>919</v>
+      </c>
+      <c r="G730" t="s">
+        <v>914</v>
+      </c>
+      <c r="H730" t="s">
+        <v>919</v>
+      </c>
+      <c r="I730" t="s">
+        <v>1033</v>
+      </c>
+      <c r="J730" t="s">
+        <v>1038</v>
+      </c>
+    </row>
+    <row r="731" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A731" t="s">
         <v>613</v>
       </c>
@@ -37269,8 +37923,29 @@
       <c r="C731" s="4">
         <v>15327</v>
       </c>
-    </row>
-    <row r="732" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D731" t="s">
+        <v>909</v>
+      </c>
+      <c r="E731">
+        <v>1</v>
+      </c>
+      <c r="F731" t="s">
+        <v>919</v>
+      </c>
+      <c r="G731" t="s">
+        <v>914</v>
+      </c>
+      <c r="H731" t="s">
+        <v>919</v>
+      </c>
+      <c r="I731" t="s">
+        <v>1033</v>
+      </c>
+      <c r="J731" t="s">
+        <v>1039</v>
+      </c>
+    </row>
+    <row r="732" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A732" t="s">
         <v>614</v>
       </c>
@@ -37280,8 +37955,29 @@
       <c r="C732" s="4">
         <v>15653</v>
       </c>
-    </row>
-    <row r="733" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D732" t="s">
+        <v>909</v>
+      </c>
+      <c r="E732">
+        <v>1</v>
+      </c>
+      <c r="F732" t="s">
+        <v>919</v>
+      </c>
+      <c r="G732" t="s">
+        <v>914</v>
+      </c>
+      <c r="H732" t="s">
+        <v>919</v>
+      </c>
+      <c r="I732" t="s">
+        <v>1033</v>
+      </c>
+      <c r="J732" t="s">
+        <v>1029</v>
+      </c>
+    </row>
+    <row r="733" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A733" t="s">
         <v>615</v>
       </c>
@@ -37291,8 +37987,29 @@
       <c r="C733" s="4">
         <v>16710</v>
       </c>
-    </row>
-    <row r="734" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D733" t="s">
+        <v>909</v>
+      </c>
+      <c r="E733">
+        <v>1</v>
+      </c>
+      <c r="F733" t="s">
+        <v>919</v>
+      </c>
+      <c r="G733" t="s">
+        <v>914</v>
+      </c>
+      <c r="H733" t="s">
+        <v>919</v>
+      </c>
+      <c r="I733" t="s">
+        <v>1047</v>
+      </c>
+      <c r="J733" t="s">
+        <v>1034</v>
+      </c>
+    </row>
+    <row r="734" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A734" t="s">
         <v>616</v>
       </c>
@@ -37302,8 +38019,29 @@
       <c r="C734" s="4">
         <v>16474</v>
       </c>
-    </row>
-    <row r="735" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D734" t="s">
+        <v>909</v>
+      </c>
+      <c r="E734">
+        <v>1</v>
+      </c>
+      <c r="F734" t="s">
+        <v>919</v>
+      </c>
+      <c r="G734" t="s">
+        <v>914</v>
+      </c>
+      <c r="H734" t="s">
+        <v>919</v>
+      </c>
+      <c r="I734" t="s">
+        <v>1047</v>
+      </c>
+      <c r="J734" t="s">
+        <v>1035</v>
+      </c>
+    </row>
+    <row r="735" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A735" t="s">
         <v>617</v>
       </c>
@@ -37313,8 +38051,29 @@
       <c r="C735" s="4">
         <v>17446</v>
       </c>
-    </row>
-    <row r="736" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D735" t="s">
+        <v>909</v>
+      </c>
+      <c r="E735">
+        <v>1</v>
+      </c>
+      <c r="F735" t="s">
+        <v>919</v>
+      </c>
+      <c r="G735" t="s">
+        <v>914</v>
+      </c>
+      <c r="H735" t="s">
+        <v>919</v>
+      </c>
+      <c r="I735" t="s">
+        <v>1047</v>
+      </c>
+      <c r="J735" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="736" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A736" t="s">
         <v>618</v>
       </c>
@@ -37324,8 +38083,29 @@
       <c r="C736" s="4">
         <v>17213</v>
       </c>
-    </row>
-    <row r="737" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D736" t="s">
+        <v>909</v>
+      </c>
+      <c r="E736">
+        <v>1</v>
+      </c>
+      <c r="F736" t="s">
+        <v>919</v>
+      </c>
+      <c r="G736" t="s">
+        <v>914</v>
+      </c>
+      <c r="H736" t="s">
+        <v>919</v>
+      </c>
+      <c r="I736" t="s">
+        <v>1047</v>
+      </c>
+      <c r="J736" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="737" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A737" t="s">
         <v>619</v>
       </c>
@@ -37335,8 +38115,29 @@
       <c r="C737" s="4">
         <v>16844</v>
       </c>
-    </row>
-    <row r="738" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D737" t="s">
+        <v>909</v>
+      </c>
+      <c r="E737">
+        <v>1</v>
+      </c>
+      <c r="F737" t="s">
+        <v>919</v>
+      </c>
+      <c r="G737" t="s">
+        <v>914</v>
+      </c>
+      <c r="H737" t="s">
+        <v>919</v>
+      </c>
+      <c r="I737" t="s">
+        <v>1047</v>
+      </c>
+      <c r="J737" t="s">
+        <v>1038</v>
+      </c>
+    </row>
+    <row r="738" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A738" t="s">
         <v>620</v>
       </c>
@@ -37346,8 +38147,29 @@
       <c r="C738" s="4">
         <v>16959</v>
       </c>
-    </row>
-    <row r="739" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D738" t="s">
+        <v>909</v>
+      </c>
+      <c r="E738">
+        <v>1</v>
+      </c>
+      <c r="F738" t="s">
+        <v>919</v>
+      </c>
+      <c r="G738" t="s">
+        <v>914</v>
+      </c>
+      <c r="H738" t="s">
+        <v>919</v>
+      </c>
+      <c r="I738" t="s">
+        <v>1047</v>
+      </c>
+      <c r="J738" t="s">
+        <v>1039</v>
+      </c>
+    </row>
+    <row r="739" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A739" t="s">
         <v>621</v>
       </c>
@@ -37357,8 +38179,29 @@
       <c r="C739" s="4">
         <v>16966</v>
       </c>
-    </row>
-    <row r="740" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D739" t="s">
+        <v>909</v>
+      </c>
+      <c r="E739">
+        <v>1</v>
+      </c>
+      <c r="F739" t="s">
+        <v>919</v>
+      </c>
+      <c r="G739" t="s">
+        <v>914</v>
+      </c>
+      <c r="H739" t="s">
+        <v>919</v>
+      </c>
+      <c r="I739" t="s">
+        <v>1048</v>
+      </c>
+      <c r="J739" t="s">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="740" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A740" t="s">
         <v>622</v>
       </c>
@@ -37368,8 +38211,29 @@
       <c r="C740" s="4">
         <v>16402</v>
       </c>
-    </row>
-    <row r="741" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D740" t="s">
+        <v>909</v>
+      </c>
+      <c r="E740">
+        <v>1</v>
+      </c>
+      <c r="F740" t="s">
+        <v>919</v>
+      </c>
+      <c r="G740" t="s">
+        <v>914</v>
+      </c>
+      <c r="H740" t="s">
+        <v>919</v>
+      </c>
+      <c r="I740" t="s">
+        <v>1048</v>
+      </c>
+      <c r="J740" t="s">
+        <v>1029</v>
+      </c>
+    </row>
+    <row r="741" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A741" t="s">
         <v>623</v>
       </c>
@@ -37379,8 +38243,29 @@
       <c r="C741" s="4">
         <v>16941</v>
       </c>
-    </row>
-    <row r="742" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D741" t="s">
+        <v>909</v>
+      </c>
+      <c r="E741">
+        <v>1</v>
+      </c>
+      <c r="F741" t="s">
+        <v>919</v>
+      </c>
+      <c r="G741" t="s">
+        <v>914</v>
+      </c>
+      <c r="H741" t="s">
+        <v>919</v>
+      </c>
+      <c r="I741" t="s">
+        <v>1048</v>
+      </c>
+      <c r="J741" t="s">
+        <v>1030</v>
+      </c>
+    </row>
+    <row r="742" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A742" t="s">
         <v>624</v>
       </c>
@@ -37391,7 +38276,7 @@
         <v>3633</v>
       </c>
     </row>
-    <row r="743" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="743" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A743" t="s">
         <v>625</v>
       </c>
@@ -37402,7 +38287,7 @@
         <v>2199</v>
       </c>
     </row>
-    <row r="744" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="744" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A744" t="s">
         <v>626</v>
       </c>
@@ -37413,7 +38298,7 @@
         <v>3981</v>
       </c>
     </row>
-    <row r="745" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="745" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A745" t="s">
         <v>627</v>
       </c>
@@ -37424,7 +38309,7 @@
         <v>3667</v>
       </c>
     </row>
-    <row r="746" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="746" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A746" t="s">
         <v>628</v>
       </c>
@@ -37435,7 +38320,7 @@
         <v>3717</v>
       </c>
     </row>
-    <row r="747" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="747" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A747" t="s">
         <v>629</v>
       </c>
@@ -37446,7 +38331,7 @@
         <v>3493</v>
       </c>
     </row>
-    <row r="748" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="748" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A748" t="s">
         <v>630</v>
       </c>
@@ -37457,7 +38342,7 @@
         <v>3779</v>
       </c>
     </row>
-    <row r="749" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="749" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A749" t="s">
         <v>631</v>
       </c>
@@ -37468,7 +38353,7 @@
         <v>3797</v>
       </c>
     </row>
-    <row r="750" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="750" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A750" t="s">
         <v>632</v>
       </c>
@@ -37479,7 +38364,7 @@
         <v>3495</v>
       </c>
     </row>
-    <row r="751" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="751" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A751" t="s">
         <v>633</v>
       </c>
@@ -37490,7 +38375,7 @@
         <v>2682</v>
       </c>
     </row>
-    <row r="752" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="752" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A752" t="s">
         <v>634</v>
       </c>
@@ -37501,7 +38386,7 @@
         <v>2798</v>
       </c>
     </row>
-    <row r="753" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="753" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A753" t="s">
         <v>635</v>
       </c>
@@ -37512,7 +38397,7 @@
         <v>2645</v>
       </c>
     </row>
-    <row r="754" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="754" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A754" t="s">
         <v>636</v>
       </c>
@@ -37523,7 +38408,7 @@
         <v>2558</v>
       </c>
     </row>
-    <row r="755" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="755" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A755" t="s">
         <v>637</v>
       </c>
@@ -37534,7 +38419,7 @@
         <v>2781</v>
       </c>
     </row>
-    <row r="756" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="756" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A756" t="s">
         <v>638</v>
       </c>
@@ -37545,7 +38430,7 @@
         <v>2547</v>
       </c>
     </row>
-    <row r="757" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="757" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A757" t="s">
         <v>639</v>
       </c>
@@ -37556,7 +38441,7 @@
         <v>3794</v>
       </c>
     </row>
-    <row r="758" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="758" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A758" t="s">
         <v>640</v>
       </c>
@@ -37567,7 +38452,7 @@
         <v>4076</v>
       </c>
     </row>
-    <row r="759" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="759" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A759" t="s">
         <v>641</v>
       </c>
@@ -37578,7 +38463,7 @@
         <v>3715</v>
       </c>
     </row>
-    <row r="760" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="760" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A760" t="s">
         <v>642</v>
       </c>
@@ -37589,7 +38474,7 @@
         <v>4040</v>
       </c>
     </row>
-    <row r="761" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="761" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A761" t="s">
         <v>643</v>
       </c>
@@ -37600,7 +38485,7 @@
         <v>3868</v>
       </c>
     </row>
-    <row r="762" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="762" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A762" t="s">
         <v>644</v>
       </c>
@@ -37611,7 +38496,7 @@
         <v>3588</v>
       </c>
     </row>
-    <row r="763" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="763" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A763" t="s">
         <v>645</v>
       </c>
@@ -37622,7 +38507,7 @@
         <v>3633</v>
       </c>
     </row>
-    <row r="764" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="764" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A764" t="s">
         <v>646</v>
       </c>
@@ -37633,7 +38518,7 @@
         <v>2199</v>
       </c>
     </row>
-    <row r="765" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="765" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A765" t="s">
         <v>647</v>
       </c>
@@ -37644,7 +38529,7 @@
         <v>3981</v>
       </c>
     </row>
-    <row r="766" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="766" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A766" t="s">
         <v>648</v>
       </c>
@@ -37654,8 +38539,29 @@
       <c r="C766" s="4">
         <v>6217</v>
       </c>
-    </row>
-    <row r="767" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D766" t="s">
+        <v>909</v>
+      </c>
+      <c r="E766">
+        <v>1</v>
+      </c>
+      <c r="F766" t="s">
+        <v>919</v>
+      </c>
+      <c r="G766" t="s">
+        <v>914</v>
+      </c>
+      <c r="H766" t="s">
+        <v>919</v>
+      </c>
+      <c r="I766" t="s">
+        <v>1049</v>
+      </c>
+      <c r="J766" t="s">
+        <v>1034</v>
+      </c>
+    </row>
+    <row r="767" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A767" t="s">
         <v>649</v>
       </c>
@@ -37665,8 +38571,29 @@
       <c r="C767" s="4">
         <v>6367</v>
       </c>
-    </row>
-    <row r="768" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D767" t="s">
+        <v>909</v>
+      </c>
+      <c r="E767">
+        <v>1</v>
+      </c>
+      <c r="F767" t="s">
+        <v>919</v>
+      </c>
+      <c r="G767" t="s">
+        <v>914</v>
+      </c>
+      <c r="H767" t="s">
+        <v>919</v>
+      </c>
+      <c r="I767" t="s">
+        <v>1049</v>
+      </c>
+      <c r="J767" t="s">
+        <v>1035</v>
+      </c>
+    </row>
+    <row r="768" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A768" t="s">
         <v>650</v>
       </c>
@@ -37676,8 +38603,29 @@
       <c r="C768" s="4">
         <v>6287</v>
       </c>
-    </row>
-    <row r="769" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D768" t="s">
+        <v>909</v>
+      </c>
+      <c r="E768">
+        <v>1</v>
+      </c>
+      <c r="F768" t="s">
+        <v>919</v>
+      </c>
+      <c r="G768" t="s">
+        <v>914</v>
+      </c>
+      <c r="H768" t="s">
+        <v>919</v>
+      </c>
+      <c r="I768" t="s">
+        <v>1049</v>
+      </c>
+      <c r="J768" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="769" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A769" t="s">
         <v>651</v>
       </c>
@@ -37687,8 +38635,29 @@
       <c r="C769" s="4">
         <v>5958</v>
       </c>
-    </row>
-    <row r="770" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D769" t="s">
+        <v>909</v>
+      </c>
+      <c r="E769">
+        <v>1</v>
+      </c>
+      <c r="F769" t="s">
+        <v>919</v>
+      </c>
+      <c r="G769" t="s">
+        <v>914</v>
+      </c>
+      <c r="H769" t="s">
+        <v>919</v>
+      </c>
+      <c r="I769" t="s">
+        <v>1049</v>
+      </c>
+      <c r="J769" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="770" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A770" t="s">
         <v>652</v>
       </c>
@@ -37698,8 +38667,29 @@
       <c r="C770" s="4">
         <v>6348</v>
       </c>
-    </row>
-    <row r="771" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D770" t="s">
+        <v>909</v>
+      </c>
+      <c r="E770">
+        <v>1</v>
+      </c>
+      <c r="F770" t="s">
+        <v>919</v>
+      </c>
+      <c r="G770" t="s">
+        <v>914</v>
+      </c>
+      <c r="H770" t="s">
+        <v>919</v>
+      </c>
+      <c r="I770" t="s">
+        <v>1049</v>
+      </c>
+      <c r="J770" t="s">
+        <v>1038</v>
+      </c>
+    </row>
+    <row r="771" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A771" t="s">
         <v>653</v>
       </c>
@@ -37709,8 +38699,29 @@
       <c r="C771" s="4">
         <v>6636</v>
       </c>
-    </row>
-    <row r="772" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D771" t="s">
+        <v>909</v>
+      </c>
+      <c r="E771">
+        <v>1</v>
+      </c>
+      <c r="F771" t="s">
+        <v>919</v>
+      </c>
+      <c r="G771" t="s">
+        <v>914</v>
+      </c>
+      <c r="H771" t="s">
+        <v>919</v>
+      </c>
+      <c r="I771" t="s">
+        <v>1049</v>
+      </c>
+      <c r="J771" t="s">
+        <v>1039</v>
+      </c>
+    </row>
+    <row r="772" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A772" t="s">
         <v>654</v>
       </c>
@@ -37720,8 +38731,29 @@
       <c r="C772" s="4">
         <v>7606</v>
       </c>
-    </row>
-    <row r="773" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D772" t="s">
+        <v>909</v>
+      </c>
+      <c r="E772">
+        <v>1</v>
+      </c>
+      <c r="F772" t="s">
+        <v>919</v>
+      </c>
+      <c r="G772" t="s">
+        <v>914</v>
+      </c>
+      <c r="H772" t="s">
+        <v>919</v>
+      </c>
+      <c r="I772" t="s">
+        <v>1049</v>
+      </c>
+      <c r="J772" t="s">
+        <v>1029</v>
+      </c>
+    </row>
+    <row r="773" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A773" t="s">
         <v>655</v>
       </c>
@@ -37731,8 +38763,29 @@
       <c r="C773" s="4">
         <v>6075</v>
       </c>
-    </row>
-    <row r="774" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D773" t="s">
+        <v>909</v>
+      </c>
+      <c r="E773">
+        <v>1</v>
+      </c>
+      <c r="F773" t="s">
+        <v>919</v>
+      </c>
+      <c r="G773" t="s">
+        <v>914</v>
+      </c>
+      <c r="H773" t="s">
+        <v>919</v>
+      </c>
+      <c r="I773" t="s">
+        <v>1049</v>
+      </c>
+      <c r="J773" t="s">
+        <v>1040</v>
+      </c>
+    </row>
+    <row r="774" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A774" t="s">
         <v>656</v>
       </c>
@@ -37742,8 +38795,29 @@
       <c r="C774" s="4">
         <v>6226</v>
       </c>
-    </row>
-    <row r="775" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D774" t="s">
+        <v>909</v>
+      </c>
+      <c r="E774">
+        <v>1</v>
+      </c>
+      <c r="F774" t="s">
+        <v>919</v>
+      </c>
+      <c r="G774" t="s">
+        <v>914</v>
+      </c>
+      <c r="H774" t="s">
+        <v>919</v>
+      </c>
+      <c r="I774" t="s">
+        <v>1049</v>
+      </c>
+      <c r="J774" t="s">
+        <v>1041</v>
+      </c>
+    </row>
+    <row r="775" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A775" t="s">
         <v>657</v>
       </c>
@@ -37753,8 +38827,29 @@
       <c r="C775" s="4">
         <v>6188</v>
       </c>
-    </row>
-    <row r="776" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D775" t="s">
+        <v>909</v>
+      </c>
+      <c r="E775">
+        <v>1</v>
+      </c>
+      <c r="F775" t="s">
+        <v>919</v>
+      </c>
+      <c r="G775" t="s">
+        <v>914</v>
+      </c>
+      <c r="H775" t="s">
+        <v>919</v>
+      </c>
+      <c r="I775" t="s">
+        <v>1049</v>
+      </c>
+      <c r="J775" t="s">
+        <v>1042</v>
+      </c>
+    </row>
+    <row r="776" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A776" t="s">
         <v>658</v>
       </c>
@@ -37764,8 +38859,29 @@
       <c r="C776" s="4">
         <v>5819</v>
       </c>
-    </row>
-    <row r="777" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D776" t="s">
+        <v>909</v>
+      </c>
+      <c r="E776">
+        <v>1</v>
+      </c>
+      <c r="F776" t="s">
+        <v>919</v>
+      </c>
+      <c r="G776" t="s">
+        <v>914</v>
+      </c>
+      <c r="H776" t="s">
+        <v>919</v>
+      </c>
+      <c r="I776" t="s">
+        <v>1049</v>
+      </c>
+      <c r="J776" t="s">
+        <v>1043</v>
+      </c>
+    </row>
+    <row r="777" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A777" t="s">
         <v>659</v>
       </c>
@@ -37775,8 +38891,29 @@
       <c r="C777" s="4">
         <v>6030</v>
       </c>
-    </row>
-    <row r="778" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D777" t="s">
+        <v>909</v>
+      </c>
+      <c r="E777">
+        <v>1</v>
+      </c>
+      <c r="F777" t="s">
+        <v>919</v>
+      </c>
+      <c r="G777" t="s">
+        <v>914</v>
+      </c>
+      <c r="H777" t="s">
+        <v>919</v>
+      </c>
+      <c r="I777" t="s">
+        <v>1049</v>
+      </c>
+      <c r="J777" t="s">
+        <v>1044</v>
+      </c>
+    </row>
+    <row r="778" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A778" t="s">
         <v>660</v>
       </c>
@@ -37786,8 +38923,29 @@
       <c r="C778" s="4">
         <v>6091</v>
       </c>
-    </row>
-    <row r="779" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D778" t="s">
+        <v>909</v>
+      </c>
+      <c r="E778">
+        <v>1</v>
+      </c>
+      <c r="F778" t="s">
+        <v>919</v>
+      </c>
+      <c r="G778" t="s">
+        <v>914</v>
+      </c>
+      <c r="H778" t="s">
+        <v>919</v>
+      </c>
+      <c r="I778" t="s">
+        <v>1049</v>
+      </c>
+      <c r="J778" t="s">
+        <v>1045</v>
+      </c>
+    </row>
+    <row r="779" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A779" t="s">
         <v>661</v>
       </c>
@@ -37797,8 +38955,29 @@
       <c r="C779" s="4">
         <v>14351</v>
       </c>
-    </row>
-    <row r="780" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D779" t="s">
+        <v>909</v>
+      </c>
+      <c r="E779">
+        <v>1</v>
+      </c>
+      <c r="F779" t="s">
+        <v>919</v>
+      </c>
+      <c r="G779" t="s">
+        <v>914</v>
+      </c>
+      <c r="H779" t="s">
+        <v>919</v>
+      </c>
+      <c r="I779" t="s">
+        <v>1050</v>
+      </c>
+      <c r="J779" t="s">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="780" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A780" t="s">
         <v>662</v>
       </c>
@@ -37808,8 +38987,29 @@
       <c r="C780" s="4">
         <v>12986</v>
       </c>
-    </row>
-    <row r="781" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D780" t="s">
+        <v>909</v>
+      </c>
+      <c r="E780">
+        <v>1</v>
+      </c>
+      <c r="F780" t="s">
+        <v>919</v>
+      </c>
+      <c r="G780" t="s">
+        <v>914</v>
+      </c>
+      <c r="H780" t="s">
+        <v>919</v>
+      </c>
+      <c r="I780" t="s">
+        <v>1050</v>
+      </c>
+      <c r="J780" t="s">
+        <v>1029</v>
+      </c>
+    </row>
+    <row r="781" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A781" t="s">
         <v>663</v>
       </c>
@@ -37819,8 +39019,29 @@
       <c r="C781" s="4">
         <v>13420</v>
       </c>
-    </row>
-    <row r="782" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D781" t="s">
+        <v>909</v>
+      </c>
+      <c r="E781">
+        <v>1</v>
+      </c>
+      <c r="F781" t="s">
+        <v>919</v>
+      </c>
+      <c r="G781" t="s">
+        <v>914</v>
+      </c>
+      <c r="H781" t="s">
+        <v>919</v>
+      </c>
+      <c r="I781" t="s">
+        <v>1050</v>
+      </c>
+      <c r="J781" t="s">
+        <v>1030</v>
+      </c>
+    </row>
+    <row r="782" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A782" t="s">
         <v>664</v>
       </c>
@@ -37830,8 +39051,29 @@
       <c r="C782" s="4">
         <v>11440</v>
       </c>
-    </row>
-    <row r="783" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D782" t="s">
+        <v>909</v>
+      </c>
+      <c r="E782">
+        <v>1</v>
+      </c>
+      <c r="F782" t="s">
+        <v>919</v>
+      </c>
+      <c r="G782" t="s">
+        <v>914</v>
+      </c>
+      <c r="H782" t="s">
+        <v>919</v>
+      </c>
+      <c r="I782" t="s">
+        <v>1051</v>
+      </c>
+      <c r="J782" t="s">
+        <v>1034</v>
+      </c>
+    </row>
+    <row r="783" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A783" t="s">
         <v>665</v>
       </c>
@@ -37841,8 +39083,29 @@
       <c r="C783" s="4">
         <v>11579</v>
       </c>
-    </row>
-    <row r="784" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D783" t="s">
+        <v>909</v>
+      </c>
+      <c r="E783">
+        <v>1</v>
+      </c>
+      <c r="F783" t="s">
+        <v>919</v>
+      </c>
+      <c r="G783" t="s">
+        <v>914</v>
+      </c>
+      <c r="H783" t="s">
+        <v>919</v>
+      </c>
+      <c r="I783" t="s">
+        <v>1051</v>
+      </c>
+      <c r="J783" t="s">
+        <v>1035</v>
+      </c>
+    </row>
+    <row r="784" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A784" t="s">
         <v>666</v>
       </c>
@@ -37852,8 +39115,29 @@
       <c r="C784" s="4">
         <v>11639</v>
       </c>
-    </row>
-    <row r="785" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D784" t="s">
+        <v>909</v>
+      </c>
+      <c r="E784">
+        <v>1</v>
+      </c>
+      <c r="F784" t="s">
+        <v>919</v>
+      </c>
+      <c r="G784" t="s">
+        <v>914</v>
+      </c>
+      <c r="H784" t="s">
+        <v>919</v>
+      </c>
+      <c r="I784" t="s">
+        <v>1051</v>
+      </c>
+      <c r="J784" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="785" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A785" t="s">
         <v>667</v>
       </c>
@@ -37863,8 +39147,29 @@
       <c r="C785" s="4">
         <v>11291</v>
       </c>
-    </row>
-    <row r="786" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D785" t="s">
+        <v>909</v>
+      </c>
+      <c r="E785">
+        <v>1</v>
+      </c>
+      <c r="F785" t="s">
+        <v>919</v>
+      </c>
+      <c r="G785" t="s">
+        <v>914</v>
+      </c>
+      <c r="H785" t="s">
+        <v>919</v>
+      </c>
+      <c r="I785" t="s">
+        <v>1051</v>
+      </c>
+      <c r="J785" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="786" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A786" t="s">
         <v>668</v>
       </c>
@@ -37874,8 +39179,29 @@
       <c r="C786" s="4">
         <v>11534</v>
       </c>
-    </row>
-    <row r="787" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D786" t="s">
+        <v>909</v>
+      </c>
+      <c r="E786">
+        <v>1</v>
+      </c>
+      <c r="F786" t="s">
+        <v>919</v>
+      </c>
+      <c r="G786" t="s">
+        <v>914</v>
+      </c>
+      <c r="H786" t="s">
+        <v>919</v>
+      </c>
+      <c r="I786" t="s">
+        <v>1051</v>
+      </c>
+      <c r="J786" t="s">
+        <v>1038</v>
+      </c>
+    </row>
+    <row r="787" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A787" t="s">
         <v>669</v>
       </c>
@@ -37885,8 +39211,29 @@
       <c r="C787" s="4">
         <v>11459</v>
       </c>
-    </row>
-    <row r="788" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D787" t="s">
+        <v>909</v>
+      </c>
+      <c r="E787">
+        <v>1</v>
+      </c>
+      <c r="F787" t="s">
+        <v>919</v>
+      </c>
+      <c r="G787" t="s">
+        <v>914</v>
+      </c>
+      <c r="H787" t="s">
+        <v>919</v>
+      </c>
+      <c r="I787" t="s">
+        <v>1051</v>
+      </c>
+      <c r="J787" t="s">
+        <v>1039</v>
+      </c>
+    </row>
+    <row r="788" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A788" t="s">
         <v>670</v>
       </c>
@@ -37896,8 +39243,29 @@
       <c r="C788" s="4">
         <v>8305</v>
       </c>
-    </row>
-    <row r="789" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D788" t="s">
+        <v>909</v>
+      </c>
+      <c r="E788">
+        <v>1</v>
+      </c>
+      <c r="F788" t="s">
+        <v>919</v>
+      </c>
+      <c r="G788" t="s">
+        <v>914</v>
+      </c>
+      <c r="H788" t="s">
+        <v>919</v>
+      </c>
+      <c r="I788" t="s">
+        <v>1051</v>
+      </c>
+      <c r="J788" t="s">
+        <v>1029</v>
+      </c>
+    </row>
+    <row r="789" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A789" t="s">
         <v>671</v>
       </c>
@@ -37907,8 +39275,29 @@
       <c r="C789" s="4">
         <v>12403</v>
       </c>
-    </row>
-    <row r="790" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D789" t="s">
+        <v>909</v>
+      </c>
+      <c r="E789">
+        <v>1</v>
+      </c>
+      <c r="F789" t="s">
+        <v>919</v>
+      </c>
+      <c r="G789" t="s">
+        <v>914</v>
+      </c>
+      <c r="H789" t="s">
+        <v>919</v>
+      </c>
+      <c r="I789" t="s">
+        <v>1051</v>
+      </c>
+      <c r="J789" t="s">
+        <v>1040</v>
+      </c>
+    </row>
+    <row r="790" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A790" t="s">
         <v>672</v>
       </c>
@@ -37918,8 +39307,29 @@
       <c r="C790" s="4">
         <v>12582</v>
       </c>
-    </row>
-    <row r="791" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D790" t="s">
+        <v>909</v>
+      </c>
+      <c r="E790">
+        <v>1</v>
+      </c>
+      <c r="F790" t="s">
+        <v>919</v>
+      </c>
+      <c r="G790" t="s">
+        <v>914</v>
+      </c>
+      <c r="H790" t="s">
+        <v>919</v>
+      </c>
+      <c r="I790" t="s">
+        <v>1051</v>
+      </c>
+      <c r="J790" t="s">
+        <v>1041</v>
+      </c>
+    </row>
+    <row r="791" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A791" t="s">
         <v>673</v>
       </c>
@@ -37929,8 +39339,29 @@
       <c r="C791" s="4">
         <v>12436</v>
       </c>
-    </row>
-    <row r="792" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D791" t="s">
+        <v>909</v>
+      </c>
+      <c r="E791">
+        <v>1</v>
+      </c>
+      <c r="F791" t="s">
+        <v>919</v>
+      </c>
+      <c r="G791" t="s">
+        <v>914</v>
+      </c>
+      <c r="H791" t="s">
+        <v>919</v>
+      </c>
+      <c r="I791" t="s">
+        <v>1051</v>
+      </c>
+      <c r="J791" t="s">
+        <v>1042</v>
+      </c>
+    </row>
+    <row r="792" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A792" t="s">
         <v>674</v>
       </c>
@@ -37940,8 +39371,29 @@
       <c r="C792" s="4">
         <v>12478</v>
       </c>
-    </row>
-    <row r="793" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D792" t="s">
+        <v>909</v>
+      </c>
+      <c r="E792">
+        <v>1</v>
+      </c>
+      <c r="F792" t="s">
+        <v>919</v>
+      </c>
+      <c r="G792" t="s">
+        <v>914</v>
+      </c>
+      <c r="H792" t="s">
+        <v>919</v>
+      </c>
+      <c r="I792" t="s">
+        <v>1051</v>
+      </c>
+      <c r="J792" t="s">
+        <v>1043</v>
+      </c>
+    </row>
+    <row r="793" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A793" t="s">
         <v>675</v>
       </c>
@@ -37951,8 +39403,29 @@
       <c r="C793" s="4">
         <v>12694</v>
       </c>
-    </row>
-    <row r="794" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D793" t="s">
+        <v>909</v>
+      </c>
+      <c r="E793">
+        <v>1</v>
+      </c>
+      <c r="F793" t="s">
+        <v>919</v>
+      </c>
+      <c r="G793" t="s">
+        <v>914</v>
+      </c>
+      <c r="H793" t="s">
+        <v>919</v>
+      </c>
+      <c r="I793" t="s">
+        <v>1051</v>
+      </c>
+      <c r="J793" t="s">
+        <v>1044</v>
+      </c>
+    </row>
+    <row r="794" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A794" t="s">
         <v>676</v>
       </c>
@@ -37962,8 +39435,29 @@
       <c r="C794" s="4">
         <v>12693</v>
       </c>
-    </row>
-    <row r="795" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D794" t="s">
+        <v>909</v>
+      </c>
+      <c r="E794">
+        <v>1</v>
+      </c>
+      <c r="F794" t="s">
+        <v>919</v>
+      </c>
+      <c r="G794" t="s">
+        <v>914</v>
+      </c>
+      <c r="H794" t="s">
+        <v>919</v>
+      </c>
+      <c r="I794" t="s">
+        <v>1051</v>
+      </c>
+      <c r="J794" t="s">
+        <v>1045</v>
+      </c>
+    </row>
+    <row r="795" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A795" t="s">
         <v>677</v>
       </c>
@@ -37973,8 +39467,29 @@
       <c r="C795" s="4">
         <v>7711</v>
       </c>
-    </row>
-    <row r="796" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D795" t="s">
+        <v>909</v>
+      </c>
+      <c r="E795">
+        <v>1</v>
+      </c>
+      <c r="F795" t="s">
+        <v>919</v>
+      </c>
+      <c r="G795" t="s">
+        <v>914</v>
+      </c>
+      <c r="H795" t="s">
+        <v>919</v>
+      </c>
+      <c r="I795" t="s">
+        <v>1052</v>
+      </c>
+      <c r="J795" t="s">
+        <v>1034</v>
+      </c>
+    </row>
+    <row r="796" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A796" t="s">
         <v>678</v>
       </c>
@@ -37984,8 +39499,29 @@
       <c r="C796" s="4">
         <v>7471</v>
       </c>
-    </row>
-    <row r="797" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D796" t="s">
+        <v>909</v>
+      </c>
+      <c r="E796">
+        <v>1</v>
+      </c>
+      <c r="F796" t="s">
+        <v>919</v>
+      </c>
+      <c r="G796" t="s">
+        <v>914</v>
+      </c>
+      <c r="H796" t="s">
+        <v>919</v>
+      </c>
+      <c r="I796" t="s">
+        <v>1052</v>
+      </c>
+      <c r="J796" t="s">
+        <v>1035</v>
+      </c>
+    </row>
+    <row r="797" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A797" t="s">
         <v>679</v>
       </c>
@@ -37995,8 +39531,29 @@
       <c r="C797" s="4">
         <v>7727</v>
       </c>
-    </row>
-    <row r="798" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D797" t="s">
+        <v>909</v>
+      </c>
+      <c r="E797">
+        <v>1</v>
+      </c>
+      <c r="F797" t="s">
+        <v>919</v>
+      </c>
+      <c r="G797" t="s">
+        <v>914</v>
+      </c>
+      <c r="H797" t="s">
+        <v>919</v>
+      </c>
+      <c r="I797" t="s">
+        <v>1052</v>
+      </c>
+      <c r="J797" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="798" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A798" t="s">
         <v>680</v>
       </c>
@@ -38006,8 +39563,29 @@
       <c r="C798" s="4">
         <v>7789</v>
       </c>
-    </row>
-    <row r="799" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D798" t="s">
+        <v>909</v>
+      </c>
+      <c r="E798">
+        <v>1</v>
+      </c>
+      <c r="F798" t="s">
+        <v>919</v>
+      </c>
+      <c r="G798" t="s">
+        <v>914</v>
+      </c>
+      <c r="H798" t="s">
+        <v>919</v>
+      </c>
+      <c r="I798" t="s">
+        <v>1052</v>
+      </c>
+      <c r="J798" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="799" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A799" t="s">
         <v>681</v>
       </c>
@@ -38017,8 +39595,29 @@
       <c r="C799" s="4">
         <v>7686</v>
       </c>
-    </row>
-    <row r="800" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D799" t="s">
+        <v>909</v>
+      </c>
+      <c r="E799">
+        <v>1</v>
+      </c>
+      <c r="F799" t="s">
+        <v>919</v>
+      </c>
+      <c r="G799" t="s">
+        <v>914</v>
+      </c>
+      <c r="H799" t="s">
+        <v>919</v>
+      </c>
+      <c r="I799" t="s">
+        <v>1052</v>
+      </c>
+      <c r="J799" t="s">
+        <v>1038</v>
+      </c>
+    </row>
+    <row r="800" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A800" t="s">
         <v>682</v>
       </c>
@@ -38028,8 +39627,29 @@
       <c r="C800" s="4">
         <v>7420</v>
       </c>
-    </row>
-    <row r="801" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D800" t="s">
+        <v>909</v>
+      </c>
+      <c r="E800">
+        <v>1</v>
+      </c>
+      <c r="F800" t="s">
+        <v>919</v>
+      </c>
+      <c r="G800" t="s">
+        <v>914</v>
+      </c>
+      <c r="H800" t="s">
+        <v>919</v>
+      </c>
+      <c r="I800" t="s">
+        <v>1052</v>
+      </c>
+      <c r="J800" t="s">
+        <v>1039</v>
+      </c>
+    </row>
+    <row r="801" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A801" t="s">
         <v>683</v>
       </c>
@@ -38039,8 +39659,29 @@
       <c r="C801" s="4">
         <v>5878</v>
       </c>
-    </row>
-    <row r="802" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D801" t="s">
+        <v>909</v>
+      </c>
+      <c r="E801">
+        <v>1</v>
+      </c>
+      <c r="F801" t="s">
+        <v>919</v>
+      </c>
+      <c r="G801" t="s">
+        <v>914</v>
+      </c>
+      <c r="H801" t="s">
+        <v>919</v>
+      </c>
+      <c r="I801" t="s">
+        <v>1052</v>
+      </c>
+      <c r="J801" t="s">
+        <v>1029</v>
+      </c>
+    </row>
+    <row r="802" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A802" t="s">
         <v>684</v>
       </c>
@@ -38050,8 +39691,29 @@
       <c r="C802" s="4">
         <v>6341</v>
       </c>
-    </row>
-    <row r="803" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D802" t="s">
+        <v>909</v>
+      </c>
+      <c r="E802">
+        <v>1</v>
+      </c>
+      <c r="F802" t="s">
+        <v>919</v>
+      </c>
+      <c r="G802" t="s">
+        <v>914</v>
+      </c>
+      <c r="H802" t="s">
+        <v>919</v>
+      </c>
+      <c r="I802" t="s">
+        <v>1052</v>
+      </c>
+      <c r="J802" t="s">
+        <v>1040</v>
+      </c>
+    </row>
+    <row r="803" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A803" t="s">
         <v>685</v>
       </c>
@@ -38061,8 +39723,29 @@
       <c r="C803" s="4">
         <v>6444</v>
       </c>
-    </row>
-    <row r="804" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D803" t="s">
+        <v>909</v>
+      </c>
+      <c r="E803">
+        <v>1</v>
+      </c>
+      <c r="F803" t="s">
+        <v>919</v>
+      </c>
+      <c r="G803" t="s">
+        <v>914</v>
+      </c>
+      <c r="H803" t="s">
+        <v>919</v>
+      </c>
+      <c r="I803" t="s">
+        <v>1052</v>
+      </c>
+      <c r="J803" t="s">
+        <v>1041</v>
+      </c>
+    </row>
+    <row r="804" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A804" t="s">
         <v>686</v>
       </c>
@@ -38072,8 +39755,29 @@
       <c r="C804" s="4">
         <v>7251</v>
       </c>
-    </row>
-    <row r="805" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D804" t="s">
+        <v>909</v>
+      </c>
+      <c r="E804">
+        <v>1</v>
+      </c>
+      <c r="F804" t="s">
+        <v>919</v>
+      </c>
+      <c r="G804" t="s">
+        <v>914</v>
+      </c>
+      <c r="H804" t="s">
+        <v>919</v>
+      </c>
+      <c r="I804" t="s">
+        <v>1052</v>
+      </c>
+      <c r="J804" t="s">
+        <v>1042</v>
+      </c>
+    </row>
+    <row r="805" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A805" t="s">
         <v>687</v>
       </c>
@@ -38083,8 +39787,29 @@
       <c r="C805" s="4">
         <v>7552</v>
       </c>
-    </row>
-    <row r="806" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D805" t="s">
+        <v>909</v>
+      </c>
+      <c r="E805">
+        <v>1</v>
+      </c>
+      <c r="F805" t="s">
+        <v>919</v>
+      </c>
+      <c r="G805" t="s">
+        <v>914</v>
+      </c>
+      <c r="H805" t="s">
+        <v>919</v>
+      </c>
+      <c r="I805" t="s">
+        <v>1052</v>
+      </c>
+      <c r="J805" t="s">
+        <v>1043</v>
+      </c>
+    </row>
+    <row r="806" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A806" t="s">
         <v>688</v>
       </c>
@@ -38094,8 +39819,29 @@
       <c r="C806" s="4">
         <v>7716</v>
       </c>
-    </row>
-    <row r="807" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D806" t="s">
+        <v>909</v>
+      </c>
+      <c r="E806">
+        <v>1</v>
+      </c>
+      <c r="F806" t="s">
+        <v>919</v>
+      </c>
+      <c r="G806" t="s">
+        <v>914</v>
+      </c>
+      <c r="H806" t="s">
+        <v>919</v>
+      </c>
+      <c r="I806" t="s">
+        <v>1052</v>
+      </c>
+      <c r="J806" t="s">
+        <v>1044</v>
+      </c>
+    </row>
+    <row r="807" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A807" t="s">
         <v>689</v>
       </c>
@@ -38105,8 +39851,29 @@
       <c r="C807" s="4">
         <v>6206</v>
       </c>
-    </row>
-    <row r="808" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D807" t="s">
+        <v>909</v>
+      </c>
+      <c r="E807">
+        <v>1</v>
+      </c>
+      <c r="F807" t="s">
+        <v>919</v>
+      </c>
+      <c r="G807" t="s">
+        <v>914</v>
+      </c>
+      <c r="H807" t="s">
+        <v>919</v>
+      </c>
+      <c r="I807" t="s">
+        <v>1052</v>
+      </c>
+      <c r="J807" t="s">
+        <v>1045</v>
+      </c>
+    </row>
+    <row r="808" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A808" t="s">
         <v>690</v>
       </c>
@@ -38116,8 +39883,29 @@
       <c r="C808" s="4">
         <v>7763</v>
       </c>
-    </row>
-    <row r="809" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D808" t="s">
+        <v>909</v>
+      </c>
+      <c r="E808">
+        <v>1</v>
+      </c>
+      <c r="F808" t="s">
+        <v>919</v>
+      </c>
+      <c r="G808" t="s">
+        <v>914</v>
+      </c>
+      <c r="H808" t="s">
+        <v>919</v>
+      </c>
+      <c r="I808" t="s">
+        <v>1053</v>
+      </c>
+      <c r="J808" t="s">
+        <v>1034</v>
+      </c>
+    </row>
+    <row r="809" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A809" t="s">
         <v>691</v>
       </c>
@@ -38127,8 +39915,29 @@
       <c r="C809" s="4">
         <v>7551</v>
       </c>
-    </row>
-    <row r="810" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D809" t="s">
+        <v>909</v>
+      </c>
+      <c r="E809">
+        <v>1</v>
+      </c>
+      <c r="F809" t="s">
+        <v>919</v>
+      </c>
+      <c r="G809" t="s">
+        <v>914</v>
+      </c>
+      <c r="H809" t="s">
+        <v>919</v>
+      </c>
+      <c r="I809" t="s">
+        <v>1053</v>
+      </c>
+      <c r="J809" t="s">
+        <v>1035</v>
+      </c>
+    </row>
+    <row r="810" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A810" t="s">
         <v>692</v>
       </c>
@@ -38138,8 +39947,29 @@
       <c r="C810" s="4">
         <v>7976</v>
       </c>
-    </row>
-    <row r="811" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D810" t="s">
+        <v>909</v>
+      </c>
+      <c r="E810">
+        <v>1</v>
+      </c>
+      <c r="F810" t="s">
+        <v>919</v>
+      </c>
+      <c r="G810" t="s">
+        <v>914</v>
+      </c>
+      <c r="H810" t="s">
+        <v>919</v>
+      </c>
+      <c r="I810" t="s">
+        <v>1053</v>
+      </c>
+      <c r="J810" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="811" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A811" t="s">
         <v>693</v>
       </c>
@@ -38149,8 +39979,29 @@
       <c r="C811" s="4">
         <v>7207</v>
       </c>
-    </row>
-    <row r="812" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D811" t="s">
+        <v>909</v>
+      </c>
+      <c r="E811">
+        <v>1</v>
+      </c>
+      <c r="F811" t="s">
+        <v>919</v>
+      </c>
+      <c r="G811" t="s">
+        <v>914</v>
+      </c>
+      <c r="H811" t="s">
+        <v>919</v>
+      </c>
+      <c r="I811" t="s">
+        <v>1053</v>
+      </c>
+      <c r="J811" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="812" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A812" t="s">
         <v>694</v>
       </c>
@@ -38160,8 +40011,29 @@
       <c r="C812" s="4">
         <v>8001</v>
       </c>
-    </row>
-    <row r="813" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D812" t="s">
+        <v>909</v>
+      </c>
+      <c r="E812">
+        <v>1</v>
+      </c>
+      <c r="F812" t="s">
+        <v>919</v>
+      </c>
+      <c r="G812" t="s">
+        <v>914</v>
+      </c>
+      <c r="H812" t="s">
+        <v>919</v>
+      </c>
+      <c r="I812" t="s">
+        <v>1053</v>
+      </c>
+      <c r="J812" t="s">
+        <v>1038</v>
+      </c>
+    </row>
+    <row r="813" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A813" t="s">
         <v>695</v>
       </c>
@@ -38171,8 +40043,29 @@
       <c r="C813" s="4">
         <v>7795</v>
       </c>
-    </row>
-    <row r="814" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D813" t="s">
+        <v>909</v>
+      </c>
+      <c r="E813">
+        <v>1</v>
+      </c>
+      <c r="F813" t="s">
+        <v>919</v>
+      </c>
+      <c r="G813" t="s">
+        <v>914</v>
+      </c>
+      <c r="H813" t="s">
+        <v>919</v>
+      </c>
+      <c r="I813" t="s">
+        <v>1053</v>
+      </c>
+      <c r="J813" t="s">
+        <v>1039</v>
+      </c>
+    </row>
+    <row r="814" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A814" t="s">
         <v>696</v>
       </c>
@@ -38182,8 +40075,29 @@
       <c r="C814" s="4">
         <v>8039</v>
       </c>
-    </row>
-    <row r="815" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D814" t="s">
+        <v>909</v>
+      </c>
+      <c r="E814">
+        <v>1</v>
+      </c>
+      <c r="F814" t="s">
+        <v>919</v>
+      </c>
+      <c r="G814" t="s">
+        <v>914</v>
+      </c>
+      <c r="H814" t="s">
+        <v>919</v>
+      </c>
+      <c r="I814" t="s">
+        <v>1053</v>
+      </c>
+      <c r="J814" t="s">
+        <v>1029</v>
+      </c>
+    </row>
+    <row r="815" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A815" t="s">
         <v>697</v>
       </c>
@@ -38193,8 +40107,29 @@
       <c r="C815" s="4">
         <v>8026</v>
       </c>
-    </row>
-    <row r="816" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D815" t="s">
+        <v>909</v>
+      </c>
+      <c r="E815">
+        <v>1</v>
+      </c>
+      <c r="F815" t="s">
+        <v>919</v>
+      </c>
+      <c r="G815" t="s">
+        <v>914</v>
+      </c>
+      <c r="H815" t="s">
+        <v>919</v>
+      </c>
+      <c r="I815" t="s">
+        <v>1053</v>
+      </c>
+      <c r="J815" t="s">
+        <v>1040</v>
+      </c>
+    </row>
+    <row r="816" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A816" t="s">
         <v>698</v>
       </c>
@@ -38204,8 +40139,29 @@
       <c r="C816" s="4">
         <v>7930</v>
       </c>
-    </row>
-    <row r="817" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D816" t="s">
+        <v>909</v>
+      </c>
+      <c r="E816">
+        <v>1</v>
+      </c>
+      <c r="F816" t="s">
+        <v>919</v>
+      </c>
+      <c r="G816" t="s">
+        <v>914</v>
+      </c>
+      <c r="H816" t="s">
+        <v>919</v>
+      </c>
+      <c r="I816" t="s">
+        <v>1053</v>
+      </c>
+      <c r="J816" t="s">
+        <v>1041</v>
+      </c>
+    </row>
+    <row r="817" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A817" t="s">
         <v>699</v>
       </c>
@@ -38215,8 +40171,29 @@
       <c r="C817" s="4">
         <v>7605</v>
       </c>
-    </row>
-    <row r="818" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D817" t="s">
+        <v>909</v>
+      </c>
+      <c r="E817">
+        <v>1</v>
+      </c>
+      <c r="F817" t="s">
+        <v>919</v>
+      </c>
+      <c r="G817" t="s">
+        <v>914</v>
+      </c>
+      <c r="H817" t="s">
+        <v>919</v>
+      </c>
+      <c r="I817" t="s">
+        <v>1053</v>
+      </c>
+      <c r="J817" t="s">
+        <v>1042</v>
+      </c>
+    </row>
+    <row r="818" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A818" t="s">
         <v>700</v>
       </c>
@@ -38226,8 +40203,29 @@
       <c r="C818" s="4">
         <v>6051</v>
       </c>
-    </row>
-    <row r="819" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D818" t="s">
+        <v>909</v>
+      </c>
+      <c r="E818">
+        <v>1</v>
+      </c>
+      <c r="F818" t="s">
+        <v>919</v>
+      </c>
+      <c r="G818" t="s">
+        <v>914</v>
+      </c>
+      <c r="H818" t="s">
+        <v>919</v>
+      </c>
+      <c r="I818" t="s">
+        <v>1053</v>
+      </c>
+      <c r="J818" t="s">
+        <v>1043</v>
+      </c>
+    </row>
+    <row r="819" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A819" t="s">
         <v>701</v>
       </c>
@@ -38237,8 +40235,29 @@
       <c r="C819" s="4">
         <v>7685</v>
       </c>
-    </row>
-    <row r="820" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D819" t="s">
+        <v>909</v>
+      </c>
+      <c r="E819">
+        <v>1</v>
+      </c>
+      <c r="F819" t="s">
+        <v>919</v>
+      </c>
+      <c r="G819" t="s">
+        <v>914</v>
+      </c>
+      <c r="H819" t="s">
+        <v>919</v>
+      </c>
+      <c r="I819" t="s">
+        <v>1053</v>
+      </c>
+      <c r="J819" t="s">
+        <v>1044</v>
+      </c>
+    </row>
+    <row r="820" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A820" t="s">
         <v>702</v>
       </c>
@@ -38248,8 +40267,29 @@
       <c r="C820" s="4">
         <v>8278</v>
       </c>
-    </row>
-    <row r="821" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D820" t="s">
+        <v>909</v>
+      </c>
+      <c r="E820">
+        <v>1</v>
+      </c>
+      <c r="F820" t="s">
+        <v>919</v>
+      </c>
+      <c r="G820" t="s">
+        <v>914</v>
+      </c>
+      <c r="H820" t="s">
+        <v>919</v>
+      </c>
+      <c r="I820" t="s">
+        <v>1053</v>
+      </c>
+      <c r="J820" t="s">
+        <v>1045</v>
+      </c>
+    </row>
+    <row r="821" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A821" t="s">
         <v>703</v>
       </c>
@@ -38259,8 +40299,29 @@
       <c r="C821" s="4">
         <v>7714</v>
       </c>
-    </row>
-    <row r="822" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D821" t="s">
+        <v>909</v>
+      </c>
+      <c r="E821">
+        <v>1</v>
+      </c>
+      <c r="F821" t="s">
+        <v>919</v>
+      </c>
+      <c r="G821" t="s">
+        <v>914</v>
+      </c>
+      <c r="H821" t="s">
+        <v>919</v>
+      </c>
+      <c r="I821" t="s">
+        <v>1054</v>
+      </c>
+      <c r="J821" t="s">
+        <v>1055</v>
+      </c>
+    </row>
+    <row r="822" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A822" t="s">
         <v>704</v>
       </c>
@@ -38270,8 +40331,29 @@
       <c r="C822" s="4">
         <v>7868</v>
       </c>
-    </row>
-    <row r="823" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D822" t="s">
+        <v>909</v>
+      </c>
+      <c r="E822">
+        <v>1</v>
+      </c>
+      <c r="F822" t="s">
+        <v>919</v>
+      </c>
+      <c r="G822" t="s">
+        <v>914</v>
+      </c>
+      <c r="H822" t="s">
+        <v>919</v>
+      </c>
+      <c r="I822" t="s">
+        <v>1054</v>
+      </c>
+      <c r="J822" t="s">
+        <v>1056</v>
+      </c>
+    </row>
+    <row r="823" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A823" t="s">
         <v>705</v>
       </c>
@@ -38281,8 +40363,29 @@
       <c r="C823" s="4">
         <v>8581</v>
       </c>
-    </row>
-    <row r="824" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D823" t="s">
+        <v>909</v>
+      </c>
+      <c r="E823">
+        <v>1</v>
+      </c>
+      <c r="F823" t="s">
+        <v>919</v>
+      </c>
+      <c r="G823" t="s">
+        <v>914</v>
+      </c>
+      <c r="H823" t="s">
+        <v>919</v>
+      </c>
+      <c r="I823" t="s">
+        <v>1054</v>
+      </c>
+      <c r="J823" t="s">
+        <v>1057</v>
+      </c>
+    </row>
+    <row r="824" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A824" t="s">
         <v>706</v>
       </c>
@@ -38292,8 +40395,29 @@
       <c r="C824" s="4">
         <v>8463</v>
       </c>
-    </row>
-    <row r="825" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D824" t="s">
+        <v>909</v>
+      </c>
+      <c r="E824">
+        <v>1</v>
+      </c>
+      <c r="F824" t="s">
+        <v>919</v>
+      </c>
+      <c r="G824" t="s">
+        <v>914</v>
+      </c>
+      <c r="H824" t="s">
+        <v>919</v>
+      </c>
+      <c r="I824" t="s">
+        <v>1054</v>
+      </c>
+      <c r="J824" t="s">
+        <v>1058</v>
+      </c>
+    </row>
+    <row r="825" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A825" t="s">
         <v>707</v>
       </c>
@@ -38303,8 +40427,29 @@
       <c r="C825" s="4">
         <v>8138</v>
       </c>
-    </row>
-    <row r="826" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D825" t="s">
+        <v>909</v>
+      </c>
+      <c r="E825">
+        <v>1</v>
+      </c>
+      <c r="F825" t="s">
+        <v>919</v>
+      </c>
+      <c r="G825" t="s">
+        <v>914</v>
+      </c>
+      <c r="H825" t="s">
+        <v>919</v>
+      </c>
+      <c r="I825" t="s">
+        <v>1054</v>
+      </c>
+      <c r="J825" t="s">
+        <v>1059</v>
+      </c>
+    </row>
+    <row r="826" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A826" t="s">
         <v>708</v>
       </c>
@@ -38314,8 +40459,29 @@
       <c r="C826" s="4">
         <v>7772</v>
       </c>
-    </row>
-    <row r="827" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D826" t="s">
+        <v>909</v>
+      </c>
+      <c r="E826">
+        <v>1</v>
+      </c>
+      <c r="F826" t="s">
+        <v>919</v>
+      </c>
+      <c r="G826" t="s">
+        <v>914</v>
+      </c>
+      <c r="H826" t="s">
+        <v>919</v>
+      </c>
+      <c r="I826" t="s">
+        <v>1054</v>
+      </c>
+      <c r="J826" t="s">
+        <v>1057</v>
+      </c>
+    </row>
+    <row r="827" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A827" t="s">
         <v>709</v>
       </c>
@@ -38326,7 +40492,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="828" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="828" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A828" t="s">
         <v>710</v>
       </c>
@@ -38336,8 +40502,32 @@
       <c r="C828" s="4">
         <v>7930</v>
       </c>
-    </row>
-    <row r="829" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D828" t="s">
+        <v>909</v>
+      </c>
+      <c r="E828">
+        <v>1</v>
+      </c>
+      <c r="F828" t="s">
+        <v>919</v>
+      </c>
+      <c r="G828" t="s">
+        <v>914</v>
+      </c>
+      <c r="H828" t="s">
+        <v>919</v>
+      </c>
+      <c r="I828" t="s">
+        <v>1054</v>
+      </c>
+      <c r="J828" t="s">
+        <v>1055</v>
+      </c>
+      <c r="K828" t="s">
+        <v>1060</v>
+      </c>
+    </row>
+    <row r="829" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A829" t="s">
         <v>711</v>
       </c>
@@ -38347,8 +40537,32 @@
       <c r="C829" s="4">
         <v>8338</v>
       </c>
-    </row>
-    <row r="830" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D829" t="s">
+        <v>909</v>
+      </c>
+      <c r="E829">
+        <v>1</v>
+      </c>
+      <c r="F829" t="s">
+        <v>919</v>
+      </c>
+      <c r="G829" t="s">
+        <v>914</v>
+      </c>
+      <c r="H829" t="s">
+        <v>919</v>
+      </c>
+      <c r="I829" t="s">
+        <v>1054</v>
+      </c>
+      <c r="J829" t="s">
+        <v>1056</v>
+      </c>
+      <c r="K829" t="s">
+        <v>1060</v>
+      </c>
+    </row>
+    <row r="830" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A830" t="s">
         <v>712</v>
       </c>
@@ -38358,8 +40572,32 @@
       <c r="C830" s="4">
         <v>8929</v>
       </c>
-    </row>
-    <row r="831" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D830" t="s">
+        <v>909</v>
+      </c>
+      <c r="E830">
+        <v>1</v>
+      </c>
+      <c r="F830" t="s">
+        <v>919</v>
+      </c>
+      <c r="G830" t="s">
+        <v>914</v>
+      </c>
+      <c r="H830" t="s">
+        <v>919</v>
+      </c>
+      <c r="I830" t="s">
+        <v>1054</v>
+      </c>
+      <c r="J830" t="s">
+        <v>1057</v>
+      </c>
+      <c r="K830" t="s">
+        <v>1060</v>
+      </c>
+    </row>
+    <row r="831" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A831" t="s">
         <v>713</v>
       </c>
@@ -38369,8 +40607,32 @@
       <c r="C831" s="4">
         <v>8246</v>
       </c>
-    </row>
-    <row r="832" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D831" t="s">
+        <v>909</v>
+      </c>
+      <c r="E831">
+        <v>1</v>
+      </c>
+      <c r="F831" t="s">
+        <v>919</v>
+      </c>
+      <c r="G831" t="s">
+        <v>914</v>
+      </c>
+      <c r="H831" t="s">
+        <v>919</v>
+      </c>
+      <c r="I831" t="s">
+        <v>1054</v>
+      </c>
+      <c r="J831" t="s">
+        <v>1058</v>
+      </c>
+      <c r="K831" t="s">
+        <v>1060</v>
+      </c>
+    </row>
+    <row r="832" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A832" t="s">
         <v>714</v>
       </c>
@@ -38380,8 +40642,32 @@
       <c r="C832" s="4">
         <v>8676</v>
       </c>
-    </row>
-    <row r="833" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D832" t="s">
+        <v>909</v>
+      </c>
+      <c r="E832">
+        <v>1</v>
+      </c>
+      <c r="F832" t="s">
+        <v>919</v>
+      </c>
+      <c r="G832" t="s">
+        <v>914</v>
+      </c>
+      <c r="H832" t="s">
+        <v>919</v>
+      </c>
+      <c r="I832" t="s">
+        <v>1054</v>
+      </c>
+      <c r="J832" t="s">
+        <v>1059</v>
+      </c>
+      <c r="K832" t="s">
+        <v>1060</v>
+      </c>
+    </row>
+    <row r="833" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A833" t="s">
         <v>715</v>
       </c>
@@ -38391,8 +40677,32 @@
       <c r="C833" s="4">
         <v>8108</v>
       </c>
-    </row>
-    <row r="834" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D833" t="s">
+        <v>909</v>
+      </c>
+      <c r="E833">
+        <v>1</v>
+      </c>
+      <c r="F833" t="s">
+        <v>919</v>
+      </c>
+      <c r="G833" t="s">
+        <v>914</v>
+      </c>
+      <c r="H833" t="s">
+        <v>919</v>
+      </c>
+      <c r="I833" t="s">
+        <v>1054</v>
+      </c>
+      <c r="J833" t="s">
+        <v>1057</v>
+      </c>
+      <c r="K833" t="s">
+        <v>1060</v>
+      </c>
+    </row>
+    <row r="834" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A834" t="s">
         <v>716</v>
       </c>
@@ -38402,8 +40712,29 @@
       <c r="C834" s="4">
         <v>12790</v>
       </c>
-    </row>
-    <row r="835" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D834" t="s">
+        <v>909</v>
+      </c>
+      <c r="E834">
+        <v>1</v>
+      </c>
+      <c r="F834" t="s">
+        <v>919</v>
+      </c>
+      <c r="G834" t="s">
+        <v>914</v>
+      </c>
+      <c r="H834" t="s">
+        <v>919</v>
+      </c>
+      <c r="I834" t="s">
+        <v>1061</v>
+      </c>
+      <c r="J834" t="s">
+        <v>1034</v>
+      </c>
+    </row>
+    <row r="835" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A835" t="s">
         <v>717</v>
       </c>
@@ -38413,8 +40744,29 @@
       <c r="C835" s="4">
         <v>12606</v>
       </c>
-    </row>
-    <row r="836" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D835" t="s">
+        <v>909</v>
+      </c>
+      <c r="E835">
+        <v>1</v>
+      </c>
+      <c r="F835" t="s">
+        <v>919</v>
+      </c>
+      <c r="G835" t="s">
+        <v>914</v>
+      </c>
+      <c r="H835" t="s">
+        <v>919</v>
+      </c>
+      <c r="I835" t="s">
+        <v>1061</v>
+      </c>
+      <c r="J835" t="s">
+        <v>1035</v>
+      </c>
+    </row>
+    <row r="836" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A836" t="s">
         <v>718</v>
       </c>
@@ -38424,8 +40776,29 @@
       <c r="C836" s="4">
         <v>12526</v>
       </c>
-    </row>
-    <row r="837" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D836" t="s">
+        <v>909</v>
+      </c>
+      <c r="E836">
+        <v>1</v>
+      </c>
+      <c r="F836" t="s">
+        <v>919</v>
+      </c>
+      <c r="G836" t="s">
+        <v>914</v>
+      </c>
+      <c r="H836" t="s">
+        <v>919</v>
+      </c>
+      <c r="I836" t="s">
+        <v>1061</v>
+      </c>
+      <c r="J836" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="837" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A837" t="s">
         <v>719</v>
       </c>
@@ -38435,8 +40808,29 @@
       <c r="C837" s="4">
         <v>12797</v>
       </c>
-    </row>
-    <row r="838" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D837" t="s">
+        <v>909</v>
+      </c>
+      <c r="E837">
+        <v>1</v>
+      </c>
+      <c r="F837" t="s">
+        <v>919</v>
+      </c>
+      <c r="G837" t="s">
+        <v>914</v>
+      </c>
+      <c r="H837" t="s">
+        <v>919</v>
+      </c>
+      <c r="I837" t="s">
+        <v>1061</v>
+      </c>
+      <c r="J837" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="838" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A838" t="s">
         <v>720</v>
       </c>
@@ -38446,8 +40840,29 @@
       <c r="C838" s="4">
         <v>12942</v>
       </c>
-    </row>
-    <row r="839" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D838" t="s">
+        <v>909</v>
+      </c>
+      <c r="E838">
+        <v>1</v>
+      </c>
+      <c r="F838" t="s">
+        <v>919</v>
+      </c>
+      <c r="G838" t="s">
+        <v>914</v>
+      </c>
+      <c r="H838" t="s">
+        <v>919</v>
+      </c>
+      <c r="I838" t="s">
+        <v>1061</v>
+      </c>
+      <c r="J838" t="s">
+        <v>1038</v>
+      </c>
+    </row>
+    <row r="839" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A839" t="s">
         <v>721</v>
       </c>
@@ -38457,8 +40872,29 @@
       <c r="C839" s="4">
         <v>12750</v>
       </c>
-    </row>
-    <row r="840" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D839" t="s">
+        <v>909</v>
+      </c>
+      <c r="E839">
+        <v>1</v>
+      </c>
+      <c r="F839" t="s">
+        <v>919</v>
+      </c>
+      <c r="G839" t="s">
+        <v>914</v>
+      </c>
+      <c r="H839" t="s">
+        <v>919</v>
+      </c>
+      <c r="I839" t="s">
+        <v>1061</v>
+      </c>
+      <c r="J839" t="s">
+        <v>1039</v>
+      </c>
+    </row>
+    <row r="840" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A840" t="s">
         <v>722</v>
       </c>
@@ -38468,8 +40904,29 @@
       <c r="C840" s="4">
         <v>11760</v>
       </c>
-    </row>
-    <row r="841" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D840" t="s">
+        <v>909</v>
+      </c>
+      <c r="E840">
+        <v>1</v>
+      </c>
+      <c r="F840" t="s">
+        <v>919</v>
+      </c>
+      <c r="G840" t="s">
+        <v>914</v>
+      </c>
+      <c r="H840" t="s">
+        <v>919</v>
+      </c>
+      <c r="I840" t="s">
+        <v>1061</v>
+      </c>
+      <c r="J840" t="s">
+        <v>1029</v>
+      </c>
+    </row>
+    <row r="841" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A841" t="s">
         <v>723</v>
       </c>
@@ -38479,8 +40936,29 @@
       <c r="C841" s="4">
         <v>11873</v>
       </c>
-    </row>
-    <row r="842" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D841" t="s">
+        <v>909</v>
+      </c>
+      <c r="E841">
+        <v>1</v>
+      </c>
+      <c r="F841" t="s">
+        <v>919</v>
+      </c>
+      <c r="G841" t="s">
+        <v>914</v>
+      </c>
+      <c r="H841" t="s">
+        <v>919</v>
+      </c>
+      <c r="I841" t="s">
+        <v>1061</v>
+      </c>
+      <c r="J841" t="s">
+        <v>1040</v>
+      </c>
+    </row>
+    <row r="842" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A842" t="s">
         <v>724</v>
       </c>
@@ -38490,8 +40968,29 @@
       <c r="C842" s="4">
         <v>12070</v>
       </c>
-    </row>
-    <row r="843" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D842" t="s">
+        <v>909</v>
+      </c>
+      <c r="E842">
+        <v>1</v>
+      </c>
+      <c r="F842" t="s">
+        <v>919</v>
+      </c>
+      <c r="G842" t="s">
+        <v>914</v>
+      </c>
+      <c r="H842" t="s">
+        <v>919</v>
+      </c>
+      <c r="I842" t="s">
+        <v>1061</v>
+      </c>
+      <c r="J842" t="s">
+        <v>1041</v>
+      </c>
+    </row>
+    <row r="843" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A843" t="s">
         <v>725</v>
       </c>
@@ -38501,8 +41000,29 @@
       <c r="C843" s="4">
         <v>12169</v>
       </c>
-    </row>
-    <row r="844" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D843" t="s">
+        <v>909</v>
+      </c>
+      <c r="E843">
+        <v>1</v>
+      </c>
+      <c r="F843" t="s">
+        <v>919</v>
+      </c>
+      <c r="G843" t="s">
+        <v>914</v>
+      </c>
+      <c r="H843" t="s">
+        <v>919</v>
+      </c>
+      <c r="I843" t="s">
+        <v>1061</v>
+      </c>
+      <c r="J843" t="s">
+        <v>1042</v>
+      </c>
+    </row>
+    <row r="844" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A844" t="s">
         <v>726</v>
       </c>
@@ -38512,8 +41032,29 @@
       <c r="C844" s="4">
         <v>11962</v>
       </c>
-    </row>
-    <row r="845" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D844" t="s">
+        <v>909</v>
+      </c>
+      <c r="E844">
+        <v>1</v>
+      </c>
+      <c r="F844" t="s">
+        <v>919</v>
+      </c>
+      <c r="G844" t="s">
+        <v>914</v>
+      </c>
+      <c r="H844" t="s">
+        <v>919</v>
+      </c>
+      <c r="I844" t="s">
+        <v>1061</v>
+      </c>
+      <c r="J844" t="s">
+        <v>1043</v>
+      </c>
+    </row>
+    <row r="845" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A845" t="s">
         <v>727</v>
       </c>
@@ -38523,8 +41064,29 @@
       <c r="C845" s="4">
         <v>12213</v>
       </c>
-    </row>
-    <row r="846" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D845" t="s">
+        <v>909</v>
+      </c>
+      <c r="E845">
+        <v>1</v>
+      </c>
+      <c r="F845" t="s">
+        <v>919</v>
+      </c>
+      <c r="G845" t="s">
+        <v>914</v>
+      </c>
+      <c r="H845" t="s">
+        <v>919</v>
+      </c>
+      <c r="I845" t="s">
+        <v>1061</v>
+      </c>
+      <c r="J845" t="s">
+        <v>1044</v>
+      </c>
+    </row>
+    <row r="846" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A846" t="s">
         <v>728</v>
       </c>
@@ -38534,8 +41096,29 @@
       <c r="C846" s="4">
         <v>12166</v>
       </c>
-    </row>
-    <row r="847" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D846" t="s">
+        <v>909</v>
+      </c>
+      <c r="E846">
+        <v>1</v>
+      </c>
+      <c r="F846" t="s">
+        <v>919</v>
+      </c>
+      <c r="G846" t="s">
+        <v>914</v>
+      </c>
+      <c r="H846" t="s">
+        <v>919</v>
+      </c>
+      <c r="I846" t="s">
+        <v>1061</v>
+      </c>
+      <c r="J846" t="s">
+        <v>1045</v>
+      </c>
+    </row>
+    <row r="847" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A847" t="s">
         <v>729</v>
       </c>
@@ -38545,8 +41128,29 @@
       <c r="C847" s="4">
         <v>15464</v>
       </c>
-    </row>
-    <row r="848" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D847" t="s">
+        <v>909</v>
+      </c>
+      <c r="E847">
+        <v>1</v>
+      </c>
+      <c r="F847" t="s">
+        <v>919</v>
+      </c>
+      <c r="G847" t="s">
+        <v>914</v>
+      </c>
+      <c r="H847" t="s">
+        <v>919</v>
+      </c>
+      <c r="I847" t="s">
+        <v>1062</v>
+      </c>
+      <c r="J847" t="s">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="848" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A848" t="s">
         <v>730</v>
       </c>
@@ -38556,8 +41160,29 @@
       <c r="C848" s="4">
         <v>13171</v>
       </c>
-    </row>
-    <row r="849" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D848" t="s">
+        <v>909</v>
+      </c>
+      <c r="E848">
+        <v>1</v>
+      </c>
+      <c r="F848" t="s">
+        <v>919</v>
+      </c>
+      <c r="G848" t="s">
+        <v>914</v>
+      </c>
+      <c r="H848" t="s">
+        <v>919</v>
+      </c>
+      <c r="I848" t="s">
+        <v>1062</v>
+      </c>
+      <c r="J848" t="s">
+        <v>1029</v>
+      </c>
+    </row>
+    <row r="849" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A849" t="s">
         <v>731</v>
       </c>
@@ -38567,8 +41192,29 @@
       <c r="C849" s="4">
         <v>14913</v>
       </c>
-    </row>
-    <row r="850" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D849" t="s">
+        <v>909</v>
+      </c>
+      <c r="E849">
+        <v>1</v>
+      </c>
+      <c r="F849" t="s">
+        <v>919</v>
+      </c>
+      <c r="G849" t="s">
+        <v>914</v>
+      </c>
+      <c r="H849" t="s">
+        <v>919</v>
+      </c>
+      <c r="I849" t="s">
+        <v>1062</v>
+      </c>
+      <c r="J849" t="s">
+        <v>1030</v>
+      </c>
+    </row>
+    <row r="850" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A850" t="s">
         <v>732</v>
       </c>
@@ -38578,8 +41224,29 @@
       <c r="C850" s="4">
         <v>25070</v>
       </c>
-    </row>
-    <row r="851" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D850" t="s">
+        <v>909</v>
+      </c>
+      <c r="E850">
+        <v>6</v>
+      </c>
+      <c r="F850" t="s">
+        <v>919</v>
+      </c>
+      <c r="G850" t="s">
+        <v>919</v>
+      </c>
+      <c r="H850" t="s">
+        <v>919</v>
+      </c>
+      <c r="I850" t="s">
+        <v>1063</v>
+      </c>
+      <c r="J850" t="s">
+        <v>1064</v>
+      </c>
+    </row>
+    <row r="851" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A851" t="s">
         <v>733</v>
       </c>
@@ -38589,8 +41256,29 @@
       <c r="C851" s="4">
         <v>8578</v>
       </c>
-    </row>
-    <row r="852" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D851" t="s">
+        <v>909</v>
+      </c>
+      <c r="E851">
+        <v>6</v>
+      </c>
+      <c r="F851" t="s">
+        <v>919</v>
+      </c>
+      <c r="G851" t="s">
+        <v>919</v>
+      </c>
+      <c r="H851" t="s">
+        <v>919</v>
+      </c>
+      <c r="I851" t="s">
+        <v>1063</v>
+      </c>
+      <c r="J851" t="s">
+        <v>1065</v>
+      </c>
+    </row>
+    <row r="852" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A852" t="s">
         <v>734</v>
       </c>
@@ -38600,8 +41288,29 @@
       <c r="C852" s="4">
         <v>8732</v>
       </c>
-    </row>
-    <row r="853" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D852" t="s">
+        <v>909</v>
+      </c>
+      <c r="E852">
+        <v>6</v>
+      </c>
+      <c r="F852" t="s">
+        <v>919</v>
+      </c>
+      <c r="G852" t="s">
+        <v>919</v>
+      </c>
+      <c r="H852" t="s">
+        <v>919</v>
+      </c>
+      <c r="I852" t="s">
+        <v>1063</v>
+      </c>
+      <c r="J852" t="s">
+        <v>1066</v>
+      </c>
+    </row>
+    <row r="853" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A853" t="s">
         <v>735</v>
       </c>
@@ -38611,8 +41320,29 @@
       <c r="C853" s="4">
         <v>16214</v>
       </c>
-    </row>
-    <row r="854" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D853" t="s">
+        <v>909</v>
+      </c>
+      <c r="E853">
+        <v>6</v>
+      </c>
+      <c r="F853" t="s">
+        <v>919</v>
+      </c>
+      <c r="G853" t="s">
+        <v>919</v>
+      </c>
+      <c r="H853" t="s">
+        <v>919</v>
+      </c>
+      <c r="I853" t="s">
+        <v>1063</v>
+      </c>
+      <c r="J853" t="s">
+        <v>1067</v>
+      </c>
+    </row>
+    <row r="854" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A854" t="s">
         <v>736</v>
       </c>
@@ -38622,8 +41352,29 @@
       <c r="C854" s="4">
         <v>30592</v>
       </c>
-    </row>
-    <row r="855" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D854" t="s">
+        <v>909</v>
+      </c>
+      <c r="E854">
+        <v>6</v>
+      </c>
+      <c r="F854" t="s">
+        <v>919</v>
+      </c>
+      <c r="G854" t="s">
+        <v>919</v>
+      </c>
+      <c r="H854" t="s">
+        <v>919</v>
+      </c>
+      <c r="I854" t="s">
+        <v>1063</v>
+      </c>
+      <c r="J854" t="s">
+        <v>1068</v>
+      </c>
+    </row>
+    <row r="855" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A855" t="s">
         <v>737</v>
       </c>
@@ -38633,8 +41384,29 @@
       <c r="C855" s="4">
         <v>9177</v>
       </c>
-    </row>
-    <row r="856" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D855" t="s">
+        <v>909</v>
+      </c>
+      <c r="E855">
+        <v>6</v>
+      </c>
+      <c r="F855" t="s">
+        <v>919</v>
+      </c>
+      <c r="G855" t="s">
+        <v>919</v>
+      </c>
+      <c r="H855" t="s">
+        <v>919</v>
+      </c>
+      <c r="I855" t="s">
+        <v>1063</v>
+      </c>
+      <c r="J855" t="s">
+        <v>1064</v>
+      </c>
+    </row>
+    <row r="856" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A856" t="s">
         <v>738</v>
       </c>
@@ -38644,8 +41416,29 @@
       <c r="C856" s="4">
         <v>8410</v>
       </c>
-    </row>
-    <row r="857" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D856" t="s">
+        <v>909</v>
+      </c>
+      <c r="E856">
+        <v>6</v>
+      </c>
+      <c r="F856" t="s">
+        <v>919</v>
+      </c>
+      <c r="G856" t="s">
+        <v>919</v>
+      </c>
+      <c r="H856" t="s">
+        <v>919</v>
+      </c>
+      <c r="I856" t="s">
+        <v>1063</v>
+      </c>
+      <c r="J856" t="s">
+        <v>1066</v>
+      </c>
+    </row>
+    <row r="857" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A857" t="s">
         <v>739</v>
       </c>
@@ -38655,8 +41448,29 @@
       <c r="C857" s="4">
         <v>19433</v>
       </c>
-    </row>
-    <row r="858" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D857" t="s">
+        <v>909</v>
+      </c>
+      <c r="E857">
+        <v>6</v>
+      </c>
+      <c r="F857" t="s">
+        <v>919</v>
+      </c>
+      <c r="G857" t="s">
+        <v>919</v>
+      </c>
+      <c r="H857" t="s">
+        <v>919</v>
+      </c>
+      <c r="I857" t="s">
+        <v>1063</v>
+      </c>
+      <c r="J857" t="s">
+        <v>1064</v>
+      </c>
+    </row>
+    <row r="858" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A858" t="s">
         <v>740</v>
       </c>
@@ -38666,8 +41480,29 @@
       <c r="C858" s="4">
         <v>15550</v>
       </c>
-    </row>
-    <row r="859" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D858" t="s">
+        <v>909</v>
+      </c>
+      <c r="E858">
+        <v>6</v>
+      </c>
+      <c r="F858" t="s">
+        <v>919</v>
+      </c>
+      <c r="G858" t="s">
+        <v>919</v>
+      </c>
+      <c r="H858" t="s">
+        <v>919</v>
+      </c>
+      <c r="I858" t="s">
+        <v>1063</v>
+      </c>
+      <c r="J858" t="s">
+        <v>1064</v>
+      </c>
+    </row>
+    <row r="859" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A859" t="s">
         <v>741</v>
       </c>
@@ -38677,8 +41512,29 @@
       <c r="C859" s="4">
         <v>7700</v>
       </c>
-    </row>
-    <row r="860" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D859" t="s">
+        <v>909</v>
+      </c>
+      <c r="E859">
+        <v>6</v>
+      </c>
+      <c r="F859" t="s">
+        <v>919</v>
+      </c>
+      <c r="G859" t="s">
+        <v>919</v>
+      </c>
+      <c r="H859" t="s">
+        <v>919</v>
+      </c>
+      <c r="I859" t="s">
+        <v>1063</v>
+      </c>
+      <c r="J859" t="s">
+        <v>1064</v>
+      </c>
+    </row>
+    <row r="860" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A860" t="s">
         <v>742</v>
       </c>
@@ -38688,8 +41544,29 @@
       <c r="C860" s="4">
         <v>26117</v>
       </c>
-    </row>
-    <row r="861" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D860" t="s">
+        <v>909</v>
+      </c>
+      <c r="E860">
+        <v>6</v>
+      </c>
+      <c r="F860" t="s">
+        <v>919</v>
+      </c>
+      <c r="G860" t="s">
+        <v>919</v>
+      </c>
+      <c r="H860" t="s">
+        <v>919</v>
+      </c>
+      <c r="I860" t="s">
+        <v>1063</v>
+      </c>
+      <c r="J860" t="s">
+        <v>1068</v>
+      </c>
+    </row>
+    <row r="861" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A861" t="s">
         <v>743</v>
       </c>
@@ -38699,8 +41576,29 @@
       <c r="C861" s="4">
         <v>13325</v>
       </c>
-    </row>
-    <row r="862" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D861" t="s">
+        <v>909</v>
+      </c>
+      <c r="E861">
+        <v>6</v>
+      </c>
+      <c r="F861" t="s">
+        <v>919</v>
+      </c>
+      <c r="G861" t="s">
+        <v>919</v>
+      </c>
+      <c r="H861" t="s">
+        <v>919</v>
+      </c>
+      <c r="I861" t="s">
+        <v>1063</v>
+      </c>
+      <c r="J861" t="s">
+        <v>1069</v>
+      </c>
+    </row>
+    <row r="862" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A862" t="s">
         <v>744</v>
       </c>
@@ -38710,8 +41608,29 @@
       <c r="C862" s="4">
         <v>28862</v>
       </c>
-    </row>
-    <row r="863" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D862" t="s">
+        <v>909</v>
+      </c>
+      <c r="E862">
+        <v>6</v>
+      </c>
+      <c r="F862" t="s">
+        <v>919</v>
+      </c>
+      <c r="G862" t="s">
+        <v>919</v>
+      </c>
+      <c r="H862" t="s">
+        <v>919</v>
+      </c>
+      <c r="I862" t="s">
+        <v>1063</v>
+      </c>
+      <c r="J862" t="s">
+        <v>1064</v>
+      </c>
+    </row>
+    <row r="863" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A863" t="s">
         <v>745</v>
       </c>
@@ -38721,8 +41640,29 @@
       <c r="C863" s="4">
         <v>14296</v>
       </c>
-    </row>
-    <row r="864" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D863" t="s">
+        <v>909</v>
+      </c>
+      <c r="E863">
+        <v>6</v>
+      </c>
+      <c r="F863" t="s">
+        <v>919</v>
+      </c>
+      <c r="G863" t="s">
+        <v>919</v>
+      </c>
+      <c r="H863" t="s">
+        <v>919</v>
+      </c>
+      <c r="I863" t="s">
+        <v>1063</v>
+      </c>
+      <c r="J863" t="s">
+        <v>1069</v>
+      </c>
+    </row>
+    <row r="864" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A864" t="s">
         <v>746</v>
       </c>
@@ -38731,6 +41671,27 @@
       </c>
       <c r="C864" s="4">
         <v>63519</v>
+      </c>
+      <c r="D864" t="s">
+        <v>909</v>
+      </c>
+      <c r="E864">
+        <v>6</v>
+      </c>
+      <c r="F864" t="s">
+        <v>919</v>
+      </c>
+      <c r="G864" t="s">
+        <v>919</v>
+      </c>
+      <c r="H864" t="s">
+        <v>919</v>
+      </c>
+      <c r="I864" t="s">
+        <v>1063</v>
+      </c>
+      <c r="J864" t="s">
+        <v>1070</v>
       </c>
     </row>
     <row r="865" spans="1:10" x14ac:dyDescent="0.25">
@@ -38743,6 +41704,27 @@
       <c r="C865" s="4">
         <v>21951</v>
       </c>
+      <c r="D865" t="s">
+        <v>909</v>
+      </c>
+      <c r="E865">
+        <v>6</v>
+      </c>
+      <c r="F865" t="s">
+        <v>919</v>
+      </c>
+      <c r="G865" t="s">
+        <v>919</v>
+      </c>
+      <c r="H865" t="s">
+        <v>919</v>
+      </c>
+      <c r="I865" t="s">
+        <v>1063</v>
+      </c>
+      <c r="J865" t="s">
+        <v>1070</v>
+      </c>
     </row>
     <row r="866" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A866" t="s">
@@ -38754,6 +41736,27 @@
       <c r="C866" s="4">
         <v>21596</v>
       </c>
+      <c r="D866" t="s">
+        <v>909</v>
+      </c>
+      <c r="E866">
+        <v>6</v>
+      </c>
+      <c r="F866" t="s">
+        <v>919</v>
+      </c>
+      <c r="G866" t="s">
+        <v>919</v>
+      </c>
+      <c r="H866" t="s">
+        <v>919</v>
+      </c>
+      <c r="I866" t="s">
+        <v>1063</v>
+      </c>
+      <c r="J866" t="s">
+        <v>1070</v>
+      </c>
     </row>
     <row r="867" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A867" t="s">
@@ -38765,6 +41768,27 @@
       <c r="C867" s="4">
         <v>21357</v>
       </c>
+      <c r="D867" t="s">
+        <v>909</v>
+      </c>
+      <c r="E867">
+        <v>6</v>
+      </c>
+      <c r="F867" t="s">
+        <v>919</v>
+      </c>
+      <c r="G867" t="s">
+        <v>919</v>
+      </c>
+      <c r="H867" t="s">
+        <v>919</v>
+      </c>
+      <c r="I867" t="s">
+        <v>1063</v>
+      </c>
+      <c r="J867" t="s">
+        <v>1070</v>
+      </c>
     </row>
     <row r="868" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A868" t="s">
@@ -38776,6 +41800,27 @@
       <c r="C868" s="4">
         <v>22222</v>
       </c>
+      <c r="D868" t="s">
+        <v>909</v>
+      </c>
+      <c r="E868">
+        <v>6</v>
+      </c>
+      <c r="F868" t="s">
+        <v>919</v>
+      </c>
+      <c r="G868" t="s">
+        <v>919</v>
+      </c>
+      <c r="H868" t="s">
+        <v>919</v>
+      </c>
+      <c r="I868" t="s">
+        <v>1063</v>
+      </c>
+      <c r="J868" t="s">
+        <v>1070</v>
+      </c>
     </row>
     <row r="869" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A869" t="s">
@@ -38787,6 +41832,27 @@
       <c r="C869" s="4">
         <v>21541</v>
       </c>
+      <c r="D869" t="s">
+        <v>909</v>
+      </c>
+      <c r="E869">
+        <v>6</v>
+      </c>
+      <c r="F869" t="s">
+        <v>919</v>
+      </c>
+      <c r="G869" t="s">
+        <v>919</v>
+      </c>
+      <c r="H869" t="s">
+        <v>919</v>
+      </c>
+      <c r="I869" t="s">
+        <v>1063</v>
+      </c>
+      <c r="J869" t="s">
+        <v>1069</v>
+      </c>
     </row>
     <row r="870" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A870" t="s">
@@ -38809,6 +41875,27 @@
       <c r="C871" s="4">
         <v>3690</v>
       </c>
+      <c r="D871" t="s">
+        <v>909</v>
+      </c>
+      <c r="E871">
+        <v>18</v>
+      </c>
+      <c r="F871" t="s">
+        <v>914</v>
+      </c>
+      <c r="G871" t="s">
+        <v>919</v>
+      </c>
+      <c r="H871" t="s">
+        <v>919</v>
+      </c>
+      <c r="I871" t="s">
+        <v>929</v>
+      </c>
+      <c r="J871" t="s">
+        <v>1072</v>
+      </c>
     </row>
     <row r="872" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A872" t="s">
@@ -38819,6 +41906,27 @@
       </c>
       <c r="C872" s="4">
         <v>3690</v>
+      </c>
+      <c r="D872" t="s">
+        <v>909</v>
+      </c>
+      <c r="E872">
+        <v>18</v>
+      </c>
+      <c r="F872" t="s">
+        <v>914</v>
+      </c>
+      <c r="G872" t="s">
+        <v>919</v>
+      </c>
+      <c r="H872" t="s">
+        <v>919</v>
+      </c>
+      <c r="I872" t="s">
+        <v>929</v>
+      </c>
+      <c r="J872" t="s">
+        <v>1071</v>
       </c>
     </row>
     <row r="873" spans="1:10" x14ac:dyDescent="0.25">
@@ -39659,7 +42767,7 @@
         <v>991</v>
       </c>
       <c r="B4" s="5">
-        <v>583</v>
+        <v>718</v>
       </c>
       <c r="C4" s="5">
         <v>746</v>
@@ -39681,7 +42789,7 @@
         <v>990</v>
       </c>
       <c r="B6" s="5">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C6" s="5">
         <v>152</v>
@@ -39692,7 +42800,7 @@
         <v>989</v>
       </c>
       <c r="B7" s="5">
-        <v>671</v>
+        <v>808</v>
       </c>
       <c r="C7" s="5">
         <v>899</v>

--- a/images/image manifest.xlsx
+++ b/images/image manifest.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\Github\CS-Graphics\images\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F75FCEE-8ACC-4451-B0FD-493E046270F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7ECD5F00-5778-4270-954D-28DC256D0E05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1320" yWindow="615" windowWidth="15930" windowHeight="8145" activeTab="1" xr2:uid="{620D0F7A-D0D3-4EA0-8A4D-C0BB25CE06A6}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{620D0F7A-D0D3-4EA0-8A4D-C0BB25CE06A6}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7367" uniqueCount="1153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8773" uniqueCount="1424">
   <si>
     <t>Filename</t>
   </si>
@@ -3500,6 +3500,819 @@
   </si>
   <si>
     <t>Cursor positions (Hover)</t>
+  </si>
+  <si>
+    <t>BABY.FLX</t>
+  </si>
+  <si>
+    <t>BGMS.FLX</t>
+  </si>
+  <si>
+    <t>BGMSH01A.FLX</t>
+  </si>
+  <si>
+    <t>BGMSH01B.FLX</t>
+  </si>
+  <si>
+    <t>BGMSH01C.FLX</t>
+  </si>
+  <si>
+    <t>BGMSH01D.FLX</t>
+  </si>
+  <si>
+    <t>BGMSH02A.FLX</t>
+  </si>
+  <si>
+    <t>BGMSH02B.FLX</t>
+  </si>
+  <si>
+    <t>BGMSH02C.FLX</t>
+  </si>
+  <si>
+    <t>BGMSH02D.FLX</t>
+  </si>
+  <si>
+    <t>BGMSH03A.FLX</t>
+  </si>
+  <si>
+    <t>BGMSH03B.FLX</t>
+  </si>
+  <si>
+    <t>BGMSH03C.FLX</t>
+  </si>
+  <si>
+    <t>BGMSH03D.FLX</t>
+  </si>
+  <si>
+    <t>BGMSH04A.FLX</t>
+  </si>
+  <si>
+    <t>BGMSH04B.FLX</t>
+  </si>
+  <si>
+    <t>BGMSH04C.FLX</t>
+  </si>
+  <si>
+    <t>BGMSH04D.FLX</t>
+  </si>
+  <si>
+    <t>BGMSH05A.FLX</t>
+  </si>
+  <si>
+    <t>BGMSH05B.FLX</t>
+  </si>
+  <si>
+    <t>BGMSH05C.FLX</t>
+  </si>
+  <si>
+    <t>BGMSH05D.FLX</t>
+  </si>
+  <si>
+    <t>BGMSH06A.FLX</t>
+  </si>
+  <si>
+    <t>BGMSH06B.FLX</t>
+  </si>
+  <si>
+    <t>BGMSH06C.FLX</t>
+  </si>
+  <si>
+    <t>BGMSH06D.FLX</t>
+  </si>
+  <si>
+    <t>BGMSH07A.FLX</t>
+  </si>
+  <si>
+    <t>BGMSH07B.FLX</t>
+  </si>
+  <si>
+    <t>BGMSH07C.FLX</t>
+  </si>
+  <si>
+    <t>BGMSH07D.FLX</t>
+  </si>
+  <si>
+    <t>BGMSH08A.FLX</t>
+  </si>
+  <si>
+    <t>BGMSH08B.FLX</t>
+  </si>
+  <si>
+    <t>BGMSH08C.FLX</t>
+  </si>
+  <si>
+    <t>BGMSH08D.FLX</t>
+  </si>
+  <si>
+    <t>BGMSH09A.FLX</t>
+  </si>
+  <si>
+    <t>BGMSH09B.FLX</t>
+  </si>
+  <si>
+    <t>BGMSH09C.FLX</t>
+  </si>
+  <si>
+    <t>BGMSH09D.FLX</t>
+  </si>
+  <si>
+    <t>BGMSH10A.FLX</t>
+  </si>
+  <si>
+    <t>BGMSH10B.FLX</t>
+  </si>
+  <si>
+    <t>BGMSH10C.FLX</t>
+  </si>
+  <si>
+    <t>BGMSH10D.FLX</t>
+  </si>
+  <si>
+    <t>BGMSH11A.FLX</t>
+  </si>
+  <si>
+    <t>BGMSH11B.FLX</t>
+  </si>
+  <si>
+    <t>BGMSH11C.FLX</t>
+  </si>
+  <si>
+    <t>BGMSH11D.FLX</t>
+  </si>
+  <si>
+    <t>BGMSH12A.FLX</t>
+  </si>
+  <si>
+    <t>BGMSH12B.FLX</t>
+  </si>
+  <si>
+    <t>BGMSH12C.FLX</t>
+  </si>
+  <si>
+    <t>BGMSH12D.FLX</t>
+  </si>
+  <si>
+    <t>BGMSH13A.FLX</t>
+  </si>
+  <si>
+    <t>BGMSH13B.FLX</t>
+  </si>
+  <si>
+    <t>BGMSH13C.FLX</t>
+  </si>
+  <si>
+    <t>BGMSH13D.FLX</t>
+  </si>
+  <si>
+    <t>BGMSH14A.FLX</t>
+  </si>
+  <si>
+    <t>BGMSH14B.FLX</t>
+  </si>
+  <si>
+    <t>BGMSH14C.FLX</t>
+  </si>
+  <si>
+    <t>BGMSH14D.FLX</t>
+  </si>
+  <si>
+    <t>BGMSH15A.FLX</t>
+  </si>
+  <si>
+    <t>BGMSH15B.FLX</t>
+  </si>
+  <si>
+    <t>BGMSH15C.FLX</t>
+  </si>
+  <si>
+    <t>BGMSH15D.FLX</t>
+  </si>
+  <si>
+    <t>BGMSH16A.FLX</t>
+  </si>
+  <si>
+    <t>BGMSH16B.FLX</t>
+  </si>
+  <si>
+    <t>BGMSH16C.FLX</t>
+  </si>
+  <si>
+    <t>BGMSH16D.FLX</t>
+  </si>
+  <si>
+    <t>BGMSH17A.FLX</t>
+  </si>
+  <si>
+    <t>BGMSH17B.FLX</t>
+  </si>
+  <si>
+    <t>BGMSH17C.FLX</t>
+  </si>
+  <si>
+    <t>BGMSH17D.FLX</t>
+  </si>
+  <si>
+    <t>BGMSH18A.FLX</t>
+  </si>
+  <si>
+    <t>BGMSH18B.FLX</t>
+  </si>
+  <si>
+    <t>BGMSH18C.FLX</t>
+  </si>
+  <si>
+    <t>BGMSH18D.FLX</t>
+  </si>
+  <si>
+    <t>BGMSH19A.FLX</t>
+  </si>
+  <si>
+    <t>BGMSH19B.FLX</t>
+  </si>
+  <si>
+    <t>BGMSH19C.FLX</t>
+  </si>
+  <si>
+    <t>BGMSH19D.FLX</t>
+  </si>
+  <si>
+    <t>BGMSH20A.FLX</t>
+  </si>
+  <si>
+    <t>BGMSH20B.FLX</t>
+  </si>
+  <si>
+    <t>BGMSH20C.FLX</t>
+  </si>
+  <si>
+    <t>BGMSH20D.FLX</t>
+  </si>
+  <si>
+    <t>BGMSH21A.FLX</t>
+  </si>
+  <si>
+    <t>BGMSH21B.FLX</t>
+  </si>
+  <si>
+    <t>BGMSH21C.FLX</t>
+  </si>
+  <si>
+    <t>BGMSH21D.FLX</t>
+  </si>
+  <si>
+    <t>BGMSH22A.FLX</t>
+  </si>
+  <si>
+    <t>BGMSH22B.FLX</t>
+  </si>
+  <si>
+    <t>BGMSH22C.FLX</t>
+  </si>
+  <si>
+    <t>BGMSH22D.FLX</t>
+  </si>
+  <si>
+    <t>BGMSH23A.FLX</t>
+  </si>
+  <si>
+    <t>BGMSH23B.FLX</t>
+  </si>
+  <si>
+    <t>BGMSH23C.FLX</t>
+  </si>
+  <si>
+    <t>BGMSH23D.FLX</t>
+  </si>
+  <si>
+    <t>BGMSH24A.FLX</t>
+  </si>
+  <si>
+    <t>BGMSH24B.FLX</t>
+  </si>
+  <si>
+    <t>BGMSH24C.FLX</t>
+  </si>
+  <si>
+    <t>BGMSH24D.FLX</t>
+  </si>
+  <si>
+    <t>BGMSH25A.FLX</t>
+  </si>
+  <si>
+    <t>BGMSH25B.FLX</t>
+  </si>
+  <si>
+    <t>BGMSH25C.FLX</t>
+  </si>
+  <si>
+    <t>BGMSH25D.FLX</t>
+  </si>
+  <si>
+    <t>BGMSH26A.FLX</t>
+  </si>
+  <si>
+    <t>BGMSH26B.FLX</t>
+  </si>
+  <si>
+    <t>BGMSH26C.FLX</t>
+  </si>
+  <si>
+    <t>BGMSH26D.FLX</t>
+  </si>
+  <si>
+    <t>BGMSH27A.FLX</t>
+  </si>
+  <si>
+    <t>BGMSH27B.FLX</t>
+  </si>
+  <si>
+    <t>BGMSH27C.FLX</t>
+  </si>
+  <si>
+    <t>BGMSH27D.FLX</t>
+  </si>
+  <si>
+    <t>BGMSH28A.FLX</t>
+  </si>
+  <si>
+    <t>BGMSH28B.FLX</t>
+  </si>
+  <si>
+    <t>BGMSH28C.FLX</t>
+  </si>
+  <si>
+    <t>BGMSH28D.FLX</t>
+  </si>
+  <si>
+    <t>BGMSH29A.FLX</t>
+  </si>
+  <si>
+    <t>BGMSH29B.FLX</t>
+  </si>
+  <si>
+    <t>BGMSH29C.FLX</t>
+  </si>
+  <si>
+    <t>BGMSH29D.FLX</t>
+  </si>
+  <si>
+    <t>BGMSH30A.FLX</t>
+  </si>
+  <si>
+    <t>BGMSH30B.FLX</t>
+  </si>
+  <si>
+    <t>BGMSH30C.FLX</t>
+  </si>
+  <si>
+    <t>BGMSH30D.FLX</t>
+  </si>
+  <si>
+    <t>BGMSH99A.FLX</t>
+  </si>
+  <si>
+    <t>BGMSH99B.FLX</t>
+  </si>
+  <si>
+    <t>BGMSH99C.FLX</t>
+  </si>
+  <si>
+    <t>BGMSH99D.FLX</t>
+  </si>
+  <si>
+    <t>BG_100A.FLX</t>
+  </si>
+  <si>
+    <t>BG_101A.FLX</t>
+  </si>
+  <si>
+    <t>BG_102A.FLX</t>
+  </si>
+  <si>
+    <t>BG_103A.FLX</t>
+  </si>
+  <si>
+    <t>BG_104A.FLX</t>
+  </si>
+  <si>
+    <t>BG_105A.FLX</t>
+  </si>
+  <si>
+    <t>BG_106A.FLX</t>
+  </si>
+  <si>
+    <t>BG_200A.FLX</t>
+  </si>
+  <si>
+    <t>BG_201A.FLX</t>
+  </si>
+  <si>
+    <t>BG_202A.FLX</t>
+  </si>
+  <si>
+    <t>BG_203A.FLX</t>
+  </si>
+  <si>
+    <t>BG_204A.FLX</t>
+  </si>
+  <si>
+    <t>BG_205A.FLX</t>
+  </si>
+  <si>
+    <t>BG_206A.FLX</t>
+  </si>
+  <si>
+    <t>BG_207A.FLX</t>
+  </si>
+  <si>
+    <t>BG_208A.FLX</t>
+  </si>
+  <si>
+    <t>BG_209A.FLX</t>
+  </si>
+  <si>
+    <t>BG_210A.FLX</t>
+  </si>
+  <si>
+    <t>BG_211A.FLX</t>
+  </si>
+  <si>
+    <t>BG_212A.FLX</t>
+  </si>
+  <si>
+    <t>BG_300A.FLX</t>
+  </si>
+  <si>
+    <t>BG_301A.FLX</t>
+  </si>
+  <si>
+    <t>BG_302A.FLX</t>
+  </si>
+  <si>
+    <t>BIODLOP1.FLX</t>
+  </si>
+  <si>
+    <t>BRAIN2.FLX</t>
+  </si>
+  <si>
+    <t>COMIDLE.FLX</t>
+  </si>
+  <si>
+    <t>CREDITS.FLX</t>
+  </si>
+  <si>
+    <t>DEFENDER.FLX</t>
+  </si>
+  <si>
+    <t>DESTROY.FLX</t>
+  </si>
+  <si>
+    <t>DROP1.FLX</t>
+  </si>
+  <si>
+    <t>HBASE.FLX</t>
+  </si>
+  <si>
+    <t>HB_AMB1.FLX</t>
+  </si>
+  <si>
+    <t>HB_AMB10.FLX</t>
+  </si>
+  <si>
+    <t>HB_AMB11.FLX</t>
+  </si>
+  <si>
+    <t>HB_AMB12.FLX</t>
+  </si>
+  <si>
+    <t>HB_AMB13.FLX</t>
+  </si>
+  <si>
+    <t>HB_AMB14.FLX</t>
+  </si>
+  <si>
+    <t>HB_AMB15.FLX</t>
+  </si>
+  <si>
+    <t>HB_AMB16.FLX</t>
+  </si>
+  <si>
+    <t>HB_AMB17.FLX</t>
+  </si>
+  <si>
+    <t>HB_AMB18.FLX</t>
+  </si>
+  <si>
+    <t>HB_AMB2.FLX</t>
+  </si>
+  <si>
+    <t>HB_AMB3.FLX</t>
+  </si>
+  <si>
+    <t>HB_AMB4.FLX</t>
+  </si>
+  <si>
+    <t>HB_AMB5.FLX</t>
+  </si>
+  <si>
+    <t>HB_AMB6.FLX</t>
+  </si>
+  <si>
+    <t>HB_AMB7.FLX</t>
+  </si>
+  <si>
+    <t>HB_AMB8.FLX</t>
+  </si>
+  <si>
+    <t>HB_AMB9.FLX</t>
+  </si>
+  <si>
+    <t>HB_BUY.FLX</t>
+  </si>
+  <si>
+    <t>HB_IDLE.FLX</t>
+  </si>
+  <si>
+    <t>HB_UPG.FLX</t>
+  </si>
+  <si>
+    <t>ICEMOON.FLX</t>
+  </si>
+  <si>
+    <t>INVADER.FLX</t>
+  </si>
+  <si>
+    <t>JUGGERN.FLX</t>
+  </si>
+  <si>
+    <t>LOSER4A.FLX</t>
+  </si>
+  <si>
+    <t>LOSER4B.FLX</t>
+  </si>
+  <si>
+    <t>LOSER4C.FLX</t>
+  </si>
+  <si>
+    <t>MLEND.FLX</t>
+  </si>
+  <si>
+    <t>MLLOOP.FLX</t>
+  </si>
+  <si>
+    <t>MLSTART.FLX</t>
+  </si>
+  <si>
+    <t>MONK.FLX</t>
+  </si>
+  <si>
+    <t>MPLBG.FLX</t>
+  </si>
+  <si>
+    <t>OGRE_ETC.FLX</t>
+  </si>
+  <si>
+    <t>OM3A.FLX</t>
+  </si>
+  <si>
+    <t>OM4A.FLX</t>
+  </si>
+  <si>
+    <t>PRE_ARAC.FLX</t>
+  </si>
+  <si>
+    <t>PRE_CERE.FLX</t>
+  </si>
+  <si>
+    <t>PRE_DEFN.FLX</t>
+  </si>
+  <si>
+    <t>PRE_DEST.FLX</t>
+  </si>
+  <si>
+    <t>PRE_GEN.FLX</t>
+  </si>
+  <si>
+    <t>PRE_GIAN.FLX</t>
+  </si>
+  <si>
+    <t>PRE_HAD.FLX</t>
+  </si>
+  <si>
+    <t>PRE_JUGG.FLX</t>
+  </si>
+  <si>
+    <t>PRE_MALI.FLX</t>
+  </si>
+  <si>
+    <t>PRE_NIH.FLX</t>
+  </si>
+  <si>
+    <t>PRE_OGRE.FLX</t>
+  </si>
+  <si>
+    <t>PRE_PARA.FLX</t>
+  </si>
+  <si>
+    <t>PRE_REMO.FLX</t>
+  </si>
+  <si>
+    <t>PRE_SENS.FLX</t>
+  </si>
+  <si>
+    <t>PRE_SHAD.FLX</t>
+  </si>
+  <si>
+    <t>PRE_SPE.FLX</t>
+  </si>
+  <si>
+    <t>PROMO1.FLX</t>
+  </si>
+  <si>
+    <t>PROMO10.FLX</t>
+  </si>
+  <si>
+    <t>PROMO11.FLX</t>
+  </si>
+  <si>
+    <t>PROMO12.FLX</t>
+  </si>
+  <si>
+    <t>PROMO13.FLX</t>
+  </si>
+  <si>
+    <t>PROMO14.FLX</t>
+  </si>
+  <si>
+    <t>PROMO2.FLX</t>
+  </si>
+  <si>
+    <t>PROMO3.FLX</t>
+  </si>
+  <si>
+    <t>PROMO4.FLX</t>
+  </si>
+  <si>
+    <t>PROMO5.FLX</t>
+  </si>
+  <si>
+    <t>PROMO6.FLX</t>
+  </si>
+  <si>
+    <t>PROMO7.FLX</t>
+  </si>
+  <si>
+    <t>PROMO8.FLX</t>
+  </si>
+  <si>
+    <t>PROMO9.FLX</t>
+  </si>
+  <si>
+    <t>PROTOS.FLX</t>
+  </si>
+  <si>
+    <t>REM_SHAD.FLX</t>
+  </si>
+  <si>
+    <t>SBEND.FLX</t>
+  </si>
+  <si>
+    <t>SBLOOP.FLX</t>
+  </si>
+  <si>
+    <t>SBSTART.FLX</t>
+  </si>
+  <si>
+    <t>TAKEOFF.FLX</t>
+  </si>
+  <si>
+    <t>TECH0.FLX</t>
+  </si>
+  <si>
+    <t>TECH1.FLX</t>
+  </si>
+  <si>
+    <t>TUTOR3A.FLX</t>
+  </si>
+  <si>
+    <t>TUTOR3B.FLX</t>
+  </si>
+  <si>
+    <t>TUTOR3C.FLX</t>
+  </si>
+  <si>
+    <t>TUTOR3D.FLX</t>
+  </si>
+  <si>
+    <t>TUTOR3E.FLX</t>
+  </si>
+  <si>
+    <t>TUTOR3F.FLX</t>
+  </si>
+  <si>
+    <t>TUTOR3G.FLX</t>
+  </si>
+  <si>
+    <t>TUTOR3H.FLX</t>
+  </si>
+  <si>
+    <t>TUTOR3I.FLX</t>
+  </si>
+  <si>
+    <t>TUTOR3J.FLX</t>
+  </si>
+  <si>
+    <t>VATDOOR.FLX</t>
+  </si>
+  <si>
+    <t>VATLOOP.FLX</t>
+  </si>
+  <si>
+    <t>VDCLOSE.FLX</t>
+  </si>
+  <si>
+    <t>VREND.FLX</t>
+  </si>
+  <si>
+    <t>VRLOOP.FLX</t>
+  </si>
+  <si>
+    <t>VRSTART.FLX</t>
+  </si>
+  <si>
+    <t>WF1A.FLX</t>
+  </si>
+  <si>
+    <t>WHOOSH.FLX</t>
+  </si>
+  <si>
+    <t>WINNINGA.FLX</t>
+  </si>
+  <si>
+    <t>WINNINGB.FLX</t>
+  </si>
+  <si>
+    <t>WINNINGC.FLX</t>
+  </si>
+  <si>
+    <t>WINNINGD.FLX</t>
+  </si>
+  <si>
+    <t>WM6A.FLX</t>
+  </si>
+  <si>
+    <t>WM7A.FLX</t>
+  </si>
+  <si>
+    <t>WM8A.FLX</t>
+  </si>
+  <si>
+    <t>WM9A.FLX</t>
+  </si>
+  <si>
+    <t>FLX</t>
+  </si>
+  <si>
+    <t>Video</t>
+  </si>
+  <si>
+    <t>Planet Intro</t>
+  </si>
+  <si>
+    <t>Name(TODO)</t>
+  </si>
+  <si>
+    <t>Bioderm showcase promotion</t>
+  </si>
+  <si>
+    <t>Video Bioderm</t>
+  </si>
+  <si>
+    <t>Tola idle healthy</t>
+  </si>
+  <si>
+    <t>Tola idle warning</t>
+  </si>
+  <si>
+    <t>Tola death</t>
+  </si>
+  <si>
+    <t>Bioderm name(TODO) Promotion</t>
+  </si>
+  <si>
+    <t>name(TODO) idle healthy</t>
+  </si>
+  <si>
+    <t>name(TODO) death</t>
+  </si>
+  <si>
+    <t>Tola idle danger</t>
+  </si>
+  <si>
+    <t>name(TODO) idle warning</t>
+  </si>
+  <si>
+    <t>name(TODO) idle danger</t>
   </si>
 </sst>
 </file>
@@ -15446,8 +16259,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D76A0E2E-5EF1-4C76-B441-AB9216212B3A}" name="Table1" displayName="Table1" ref="A1:K905" totalsRowShown="0">
-  <autoFilter ref="A1:K905" xr:uid="{D76A0E2E-5EF1-4C76-B441-AB9216212B3A}">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D76A0E2E-5EF1-4C76-B441-AB9216212B3A}" name="Table1" displayName="Table1" ref="A1:K1161" totalsRowShown="0">
+  <autoFilter ref="A1:K1161" xr:uid="{D76A0E2E-5EF1-4C76-B441-AB9216212B3A}">
     <filterColumn colId="3">
       <filters blank="1"/>
     </filterColumn>
@@ -15789,7 +16602,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{847C270E-F408-4D3B-B2DA-3B018BAD355D}">
-  <dimension ref="A1:K905"/>
+  <dimension ref="A1:K1161"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.7109375" bestFit="1" customWidth="1"/>
@@ -45093,6 +45906,5951 @@
       </c>
       <c r="J905" t="s">
         <v>1152</v>
+      </c>
+    </row>
+    <row r="906" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A906" t="s">
+        <v>1153</v>
+      </c>
+      <c r="B906" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C906" s="4">
+        <v>1483307</v>
+      </c>
+      <c r="D906" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E906">
+        <v>91</v>
+      </c>
+      <c r="F906" t="s">
+        <v>914</v>
+      </c>
+      <c r="G906" t="s">
+        <v>919</v>
+      </c>
+      <c r="H906" t="s">
+        <v>919</v>
+      </c>
+      <c r="I906" t="s">
+        <v>1410</v>
+      </c>
+      <c r="J906" t="s">
+        <v>1418</v>
+      </c>
+    </row>
+    <row r="907" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A907" t="s">
+        <v>1154</v>
+      </c>
+      <c r="B907" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C907" s="4">
+        <v>236436</v>
+      </c>
+      <c r="D907" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E907">
+        <v>91</v>
+      </c>
+      <c r="F907" t="s">
+        <v>914</v>
+      </c>
+      <c r="G907" t="s">
+        <v>919</v>
+      </c>
+      <c r="H907" t="s">
+        <v>919</v>
+      </c>
+      <c r="I907" t="s">
+        <v>1410</v>
+      </c>
+      <c r="J907" t="s">
+        <v>1413</v>
+      </c>
+    </row>
+    <row r="908" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A908" t="s">
+        <v>1155</v>
+      </c>
+      <c r="B908" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C908" s="4">
+        <v>304288</v>
+      </c>
+      <c r="D908" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E908">
+        <v>91</v>
+      </c>
+      <c r="F908" t="s">
+        <v>914</v>
+      </c>
+      <c r="G908" t="s">
+        <v>919</v>
+      </c>
+      <c r="H908" t="s">
+        <v>919</v>
+      </c>
+      <c r="I908" t="s">
+        <v>1414</v>
+      </c>
+      <c r="J908" t="s">
+        <v>1415</v>
+      </c>
+    </row>
+    <row r="909" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A909" t="s">
+        <v>1156</v>
+      </c>
+      <c r="B909" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C909" s="4">
+        <v>372180</v>
+      </c>
+      <c r="D909" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E909">
+        <v>91</v>
+      </c>
+      <c r="F909" t="s">
+        <v>914</v>
+      </c>
+      <c r="G909" t="s">
+        <v>919</v>
+      </c>
+      <c r="H909" t="s">
+        <v>919</v>
+      </c>
+      <c r="I909" t="s">
+        <v>1414</v>
+      </c>
+      <c r="J909" t="s">
+        <v>1416</v>
+      </c>
+    </row>
+    <row r="910" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A910" t="s">
+        <v>1157</v>
+      </c>
+      <c r="B910" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C910" s="4">
+        <v>416814</v>
+      </c>
+      <c r="D910" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E910">
+        <v>91</v>
+      </c>
+      <c r="F910" t="s">
+        <v>914</v>
+      </c>
+      <c r="G910" t="s">
+        <v>919</v>
+      </c>
+      <c r="H910" t="s">
+        <v>919</v>
+      </c>
+      <c r="I910" t="s">
+        <v>1414</v>
+      </c>
+      <c r="J910" t="s">
+        <v>1421</v>
+      </c>
+    </row>
+    <row r="911" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A911" t="s">
+        <v>1158</v>
+      </c>
+      <c r="B911" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C911" s="4">
+        <v>380313</v>
+      </c>
+      <c r="D911" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E911">
+        <v>91</v>
+      </c>
+      <c r="F911" t="s">
+        <v>914</v>
+      </c>
+      <c r="G911" t="s">
+        <v>919</v>
+      </c>
+      <c r="H911" t="s">
+        <v>919</v>
+      </c>
+      <c r="I911" t="s">
+        <v>1414</v>
+      </c>
+      <c r="J911" t="s">
+        <v>1417</v>
+      </c>
+    </row>
+    <row r="912" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A912" t="s">
+        <v>1159</v>
+      </c>
+      <c r="B912" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C912" s="4">
+        <v>188734</v>
+      </c>
+      <c r="D912" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E912">
+        <v>91</v>
+      </c>
+      <c r="F912" t="s">
+        <v>914</v>
+      </c>
+      <c r="G912" t="s">
+        <v>919</v>
+      </c>
+      <c r="H912" t="s">
+        <v>919</v>
+      </c>
+      <c r="I912" t="s">
+        <v>1414</v>
+      </c>
+      <c r="J912" t="s">
+        <v>1419</v>
+      </c>
+    </row>
+    <row r="913" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A913" t="s">
+        <v>1160</v>
+      </c>
+      <c r="B913" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C913" s="4">
+        <v>220338</v>
+      </c>
+      <c r="D913" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E913">
+        <v>91</v>
+      </c>
+      <c r="F913" t="s">
+        <v>914</v>
+      </c>
+      <c r="G913" t="s">
+        <v>919</v>
+      </c>
+      <c r="H913" t="s">
+        <v>919</v>
+      </c>
+      <c r="I913" t="s">
+        <v>1414</v>
+      </c>
+      <c r="J913" t="s">
+        <v>1422</v>
+      </c>
+    </row>
+    <row r="914" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A914" t="s">
+        <v>1161</v>
+      </c>
+      <c r="B914" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C914" s="4">
+        <v>279364</v>
+      </c>
+      <c r="D914" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E914">
+        <v>91</v>
+      </c>
+      <c r="F914" t="s">
+        <v>914</v>
+      </c>
+      <c r="G914" t="s">
+        <v>919</v>
+      </c>
+      <c r="H914" t="s">
+        <v>919</v>
+      </c>
+      <c r="I914" t="s">
+        <v>1414</v>
+      </c>
+      <c r="J914" t="s">
+        <v>1423</v>
+      </c>
+    </row>
+    <row r="915" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A915" t="s">
+        <v>1162</v>
+      </c>
+      <c r="B915" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C915" s="4">
+        <v>221075</v>
+      </c>
+      <c r="D915" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E915">
+        <v>91</v>
+      </c>
+      <c r="F915" t="s">
+        <v>914</v>
+      </c>
+      <c r="G915" t="s">
+        <v>919</v>
+      </c>
+      <c r="H915" t="s">
+        <v>919</v>
+      </c>
+      <c r="I915" t="s">
+        <v>1414</v>
+      </c>
+      <c r="J915" t="s">
+        <v>1420</v>
+      </c>
+    </row>
+    <row r="916" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A916" t="s">
+        <v>1163</v>
+      </c>
+      <c r="B916" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C916" s="4">
+        <v>367668</v>
+      </c>
+      <c r="D916" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E916">
+        <v>91</v>
+      </c>
+      <c r="F916" t="s">
+        <v>914</v>
+      </c>
+      <c r="G916" t="s">
+        <v>919</v>
+      </c>
+      <c r="H916" t="s">
+        <v>919</v>
+      </c>
+      <c r="I916" t="s">
+        <v>1414</v>
+      </c>
+      <c r="J916" t="s">
+        <v>1419</v>
+      </c>
+    </row>
+    <row r="917" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A917" t="s">
+        <v>1164</v>
+      </c>
+      <c r="B917" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C917" s="4">
+        <v>467195</v>
+      </c>
+      <c r="D917" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E917">
+        <v>91</v>
+      </c>
+      <c r="F917" t="s">
+        <v>914</v>
+      </c>
+      <c r="G917" t="s">
+        <v>919</v>
+      </c>
+      <c r="H917" t="s">
+        <v>919</v>
+      </c>
+      <c r="I917" t="s">
+        <v>1414</v>
+      </c>
+      <c r="J917" t="s">
+        <v>1422</v>
+      </c>
+    </row>
+    <row r="918" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A918" t="s">
+        <v>1165</v>
+      </c>
+      <c r="B918" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C918" s="4">
+        <v>483928</v>
+      </c>
+      <c r="D918" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E918">
+        <v>91</v>
+      </c>
+      <c r="F918" t="s">
+        <v>914</v>
+      </c>
+      <c r="G918" t="s">
+        <v>919</v>
+      </c>
+      <c r="H918" t="s">
+        <v>919</v>
+      </c>
+      <c r="I918" t="s">
+        <v>1414</v>
+      </c>
+      <c r="J918" t="s">
+        <v>1423</v>
+      </c>
+    </row>
+    <row r="919" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A919" t="s">
+        <v>1166</v>
+      </c>
+      <c r="B919" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C919" s="4">
+        <v>238740</v>
+      </c>
+      <c r="D919" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E919">
+        <v>91</v>
+      </c>
+      <c r="F919" t="s">
+        <v>914</v>
+      </c>
+      <c r="G919" t="s">
+        <v>919</v>
+      </c>
+      <c r="H919" t="s">
+        <v>919</v>
+      </c>
+      <c r="I919" t="s">
+        <v>1414</v>
+      </c>
+      <c r="J919" t="s">
+        <v>1420</v>
+      </c>
+    </row>
+    <row r="920" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A920" t="s">
+        <v>1167</v>
+      </c>
+      <c r="B920" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C920" s="4">
+        <v>462762</v>
+      </c>
+      <c r="D920" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E920">
+        <v>91</v>
+      </c>
+      <c r="F920" t="s">
+        <v>914</v>
+      </c>
+      <c r="G920" t="s">
+        <v>919</v>
+      </c>
+      <c r="H920" t="s">
+        <v>919</v>
+      </c>
+      <c r="I920" t="s">
+        <v>1414</v>
+      </c>
+      <c r="J920" t="s">
+        <v>1419</v>
+      </c>
+    </row>
+    <row r="921" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A921" t="s">
+        <v>1168</v>
+      </c>
+      <c r="B921" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C921" s="4">
+        <v>290265</v>
+      </c>
+      <c r="D921" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E921">
+        <v>91</v>
+      </c>
+      <c r="F921" t="s">
+        <v>914</v>
+      </c>
+      <c r="G921" t="s">
+        <v>919</v>
+      </c>
+      <c r="H921" t="s">
+        <v>919</v>
+      </c>
+      <c r="I921" t="s">
+        <v>1414</v>
+      </c>
+      <c r="J921" t="s">
+        <v>1422</v>
+      </c>
+    </row>
+    <row r="922" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A922" t="s">
+        <v>1169</v>
+      </c>
+      <c r="B922" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C922" s="4">
+        <v>370828</v>
+      </c>
+      <c r="D922" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E922">
+        <v>91</v>
+      </c>
+      <c r="F922" t="s">
+        <v>914</v>
+      </c>
+      <c r="G922" t="s">
+        <v>919</v>
+      </c>
+      <c r="H922" t="s">
+        <v>919</v>
+      </c>
+      <c r="I922" t="s">
+        <v>1414</v>
+      </c>
+      <c r="J922" t="s">
+        <v>1423</v>
+      </c>
+    </row>
+    <row r="923" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A923" t="s">
+        <v>1170</v>
+      </c>
+      <c r="B923" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C923" s="4">
+        <v>257677</v>
+      </c>
+      <c r="D923" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E923">
+        <v>91</v>
+      </c>
+      <c r="F923" t="s">
+        <v>914</v>
+      </c>
+      <c r="G923" t="s">
+        <v>919</v>
+      </c>
+      <c r="H923" t="s">
+        <v>919</v>
+      </c>
+      <c r="I923" t="s">
+        <v>1414</v>
+      </c>
+      <c r="J923" t="s">
+        <v>1420</v>
+      </c>
+    </row>
+    <row r="924" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A924" t="s">
+        <v>1171</v>
+      </c>
+      <c r="B924" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C924" s="4">
+        <v>239716</v>
+      </c>
+      <c r="D924" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E924">
+        <v>91</v>
+      </c>
+      <c r="F924" t="s">
+        <v>914</v>
+      </c>
+      <c r="G924" t="s">
+        <v>919</v>
+      </c>
+      <c r="H924" t="s">
+        <v>919</v>
+      </c>
+      <c r="I924" t="s">
+        <v>1414</v>
+      </c>
+      <c r="J924" t="s">
+        <v>1419</v>
+      </c>
+    </row>
+    <row r="925" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A925" t="s">
+        <v>1172</v>
+      </c>
+      <c r="B925" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C925" s="4">
+        <v>276185</v>
+      </c>
+      <c r="D925" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E925">
+        <v>91</v>
+      </c>
+      <c r="F925" t="s">
+        <v>914</v>
+      </c>
+      <c r="G925" t="s">
+        <v>919</v>
+      </c>
+      <c r="H925" t="s">
+        <v>919</v>
+      </c>
+      <c r="I925" t="s">
+        <v>1414</v>
+      </c>
+      <c r="J925" t="s">
+        <v>1422</v>
+      </c>
+    </row>
+    <row r="926" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A926" t="s">
+        <v>1173</v>
+      </c>
+      <c r="B926" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C926" s="4">
+        <v>310458</v>
+      </c>
+      <c r="D926" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E926">
+        <v>91</v>
+      </c>
+      <c r="F926" t="s">
+        <v>914</v>
+      </c>
+      <c r="G926" t="s">
+        <v>919</v>
+      </c>
+      <c r="H926" t="s">
+        <v>919</v>
+      </c>
+      <c r="I926" t="s">
+        <v>1414</v>
+      </c>
+      <c r="J926" t="s">
+        <v>1423</v>
+      </c>
+    </row>
+    <row r="927" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A927" t="s">
+        <v>1174</v>
+      </c>
+      <c r="B927" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C927" s="4">
+        <v>308622</v>
+      </c>
+      <c r="D927" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E927">
+        <v>91</v>
+      </c>
+      <c r="F927" t="s">
+        <v>914</v>
+      </c>
+      <c r="G927" t="s">
+        <v>919</v>
+      </c>
+      <c r="H927" t="s">
+        <v>919</v>
+      </c>
+      <c r="I927" t="s">
+        <v>1414</v>
+      </c>
+      <c r="J927" t="s">
+        <v>1420</v>
+      </c>
+    </row>
+    <row r="928" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A928" t="s">
+        <v>1175</v>
+      </c>
+      <c r="B928" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C928" s="4">
+        <v>303151</v>
+      </c>
+      <c r="D928" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E928">
+        <v>91</v>
+      </c>
+      <c r="F928" t="s">
+        <v>914</v>
+      </c>
+      <c r="G928" t="s">
+        <v>919</v>
+      </c>
+      <c r="H928" t="s">
+        <v>919</v>
+      </c>
+      <c r="I928" t="s">
+        <v>1414</v>
+      </c>
+      <c r="J928" t="s">
+        <v>1419</v>
+      </c>
+    </row>
+    <row r="929" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A929" t="s">
+        <v>1176</v>
+      </c>
+      <c r="B929" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C929" s="4">
+        <v>379349</v>
+      </c>
+      <c r="D929" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E929">
+        <v>91</v>
+      </c>
+      <c r="F929" t="s">
+        <v>914</v>
+      </c>
+      <c r="G929" t="s">
+        <v>919</v>
+      </c>
+      <c r="H929" t="s">
+        <v>919</v>
+      </c>
+      <c r="I929" t="s">
+        <v>1414</v>
+      </c>
+      <c r="J929" t="s">
+        <v>1422</v>
+      </c>
+    </row>
+    <row r="930" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A930" t="s">
+        <v>1177</v>
+      </c>
+      <c r="B930" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C930" s="4">
+        <v>407333</v>
+      </c>
+      <c r="D930" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E930">
+        <v>91</v>
+      </c>
+      <c r="F930" t="s">
+        <v>914</v>
+      </c>
+      <c r="G930" t="s">
+        <v>919</v>
+      </c>
+      <c r="H930" t="s">
+        <v>919</v>
+      </c>
+      <c r="I930" t="s">
+        <v>1414</v>
+      </c>
+      <c r="J930" t="s">
+        <v>1423</v>
+      </c>
+    </row>
+    <row r="931" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A931" t="s">
+        <v>1178</v>
+      </c>
+      <c r="B931" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C931" s="4">
+        <v>364801</v>
+      </c>
+      <c r="D931" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E931">
+        <v>91</v>
+      </c>
+      <c r="F931" t="s">
+        <v>914</v>
+      </c>
+      <c r="G931" t="s">
+        <v>919</v>
+      </c>
+      <c r="H931" t="s">
+        <v>919</v>
+      </c>
+      <c r="I931" t="s">
+        <v>1414</v>
+      </c>
+      <c r="J931" t="s">
+        <v>1420</v>
+      </c>
+    </row>
+    <row r="932" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A932" t="s">
+        <v>1179</v>
+      </c>
+      <c r="B932" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C932" s="4">
+        <v>369563</v>
+      </c>
+      <c r="D932" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E932">
+        <v>91</v>
+      </c>
+      <c r="F932" t="s">
+        <v>914</v>
+      </c>
+      <c r="G932" t="s">
+        <v>919</v>
+      </c>
+      <c r="H932" t="s">
+        <v>919</v>
+      </c>
+      <c r="I932" t="s">
+        <v>1414</v>
+      </c>
+      <c r="J932" t="s">
+        <v>1419</v>
+      </c>
+    </row>
+    <row r="933" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A933" t="s">
+        <v>1180</v>
+      </c>
+      <c r="B933" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C933" s="4">
+        <v>338237</v>
+      </c>
+      <c r="D933" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E933">
+        <v>91</v>
+      </c>
+      <c r="F933" t="s">
+        <v>914</v>
+      </c>
+      <c r="G933" t="s">
+        <v>919</v>
+      </c>
+      <c r="H933" t="s">
+        <v>919</v>
+      </c>
+      <c r="I933" t="s">
+        <v>1414</v>
+      </c>
+      <c r="J933" t="s">
+        <v>1422</v>
+      </c>
+    </row>
+    <row r="934" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A934" t="s">
+        <v>1181</v>
+      </c>
+      <c r="B934" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C934" s="4">
+        <v>388549</v>
+      </c>
+      <c r="D934" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E934">
+        <v>91</v>
+      </c>
+      <c r="F934" t="s">
+        <v>914</v>
+      </c>
+      <c r="G934" t="s">
+        <v>919</v>
+      </c>
+      <c r="H934" t="s">
+        <v>919</v>
+      </c>
+      <c r="I934" t="s">
+        <v>1414</v>
+      </c>
+      <c r="J934" t="s">
+        <v>1423</v>
+      </c>
+    </row>
+    <row r="935" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A935" t="s">
+        <v>1182</v>
+      </c>
+      <c r="B935" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C935" s="4">
+        <v>433594</v>
+      </c>
+      <c r="D935" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E935">
+        <v>91</v>
+      </c>
+      <c r="F935" t="s">
+        <v>914</v>
+      </c>
+      <c r="G935" t="s">
+        <v>919</v>
+      </c>
+      <c r="H935" t="s">
+        <v>919</v>
+      </c>
+      <c r="I935" t="s">
+        <v>1414</v>
+      </c>
+      <c r="J935" t="s">
+        <v>1420</v>
+      </c>
+    </row>
+    <row r="936" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A936" t="s">
+        <v>1183</v>
+      </c>
+      <c r="B936" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C936" s="4">
+        <v>297261</v>
+      </c>
+      <c r="D936" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E936">
+        <v>91</v>
+      </c>
+      <c r="F936" t="s">
+        <v>914</v>
+      </c>
+      <c r="G936" t="s">
+        <v>919</v>
+      </c>
+      <c r="H936" t="s">
+        <v>919</v>
+      </c>
+      <c r="I936" t="s">
+        <v>1414</v>
+      </c>
+      <c r="J936" t="s">
+        <v>1419</v>
+      </c>
+    </row>
+    <row r="937" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A937" t="s">
+        <v>1184</v>
+      </c>
+      <c r="B937" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C937" s="4">
+        <v>369021</v>
+      </c>
+      <c r="D937" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E937">
+        <v>91</v>
+      </c>
+      <c r="F937" t="s">
+        <v>914</v>
+      </c>
+      <c r="G937" t="s">
+        <v>919</v>
+      </c>
+      <c r="H937" t="s">
+        <v>919</v>
+      </c>
+      <c r="I937" t="s">
+        <v>1414</v>
+      </c>
+      <c r="J937" t="s">
+        <v>1422</v>
+      </c>
+    </row>
+    <row r="938" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A938" t="s">
+        <v>1185</v>
+      </c>
+      <c r="B938" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C938" s="4">
+        <v>396565</v>
+      </c>
+      <c r="D938" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E938">
+        <v>91</v>
+      </c>
+      <c r="F938" t="s">
+        <v>914</v>
+      </c>
+      <c r="G938" t="s">
+        <v>919</v>
+      </c>
+      <c r="H938" t="s">
+        <v>919</v>
+      </c>
+      <c r="I938" t="s">
+        <v>1414</v>
+      </c>
+      <c r="J938" t="s">
+        <v>1423</v>
+      </c>
+    </row>
+    <row r="939" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A939" t="s">
+        <v>1186</v>
+      </c>
+      <c r="B939" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C939" s="4">
+        <v>345727</v>
+      </c>
+      <c r="D939" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E939">
+        <v>91</v>
+      </c>
+      <c r="F939" t="s">
+        <v>914</v>
+      </c>
+      <c r="G939" t="s">
+        <v>919</v>
+      </c>
+      <c r="H939" t="s">
+        <v>919</v>
+      </c>
+      <c r="I939" t="s">
+        <v>1414</v>
+      </c>
+      <c r="J939" t="s">
+        <v>1420</v>
+      </c>
+    </row>
+    <row r="940" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A940" t="s">
+        <v>1187</v>
+      </c>
+      <c r="B940" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C940" s="4">
+        <v>313148</v>
+      </c>
+      <c r="D940" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E940">
+        <v>91</v>
+      </c>
+      <c r="F940" t="s">
+        <v>914</v>
+      </c>
+      <c r="G940" t="s">
+        <v>919</v>
+      </c>
+      <c r="H940" t="s">
+        <v>919</v>
+      </c>
+      <c r="I940" t="s">
+        <v>1414</v>
+      </c>
+      <c r="J940" t="s">
+        <v>1419</v>
+      </c>
+    </row>
+    <row r="941" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A941" t="s">
+        <v>1188</v>
+      </c>
+      <c r="B941" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C941" s="4">
+        <v>331448</v>
+      </c>
+      <c r="D941" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E941">
+        <v>91</v>
+      </c>
+      <c r="F941" t="s">
+        <v>914</v>
+      </c>
+      <c r="G941" t="s">
+        <v>919</v>
+      </c>
+      <c r="H941" t="s">
+        <v>919</v>
+      </c>
+      <c r="I941" t="s">
+        <v>1414</v>
+      </c>
+      <c r="J941" t="s">
+        <v>1422</v>
+      </c>
+    </row>
+    <row r="942" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A942" t="s">
+        <v>1189</v>
+      </c>
+      <c r="B942" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C942" s="4">
+        <v>361619</v>
+      </c>
+      <c r="D942" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E942">
+        <v>91</v>
+      </c>
+      <c r="F942" t="s">
+        <v>914</v>
+      </c>
+      <c r="G942" t="s">
+        <v>919</v>
+      </c>
+      <c r="H942" t="s">
+        <v>919</v>
+      </c>
+      <c r="I942" t="s">
+        <v>1414</v>
+      </c>
+      <c r="J942" t="s">
+        <v>1423</v>
+      </c>
+    </row>
+    <row r="943" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A943" t="s">
+        <v>1190</v>
+      </c>
+      <c r="B943" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C943" s="4">
+        <v>416718</v>
+      </c>
+      <c r="D943" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E943">
+        <v>91</v>
+      </c>
+      <c r="F943" t="s">
+        <v>914</v>
+      </c>
+      <c r="G943" t="s">
+        <v>919</v>
+      </c>
+      <c r="H943" t="s">
+        <v>919</v>
+      </c>
+      <c r="I943" t="s">
+        <v>1414</v>
+      </c>
+      <c r="J943" t="s">
+        <v>1420</v>
+      </c>
+    </row>
+    <row r="944" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A944" t="s">
+        <v>1191</v>
+      </c>
+      <c r="B944" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C944" s="4">
+        <v>222633</v>
+      </c>
+      <c r="D944" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E944">
+        <v>91</v>
+      </c>
+      <c r="F944" t="s">
+        <v>914</v>
+      </c>
+      <c r="G944" t="s">
+        <v>919</v>
+      </c>
+      <c r="H944" t="s">
+        <v>919</v>
+      </c>
+      <c r="I944" t="s">
+        <v>1414</v>
+      </c>
+      <c r="J944" t="s">
+        <v>1419</v>
+      </c>
+    </row>
+    <row r="945" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A945" t="s">
+        <v>1192</v>
+      </c>
+      <c r="B945" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C945" s="4">
+        <v>240661</v>
+      </c>
+      <c r="D945" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E945">
+        <v>91</v>
+      </c>
+      <c r="F945" t="s">
+        <v>914</v>
+      </c>
+      <c r="G945" t="s">
+        <v>919</v>
+      </c>
+      <c r="H945" t="s">
+        <v>919</v>
+      </c>
+      <c r="I945" t="s">
+        <v>1414</v>
+      </c>
+      <c r="J945" t="s">
+        <v>1422</v>
+      </c>
+    </row>
+    <row r="946" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A946" t="s">
+        <v>1193</v>
+      </c>
+      <c r="B946" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C946" s="4">
+        <v>270220</v>
+      </c>
+      <c r="D946" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E946">
+        <v>91</v>
+      </c>
+      <c r="F946" t="s">
+        <v>914</v>
+      </c>
+      <c r="G946" t="s">
+        <v>919</v>
+      </c>
+      <c r="H946" t="s">
+        <v>919</v>
+      </c>
+      <c r="I946" t="s">
+        <v>1414</v>
+      </c>
+      <c r="J946" t="s">
+        <v>1423</v>
+      </c>
+    </row>
+    <row r="947" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A947" t="s">
+        <v>1194</v>
+      </c>
+      <c r="B947" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C947" s="4">
+        <v>251864</v>
+      </c>
+      <c r="D947" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E947">
+        <v>91</v>
+      </c>
+      <c r="F947" t="s">
+        <v>914</v>
+      </c>
+      <c r="G947" t="s">
+        <v>919</v>
+      </c>
+      <c r="H947" t="s">
+        <v>919</v>
+      </c>
+      <c r="I947" t="s">
+        <v>1414</v>
+      </c>
+      <c r="J947" t="s">
+        <v>1420</v>
+      </c>
+    </row>
+    <row r="948" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A948" t="s">
+        <v>1195</v>
+      </c>
+      <c r="B948" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C948" s="4">
+        <v>96244</v>
+      </c>
+      <c r="D948" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E948">
+        <v>91</v>
+      </c>
+      <c r="F948" t="s">
+        <v>914</v>
+      </c>
+      <c r="G948" t="s">
+        <v>919</v>
+      </c>
+      <c r="H948" t="s">
+        <v>919</v>
+      </c>
+      <c r="I948" t="s">
+        <v>1414</v>
+      </c>
+      <c r="J948" t="s">
+        <v>1419</v>
+      </c>
+    </row>
+    <row r="949" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A949" t="s">
+        <v>1196</v>
+      </c>
+      <c r="B949" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C949" s="4">
+        <v>124963</v>
+      </c>
+      <c r="D949" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E949">
+        <v>91</v>
+      </c>
+      <c r="F949" t="s">
+        <v>914</v>
+      </c>
+      <c r="G949" t="s">
+        <v>919</v>
+      </c>
+      <c r="H949" t="s">
+        <v>919</v>
+      </c>
+      <c r="I949" t="s">
+        <v>1414</v>
+      </c>
+      <c r="J949" t="s">
+        <v>1422</v>
+      </c>
+    </row>
+    <row r="950" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A950" t="s">
+        <v>1197</v>
+      </c>
+      <c r="B950" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C950" s="4">
+        <v>135207</v>
+      </c>
+      <c r="D950" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E950">
+        <v>91</v>
+      </c>
+      <c r="F950" t="s">
+        <v>914</v>
+      </c>
+      <c r="G950" t="s">
+        <v>919</v>
+      </c>
+      <c r="H950" t="s">
+        <v>919</v>
+      </c>
+      <c r="I950" t="s">
+        <v>1414</v>
+      </c>
+      <c r="J950" t="s">
+        <v>1423</v>
+      </c>
+    </row>
+    <row r="951" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A951" t="s">
+        <v>1198</v>
+      </c>
+      <c r="B951" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C951" s="4">
+        <v>183780</v>
+      </c>
+      <c r="D951" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E951">
+        <v>91</v>
+      </c>
+      <c r="F951" t="s">
+        <v>914</v>
+      </c>
+      <c r="G951" t="s">
+        <v>919</v>
+      </c>
+      <c r="H951" t="s">
+        <v>919</v>
+      </c>
+      <c r="I951" t="s">
+        <v>1414</v>
+      </c>
+      <c r="J951" t="s">
+        <v>1420</v>
+      </c>
+    </row>
+    <row r="952" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A952" t="s">
+        <v>1199</v>
+      </c>
+      <c r="B952" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C952" s="4">
+        <v>181640</v>
+      </c>
+      <c r="D952" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E952">
+        <v>91</v>
+      </c>
+      <c r="F952" t="s">
+        <v>914</v>
+      </c>
+      <c r="G952" t="s">
+        <v>919</v>
+      </c>
+      <c r="H952" t="s">
+        <v>919</v>
+      </c>
+      <c r="I952" t="s">
+        <v>1414</v>
+      </c>
+      <c r="J952" t="s">
+        <v>1419</v>
+      </c>
+    </row>
+    <row r="953" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A953" t="s">
+        <v>1200</v>
+      </c>
+      <c r="B953" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C953" s="4">
+        <v>243873</v>
+      </c>
+      <c r="D953" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E953">
+        <v>91</v>
+      </c>
+      <c r="F953" t="s">
+        <v>914</v>
+      </c>
+      <c r="G953" t="s">
+        <v>919</v>
+      </c>
+      <c r="H953" t="s">
+        <v>919</v>
+      </c>
+      <c r="I953" t="s">
+        <v>1414</v>
+      </c>
+      <c r="J953" t="s">
+        <v>1422</v>
+      </c>
+    </row>
+    <row r="954" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A954" t="s">
+        <v>1201</v>
+      </c>
+      <c r="B954" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C954" s="4">
+        <v>280885</v>
+      </c>
+      <c r="D954" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E954">
+        <v>91</v>
+      </c>
+      <c r="F954" t="s">
+        <v>914</v>
+      </c>
+      <c r="G954" t="s">
+        <v>919</v>
+      </c>
+      <c r="H954" t="s">
+        <v>919</v>
+      </c>
+      <c r="I954" t="s">
+        <v>1414</v>
+      </c>
+      <c r="J954" t="s">
+        <v>1423</v>
+      </c>
+    </row>
+    <row r="955" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A955" t="s">
+        <v>1202</v>
+      </c>
+      <c r="B955" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C955" s="4">
+        <v>294867</v>
+      </c>
+      <c r="D955" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E955">
+        <v>91</v>
+      </c>
+      <c r="F955" t="s">
+        <v>914</v>
+      </c>
+      <c r="G955" t="s">
+        <v>919</v>
+      </c>
+      <c r="H955" t="s">
+        <v>919</v>
+      </c>
+      <c r="I955" t="s">
+        <v>1414</v>
+      </c>
+      <c r="J955" t="s">
+        <v>1420</v>
+      </c>
+    </row>
+    <row r="956" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A956" t="s">
+        <v>1203</v>
+      </c>
+      <c r="B956" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C956" s="4">
+        <v>184511</v>
+      </c>
+      <c r="D956" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E956">
+        <v>91</v>
+      </c>
+      <c r="F956" t="s">
+        <v>914</v>
+      </c>
+      <c r="G956" t="s">
+        <v>919</v>
+      </c>
+      <c r="H956" t="s">
+        <v>919</v>
+      </c>
+      <c r="I956" t="s">
+        <v>1414</v>
+      </c>
+      <c r="J956" t="s">
+        <v>1419</v>
+      </c>
+    </row>
+    <row r="957" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A957" t="s">
+        <v>1204</v>
+      </c>
+      <c r="B957" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C957" s="4">
+        <v>296229</v>
+      </c>
+      <c r="D957" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E957">
+        <v>91</v>
+      </c>
+      <c r="F957" t="s">
+        <v>914</v>
+      </c>
+      <c r="G957" t="s">
+        <v>919</v>
+      </c>
+      <c r="H957" t="s">
+        <v>919</v>
+      </c>
+      <c r="I957" t="s">
+        <v>1414</v>
+      </c>
+      <c r="J957" t="s">
+        <v>1422</v>
+      </c>
+    </row>
+    <row r="958" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A958" t="s">
+        <v>1205</v>
+      </c>
+      <c r="B958" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C958" s="4">
+        <v>343556</v>
+      </c>
+      <c r="D958" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E958">
+        <v>91</v>
+      </c>
+      <c r="F958" t="s">
+        <v>914</v>
+      </c>
+      <c r="G958" t="s">
+        <v>919</v>
+      </c>
+      <c r="H958" t="s">
+        <v>919</v>
+      </c>
+      <c r="I958" t="s">
+        <v>1414</v>
+      </c>
+      <c r="J958" t="s">
+        <v>1423</v>
+      </c>
+    </row>
+    <row r="959" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A959" t="s">
+        <v>1206</v>
+      </c>
+      <c r="B959" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C959" s="4">
+        <v>348358</v>
+      </c>
+      <c r="D959" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E959">
+        <v>91</v>
+      </c>
+      <c r="F959" t="s">
+        <v>914</v>
+      </c>
+      <c r="G959" t="s">
+        <v>919</v>
+      </c>
+      <c r="H959" t="s">
+        <v>919</v>
+      </c>
+      <c r="I959" t="s">
+        <v>1414</v>
+      </c>
+      <c r="J959" t="s">
+        <v>1420</v>
+      </c>
+    </row>
+    <row r="960" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A960" t="s">
+        <v>1207</v>
+      </c>
+      <c r="B960" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C960" s="4">
+        <v>284267</v>
+      </c>
+      <c r="D960" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E960">
+        <v>91</v>
+      </c>
+      <c r="F960" t="s">
+        <v>914</v>
+      </c>
+      <c r="G960" t="s">
+        <v>919</v>
+      </c>
+      <c r="H960" t="s">
+        <v>919</v>
+      </c>
+      <c r="I960" t="s">
+        <v>1414</v>
+      </c>
+      <c r="J960" t="s">
+        <v>1419</v>
+      </c>
+    </row>
+    <row r="961" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A961" t="s">
+        <v>1208</v>
+      </c>
+      <c r="B961" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C961" s="4">
+        <v>306540</v>
+      </c>
+      <c r="D961" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E961">
+        <v>91</v>
+      </c>
+      <c r="F961" t="s">
+        <v>914</v>
+      </c>
+      <c r="G961" t="s">
+        <v>919</v>
+      </c>
+      <c r="H961" t="s">
+        <v>919</v>
+      </c>
+      <c r="I961" t="s">
+        <v>1414</v>
+      </c>
+      <c r="J961" t="s">
+        <v>1422</v>
+      </c>
+    </row>
+    <row r="962" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A962" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B962" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C962" s="4">
+        <v>340424</v>
+      </c>
+      <c r="D962" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E962">
+        <v>91</v>
+      </c>
+      <c r="F962" t="s">
+        <v>914</v>
+      </c>
+      <c r="G962" t="s">
+        <v>919</v>
+      </c>
+      <c r="H962" t="s">
+        <v>919</v>
+      </c>
+      <c r="I962" t="s">
+        <v>1414</v>
+      </c>
+      <c r="J962" t="s">
+        <v>1423</v>
+      </c>
+    </row>
+    <row r="963" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A963" t="s">
+        <v>1210</v>
+      </c>
+      <c r="B963" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C963" s="4">
+        <v>328300</v>
+      </c>
+      <c r="D963" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E963">
+        <v>91</v>
+      </c>
+      <c r="F963" t="s">
+        <v>914</v>
+      </c>
+      <c r="G963" t="s">
+        <v>919</v>
+      </c>
+      <c r="H963" t="s">
+        <v>919</v>
+      </c>
+      <c r="I963" t="s">
+        <v>1414</v>
+      </c>
+      <c r="J963" t="s">
+        <v>1420</v>
+      </c>
+    </row>
+    <row r="964" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A964" t="s">
+        <v>1211</v>
+      </c>
+      <c r="B964" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C964" s="4">
+        <v>224945</v>
+      </c>
+      <c r="D964" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E964">
+        <v>91</v>
+      </c>
+      <c r="F964" t="s">
+        <v>914</v>
+      </c>
+      <c r="G964" t="s">
+        <v>919</v>
+      </c>
+      <c r="H964" t="s">
+        <v>919</v>
+      </c>
+      <c r="I964" t="s">
+        <v>1414</v>
+      </c>
+      <c r="J964" t="s">
+        <v>1419</v>
+      </c>
+    </row>
+    <row r="965" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A965" t="s">
+        <v>1212</v>
+      </c>
+      <c r="B965" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C965" s="4">
+        <v>317325</v>
+      </c>
+      <c r="D965" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E965">
+        <v>91</v>
+      </c>
+      <c r="F965" t="s">
+        <v>914</v>
+      </c>
+      <c r="G965" t="s">
+        <v>919</v>
+      </c>
+      <c r="H965" t="s">
+        <v>919</v>
+      </c>
+      <c r="I965" t="s">
+        <v>1414</v>
+      </c>
+      <c r="J965" t="s">
+        <v>1422</v>
+      </c>
+    </row>
+    <row r="966" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A966" t="s">
+        <v>1213</v>
+      </c>
+      <c r="B966" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C966" s="4">
+        <v>352460</v>
+      </c>
+      <c r="D966" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E966">
+        <v>91</v>
+      </c>
+      <c r="F966" t="s">
+        <v>914</v>
+      </c>
+      <c r="G966" t="s">
+        <v>919</v>
+      </c>
+      <c r="H966" t="s">
+        <v>919</v>
+      </c>
+      <c r="I966" t="s">
+        <v>1414</v>
+      </c>
+      <c r="J966" t="s">
+        <v>1423</v>
+      </c>
+    </row>
+    <row r="967" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A967" t="s">
+        <v>1214</v>
+      </c>
+      <c r="B967" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C967" s="4">
+        <v>297583</v>
+      </c>
+      <c r="D967" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E967">
+        <v>91</v>
+      </c>
+      <c r="F967" t="s">
+        <v>914</v>
+      </c>
+      <c r="G967" t="s">
+        <v>919</v>
+      </c>
+      <c r="H967" t="s">
+        <v>919</v>
+      </c>
+      <c r="I967" t="s">
+        <v>1414</v>
+      </c>
+      <c r="J967" t="s">
+        <v>1420</v>
+      </c>
+    </row>
+    <row r="968" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A968" t="s">
+        <v>1215</v>
+      </c>
+      <c r="B968" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C968" s="4">
+        <v>153303</v>
+      </c>
+      <c r="D968" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E968">
+        <v>91</v>
+      </c>
+      <c r="F968" t="s">
+        <v>914</v>
+      </c>
+      <c r="G968" t="s">
+        <v>919</v>
+      </c>
+      <c r="H968" t="s">
+        <v>919</v>
+      </c>
+      <c r="I968" t="s">
+        <v>1414</v>
+      </c>
+      <c r="J968" t="s">
+        <v>1419</v>
+      </c>
+    </row>
+    <row r="969" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A969" t="s">
+        <v>1216</v>
+      </c>
+      <c r="B969" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C969" s="4">
+        <v>243435</v>
+      </c>
+      <c r="D969" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E969">
+        <v>91</v>
+      </c>
+      <c r="F969" t="s">
+        <v>914</v>
+      </c>
+      <c r="G969" t="s">
+        <v>919</v>
+      </c>
+      <c r="H969" t="s">
+        <v>919</v>
+      </c>
+      <c r="I969" t="s">
+        <v>1414</v>
+      </c>
+      <c r="J969" t="s">
+        <v>1422</v>
+      </c>
+    </row>
+    <row r="970" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A970" t="s">
+        <v>1217</v>
+      </c>
+      <c r="B970" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C970" s="4">
+        <v>308028</v>
+      </c>
+      <c r="D970" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E970">
+        <v>91</v>
+      </c>
+      <c r="F970" t="s">
+        <v>914</v>
+      </c>
+      <c r="G970" t="s">
+        <v>919</v>
+      </c>
+      <c r="H970" t="s">
+        <v>919</v>
+      </c>
+      <c r="I970" t="s">
+        <v>1414</v>
+      </c>
+      <c r="J970" t="s">
+        <v>1423</v>
+      </c>
+    </row>
+    <row r="971" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A971" t="s">
+        <v>1218</v>
+      </c>
+      <c r="B971" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C971" s="4">
+        <v>231224</v>
+      </c>
+      <c r="D971" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E971">
+        <v>91</v>
+      </c>
+      <c r="F971" t="s">
+        <v>914</v>
+      </c>
+      <c r="G971" t="s">
+        <v>919</v>
+      </c>
+      <c r="H971" t="s">
+        <v>919</v>
+      </c>
+      <c r="I971" t="s">
+        <v>1414</v>
+      </c>
+      <c r="J971" t="s">
+        <v>1420</v>
+      </c>
+    </row>
+    <row r="972" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A972" t="s">
+        <v>1219</v>
+      </c>
+      <c r="B972" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C972" s="4">
+        <v>173183</v>
+      </c>
+      <c r="D972" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E972">
+        <v>91</v>
+      </c>
+      <c r="F972" t="s">
+        <v>914</v>
+      </c>
+      <c r="G972" t="s">
+        <v>919</v>
+      </c>
+      <c r="H972" t="s">
+        <v>919</v>
+      </c>
+      <c r="I972" t="s">
+        <v>1414</v>
+      </c>
+      <c r="J972" t="s">
+        <v>1419</v>
+      </c>
+    </row>
+    <row r="973" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A973" t="s">
+        <v>1220</v>
+      </c>
+      <c r="B973" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C973" s="4">
+        <v>241341</v>
+      </c>
+      <c r="D973" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E973">
+        <v>91</v>
+      </c>
+      <c r="F973" t="s">
+        <v>914</v>
+      </c>
+      <c r="G973" t="s">
+        <v>919</v>
+      </c>
+      <c r="H973" t="s">
+        <v>919</v>
+      </c>
+      <c r="I973" t="s">
+        <v>1414</v>
+      </c>
+      <c r="J973" t="s">
+        <v>1422</v>
+      </c>
+    </row>
+    <row r="974" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A974" t="s">
+        <v>1221</v>
+      </c>
+      <c r="B974" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C974" s="4">
+        <v>291788</v>
+      </c>
+      <c r="D974" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E974">
+        <v>91</v>
+      </c>
+      <c r="F974" t="s">
+        <v>914</v>
+      </c>
+      <c r="G974" t="s">
+        <v>919</v>
+      </c>
+      <c r="H974" t="s">
+        <v>919</v>
+      </c>
+      <c r="I974" t="s">
+        <v>1414</v>
+      </c>
+      <c r="J974" t="s">
+        <v>1423</v>
+      </c>
+    </row>
+    <row r="975" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A975" t="s">
+        <v>1222</v>
+      </c>
+      <c r="B975" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C975" s="4">
+        <v>330329</v>
+      </c>
+      <c r="D975" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E975">
+        <v>91</v>
+      </c>
+      <c r="F975" t="s">
+        <v>914</v>
+      </c>
+      <c r="G975" t="s">
+        <v>919</v>
+      </c>
+      <c r="H975" t="s">
+        <v>919</v>
+      </c>
+      <c r="I975" t="s">
+        <v>1414</v>
+      </c>
+      <c r="J975" t="s">
+        <v>1420</v>
+      </c>
+    </row>
+    <row r="976" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A976" t="s">
+        <v>1223</v>
+      </c>
+      <c r="B976" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C976" s="4">
+        <v>99011</v>
+      </c>
+      <c r="D976" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E976">
+        <v>91</v>
+      </c>
+      <c r="F976" t="s">
+        <v>914</v>
+      </c>
+      <c r="G976" t="s">
+        <v>919</v>
+      </c>
+      <c r="H976" t="s">
+        <v>919</v>
+      </c>
+      <c r="I976" t="s">
+        <v>1414</v>
+      </c>
+      <c r="J976" t="s">
+        <v>1419</v>
+      </c>
+    </row>
+    <row r="977" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A977" t="s">
+        <v>1224</v>
+      </c>
+      <c r="B977" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C977" s="4">
+        <v>235797</v>
+      </c>
+      <c r="D977" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E977">
+        <v>91</v>
+      </c>
+      <c r="F977" t="s">
+        <v>914</v>
+      </c>
+      <c r="G977" t="s">
+        <v>919</v>
+      </c>
+      <c r="H977" t="s">
+        <v>919</v>
+      </c>
+      <c r="I977" t="s">
+        <v>1414</v>
+      </c>
+      <c r="J977" t="s">
+        <v>1422</v>
+      </c>
+    </row>
+    <row r="978" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A978" t="s">
+        <v>1225</v>
+      </c>
+      <c r="B978" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C978" s="4">
+        <v>347541</v>
+      </c>
+      <c r="D978" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E978">
+        <v>91</v>
+      </c>
+      <c r="F978" t="s">
+        <v>914</v>
+      </c>
+      <c r="G978" t="s">
+        <v>919</v>
+      </c>
+      <c r="H978" t="s">
+        <v>919</v>
+      </c>
+      <c r="I978" t="s">
+        <v>1414</v>
+      </c>
+      <c r="J978" t="s">
+        <v>1423</v>
+      </c>
+    </row>
+    <row r="979" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A979" t="s">
+        <v>1226</v>
+      </c>
+      <c r="B979" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C979" s="4">
+        <v>340860</v>
+      </c>
+      <c r="D979" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E979">
+        <v>91</v>
+      </c>
+      <c r="F979" t="s">
+        <v>914</v>
+      </c>
+      <c r="G979" t="s">
+        <v>919</v>
+      </c>
+      <c r="H979" t="s">
+        <v>919</v>
+      </c>
+      <c r="I979" t="s">
+        <v>1414</v>
+      </c>
+      <c r="J979" t="s">
+        <v>1420</v>
+      </c>
+    </row>
+    <row r="980" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A980" t="s">
+        <v>1227</v>
+      </c>
+      <c r="B980" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C980" s="4">
+        <v>223531</v>
+      </c>
+      <c r="D980" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E980">
+        <v>91</v>
+      </c>
+      <c r="F980" t="s">
+        <v>914</v>
+      </c>
+      <c r="G980" t="s">
+        <v>919</v>
+      </c>
+      <c r="H980" t="s">
+        <v>919</v>
+      </c>
+      <c r="I980" t="s">
+        <v>1414</v>
+      </c>
+      <c r="J980" t="s">
+        <v>1419</v>
+      </c>
+    </row>
+    <row r="981" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A981" t="s">
+        <v>1228</v>
+      </c>
+      <c r="B981" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C981" s="4">
+        <v>253218</v>
+      </c>
+      <c r="D981" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E981">
+        <v>91</v>
+      </c>
+      <c r="F981" t="s">
+        <v>914</v>
+      </c>
+      <c r="G981" t="s">
+        <v>919</v>
+      </c>
+      <c r="H981" t="s">
+        <v>919</v>
+      </c>
+      <c r="I981" t="s">
+        <v>1414</v>
+      </c>
+      <c r="J981" t="s">
+        <v>1422</v>
+      </c>
+    </row>
+    <row r="982" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A982" t="s">
+        <v>1229</v>
+      </c>
+      <c r="B982" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C982" s="4">
+        <v>313259</v>
+      </c>
+      <c r="D982" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E982">
+        <v>91</v>
+      </c>
+      <c r="F982" t="s">
+        <v>914</v>
+      </c>
+      <c r="G982" t="s">
+        <v>919</v>
+      </c>
+      <c r="H982" t="s">
+        <v>919</v>
+      </c>
+      <c r="I982" t="s">
+        <v>1414</v>
+      </c>
+      <c r="J982" t="s">
+        <v>1423</v>
+      </c>
+    </row>
+    <row r="983" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A983" t="s">
+        <v>1230</v>
+      </c>
+      <c r="B983" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C983" s="4">
+        <v>299246</v>
+      </c>
+      <c r="D983" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E983">
+        <v>91</v>
+      </c>
+      <c r="F983" t="s">
+        <v>914</v>
+      </c>
+      <c r="G983" t="s">
+        <v>919</v>
+      </c>
+      <c r="H983" t="s">
+        <v>919</v>
+      </c>
+      <c r="I983" t="s">
+        <v>1414</v>
+      </c>
+      <c r="J983" t="s">
+        <v>1420</v>
+      </c>
+    </row>
+    <row r="984" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A984" t="s">
+        <v>1231</v>
+      </c>
+      <c r="B984" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C984" s="4">
+        <v>310673</v>
+      </c>
+      <c r="D984" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E984">
+        <v>91</v>
+      </c>
+      <c r="F984" t="s">
+        <v>914</v>
+      </c>
+      <c r="G984" t="s">
+        <v>919</v>
+      </c>
+      <c r="H984" t="s">
+        <v>919</v>
+      </c>
+      <c r="I984" t="s">
+        <v>1414</v>
+      </c>
+      <c r="J984" t="s">
+        <v>1419</v>
+      </c>
+    </row>
+    <row r="985" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A985" t="s">
+        <v>1232</v>
+      </c>
+      <c r="B985" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C985" s="4">
+        <v>316312</v>
+      </c>
+      <c r="D985" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E985">
+        <v>91</v>
+      </c>
+      <c r="F985" t="s">
+        <v>914</v>
+      </c>
+      <c r="G985" t="s">
+        <v>919</v>
+      </c>
+      <c r="H985" t="s">
+        <v>919</v>
+      </c>
+      <c r="I985" t="s">
+        <v>1414</v>
+      </c>
+      <c r="J985" t="s">
+        <v>1422</v>
+      </c>
+    </row>
+    <row r="986" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A986" t="s">
+        <v>1233</v>
+      </c>
+      <c r="B986" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C986" s="4">
+        <v>356755</v>
+      </c>
+      <c r="D986" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E986">
+        <v>91</v>
+      </c>
+      <c r="F986" t="s">
+        <v>914</v>
+      </c>
+      <c r="G986" t="s">
+        <v>919</v>
+      </c>
+      <c r="H986" t="s">
+        <v>919</v>
+      </c>
+      <c r="I986" t="s">
+        <v>1414</v>
+      </c>
+      <c r="J986" t="s">
+        <v>1423</v>
+      </c>
+    </row>
+    <row r="987" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A987" t="s">
+        <v>1234</v>
+      </c>
+      <c r="B987" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C987" s="4">
+        <v>293841</v>
+      </c>
+      <c r="D987" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E987">
+        <v>91</v>
+      </c>
+      <c r="F987" t="s">
+        <v>914</v>
+      </c>
+      <c r="G987" t="s">
+        <v>919</v>
+      </c>
+      <c r="H987" t="s">
+        <v>919</v>
+      </c>
+      <c r="I987" t="s">
+        <v>1414</v>
+      </c>
+      <c r="J987" t="s">
+        <v>1420</v>
+      </c>
+    </row>
+    <row r="988" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A988" t="s">
+        <v>1235</v>
+      </c>
+      <c r="B988" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C988" s="4">
+        <v>97390</v>
+      </c>
+      <c r="D988" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E988">
+        <v>91</v>
+      </c>
+      <c r="F988" t="s">
+        <v>914</v>
+      </c>
+      <c r="G988" t="s">
+        <v>919</v>
+      </c>
+      <c r="H988" t="s">
+        <v>919</v>
+      </c>
+      <c r="I988" t="s">
+        <v>1414</v>
+      </c>
+      <c r="J988" t="s">
+        <v>1419</v>
+      </c>
+    </row>
+    <row r="989" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A989" t="s">
+        <v>1236</v>
+      </c>
+      <c r="B989" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C989" s="4">
+        <v>157310</v>
+      </c>
+      <c r="D989" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E989">
+        <v>91</v>
+      </c>
+      <c r="F989" t="s">
+        <v>914</v>
+      </c>
+      <c r="G989" t="s">
+        <v>919</v>
+      </c>
+      <c r="H989" t="s">
+        <v>919</v>
+      </c>
+      <c r="I989" t="s">
+        <v>1414</v>
+      </c>
+      <c r="J989" t="s">
+        <v>1422</v>
+      </c>
+    </row>
+    <row r="990" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A990" t="s">
+        <v>1237</v>
+      </c>
+      <c r="B990" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C990" s="4">
+        <v>217173</v>
+      </c>
+      <c r="D990" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E990">
+        <v>91</v>
+      </c>
+      <c r="F990" t="s">
+        <v>914</v>
+      </c>
+      <c r="G990" t="s">
+        <v>919</v>
+      </c>
+      <c r="H990" t="s">
+        <v>919</v>
+      </c>
+      <c r="I990" t="s">
+        <v>1414</v>
+      </c>
+      <c r="J990" t="s">
+        <v>1423</v>
+      </c>
+    </row>
+    <row r="991" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A991" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B991" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C991" s="4">
+        <v>197685</v>
+      </c>
+      <c r="D991" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E991">
+        <v>91</v>
+      </c>
+      <c r="F991" t="s">
+        <v>914</v>
+      </c>
+      <c r="G991" t="s">
+        <v>919</v>
+      </c>
+      <c r="H991" t="s">
+        <v>919</v>
+      </c>
+      <c r="I991" t="s">
+        <v>1414</v>
+      </c>
+      <c r="J991" t="s">
+        <v>1420</v>
+      </c>
+    </row>
+    <row r="992" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A992" t="s">
+        <v>1239</v>
+      </c>
+      <c r="B992" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C992" s="4">
+        <v>303381</v>
+      </c>
+      <c r="D992" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E992">
+        <v>91</v>
+      </c>
+      <c r="F992" t="s">
+        <v>914</v>
+      </c>
+      <c r="G992" t="s">
+        <v>919</v>
+      </c>
+      <c r="H992" t="s">
+        <v>919</v>
+      </c>
+      <c r="I992" t="s">
+        <v>1414</v>
+      </c>
+      <c r="J992" t="s">
+        <v>1419</v>
+      </c>
+    </row>
+    <row r="993" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A993" t="s">
+        <v>1240</v>
+      </c>
+      <c r="B993" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C993" s="4">
+        <v>329885</v>
+      </c>
+      <c r="D993" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E993">
+        <v>91</v>
+      </c>
+      <c r="F993" t="s">
+        <v>914</v>
+      </c>
+      <c r="G993" t="s">
+        <v>919</v>
+      </c>
+      <c r="H993" t="s">
+        <v>919</v>
+      </c>
+      <c r="I993" t="s">
+        <v>1414</v>
+      </c>
+      <c r="J993" t="s">
+        <v>1422</v>
+      </c>
+    </row>
+    <row r="994" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A994" t="s">
+        <v>1241</v>
+      </c>
+      <c r="B994" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C994" s="4">
+        <v>315713</v>
+      </c>
+      <c r="D994" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E994">
+        <v>91</v>
+      </c>
+      <c r="F994" t="s">
+        <v>914</v>
+      </c>
+      <c r="G994" t="s">
+        <v>919</v>
+      </c>
+      <c r="H994" t="s">
+        <v>919</v>
+      </c>
+      <c r="I994" t="s">
+        <v>1414</v>
+      </c>
+      <c r="J994" t="s">
+        <v>1423</v>
+      </c>
+    </row>
+    <row r="995" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A995" t="s">
+        <v>1242</v>
+      </c>
+      <c r="B995" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C995" s="4">
+        <v>242231</v>
+      </c>
+      <c r="D995" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E995">
+        <v>91</v>
+      </c>
+      <c r="F995" t="s">
+        <v>914</v>
+      </c>
+      <c r="G995" t="s">
+        <v>919</v>
+      </c>
+      <c r="H995" t="s">
+        <v>919</v>
+      </c>
+      <c r="I995" t="s">
+        <v>1414</v>
+      </c>
+      <c r="J995" t="s">
+        <v>1420</v>
+      </c>
+    </row>
+    <row r="996" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A996" t="s">
+        <v>1243</v>
+      </c>
+      <c r="B996" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C996" s="4">
+        <v>211667</v>
+      </c>
+      <c r="D996" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E996">
+        <v>91</v>
+      </c>
+      <c r="F996" t="s">
+        <v>914</v>
+      </c>
+      <c r="G996" t="s">
+        <v>919</v>
+      </c>
+      <c r="H996" t="s">
+        <v>919</v>
+      </c>
+      <c r="I996" t="s">
+        <v>1414</v>
+      </c>
+      <c r="J996" t="s">
+        <v>1419</v>
+      </c>
+    </row>
+    <row r="997" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A997" t="s">
+        <v>1244</v>
+      </c>
+      <c r="B997" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C997" s="4">
+        <v>274379</v>
+      </c>
+      <c r="D997" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E997">
+        <v>91</v>
+      </c>
+      <c r="F997" t="s">
+        <v>914</v>
+      </c>
+      <c r="G997" t="s">
+        <v>919</v>
+      </c>
+      <c r="H997" t="s">
+        <v>919</v>
+      </c>
+      <c r="I997" t="s">
+        <v>1414</v>
+      </c>
+      <c r="J997" t="s">
+        <v>1422</v>
+      </c>
+    </row>
+    <row r="998" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A998" t="s">
+        <v>1245</v>
+      </c>
+      <c r="B998" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C998" s="4">
+        <v>338928</v>
+      </c>
+      <c r="D998" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E998">
+        <v>91</v>
+      </c>
+      <c r="F998" t="s">
+        <v>914</v>
+      </c>
+      <c r="G998" t="s">
+        <v>919</v>
+      </c>
+      <c r="H998" t="s">
+        <v>919</v>
+      </c>
+      <c r="I998" t="s">
+        <v>1414</v>
+      </c>
+      <c r="J998" t="s">
+        <v>1423</v>
+      </c>
+    </row>
+    <row r="999" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A999" t="s">
+        <v>1246</v>
+      </c>
+      <c r="B999" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C999" s="4">
+        <v>333547</v>
+      </c>
+      <c r="D999" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E999">
+        <v>91</v>
+      </c>
+      <c r="F999" t="s">
+        <v>914</v>
+      </c>
+      <c r="G999" t="s">
+        <v>919</v>
+      </c>
+      <c r="H999" t="s">
+        <v>919</v>
+      </c>
+      <c r="I999" t="s">
+        <v>1414</v>
+      </c>
+      <c r="J999" t="s">
+        <v>1420</v>
+      </c>
+    </row>
+    <row r="1000" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1000" t="s">
+        <v>1247</v>
+      </c>
+      <c r="B1000" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C1000" s="4">
+        <v>128755</v>
+      </c>
+      <c r="D1000" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E1000">
+        <v>91</v>
+      </c>
+      <c r="F1000" t="s">
+        <v>914</v>
+      </c>
+      <c r="G1000" t="s">
+        <v>919</v>
+      </c>
+      <c r="H1000" t="s">
+        <v>919</v>
+      </c>
+      <c r="I1000" t="s">
+        <v>1414</v>
+      </c>
+      <c r="J1000" t="s">
+        <v>1419</v>
+      </c>
+    </row>
+    <row r="1001" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1001" t="s">
+        <v>1248</v>
+      </c>
+      <c r="B1001" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C1001" s="4">
+        <v>188461</v>
+      </c>
+      <c r="D1001" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E1001">
+        <v>91</v>
+      </c>
+      <c r="F1001" t="s">
+        <v>914</v>
+      </c>
+      <c r="G1001" t="s">
+        <v>919</v>
+      </c>
+      <c r="H1001" t="s">
+        <v>919</v>
+      </c>
+      <c r="I1001" t="s">
+        <v>1414</v>
+      </c>
+      <c r="J1001" t="s">
+        <v>1422</v>
+      </c>
+    </row>
+    <row r="1002" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1002" t="s">
+        <v>1249</v>
+      </c>
+      <c r="B1002" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C1002" s="4">
+        <v>260045</v>
+      </c>
+      <c r="D1002" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E1002">
+        <v>91</v>
+      </c>
+      <c r="F1002" t="s">
+        <v>914</v>
+      </c>
+      <c r="G1002" t="s">
+        <v>919</v>
+      </c>
+      <c r="H1002" t="s">
+        <v>919</v>
+      </c>
+      <c r="I1002" t="s">
+        <v>1414</v>
+      </c>
+      <c r="J1002" t="s">
+        <v>1423</v>
+      </c>
+    </row>
+    <row r="1003" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1003" t="s">
+        <v>1250</v>
+      </c>
+      <c r="B1003" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C1003" s="4">
+        <v>233134</v>
+      </c>
+      <c r="D1003" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E1003">
+        <v>91</v>
+      </c>
+      <c r="F1003" t="s">
+        <v>914</v>
+      </c>
+      <c r="G1003" t="s">
+        <v>919</v>
+      </c>
+      <c r="H1003" t="s">
+        <v>919</v>
+      </c>
+      <c r="I1003" t="s">
+        <v>1414</v>
+      </c>
+      <c r="J1003" t="s">
+        <v>1420</v>
+      </c>
+    </row>
+    <row r="1004" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1004" t="s">
+        <v>1251</v>
+      </c>
+      <c r="B1004" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C1004" s="4">
+        <v>33311</v>
+      </c>
+      <c r="D1004" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E1004">
+        <v>91</v>
+      </c>
+      <c r="F1004" t="s">
+        <v>914</v>
+      </c>
+      <c r="G1004" t="s">
+        <v>919</v>
+      </c>
+      <c r="H1004" t="s">
+        <v>919</v>
+      </c>
+      <c r="I1004" t="s">
+        <v>1414</v>
+      </c>
+      <c r="J1004" t="s">
+        <v>1419</v>
+      </c>
+    </row>
+    <row r="1005" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1005" t="s">
+        <v>1252</v>
+      </c>
+      <c r="B1005" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C1005" s="4">
+        <v>51535</v>
+      </c>
+      <c r="D1005" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E1005">
+        <v>91</v>
+      </c>
+      <c r="F1005" t="s">
+        <v>914</v>
+      </c>
+      <c r="G1005" t="s">
+        <v>919</v>
+      </c>
+      <c r="H1005" t="s">
+        <v>919</v>
+      </c>
+      <c r="I1005" t="s">
+        <v>1414</v>
+      </c>
+      <c r="J1005" t="s">
+        <v>1422</v>
+      </c>
+    </row>
+    <row r="1006" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1006" t="s">
+        <v>1253</v>
+      </c>
+      <c r="B1006" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C1006" s="4">
+        <v>64233</v>
+      </c>
+      <c r="D1006" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E1006">
+        <v>91</v>
+      </c>
+      <c r="F1006" t="s">
+        <v>914</v>
+      </c>
+      <c r="G1006" t="s">
+        <v>919</v>
+      </c>
+      <c r="H1006" t="s">
+        <v>919</v>
+      </c>
+      <c r="I1006" t="s">
+        <v>1414</v>
+      </c>
+      <c r="J1006" t="s">
+        <v>1423</v>
+      </c>
+    </row>
+    <row r="1007" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1007" t="s">
+        <v>1254</v>
+      </c>
+      <c r="B1007" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C1007" s="4">
+        <v>317561</v>
+      </c>
+      <c r="D1007" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E1007">
+        <v>401</v>
+      </c>
+      <c r="F1007" t="s">
+        <v>914</v>
+      </c>
+      <c r="G1007" t="s">
+        <v>919</v>
+      </c>
+      <c r="H1007" t="s">
+        <v>919</v>
+      </c>
+      <c r="I1007" t="s">
+        <v>1414</v>
+      </c>
+      <c r="J1007" t="s">
+        <v>1420</v>
+      </c>
+    </row>
+    <row r="1008" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1008" t="s">
+        <v>1255</v>
+      </c>
+      <c r="B1008" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C1008" s="4">
+        <v>229462</v>
+      </c>
+      <c r="D1008" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E1008">
+        <v>91</v>
+      </c>
+      <c r="F1008" t="s">
+        <v>914</v>
+      </c>
+      <c r="G1008" t="s">
+        <v>919</v>
+      </c>
+      <c r="H1008" t="s">
+        <v>919</v>
+      </c>
+      <c r="I1008" t="s">
+        <v>1414</v>
+      </c>
+      <c r="J1008" t="s">
+        <v>1419</v>
+      </c>
+    </row>
+    <row r="1009" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1009" t="s">
+        <v>1256</v>
+      </c>
+      <c r="B1009" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C1009" s="4">
+        <v>272951</v>
+      </c>
+      <c r="D1009" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E1009">
+        <v>91</v>
+      </c>
+      <c r="F1009" t="s">
+        <v>914</v>
+      </c>
+      <c r="G1009" t="s">
+        <v>919</v>
+      </c>
+      <c r="H1009" t="s">
+        <v>919</v>
+      </c>
+      <c r="I1009" t="s">
+        <v>1414</v>
+      </c>
+      <c r="J1009" t="s">
+        <v>1422</v>
+      </c>
+    </row>
+    <row r="1010" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1010" t="s">
+        <v>1257</v>
+      </c>
+      <c r="B1010" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C1010" s="4">
+        <v>333082</v>
+      </c>
+      <c r="D1010" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E1010">
+        <v>91</v>
+      </c>
+      <c r="F1010" t="s">
+        <v>914</v>
+      </c>
+      <c r="G1010" t="s">
+        <v>919</v>
+      </c>
+      <c r="H1010" t="s">
+        <v>919</v>
+      </c>
+      <c r="I1010" t="s">
+        <v>1414</v>
+      </c>
+      <c r="J1010" t="s">
+        <v>1423</v>
+      </c>
+    </row>
+    <row r="1011" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1011" t="s">
+        <v>1258</v>
+      </c>
+      <c r="B1011" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C1011" s="4">
+        <v>324967</v>
+      </c>
+      <c r="D1011" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E1011">
+        <v>91</v>
+      </c>
+      <c r="F1011" t="s">
+        <v>914</v>
+      </c>
+      <c r="G1011" t="s">
+        <v>919</v>
+      </c>
+      <c r="H1011" t="s">
+        <v>919</v>
+      </c>
+      <c r="I1011" t="s">
+        <v>1414</v>
+      </c>
+      <c r="J1011" t="s">
+        <v>1420</v>
+      </c>
+    </row>
+    <row r="1012" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1012" t="s">
+        <v>1259</v>
+      </c>
+      <c r="B1012" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C1012" s="4">
+        <v>205484</v>
+      </c>
+      <c r="D1012" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E1012">
+        <v>91</v>
+      </c>
+      <c r="F1012" t="s">
+        <v>914</v>
+      </c>
+      <c r="G1012" t="s">
+        <v>919</v>
+      </c>
+      <c r="H1012" t="s">
+        <v>919</v>
+      </c>
+      <c r="I1012" t="s">
+        <v>1414</v>
+      </c>
+      <c r="J1012" t="s">
+        <v>1419</v>
+      </c>
+    </row>
+    <row r="1013" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1013" t="s">
+        <v>1260</v>
+      </c>
+      <c r="B1013" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C1013" s="4">
+        <v>225865</v>
+      </c>
+      <c r="D1013" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E1013">
+        <v>91</v>
+      </c>
+      <c r="F1013" t="s">
+        <v>914</v>
+      </c>
+      <c r="G1013" t="s">
+        <v>919</v>
+      </c>
+      <c r="H1013" t="s">
+        <v>919</v>
+      </c>
+      <c r="I1013" t="s">
+        <v>1414</v>
+      </c>
+      <c r="J1013" t="s">
+        <v>1422</v>
+      </c>
+    </row>
+    <row r="1014" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1014" t="s">
+        <v>1261</v>
+      </c>
+      <c r="B1014" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C1014" s="4">
+        <v>256877</v>
+      </c>
+      <c r="D1014" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E1014">
+        <v>91</v>
+      </c>
+      <c r="F1014" t="s">
+        <v>914</v>
+      </c>
+      <c r="G1014" t="s">
+        <v>919</v>
+      </c>
+      <c r="H1014" t="s">
+        <v>919</v>
+      </c>
+      <c r="I1014" t="s">
+        <v>1414</v>
+      </c>
+      <c r="J1014" t="s">
+        <v>1423</v>
+      </c>
+    </row>
+    <row r="1015" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1015" t="s">
+        <v>1262</v>
+      </c>
+      <c r="B1015" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C1015" s="4">
+        <v>297930</v>
+      </c>
+      <c r="D1015" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E1015">
+        <v>91</v>
+      </c>
+      <c r="F1015" t="s">
+        <v>914</v>
+      </c>
+      <c r="G1015" t="s">
+        <v>919</v>
+      </c>
+      <c r="H1015" t="s">
+        <v>919</v>
+      </c>
+      <c r="I1015" t="s">
+        <v>1414</v>
+      </c>
+      <c r="J1015" t="s">
+        <v>1420</v>
+      </c>
+    </row>
+    <row r="1016" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1016" t="s">
+        <v>1263</v>
+      </c>
+      <c r="B1016" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C1016" s="4">
+        <v>220180</v>
+      </c>
+      <c r="D1016" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E1016">
+        <v>91</v>
+      </c>
+      <c r="F1016" t="s">
+        <v>914</v>
+      </c>
+      <c r="G1016" t="s">
+        <v>919</v>
+      </c>
+      <c r="H1016" t="s">
+        <v>919</v>
+      </c>
+      <c r="I1016" t="s">
+        <v>1414</v>
+      </c>
+      <c r="J1016" t="s">
+        <v>1419</v>
+      </c>
+    </row>
+    <row r="1017" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1017" t="s">
+        <v>1264</v>
+      </c>
+      <c r="B1017" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C1017" s="4">
+        <v>220172</v>
+      </c>
+      <c r="D1017" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E1017">
+        <v>91</v>
+      </c>
+      <c r="F1017" t="s">
+        <v>914</v>
+      </c>
+      <c r="G1017" t="s">
+        <v>919</v>
+      </c>
+      <c r="H1017" t="s">
+        <v>919</v>
+      </c>
+      <c r="I1017" t="s">
+        <v>1414</v>
+      </c>
+      <c r="J1017" t="s">
+        <v>1422</v>
+      </c>
+    </row>
+    <row r="1018" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1018" t="s">
+        <v>1265</v>
+      </c>
+      <c r="B1018" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C1018" s="4">
+        <v>169376</v>
+      </c>
+      <c r="D1018" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E1018">
+        <v>91</v>
+      </c>
+      <c r="F1018" t="s">
+        <v>914</v>
+      </c>
+      <c r="G1018" t="s">
+        <v>919</v>
+      </c>
+      <c r="H1018" t="s">
+        <v>919</v>
+      </c>
+      <c r="I1018" t="s">
+        <v>1414</v>
+      </c>
+      <c r="J1018" t="s">
+        <v>1423</v>
+      </c>
+    </row>
+    <row r="1019" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1019" t="s">
+        <v>1266</v>
+      </c>
+      <c r="B1019" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C1019" s="4">
+        <v>237071</v>
+      </c>
+      <c r="D1019" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E1019">
+        <v>91</v>
+      </c>
+      <c r="F1019" t="s">
+        <v>914</v>
+      </c>
+      <c r="G1019" t="s">
+        <v>919</v>
+      </c>
+      <c r="H1019" t="s">
+        <v>919</v>
+      </c>
+      <c r="I1019" t="s">
+        <v>1414</v>
+      </c>
+      <c r="J1019" t="s">
+        <v>1420</v>
+      </c>
+    </row>
+    <row r="1020" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1020" t="s">
+        <v>1267</v>
+      </c>
+      <c r="B1020" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C1020" s="4">
+        <v>332662</v>
+      </c>
+      <c r="D1020" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E1020">
+        <v>91</v>
+      </c>
+      <c r="F1020" t="s">
+        <v>914</v>
+      </c>
+      <c r="G1020" t="s">
+        <v>919</v>
+      </c>
+      <c r="H1020" t="s">
+        <v>919</v>
+      </c>
+      <c r="I1020" t="s">
+        <v>1414</v>
+      </c>
+      <c r="J1020" t="s">
+        <v>1419</v>
+      </c>
+    </row>
+    <row r="1021" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1021" t="s">
+        <v>1268</v>
+      </c>
+      <c r="B1021" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C1021" s="4">
+        <v>401567</v>
+      </c>
+      <c r="D1021" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E1021">
+        <v>91</v>
+      </c>
+      <c r="F1021" t="s">
+        <v>914</v>
+      </c>
+      <c r="G1021" t="s">
+        <v>919</v>
+      </c>
+      <c r="H1021" t="s">
+        <v>919</v>
+      </c>
+      <c r="I1021" t="s">
+        <v>1414</v>
+      </c>
+      <c r="J1021" t="s">
+        <v>1422</v>
+      </c>
+    </row>
+    <row r="1022" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1022" t="s">
+        <v>1269</v>
+      </c>
+      <c r="B1022" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C1022" s="4">
+        <v>436890</v>
+      </c>
+      <c r="D1022" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E1022">
+        <v>91</v>
+      </c>
+      <c r="F1022" t="s">
+        <v>914</v>
+      </c>
+      <c r="G1022" t="s">
+        <v>919</v>
+      </c>
+      <c r="H1022" t="s">
+        <v>919</v>
+      </c>
+      <c r="I1022" t="s">
+        <v>1414</v>
+      </c>
+      <c r="J1022" t="s">
+        <v>1423</v>
+      </c>
+    </row>
+    <row r="1023" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1023" t="s">
+        <v>1270</v>
+      </c>
+      <c r="B1023" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C1023" s="4">
+        <v>387069</v>
+      </c>
+      <c r="D1023" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E1023">
+        <v>91</v>
+      </c>
+      <c r="F1023" t="s">
+        <v>914</v>
+      </c>
+      <c r="G1023" t="s">
+        <v>919</v>
+      </c>
+      <c r="H1023" t="s">
+        <v>919</v>
+      </c>
+      <c r="I1023" t="s">
+        <v>1414</v>
+      </c>
+      <c r="J1023" t="s">
+        <v>1420</v>
+      </c>
+    </row>
+    <row r="1024" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1024" t="s">
+        <v>1271</v>
+      </c>
+      <c r="B1024" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C1024" s="4">
+        <v>308351</v>
+      </c>
+      <c r="D1024" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E1024">
+        <v>91</v>
+      </c>
+      <c r="F1024" t="s">
+        <v>914</v>
+      </c>
+      <c r="G1024" t="s">
+        <v>919</v>
+      </c>
+      <c r="H1024" t="s">
+        <v>919</v>
+      </c>
+      <c r="I1024" t="s">
+        <v>1414</v>
+      </c>
+      <c r="J1024" t="s">
+        <v>1419</v>
+      </c>
+    </row>
+    <row r="1025" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1025" t="s">
+        <v>1272</v>
+      </c>
+      <c r="B1025" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C1025" s="4">
+        <v>302611</v>
+      </c>
+      <c r="D1025" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E1025">
+        <v>91</v>
+      </c>
+      <c r="F1025" t="s">
+        <v>914</v>
+      </c>
+      <c r="G1025" t="s">
+        <v>919</v>
+      </c>
+      <c r="H1025" t="s">
+        <v>919</v>
+      </c>
+      <c r="I1025" t="s">
+        <v>1414</v>
+      </c>
+      <c r="J1025" t="s">
+        <v>1422</v>
+      </c>
+    </row>
+    <row r="1026" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1026" t="s">
+        <v>1273</v>
+      </c>
+      <c r="B1026" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C1026" s="4">
+        <v>315516</v>
+      </c>
+      <c r="D1026" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E1026">
+        <v>91</v>
+      </c>
+      <c r="F1026" t="s">
+        <v>914</v>
+      </c>
+      <c r="G1026" t="s">
+        <v>919</v>
+      </c>
+      <c r="H1026" t="s">
+        <v>919</v>
+      </c>
+      <c r="I1026" t="s">
+        <v>1414</v>
+      </c>
+      <c r="J1026" t="s">
+        <v>1423</v>
+      </c>
+    </row>
+    <row r="1027" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1027" t="s">
+        <v>1274</v>
+      </c>
+      <c r="B1027" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C1027" s="4">
+        <v>221373</v>
+      </c>
+      <c r="D1027" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E1027">
+        <v>91</v>
+      </c>
+      <c r="F1027" t="s">
+        <v>914</v>
+      </c>
+      <c r="G1027" t="s">
+        <v>919</v>
+      </c>
+      <c r="H1027" t="s">
+        <v>919</v>
+      </c>
+      <c r="I1027" t="s">
+        <v>1414</v>
+      </c>
+      <c r="J1027" t="s">
+        <v>1420</v>
+      </c>
+    </row>
+    <row r="1028" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1028" t="s">
+        <v>1275</v>
+      </c>
+      <c r="B1028" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C1028" s="4">
+        <v>99011</v>
+      </c>
+      <c r="D1028" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E1028">
+        <v>91</v>
+      </c>
+      <c r="F1028" t="s">
+        <v>914</v>
+      </c>
+      <c r="G1028" t="s">
+        <v>919</v>
+      </c>
+      <c r="H1028" t="s">
+        <v>919</v>
+      </c>
+      <c r="I1028" t="s">
+        <v>1414</v>
+      </c>
+      <c r="J1028" t="s">
+        <v>1419</v>
+      </c>
+    </row>
+    <row r="1029" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1029" t="s">
+        <v>1276</v>
+      </c>
+      <c r="B1029" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C1029" s="4">
+        <v>235797</v>
+      </c>
+      <c r="D1029" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E1029">
+        <v>91</v>
+      </c>
+      <c r="F1029" t="s">
+        <v>914</v>
+      </c>
+      <c r="G1029" t="s">
+        <v>919</v>
+      </c>
+      <c r="H1029" t="s">
+        <v>919</v>
+      </c>
+      <c r="I1029" t="s">
+        <v>1414</v>
+      </c>
+      <c r="J1029" t="s">
+        <v>1422</v>
+      </c>
+    </row>
+    <row r="1030" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1030" t="s">
+        <v>1277</v>
+      </c>
+      <c r="B1030" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C1030" s="4">
+        <v>347541</v>
+      </c>
+      <c r="D1030" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E1030">
+        <v>91</v>
+      </c>
+      <c r="F1030" t="s">
+        <v>914</v>
+      </c>
+      <c r="G1030" t="s">
+        <v>919</v>
+      </c>
+      <c r="H1030" t="s">
+        <v>919</v>
+      </c>
+      <c r="I1030" t="s">
+        <v>1414</v>
+      </c>
+      <c r="J1030" t="s">
+        <v>1423</v>
+      </c>
+    </row>
+    <row r="1031" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1031" t="s">
+        <v>1278</v>
+      </c>
+      <c r="B1031" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C1031" s="4">
+        <v>340860</v>
+      </c>
+      <c r="D1031" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E1031">
+        <v>91</v>
+      </c>
+      <c r="F1031" t="s">
+        <v>914</v>
+      </c>
+      <c r="G1031" t="s">
+        <v>919</v>
+      </c>
+      <c r="H1031" t="s">
+        <v>919</v>
+      </c>
+      <c r="I1031" t="s">
+        <v>1414</v>
+      </c>
+      <c r="J1031" t="s">
+        <v>1420</v>
+      </c>
+    </row>
+    <row r="1032" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1032" t="s">
+        <v>1279</v>
+      </c>
+      <c r="B1032" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C1032" s="4">
+        <v>1308379</v>
+      </c>
+      <c r="D1032" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E1032">
+        <v>121</v>
+      </c>
+      <c r="F1032" t="s">
+        <v>914</v>
+      </c>
+      <c r="G1032" t="s">
+        <v>919</v>
+      </c>
+      <c r="H1032" t="s">
+        <v>919</v>
+      </c>
+      <c r="I1032" t="s">
+        <v>1411</v>
+      </c>
+      <c r="J1032" t="s">
+        <v>1412</v>
+      </c>
+    </row>
+    <row r="1033" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1033" t="s">
+        <v>1280</v>
+      </c>
+      <c r="B1033" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C1033" s="4">
+        <v>1386645</v>
+      </c>
+      <c r="D1033" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E1033">
+        <v>121</v>
+      </c>
+      <c r="F1033" t="s">
+        <v>914</v>
+      </c>
+      <c r="G1033" t="s">
+        <v>919</v>
+      </c>
+      <c r="H1033" t="s">
+        <v>919</v>
+      </c>
+      <c r="I1033" t="s">
+        <v>1411</v>
+      </c>
+      <c r="J1033" t="s">
+        <v>1412</v>
+      </c>
+    </row>
+    <row r="1034" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1034" t="s">
+        <v>1281</v>
+      </c>
+      <c r="B1034" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C1034" s="4">
+        <v>1586835</v>
+      </c>
+      <c r="D1034" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E1034">
+        <v>121</v>
+      </c>
+      <c r="F1034" t="s">
+        <v>914</v>
+      </c>
+      <c r="G1034" t="s">
+        <v>919</v>
+      </c>
+      <c r="H1034" t="s">
+        <v>919</v>
+      </c>
+      <c r="I1034" t="s">
+        <v>1411</v>
+      </c>
+      <c r="J1034" t="s">
+        <v>1412</v>
+      </c>
+    </row>
+    <row r="1035" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1035" t="s">
+        <v>1282</v>
+      </c>
+      <c r="B1035" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C1035" s="4">
+        <v>1512517</v>
+      </c>
+      <c r="D1035" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E1035">
+        <v>121</v>
+      </c>
+      <c r="F1035" t="s">
+        <v>914</v>
+      </c>
+      <c r="G1035" t="s">
+        <v>919</v>
+      </c>
+      <c r="H1035" t="s">
+        <v>919</v>
+      </c>
+      <c r="I1035" t="s">
+        <v>1411</v>
+      </c>
+      <c r="J1035" t="s">
+        <v>1412</v>
+      </c>
+    </row>
+    <row r="1036" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1036" t="s">
+        <v>1283</v>
+      </c>
+      <c r="B1036" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C1036" s="4">
+        <v>1260785</v>
+      </c>
+      <c r="D1036" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E1036">
+        <v>121</v>
+      </c>
+      <c r="F1036" t="s">
+        <v>914</v>
+      </c>
+      <c r="G1036" t="s">
+        <v>919</v>
+      </c>
+      <c r="H1036" t="s">
+        <v>919</v>
+      </c>
+      <c r="I1036" t="s">
+        <v>1411</v>
+      </c>
+      <c r="J1036" t="s">
+        <v>1412</v>
+      </c>
+    </row>
+    <row r="1037" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1037" t="s">
+        <v>1284</v>
+      </c>
+      <c r="B1037" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C1037" s="4">
+        <v>1395083</v>
+      </c>
+      <c r="D1037" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E1037">
+        <v>121</v>
+      </c>
+      <c r="F1037" t="s">
+        <v>914</v>
+      </c>
+      <c r="G1037" t="s">
+        <v>919</v>
+      </c>
+      <c r="H1037" t="s">
+        <v>919</v>
+      </c>
+      <c r="I1037" t="s">
+        <v>1411</v>
+      </c>
+      <c r="J1037" t="s">
+        <v>1412</v>
+      </c>
+    </row>
+    <row r="1038" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1038" t="s">
+        <v>1285</v>
+      </c>
+      <c r="B1038" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C1038" s="4">
+        <v>1258325</v>
+      </c>
+      <c r="D1038" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E1038">
+        <v>121</v>
+      </c>
+      <c r="F1038" t="s">
+        <v>914</v>
+      </c>
+      <c r="G1038" t="s">
+        <v>919</v>
+      </c>
+      <c r="H1038" t="s">
+        <v>919</v>
+      </c>
+      <c r="I1038" t="s">
+        <v>1411</v>
+      </c>
+      <c r="J1038" t="s">
+        <v>1412</v>
+      </c>
+    </row>
+    <row r="1039" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1039" t="s">
+        <v>1286</v>
+      </c>
+      <c r="B1039" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C1039" s="4">
+        <v>1374903</v>
+      </c>
+      <c r="D1039" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E1039">
+        <v>121</v>
+      </c>
+      <c r="F1039" t="s">
+        <v>914</v>
+      </c>
+      <c r="G1039" t="s">
+        <v>919</v>
+      </c>
+      <c r="H1039" t="s">
+        <v>919</v>
+      </c>
+      <c r="I1039" t="s">
+        <v>1411</v>
+      </c>
+      <c r="J1039" t="s">
+        <v>1412</v>
+      </c>
+    </row>
+    <row r="1040" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1040" t="s">
+        <v>1287</v>
+      </c>
+      <c r="B1040" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C1040" s="4">
+        <v>1513054</v>
+      </c>
+      <c r="D1040" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E1040">
+        <v>121</v>
+      </c>
+      <c r="F1040" t="s">
+        <v>914</v>
+      </c>
+      <c r="G1040" t="s">
+        <v>919</v>
+      </c>
+      <c r="H1040" t="s">
+        <v>919</v>
+      </c>
+      <c r="I1040" t="s">
+        <v>1411</v>
+      </c>
+      <c r="J1040" t="s">
+        <v>1412</v>
+      </c>
+    </row>
+    <row r="1041" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1041" t="s">
+        <v>1288</v>
+      </c>
+      <c r="B1041" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C1041" s="4">
+        <v>1349441</v>
+      </c>
+      <c r="D1041" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E1041">
+        <v>121</v>
+      </c>
+      <c r="F1041" t="s">
+        <v>914</v>
+      </c>
+      <c r="G1041" t="s">
+        <v>919</v>
+      </c>
+      <c r="H1041" t="s">
+        <v>919</v>
+      </c>
+      <c r="I1041" t="s">
+        <v>1411</v>
+      </c>
+      <c r="J1041" t="s">
+        <v>1412</v>
+      </c>
+    </row>
+    <row r="1042" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1042" t="s">
+        <v>1289</v>
+      </c>
+      <c r="B1042" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C1042" s="4">
+        <v>1537570</v>
+      </c>
+      <c r="D1042" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E1042">
+        <v>121</v>
+      </c>
+      <c r="F1042" t="s">
+        <v>914</v>
+      </c>
+      <c r="G1042" t="s">
+        <v>919</v>
+      </c>
+      <c r="H1042" t="s">
+        <v>919</v>
+      </c>
+      <c r="I1042" t="s">
+        <v>1411</v>
+      </c>
+      <c r="J1042" t="s">
+        <v>1412</v>
+      </c>
+    </row>
+    <row r="1043" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1043" t="s">
+        <v>1290</v>
+      </c>
+      <c r="B1043" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C1043" s="4">
+        <v>1508755</v>
+      </c>
+      <c r="D1043" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E1043">
+        <v>121</v>
+      </c>
+      <c r="F1043" t="s">
+        <v>914</v>
+      </c>
+      <c r="G1043" t="s">
+        <v>919</v>
+      </c>
+      <c r="H1043" t="s">
+        <v>919</v>
+      </c>
+      <c r="I1043" t="s">
+        <v>1411</v>
+      </c>
+      <c r="J1043" t="s">
+        <v>1412</v>
+      </c>
+    </row>
+    <row r="1044" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1044" t="s">
+        <v>1291</v>
+      </c>
+      <c r="B1044" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C1044" s="4">
+        <v>1410335</v>
+      </c>
+      <c r="D1044" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E1044">
+        <v>121</v>
+      </c>
+      <c r="F1044" t="s">
+        <v>914</v>
+      </c>
+      <c r="G1044" t="s">
+        <v>919</v>
+      </c>
+      <c r="H1044" t="s">
+        <v>919</v>
+      </c>
+      <c r="I1044" t="s">
+        <v>1411</v>
+      </c>
+      <c r="J1044" t="s">
+        <v>1412</v>
+      </c>
+    </row>
+    <row r="1045" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1045" t="s">
+        <v>1292</v>
+      </c>
+      <c r="B1045" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C1045" s="4">
+        <v>1412950</v>
+      </c>
+      <c r="D1045" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E1045">
+        <v>121</v>
+      </c>
+      <c r="F1045" t="s">
+        <v>914</v>
+      </c>
+      <c r="G1045" t="s">
+        <v>919</v>
+      </c>
+      <c r="H1045" t="s">
+        <v>919</v>
+      </c>
+      <c r="I1045" t="s">
+        <v>1411</v>
+      </c>
+      <c r="J1045" t="s">
+        <v>1412</v>
+      </c>
+    </row>
+    <row r="1046" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1046" t="s">
+        <v>1293</v>
+      </c>
+      <c r="B1046" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C1046" s="4">
+        <v>1233159</v>
+      </c>
+      <c r="D1046" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E1046">
+        <v>121</v>
+      </c>
+      <c r="F1046" t="s">
+        <v>914</v>
+      </c>
+      <c r="G1046" t="s">
+        <v>919</v>
+      </c>
+      <c r="H1046" t="s">
+        <v>919</v>
+      </c>
+      <c r="I1046" t="s">
+        <v>1411</v>
+      </c>
+      <c r="J1046" t="s">
+        <v>1412</v>
+      </c>
+    </row>
+    <row r="1047" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1047" t="s">
+        <v>1294</v>
+      </c>
+      <c r="B1047" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C1047" s="4">
+        <v>1459840</v>
+      </c>
+      <c r="D1047" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E1047">
+        <v>121</v>
+      </c>
+      <c r="F1047" t="s">
+        <v>914</v>
+      </c>
+      <c r="G1047" t="s">
+        <v>919</v>
+      </c>
+      <c r="H1047" t="s">
+        <v>919</v>
+      </c>
+      <c r="I1047" t="s">
+        <v>1411</v>
+      </c>
+      <c r="J1047" t="s">
+        <v>1412</v>
+      </c>
+    </row>
+    <row r="1048" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1048" t="s">
+        <v>1295</v>
+      </c>
+      <c r="B1048" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C1048" s="4">
+        <v>1284194</v>
+      </c>
+      <c r="D1048" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E1048">
+        <v>121</v>
+      </c>
+      <c r="F1048" t="s">
+        <v>914</v>
+      </c>
+      <c r="G1048" t="s">
+        <v>919</v>
+      </c>
+      <c r="H1048" t="s">
+        <v>919</v>
+      </c>
+      <c r="I1048" t="s">
+        <v>1411</v>
+      </c>
+      <c r="J1048" t="s">
+        <v>1412</v>
+      </c>
+    </row>
+    <row r="1049" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1049" t="s">
+        <v>1296</v>
+      </c>
+      <c r="B1049" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C1049" s="4">
+        <v>1763968</v>
+      </c>
+      <c r="D1049" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E1049">
+        <v>121</v>
+      </c>
+      <c r="F1049" t="s">
+        <v>914</v>
+      </c>
+      <c r="G1049" t="s">
+        <v>919</v>
+      </c>
+      <c r="H1049" t="s">
+        <v>919</v>
+      </c>
+      <c r="I1049" t="s">
+        <v>1411</v>
+      </c>
+      <c r="J1049" t="s">
+        <v>1412</v>
+      </c>
+    </row>
+    <row r="1050" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1050" t="s">
+        <v>1297</v>
+      </c>
+      <c r="B1050" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C1050" s="4">
+        <v>1917336</v>
+      </c>
+      <c r="D1050" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E1050">
+        <v>121</v>
+      </c>
+      <c r="F1050" t="s">
+        <v>914</v>
+      </c>
+      <c r="G1050" t="s">
+        <v>919</v>
+      </c>
+      <c r="H1050" t="s">
+        <v>919</v>
+      </c>
+      <c r="I1050" t="s">
+        <v>1411</v>
+      </c>
+      <c r="J1050" t="s">
+        <v>1412</v>
+      </c>
+    </row>
+    <row r="1051" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1051" t="s">
+        <v>1298</v>
+      </c>
+      <c r="B1051" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C1051" s="4">
+        <v>1597329</v>
+      </c>
+      <c r="D1051" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E1051">
+        <v>121</v>
+      </c>
+      <c r="F1051" t="s">
+        <v>914</v>
+      </c>
+      <c r="G1051" t="s">
+        <v>919</v>
+      </c>
+      <c r="H1051" t="s">
+        <v>919</v>
+      </c>
+      <c r="I1051" t="s">
+        <v>1411</v>
+      </c>
+      <c r="J1051" t="s">
+        <v>1412</v>
+      </c>
+    </row>
+    <row r="1052" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1052" t="s">
+        <v>1299</v>
+      </c>
+      <c r="B1052" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C1052" s="4">
+        <v>1975485</v>
+      </c>
+      <c r="D1052" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E1052">
+        <v>121</v>
+      </c>
+      <c r="F1052" t="s">
+        <v>914</v>
+      </c>
+      <c r="G1052" t="s">
+        <v>919</v>
+      </c>
+      <c r="H1052" t="s">
+        <v>919</v>
+      </c>
+      <c r="I1052" t="s">
+        <v>1411</v>
+      </c>
+      <c r="J1052" t="s">
+        <v>1412</v>
+      </c>
+    </row>
+    <row r="1053" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1053" t="s">
+        <v>1300</v>
+      </c>
+      <c r="B1053" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C1053" s="4">
+        <v>1950561</v>
+      </c>
+      <c r="D1053" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E1053">
+        <v>121</v>
+      </c>
+      <c r="F1053" t="s">
+        <v>914</v>
+      </c>
+      <c r="G1053" t="s">
+        <v>919</v>
+      </c>
+      <c r="H1053" t="s">
+        <v>919</v>
+      </c>
+      <c r="I1053" t="s">
+        <v>1411</v>
+      </c>
+      <c r="J1053" t="s">
+        <v>1412</v>
+      </c>
+    </row>
+    <row r="1054" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1054" t="s">
+        <v>1301</v>
+      </c>
+      <c r="B1054" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C1054" s="4">
+        <v>2057215</v>
+      </c>
+      <c r="D1054" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E1054">
+        <v>121</v>
+      </c>
+      <c r="F1054" t="s">
+        <v>914</v>
+      </c>
+      <c r="G1054" t="s">
+        <v>919</v>
+      </c>
+      <c r="H1054" t="s">
+        <v>919</v>
+      </c>
+      <c r="I1054" t="s">
+        <v>1411</v>
+      </c>
+      <c r="J1054" t="s">
+        <v>1412</v>
+      </c>
+    </row>
+    <row r="1055" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1055" t="s">
+        <v>1302</v>
+      </c>
+      <c r="B1055" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C1055" s="4">
+        <v>113401</v>
+      </c>
+    </row>
+    <row r="1056" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1056" t="s">
+        <v>1303</v>
+      </c>
+      <c r="B1056" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C1056" s="4">
+        <v>1104621</v>
+      </c>
+    </row>
+    <row r="1057" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1057" t="s">
+        <v>1304</v>
+      </c>
+      <c r="B1057" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C1057" s="4">
+        <v>82563</v>
+      </c>
+    </row>
+    <row r="1058" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1058" t="s">
+        <v>1305</v>
+      </c>
+      <c r="B1058" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C1058" s="4">
+        <v>4969437</v>
+      </c>
+    </row>
+    <row r="1059" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1059" t="s">
+        <v>1306</v>
+      </c>
+      <c r="B1059" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C1059" s="4">
+        <v>2026180</v>
+      </c>
+    </row>
+    <row r="1060" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1060" t="s">
+        <v>1307</v>
+      </c>
+      <c r="B1060" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C1060" s="4">
+        <v>691774</v>
+      </c>
+    </row>
+    <row r="1061" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1061" t="s">
+        <v>1308</v>
+      </c>
+      <c r="B1061" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C1061" s="4">
+        <v>732108</v>
+      </c>
+    </row>
+    <row r="1062" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1062" t="s">
+        <v>1309</v>
+      </c>
+      <c r="B1062" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C1062" s="4">
+        <v>99738</v>
+      </c>
+    </row>
+    <row r="1063" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1063" t="s">
+        <v>1310</v>
+      </c>
+      <c r="B1063" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C1063" s="4">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="1064" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1064" t="s">
+        <v>1311</v>
+      </c>
+      <c r="B1064" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C1064" s="4">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="1065" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1065" t="s">
+        <v>1312</v>
+      </c>
+      <c r="B1065" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C1065" s="4">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="1066" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1066" t="s">
+        <v>1313</v>
+      </c>
+      <c r="B1066" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C1066" s="4">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="1067" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1067" t="s">
+        <v>1314</v>
+      </c>
+      <c r="B1067" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C1067" s="4">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="1068" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1068" t="s">
+        <v>1315</v>
+      </c>
+      <c r="B1068" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C1068" s="4">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="1069" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1069" t="s">
+        <v>1316</v>
+      </c>
+      <c r="B1069" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C1069" s="4">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="1070" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1070" t="s">
+        <v>1317</v>
+      </c>
+      <c r="B1070" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C1070" s="4">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="1071" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1071" t="s">
+        <v>1318</v>
+      </c>
+      <c r="B1071" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C1071" s="4">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="1072" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1072" t="s">
+        <v>1319</v>
+      </c>
+      <c r="B1072" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C1072" s="4">
+        <v>1282</v>
+      </c>
+    </row>
+    <row r="1073" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1073" t="s">
+        <v>1320</v>
+      </c>
+      <c r="B1073" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C1073" s="4">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="1074" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1074" t="s">
+        <v>1321</v>
+      </c>
+      <c r="B1074" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C1074" s="4">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="1075" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1075" t="s">
+        <v>1322</v>
+      </c>
+      <c r="B1075" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C1075" s="4">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="1076" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1076" t="s">
+        <v>1323</v>
+      </c>
+      <c r="B1076" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C1076" s="4">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="1077" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1077" t="s">
+        <v>1324</v>
+      </c>
+      <c r="B1077" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C1077" s="4">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="1078" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1078" t="s">
+        <v>1325</v>
+      </c>
+      <c r="B1078" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C1078" s="4">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="1079" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1079" t="s">
+        <v>1326</v>
+      </c>
+      <c r="B1079" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C1079" s="4">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="1080" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1080" t="s">
+        <v>1327</v>
+      </c>
+      <c r="B1080" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C1080" s="4">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="1081" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1081" t="s">
+        <v>1328</v>
+      </c>
+      <c r="B1081" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C1081" s="4">
+        <v>138349</v>
+      </c>
+    </row>
+    <row r="1082" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1082" t="s">
+        <v>1329</v>
+      </c>
+      <c r="B1082" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C1082" s="4">
+        <v>65807</v>
+      </c>
+    </row>
+    <row r="1083" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1083" t="s">
+        <v>1330</v>
+      </c>
+      <c r="B1083" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C1083" s="4">
+        <v>450299</v>
+      </c>
+    </row>
+    <row r="1084" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1084" t="s">
+        <v>1331</v>
+      </c>
+      <c r="B1084" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C1084" s="4">
+        <v>176640</v>
+      </c>
+    </row>
+    <row r="1085" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1085" t="s">
+        <v>1332</v>
+      </c>
+      <c r="B1085" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C1085" s="4">
+        <v>1145237</v>
+      </c>
+    </row>
+    <row r="1086" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1086" t="s">
+        <v>1333</v>
+      </c>
+      <c r="B1086" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C1086" s="4">
+        <v>897868</v>
+      </c>
+    </row>
+    <row r="1087" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1087" t="s">
+        <v>1334</v>
+      </c>
+      <c r="B1087" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C1087" s="4">
+        <v>191432</v>
+      </c>
+    </row>
+    <row r="1088" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1088" t="s">
+        <v>1335</v>
+      </c>
+      <c r="B1088" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C1088" s="4">
+        <v>66520</v>
+      </c>
+    </row>
+    <row r="1089" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1089" t="s">
+        <v>1336</v>
+      </c>
+      <c r="B1089" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C1089" s="4">
+        <v>2760740</v>
+      </c>
+    </row>
+    <row r="1090" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1090" t="s">
+        <v>1337</v>
+      </c>
+      <c r="B1090" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C1090" s="4">
+        <v>364284</v>
+      </c>
+    </row>
+    <row r="1091" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1091" t="s">
+        <v>1338</v>
+      </c>
+      <c r="B1091" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C1091" s="4">
+        <v>228640</v>
+      </c>
+    </row>
+    <row r="1092" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1092" t="s">
+        <v>1339</v>
+      </c>
+      <c r="B1092" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C1092" s="4">
+        <v>352649</v>
+      </c>
+    </row>
+    <row r="1093" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1093" t="s">
+        <v>1340</v>
+      </c>
+      <c r="B1093" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C1093" s="4">
+        <v>3372255</v>
+      </c>
+    </row>
+    <row r="1094" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1094" t="s">
+        <v>1341</v>
+      </c>
+      <c r="B1094" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C1094" s="4">
+        <v>58575</v>
+      </c>
+    </row>
+    <row r="1095" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1095" t="s">
+        <v>1342</v>
+      </c>
+      <c r="B1095" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C1095" s="4">
+        <v>718664</v>
+      </c>
+    </row>
+    <row r="1096" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1096" t="s">
+        <v>1343</v>
+      </c>
+      <c r="B1096" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C1096" s="4">
+        <v>2552017</v>
+      </c>
+    </row>
+    <row r="1097" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1097" t="s">
+        <v>1344</v>
+      </c>
+      <c r="B1097" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C1097" s="4">
+        <v>2764400</v>
+      </c>
+    </row>
+    <row r="1098" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1098" t="s">
+        <v>1345</v>
+      </c>
+      <c r="B1098" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C1098" s="4">
+        <v>533473</v>
+      </c>
+    </row>
+    <row r="1099" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1099" t="s">
+        <v>1346</v>
+      </c>
+      <c r="B1099" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C1099" s="4">
+        <v>1437424</v>
+      </c>
+    </row>
+    <row r="1100" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1100" t="s">
+        <v>1347</v>
+      </c>
+      <c r="B1100" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C1100" s="4">
+        <v>1104204</v>
+      </c>
+    </row>
+    <row r="1101" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1101" t="s">
+        <v>1348</v>
+      </c>
+      <c r="B1101" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C1101" s="4">
+        <v>1597432</v>
+      </c>
+    </row>
+    <row r="1102" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1102" t="s">
+        <v>1349</v>
+      </c>
+      <c r="B1102" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C1102" s="4">
+        <v>1107679</v>
+      </c>
+    </row>
+    <row r="1103" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1103" t="s">
+        <v>1350</v>
+      </c>
+      <c r="B1103" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C1103" s="4">
+        <v>1244832</v>
+      </c>
+    </row>
+    <row r="1104" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1104" t="s">
+        <v>1351</v>
+      </c>
+      <c r="B1104" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C1104" s="4">
+        <v>1147126</v>
+      </c>
+    </row>
+    <row r="1105" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1105" t="s">
+        <v>1352</v>
+      </c>
+      <c r="B1105" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C1105" s="4">
+        <v>1231072</v>
+      </c>
+    </row>
+    <row r="1106" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1106" t="s">
+        <v>1353</v>
+      </c>
+      <c r="B1106" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C1106" s="4">
+        <v>312545</v>
+      </c>
+    </row>
+    <row r="1107" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1107" t="s">
+        <v>1354</v>
+      </c>
+      <c r="B1107" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C1107" s="4">
+        <v>933591</v>
+      </c>
+    </row>
+    <row r="1108" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1108" t="s">
+        <v>1355</v>
+      </c>
+      <c r="B1108" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C1108" s="4">
+        <v>1002169</v>
+      </c>
+    </row>
+    <row r="1109" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1109" t="s">
+        <v>1356</v>
+      </c>
+      <c r="B1109" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C1109" s="4">
+        <v>802464</v>
+      </c>
+    </row>
+    <row r="1110" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1110" t="s">
+        <v>1357</v>
+      </c>
+      <c r="B1110" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C1110" s="4">
+        <v>336637</v>
+      </c>
+    </row>
+    <row r="1111" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1111" t="s">
+        <v>1358</v>
+      </c>
+      <c r="B1111" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C1111" s="4">
+        <v>414191</v>
+      </c>
+    </row>
+    <row r="1112" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1112" t="s">
+        <v>1359</v>
+      </c>
+      <c r="B1112" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C1112" s="4">
+        <v>666111</v>
+      </c>
+    </row>
+    <row r="1113" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1113" t="s">
+        <v>1360</v>
+      </c>
+      <c r="B1113" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C1113" s="4">
+        <v>787797</v>
+      </c>
+    </row>
+    <row r="1114" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1114" t="s">
+        <v>1361</v>
+      </c>
+      <c r="B1114" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C1114" s="4">
+        <v>184250</v>
+      </c>
+    </row>
+    <row r="1115" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1115" t="s">
+        <v>1362</v>
+      </c>
+      <c r="B1115" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C1115" s="4">
+        <v>115916</v>
+      </c>
+    </row>
+    <row r="1116" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1116" t="s">
+        <v>1363</v>
+      </c>
+      <c r="B1116" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C1116" s="4">
+        <v>114355</v>
+      </c>
+    </row>
+    <row r="1117" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1117" t="s">
+        <v>1364</v>
+      </c>
+      <c r="B1117" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C1117" s="4">
+        <v>103966</v>
+      </c>
+    </row>
+    <row r="1118" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1118" t="s">
+        <v>1365</v>
+      </c>
+      <c r="B1118" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C1118" s="4">
+        <v>102173</v>
+      </c>
+    </row>
+    <row r="1119" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1119" t="s">
+        <v>1366</v>
+      </c>
+      <c r="B1119" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C1119" s="4">
+        <v>134907</v>
+      </c>
+    </row>
+    <row r="1120" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1120" t="s">
+        <v>1367</v>
+      </c>
+      <c r="B1120" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C1120" s="4">
+        <v>119395</v>
+      </c>
+    </row>
+    <row r="1121" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1121" t="s">
+        <v>1368</v>
+      </c>
+      <c r="B1121" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C1121" s="4">
+        <v>121414</v>
+      </c>
+    </row>
+    <row r="1122" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1122" t="s">
+        <v>1369</v>
+      </c>
+      <c r="B1122" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C1122" s="4">
+        <v>119931</v>
+      </c>
+    </row>
+    <row r="1123" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1123" t="s">
+        <v>1370</v>
+      </c>
+      <c r="B1123" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C1123" s="4">
+        <v>119931</v>
+      </c>
+    </row>
+    <row r="1124" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1124" t="s">
+        <v>1371</v>
+      </c>
+      <c r="B1124" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C1124" s="4">
+        <v>123991</v>
+      </c>
+    </row>
+    <row r="1125" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1125" t="s">
+        <v>1372</v>
+      </c>
+      <c r="B1125" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C1125" s="4">
+        <v>121192</v>
+      </c>
+    </row>
+    <row r="1126" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1126" t="s">
+        <v>1373</v>
+      </c>
+      <c r="B1126" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C1126" s="4">
+        <v>120272</v>
+      </c>
+    </row>
+    <row r="1127" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1127" t="s">
+        <v>1374</v>
+      </c>
+      <c r="B1127" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C1127" s="4">
+        <v>118439</v>
+      </c>
+    </row>
+    <row r="1128" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1128" t="s">
+        <v>1375</v>
+      </c>
+      <c r="B1128" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C1128" s="4">
+        <v>922116</v>
+      </c>
+    </row>
+    <row r="1129" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1129" t="s">
+        <v>1376</v>
+      </c>
+      <c r="B1129" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C1129" s="4">
+        <v>380503</v>
+      </c>
+    </row>
+    <row r="1130" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1130" t="s">
+        <v>1377</v>
+      </c>
+      <c r="B1130" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C1130" s="4">
+        <v>241337</v>
+      </c>
+    </row>
+    <row r="1131" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1131" t="s">
+        <v>1378</v>
+      </c>
+      <c r="B1131" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C1131" s="4">
+        <v>233715</v>
+      </c>
+    </row>
+    <row r="1132" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1132" t="s">
+        <v>1379</v>
+      </c>
+      <c r="B1132" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C1132" s="4">
+        <v>232871</v>
+      </c>
+    </row>
+    <row r="1133" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1133" t="s">
+        <v>1380</v>
+      </c>
+      <c r="B1133" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C1133" s="4">
+        <v>419334</v>
+      </c>
+    </row>
+    <row r="1134" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1134" t="s">
+        <v>1381</v>
+      </c>
+      <c r="B1134" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C1134" s="4">
+        <v>380503</v>
+      </c>
+    </row>
+    <row r="1135" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1135" t="s">
+        <v>1382</v>
+      </c>
+      <c r="B1135" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C1135" s="4">
+        <v>269577</v>
+      </c>
+    </row>
+    <row r="1136" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1136" t="s">
+        <v>1383</v>
+      </c>
+      <c r="B1136" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C1136" s="4">
+        <v>1328484</v>
+      </c>
+    </row>
+    <row r="1137" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1137" t="s">
+        <v>1384</v>
+      </c>
+      <c r="B1137" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C1137" s="4">
+        <v>2402745</v>
+      </c>
+    </row>
+    <row r="1138" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1138" t="s">
+        <v>1385</v>
+      </c>
+      <c r="B1138" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C1138" s="4">
+        <v>4153928</v>
+      </c>
+    </row>
+    <row r="1139" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1139" t="s">
+        <v>1386</v>
+      </c>
+      <c r="B1139" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C1139" s="4">
+        <v>212960</v>
+      </c>
+    </row>
+    <row r="1140" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1140" t="s">
+        <v>1387</v>
+      </c>
+      <c r="B1140" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C1140" s="4">
+        <v>175772</v>
+      </c>
+    </row>
+    <row r="1141" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1141" t="s">
+        <v>1388</v>
+      </c>
+      <c r="B1141" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C1141" s="4">
+        <v>205204</v>
+      </c>
+    </row>
+    <row r="1142" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1142" t="s">
+        <v>1389</v>
+      </c>
+      <c r="B1142" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C1142" s="4">
+        <v>315850</v>
+      </c>
+    </row>
+    <row r="1143" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1143" t="s">
+        <v>1390</v>
+      </c>
+      <c r="B1143" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C1143" s="4">
+        <v>360127</v>
+      </c>
+    </row>
+    <row r="1144" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1144" t="s">
+        <v>1391</v>
+      </c>
+      <c r="B1144" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C1144" s="4">
+        <v>78162</v>
+      </c>
+    </row>
+    <row r="1145" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1145" t="s">
+        <v>1392</v>
+      </c>
+      <c r="B1145" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C1145" s="4">
+        <v>1911</v>
+      </c>
+    </row>
+    <row r="1146" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1146" t="s">
+        <v>1393</v>
+      </c>
+      <c r="B1146" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C1146" s="4">
+        <v>192819</v>
+      </c>
+    </row>
+    <row r="1147" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1147" t="s">
+        <v>1394</v>
+      </c>
+      <c r="B1147" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C1147" s="4">
+        <v>140076</v>
+      </c>
+    </row>
+    <row r="1148" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1148" t="s">
+        <v>1395</v>
+      </c>
+      <c r="B1148" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C1148" s="4">
+        <v>198828</v>
+      </c>
+    </row>
+    <row r="1149" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1149" t="s">
+        <v>1396</v>
+      </c>
+      <c r="B1149" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C1149" s="4">
+        <v>495086</v>
+      </c>
+    </row>
+    <row r="1150" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1150" t="s">
+        <v>1397</v>
+      </c>
+      <c r="B1150" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C1150" s="4">
+        <v>129154</v>
+      </c>
+    </row>
+    <row r="1151" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1151" t="s">
+        <v>1398</v>
+      </c>
+      <c r="B1151" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C1151" s="4">
+        <v>481034</v>
+      </c>
+    </row>
+    <row r="1152" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1152" t="s">
+        <v>1399</v>
+      </c>
+      <c r="B1152" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C1152" s="4">
+        <v>1578016</v>
+      </c>
+    </row>
+    <row r="1153" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1153" t="s">
+        <v>1400</v>
+      </c>
+      <c r="B1153" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C1153" s="4">
+        <v>1879615</v>
+      </c>
+    </row>
+    <row r="1154" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1154" t="s">
+        <v>1401</v>
+      </c>
+      <c r="B1154" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C1154" s="4">
+        <v>5619883</v>
+      </c>
+    </row>
+    <row r="1155" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1155" t="s">
+        <v>1402</v>
+      </c>
+      <c r="B1155" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C1155" s="4">
+        <v>1466510</v>
+      </c>
+    </row>
+    <row r="1156" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1156" t="s">
+        <v>1403</v>
+      </c>
+      <c r="B1156" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C1156" s="4">
+        <v>2982483</v>
+      </c>
+    </row>
+    <row r="1157" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1157" t="s">
+        <v>1404</v>
+      </c>
+      <c r="B1157" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C1157" s="4">
+        <v>1247919</v>
+      </c>
+    </row>
+    <row r="1158" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1158" t="s">
+        <v>1405</v>
+      </c>
+      <c r="B1158" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C1158" s="4">
+        <v>3099362</v>
+      </c>
+    </row>
+    <row r="1159" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1159" t="s">
+        <v>1406</v>
+      </c>
+      <c r="B1159" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C1159" s="4">
+        <v>3208052</v>
+      </c>
+    </row>
+    <row r="1160" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1160" t="s">
+        <v>1407</v>
+      </c>
+      <c r="B1160" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C1160" s="4">
+        <v>1477350</v>
+      </c>
+    </row>
+    <row r="1161" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1161" t="s">
+        <v>1408</v>
+      </c>
+      <c r="B1161" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C1161" s="4">
+        <v>2327897</v>
       </c>
     </row>
   </sheetData>
